--- a/product catalogue.xlsx
+++ b/product catalogue.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P319"/>
+  <dimension ref="A1:P316"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3680,7 +3680,7 @@
         <v>opell-prima-003-main.png</v>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>opell-prima-003-main.png,opell-prima-004-main.png</v>
       </c>
       <c r="K66" t="str">
         <v/>
@@ -3706,16 +3706,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B67" t="str">
-        <v>opell-prima-004</v>
+        <v>opell-prima-005</v>
       </c>
       <c r="C67" t="str">
-        <v>OPELL-PRIMA-004</v>
+        <v>OPELL-PRIMA-005</v>
       </c>
       <c r="D67" t="str">
-        <v>Alive Shower Head</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E67" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F67" t="str">
         <v/>
@@ -3727,7 +3727,7 @@
         <v/>
       </c>
       <c r="I67" t="str">
-        <v>opell-prima-004-main.png</v>
+        <v>opell-prima-005-main.jpg</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -3756,13 +3756,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B68" t="str">
-        <v>opell-prima-005</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C68" t="str">
-        <v>OPELL-PRIMA-005</v>
+        <v>OPELL-PRIMA-006</v>
       </c>
       <c r="D68" t="str">
-        <v>Angle Valve</v>
+        <v>Basin Mixer Upper Part</v>
       </c>
       <c r="E68" t="str">
         <v>Faucets</v>
@@ -3777,7 +3777,7 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>opell-prima-005-main.jpg</v>
+        <v>opell-prima-006-main.png</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3806,13 +3806,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B69" t="str">
-        <v>opell-prima-006</v>
+        <v>opell-prima-007</v>
       </c>
       <c r="C69" t="str">
-        <v>OPELL-PRIMA-006</v>
+        <v>OPELL-PRIMA-007</v>
       </c>
       <c r="D69" t="str">
-        <v>Basin Mixer Upper Part</v>
+        <v>Basin Mixer Upper Parts</v>
       </c>
       <c r="E69" t="str">
         <v>Faucets</v>
@@ -3827,7 +3827,7 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>opell-prima-006-main.png</v>
+        <v>opell-prima-007-main.png</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3856,13 +3856,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B70" t="str">
-        <v>opell-prima-007</v>
+        <v>opell-prima-008</v>
       </c>
       <c r="C70" t="str">
-        <v>OPELL-PRIMA-007</v>
+        <v>OPELL-PRIMA-008</v>
       </c>
       <c r="D70" t="str">
-        <v>Basin Mixer Upper Parts</v>
+        <v>Basin Mixer Wall Mounted</v>
       </c>
       <c r="E70" t="str">
         <v>Faucets</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>opell-prima-007-main.png</v>
+        <v>opell-prima-008-main.png</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3906,13 +3906,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B71" t="str">
-        <v>opell-prima-008</v>
+        <v>opell-prima-009</v>
       </c>
       <c r="C71" t="str">
-        <v>OPELL-PRIMA-008</v>
+        <v>OPELL-PRIMA-009</v>
       </c>
       <c r="D71" t="str">
-        <v>Basin Mixer Wall Mounted</v>
+        <v>Basin Mixer Wall Mounted Upper Parts</v>
       </c>
       <c r="E71" t="str">
         <v>Faucets</v>
@@ -3927,7 +3927,7 @@
         <v/>
       </c>
       <c r="I71" t="str">
-        <v>opell-prima-008-main.png</v>
+        <v>opell-prima-009-main.png</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -3956,13 +3956,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B72" t="str">
-        <v>opell-prima-009</v>
+        <v>opell-prima-010</v>
       </c>
       <c r="C72" t="str">
-        <v>OPELL-PRIMA-009</v>
+        <v>OPELL-PRIMA-010</v>
       </c>
       <c r="D72" t="str">
-        <v>Basin Mixer Wall Mounted Upper Parts</v>
+        <v>Bath TUB Spout</v>
       </c>
       <c r="E72" t="str">
         <v>Faucets</v>
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>opell-prima-009-main.png</v>
+        <v>opell-prima-010-main.jpg</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -4006,16 +4006,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B73" t="str">
-        <v>opell-prima-010</v>
+        <v>opell-prima-015</v>
       </c>
       <c r="C73" t="str">
-        <v>OPELL-PRIMA-010</v>
+        <v>OPELL-PRIMA-015</v>
       </c>
       <c r="D73" t="str">
-        <v>Bath TUB Spout</v>
+        <v>Bottle Trap</v>
       </c>
       <c r="E73" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F73" t="str">
         <v/>
@@ -4027,7 +4027,7 @@
         <v/>
       </c>
       <c r="I73" t="str">
-        <v>opell-prima-010-main.jpg</v>
+        <v>opell-prima-015-main.png</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -4056,19 +4056,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B74" t="str">
-        <v>opell-prima-011</v>
+        <v>opell-prima-015</v>
       </c>
       <c r="C74" t="str">
         <v>OPELL-PRIMA-011</v>
       </c>
       <c r="D74" t="str">
-        <v>Beige Bottle Traps</v>
+        <v/>
       </c>
       <c r="E74" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F74" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4106,19 +4106,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B75" t="str">
-        <v>opell-prima-012</v>
+        <v>opell-prima-015</v>
       </c>
       <c r="C75" t="str">
-        <v>OPELL-PRIMA-012</v>
+        <v>OPELL-PRIMA-014</v>
       </c>
       <c r="D75" t="str">
-        <v>Beige Gold Alive</v>
+        <v/>
       </c>
       <c r="E75" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F75" t="str">
-        <v/>
+        <v>Matt Black</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4127,7 +4127,7 @@
         <v/>
       </c>
       <c r="I75" t="str">
-        <v>opell-prima-012-main.png</v>
+        <v>opell-prima-014-main.png</v>
       </c>
       <c r="J75" t="str">
         <v/>
@@ -4156,19 +4156,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B76" t="str">
-        <v>opell-prima-013</v>
+        <v>opell-prima-015</v>
       </c>
       <c r="C76" t="str">
-        <v>OPELL-PRIMA-013</v>
+        <v>OPELL-PRIMA-016</v>
       </c>
       <c r="D76" t="str">
-        <v>Beige Gold Shower</v>
+        <v/>
       </c>
       <c r="E76" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F76" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I76" t="str">
-        <v>opell-prima-013-main.png</v>
+        <v>opell-prima-016-main.png</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -4206,13 +4206,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B77" t="str">
-        <v>opell-prima-014</v>
+        <v>opell-prima-012</v>
       </c>
       <c r="C77" t="str">
-        <v>OPELL-PRIMA-014</v>
+        <v>OPELL-PRIMA-012</v>
       </c>
       <c r="D77" t="str">
-        <v>Black Bottle Trap</v>
+        <v>Beige Gold Alive</v>
       </c>
       <c r="E77" t="str">
         <v>Accessories</v>
@@ -4227,7 +4227,7 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>opell-prima-014-main.png</v>
+        <v>opell-prima-012-main.png</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4256,16 +4256,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B78" t="str">
-        <v>opell-prima-015</v>
+        <v>opell-prima-013</v>
       </c>
       <c r="C78" t="str">
-        <v>OPELL-PRIMA-015</v>
+        <v>OPELL-PRIMA-013</v>
       </c>
       <c r="D78" t="str">
-        <v>Bottle Trap</v>
+        <v>Beige Gold Shower</v>
       </c>
       <c r="E78" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F78" t="str">
         <v/>
@@ -4277,7 +4277,7 @@
         <v/>
       </c>
       <c r="I78" t="str">
-        <v>opell-prima-015-main.png</v>
+        <v>opell-prima-013-main.png</v>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -4306,16 +4306,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B79" t="str">
-        <v>opell-prima-016</v>
+        <v>opell-prima-017</v>
       </c>
       <c r="C79" t="str">
-        <v>OPELL-PRIMA-016</v>
+        <v>OPELL-PRIMA-017</v>
       </c>
       <c r="D79" t="str">
-        <v>Bottle Trap White</v>
+        <v>Button Spout</v>
       </c>
       <c r="E79" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F79" t="str">
         <v/>
@@ -4327,7 +4327,7 @@
         <v/>
       </c>
       <c r="I79" t="str">
-        <v>opell-prima-016-main.png</v>
+        <v>opell-prima-017-main.jpg</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -4356,16 +4356,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B80" t="str">
-        <v>opell-prima-017</v>
+        <v>opell-prima-018</v>
       </c>
       <c r="C80" t="str">
-        <v>OPELL-PRIMA-017</v>
+        <v>OPELL-PRIMA-018</v>
       </c>
       <c r="D80" t="str">
-        <v>Button Spout</v>
+        <v>Center Hole</v>
       </c>
       <c r="E80" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F80" t="str">
         <v/>
@@ -4377,7 +4377,7 @@
         <v/>
       </c>
       <c r="I80" t="str">
-        <v>opell-prima-017-main.jpg</v>
+        <v>opell-prima-018-main.jpg</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -4406,16 +4406,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B81" t="str">
-        <v>opell-prima-018</v>
+        <v>opell-prima-019</v>
       </c>
       <c r="C81" t="str">
-        <v>OPELL-PRIMA-018</v>
+        <v>OPELL-PRIMA-019</v>
       </c>
       <c r="D81" t="str">
-        <v>Center Hole</v>
+        <v>Concealed Stop Cock</v>
       </c>
       <c r="E81" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -4427,7 +4427,7 @@
         <v/>
       </c>
       <c r="I81" t="str">
-        <v>opell-prima-018-main.jpg</v>
+        <v>opell-prima-019-main.jpg</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -4456,13 +4456,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B82" t="str">
-        <v>opell-prima-019</v>
+        <v>opell-prima-020</v>
       </c>
       <c r="C82" t="str">
-        <v>OPELL-PRIMA-019</v>
+        <v>OPELL-PRIMA-020</v>
       </c>
       <c r="D82" t="str">
-        <v>Concealed Stop Cock</v>
+        <v>Diverter Body</v>
       </c>
       <c r="E82" t="str">
         <v>Faucets</v>
@@ -4477,7 +4477,7 @@
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>opell-prima-019-main.jpg</v>
+        <v>opell-prima-020-main.png</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -4509,16 +4509,16 @@
         <v>opell-prima-020</v>
       </c>
       <c r="C83" t="str">
-        <v>OPELL-PRIMA-020</v>
+        <v>OPELL-PRIMA-022</v>
       </c>
       <c r="D83" t="str">
-        <v>Diverter Body</v>
+        <v/>
       </c>
       <c r="E83" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F83" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>opell-prima-020-main.png</v>
+        <v>opell-prima-022-main.png</v>
       </c>
       <c r="J83" t="str">
         <v/>
@@ -4556,19 +4556,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B84" t="str">
-        <v>opell-prima-021</v>
+        <v>opell-prima-020</v>
       </c>
       <c r="C84" t="str">
-        <v>OPELL-PRIMA-021</v>
+        <v>OPELL-PRIMA-023</v>
       </c>
       <c r="D84" t="str">
-        <v>Diverter Body for ALL Colour and Gold Combination</v>
+        <v/>
       </c>
       <c r="E84" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F84" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -4577,7 +4577,7 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>opell-prima-021-main.png</v>
+        <v>opell-prima-023-main.png</v>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -4606,13 +4606,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B85" t="str">
-        <v>opell-prima-022</v>
+        <v>opell-prima-021</v>
       </c>
       <c r="C85" t="str">
-        <v>OPELL-PRIMA-022</v>
+        <v>OPELL-PRIMA-021</v>
       </c>
       <c r="D85" t="str">
-        <v>Diverter Body Gold</v>
+        <v>Diverter Body for ALL Colour and Gold Combination</v>
       </c>
       <c r="E85" t="str">
         <v>Faucets</v>
@@ -4627,7 +4627,7 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>opell-prima-022-main.png</v>
+        <v>opell-prima-021-main.png</v>
       </c>
       <c r="J85" t="str">
         <v/>
@@ -4656,13 +4656,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B86" t="str">
-        <v>opell-prima-023</v>
+        <v>opell-prima-024</v>
       </c>
       <c r="C86" t="str">
-        <v>OPELL-PRIMA-023</v>
+        <v>OPELL-PRIMA-024</v>
       </c>
       <c r="D86" t="str">
-        <v>Diverter Body Matt Beige</v>
+        <v>Diverter Upper Part</v>
       </c>
       <c r="E86" t="str">
         <v>Faucets</v>
@@ -4677,7 +4677,7 @@
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>opell-prima-023-main.png</v>
+        <v>opell-prima-024-main.png</v>
       </c>
       <c r="J86" t="str">
         <v/>
@@ -4706,13 +4706,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B87" t="str">
-        <v>opell-prima-024</v>
+        <v>opell-prima-025</v>
       </c>
       <c r="C87" t="str">
-        <v>OPELL-PRIMA-024</v>
+        <v>OPELL-PRIMA-025</v>
       </c>
       <c r="D87" t="str">
-        <v>Diverter Upper Part</v>
+        <v>Diverter Upper Parts</v>
       </c>
       <c r="E87" t="str">
         <v>Faucets</v>
@@ -4727,7 +4727,7 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>opell-prima-024-main.png</v>
+        <v>opell-prima-025-main.png</v>
       </c>
       <c r="J87" t="str">
         <v/>
@@ -4756,13 +4756,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B88" t="str">
-        <v>opell-prima-025</v>
+        <v>opell-prima-026</v>
       </c>
       <c r="C88" t="str">
-        <v>OPELL-PRIMA-025</v>
+        <v>OPELL-PRIMA-026</v>
       </c>
       <c r="D88" t="str">
-        <v>Diverter Upper Parts</v>
+        <v>Exposed Parts for Single Lever High Flow Diverter Body</v>
       </c>
       <c r="E88" t="str">
         <v>Faucets</v>
@@ -4777,7 +4777,7 @@
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>opell-prima-025-main.png</v>
+        <v>opell-prima-026-main.jpg</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -4806,16 +4806,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B89" t="str">
-        <v>opell-prima-026</v>
+        <v>opell-prima-027</v>
       </c>
       <c r="C89" t="str">
-        <v>OPELL-PRIMA-026</v>
+        <v>OPELL-PRIMA-027</v>
       </c>
       <c r="D89" t="str">
-        <v>Exposed Parts for Single Lever High Flow Diverter Body</v>
+        <v>Gold</v>
       </c>
       <c r="E89" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F89" t="str">
         <v/>
@@ -4827,7 +4827,7 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>opell-prima-026-main.jpg</v>
+        <v>opell-prima-027-main.png</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4856,16 +4856,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B90" t="str">
-        <v>opell-prima-027</v>
+        <v>opell-prima-029</v>
       </c>
       <c r="C90" t="str">
-        <v>OPELL-PRIMA-027</v>
+        <v>OPELL-PRIMA-029</v>
       </c>
       <c r="D90" t="str">
-        <v>Gold</v>
+        <v>Hand Shower</v>
       </c>
       <c r="E90" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F90" t="str">
         <v/>
@@ -4877,7 +4877,7 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>opell-prima-027-main.png</v>
+        <v>opell-prima-029-main.png</v>
       </c>
       <c r="J90" t="str">
         <v/>
@@ -4906,19 +4906,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B91" t="str">
-        <v>opell-prima-028</v>
+        <v>opell-prima-029</v>
       </c>
       <c r="C91" t="str">
         <v>OPELL-PRIMA-028</v>
       </c>
       <c r="D91" t="str">
-        <v>Hand Shoer Rose Gold</v>
+        <v/>
       </c>
       <c r="E91" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F91" t="str">
-        <v/>
+        <v>Rose Gold</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4959,16 +4959,16 @@
         <v>opell-prima-029</v>
       </c>
       <c r="C92" t="str">
-        <v>OPELL-PRIMA-029</v>
+        <v>OPELL-PRIMA-030</v>
       </c>
       <c r="D92" t="str">
-        <v>Hand Shower</v>
+        <v/>
       </c>
       <c r="E92" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F92" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -4977,7 +4977,7 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v>opell-prima-029-main.png</v>
+        <v>opell-prima-030-main.png</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -5006,16 +5006,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B93" t="str">
-        <v>opell-prima-030</v>
+        <v>opell-prima-031</v>
       </c>
       <c r="C93" t="str">
-        <v>OPELL-PRIMA-030</v>
+        <v>OPELL-PRIMA-031</v>
       </c>
       <c r="D93" t="str">
-        <v>Hand Shower Gold</v>
+        <v>Health Faucet</v>
       </c>
       <c r="E93" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F93" t="str">
         <v/>
@@ -5027,7 +5027,7 @@
         <v/>
       </c>
       <c r="I93" t="str">
-        <v>opell-prima-030-main.png</v>
+        <v>opell-prima-031-main.png</v>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -5056,16 +5056,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B94" t="str">
-        <v>opell-prima-031</v>
+        <v>opell-prima-032</v>
       </c>
       <c r="C94" t="str">
-        <v>OPELL-PRIMA-031</v>
+        <v>OPELL-PRIMA-032</v>
       </c>
       <c r="D94" t="str">
-        <v>Health Faucet</v>
+        <v>Long Body</v>
       </c>
       <c r="E94" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F94" t="str">
         <v/>
@@ -5077,7 +5077,7 @@
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>opell-prima-031-main.png</v>
+        <v>opell-prima-032-main.jpg</v>
       </c>
       <c r="J94" t="str">
         <v/>
@@ -5106,16 +5106,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B95" t="str">
-        <v>opell-prima-032</v>
+        <v>opell-prima-033</v>
       </c>
       <c r="C95" t="str">
-        <v>OPELL-PRIMA-032</v>
+        <v>OPELL-PRIMA-033</v>
       </c>
       <c r="D95" t="str">
-        <v>Long Body</v>
+        <v>Matte Beige Alive</v>
       </c>
       <c r="E95" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F95" t="str">
         <v/>
@@ -5127,7 +5127,7 @@
         <v/>
       </c>
       <c r="I95" t="str">
-        <v>opell-prima-032-main.jpg</v>
+        <v>opell-prima-033-main.png</v>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -5156,16 +5156,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B96" t="str">
-        <v>opell-prima-033</v>
+        <v>opell-prima-034</v>
       </c>
       <c r="C96" t="str">
-        <v>OPELL-PRIMA-033</v>
+        <v>OPELL-PRIMA-034</v>
       </c>
       <c r="D96" t="str">
-        <v>Matte Beige Alive</v>
+        <v>Matte White Shower Head</v>
       </c>
       <c r="E96" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F96" t="str">
         <v/>
@@ -5177,7 +5177,7 @@
         <v/>
       </c>
       <c r="I96" t="str">
-        <v>opell-prima-033-main.png</v>
+        <v>opell-prima-034-main.png</v>
       </c>
       <c r="J96" t="str">
         <v/>
@@ -5206,16 +5206,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B97" t="str">
-        <v>opell-prima-034</v>
+        <v>opell-prima-035</v>
       </c>
       <c r="C97" t="str">
-        <v>OPELL-PRIMA-034</v>
+        <v>OPELL-PRIMA-035</v>
       </c>
       <c r="D97" t="str">
-        <v>Matte White Shower Head</v>
+        <v>NON Telephonic</v>
       </c>
       <c r="E97" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F97" t="str">
         <v/>
@@ -5227,7 +5227,7 @@
         <v/>
       </c>
       <c r="I97" t="str">
-        <v>opell-prima-034-main.png</v>
+        <v>opell-prima-035-main.jpg</v>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -5256,16 +5256,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B98" t="str">
-        <v>opell-prima-035</v>
+        <v>opell-prima-036</v>
       </c>
       <c r="C98" t="str">
-        <v>OPELL-PRIMA-035</v>
+        <v>OPELL-PRIMA-036</v>
       </c>
       <c r="D98" t="str">
-        <v>NON Telephonic</v>
+        <v>Nozzle BIB Cock</v>
       </c>
       <c r="E98" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F98" t="str">
         <v/>
@@ -5277,7 +5277,7 @@
         <v/>
       </c>
       <c r="I98" t="str">
-        <v>opell-prima-035-main.jpg</v>
+        <v>opell-prima-036-main.jpg</v>
       </c>
       <c r="J98" t="str">
         <v/>
@@ -5306,13 +5306,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B99" t="str">
-        <v>opell-prima-036</v>
+        <v>opell-prima-037</v>
       </c>
       <c r="C99" t="str">
-        <v>OPELL-PRIMA-036</v>
+        <v>OPELL-PRIMA-037</v>
       </c>
       <c r="D99" t="str">
-        <v>Nozzle BIB Cock</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E99" t="str">
         <v>Faucets</v>
@@ -5327,7 +5327,7 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v>opell-prima-036-main.jpg</v>
+        <v>opell-prima-037-main.jpg</v>
       </c>
       <c r="J99" t="str">
         <v/>
@@ -5356,13 +5356,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B100" t="str">
-        <v>opell-prima-037</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C100" t="str">
-        <v>OPELL-PRIMA-037</v>
+        <v>OPELL-PRIMA-038</v>
       </c>
       <c r="D100" t="str">
-        <v>Pillar Cock</v>
+        <v>Pillar Cock Extend</v>
       </c>
       <c r="E100" t="str">
         <v>Faucets</v>
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="I100" t="str">
-        <v>opell-prima-037-main.jpg</v>
+        <v>opell-prima-038-main.png</v>
       </c>
       <c r="J100" t="str">
         <v/>
@@ -5406,13 +5406,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B101" t="str">
-        <v>opell-prima-038</v>
+        <v>opell-prima-039</v>
       </c>
       <c r="C101" t="str">
-        <v>OPELL-PRIMA-038</v>
+        <v>OPELL-PRIMA-039</v>
       </c>
       <c r="D101" t="str">
-        <v>Pillar Cock Extend</v>
+        <v>Pillar Cock Extended</v>
       </c>
       <c r="E101" t="str">
         <v>Faucets</v>
@@ -5427,7 +5427,7 @@
         <v/>
       </c>
       <c r="I101" t="str">
-        <v>opell-prima-038-main.png</v>
+        <v>opell-prima-039-main.png</v>
       </c>
       <c r="J101" t="str">
         <v/>
@@ -5456,13 +5456,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B102" t="str">
-        <v>opell-prima-039</v>
+        <v>opell-prima-040</v>
       </c>
       <c r="C102" t="str">
-        <v>OPELL-PRIMA-039</v>
+        <v>OPELL-PRIMA-040</v>
       </c>
       <c r="D102" t="str">
-        <v>Pillar Cock Extended</v>
+        <v>Pillar Cock Extended Body</v>
       </c>
       <c r="E102" t="str">
         <v>Faucets</v>
@@ -5477,7 +5477,7 @@
         <v/>
       </c>
       <c r="I102" t="str">
-        <v>opell-prima-039-main.png</v>
+        <v>opell-prima-040-main.jpg</v>
       </c>
       <c r="J102" t="str">
         <v/>
@@ -5506,13 +5506,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B103" t="str">
-        <v>opell-prima-040</v>
+        <v>opell-prima-041</v>
       </c>
       <c r="C103" t="str">
-        <v>OPELL-PRIMA-040</v>
+        <v>OPELL-PRIMA-041</v>
       </c>
       <c r="D103" t="str">
-        <v>Pillar Cock Extended Body</v>
+        <v>Plain Spout</v>
       </c>
       <c r="E103" t="str">
         <v>Faucets</v>
@@ -5527,7 +5527,7 @@
         <v/>
       </c>
       <c r="I103" t="str">
-        <v>opell-prima-040-main.jpg</v>
+        <v>opell-prima-041-main.png</v>
       </c>
       <c r="J103" t="str">
         <v/>
@@ -5556,16 +5556,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B104" t="str">
-        <v>opell-prima-041</v>
+        <v>opell-prima-042</v>
       </c>
       <c r="C104" t="str">
-        <v>OPELL-PRIMA-041</v>
+        <v>OPELL-PRIMA-042</v>
       </c>
       <c r="D104" t="str">
-        <v>Plain Spout</v>
+        <v>Shower ARM</v>
       </c>
       <c r="E104" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F104" t="str">
         <v/>
@@ -5577,7 +5577,7 @@
         <v/>
       </c>
       <c r="I104" t="str">
-        <v>opell-prima-041-main.png</v>
+        <v>opell-prima-042-main.png</v>
       </c>
       <c r="J104" t="str">
         <v/>
@@ -5609,16 +5609,16 @@
         <v>opell-prima-042</v>
       </c>
       <c r="C105" t="str">
-        <v>OPELL-PRIMA-042</v>
+        <v>OPELL-PRIMA-043</v>
       </c>
       <c r="D105" t="str">
-        <v>Shower ARM</v>
+        <v/>
       </c>
       <c r="E105" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F105" t="str">
-        <v/>
+        <v>Matt Black Gold</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -5627,7 +5627,7 @@
         <v/>
       </c>
       <c r="I105" t="str">
-        <v>opell-prima-042-main.png</v>
+        <v>opell-prima-043-main.png</v>
       </c>
       <c r="J105" t="str">
         <v/>
@@ -5656,13 +5656,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B106" t="str">
-        <v>opell-prima-043</v>
+        <v>opell-prima-044</v>
       </c>
       <c r="C106" t="str">
-        <v>OPELL-PRIMA-043</v>
+        <v>OPELL-PRIMA-044</v>
       </c>
       <c r="D106" t="str">
-        <v>Shower ARM Black Gold</v>
+        <v>Shower Head</v>
       </c>
       <c r="E106" t="str">
         <v>Showers</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="I106" t="str">
-        <v>opell-prima-043-main.png</v>
+        <v>opell-prima-044-main.png</v>
       </c>
       <c r="J106" t="str">
         <v/>
@@ -5709,16 +5709,16 @@
         <v>opell-prima-044</v>
       </c>
       <c r="C107" t="str">
-        <v>OPELL-PRIMA-044</v>
+        <v>OPELL-PRIMA-045</v>
       </c>
       <c r="D107" t="str">
-        <v>Shower Head</v>
+        <v/>
       </c>
       <c r="E107" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F107" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v/>
       </c>
       <c r="I107" t="str">
-        <v>opell-prima-044-main.png</v>
+        <v>opell-prima-045-main.png</v>
       </c>
       <c r="J107" t="str">
         <v/>
@@ -5756,13 +5756,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B108" t="str">
-        <v>opell-prima-045</v>
+        <v>opell-prima-046</v>
       </c>
       <c r="C108" t="str">
-        <v>OPELL-PRIMA-045</v>
+        <v>OPELL-PRIMA-046</v>
       </c>
       <c r="D108" t="str">
-        <v>Shower Head Beige</v>
+        <v>Shower Mixer for Spout Only</v>
       </c>
       <c r="E108" t="str">
         <v>Showers</v>
@@ -5777,7 +5777,7 @@
         <v/>
       </c>
       <c r="I108" t="str">
-        <v>opell-prima-045-main.png</v>
+        <v>opell-prima-046-main.jpg</v>
       </c>
       <c r="J108" t="str">
         <v/>
@@ -5806,16 +5806,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B109" t="str">
-        <v>opell-prima-046</v>
+        <v>opell-prima-047</v>
       </c>
       <c r="C109" t="str">
-        <v>OPELL-PRIMA-046</v>
+        <v>OPELL-PRIMA-047</v>
       </c>
       <c r="D109" t="str">
-        <v>Shower Mixer for Spout Only</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E109" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F109" t="str">
         <v/>
@@ -5827,10 +5827,10 @@
         <v/>
       </c>
       <c r="I109" t="str">
-        <v>opell-prima-046-main.jpg</v>
+        <v>opell-prima-047-main.jpg</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>opell-prima-047-main.jpg,opell-prima-059-main.png</v>
       </c>
       <c r="K109" t="str">
         <v/>
@@ -5856,13 +5856,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B110" t="str">
-        <v>opell-prima-047</v>
+        <v>opell-prima-048</v>
       </c>
       <c r="C110" t="str">
-        <v>OPELL-PRIMA-047</v>
+        <v>OPELL-PRIMA-048</v>
       </c>
       <c r="D110" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Single Lever Basin Mixer Extended Body</v>
       </c>
       <c r="E110" t="str">
         <v>Faucets</v>
@@ -5877,7 +5877,7 @@
         <v/>
       </c>
       <c r="I110" t="str">
-        <v>opell-prima-047-main.jpg</v>
+        <v>opell-prima-048-main.jpg</v>
       </c>
       <c r="J110" t="str">
         <v/>
@@ -5906,13 +5906,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B111" t="str">
-        <v>opell-prima-048</v>
+        <v>opell-prima-049</v>
       </c>
       <c r="C111" t="str">
-        <v>OPELL-PRIMA-048</v>
+        <v>OPELL-PRIMA-049</v>
       </c>
       <c r="D111" t="str">
-        <v>Single Lever Basin Mixer Extended Body</v>
+        <v>Single Lever Basin Mixer Tall</v>
       </c>
       <c r="E111" t="str">
         <v>Faucets</v>
@@ -5927,10 +5927,10 @@
         <v/>
       </c>
       <c r="I111" t="str">
-        <v>opell-prima-048-main.jpg</v>
+        <v>opell-prima-049-main.png</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>opell-prima-049-main.png,opell-prima-060-main.png</v>
       </c>
       <c r="K111" t="str">
         <v/>
@@ -5956,16 +5956,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B112" t="str">
-        <v>opell-prima-049</v>
+        <v>opell-prima-050</v>
       </c>
       <c r="C112" t="str">
-        <v>OPELL-PRIMA-049</v>
+        <v>OPELL-PRIMA-050</v>
       </c>
       <c r="D112" t="str">
-        <v>Single Lever Basin Mixer Tall</v>
+        <v>Single Lever Basin Tall</v>
       </c>
       <c r="E112" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -5977,7 +5977,7 @@
         <v/>
       </c>
       <c r="I112" t="str">
-        <v>opell-prima-049-main.png</v>
+        <v>opell-prima-050-main.png</v>
       </c>
       <c r="J112" t="str">
         <v/>
@@ -6006,16 +6006,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B113" t="str">
-        <v>opell-prima-050</v>
+        <v>opell-prima-051</v>
       </c>
       <c r="C113" t="str">
-        <v>OPELL-PRIMA-050</v>
+        <v>OPELL-PRIMA-051</v>
       </c>
       <c r="D113" t="str">
-        <v>Single Lever Basin Tall</v>
+        <v>Single Lever Exposed Shower Mixer</v>
       </c>
       <c r="E113" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="I113" t="str">
-        <v>opell-prima-050-main.png</v>
+        <v>opell-prima-051-main.jpg</v>
       </c>
       <c r="J113" t="str">
         <v/>
@@ -6056,16 +6056,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B114" t="str">
-        <v>opell-prima-051</v>
+        <v>opell-prima-052</v>
       </c>
       <c r="C114" t="str">
-        <v>OPELL-PRIMA-051</v>
+        <v>OPELL-PRIMA-052</v>
       </c>
       <c r="D114" t="str">
-        <v>Single Lever Exposed Shower Mixer</v>
+        <v>Single Lever Sink Mixer Table Mounted Angular Spout</v>
       </c>
       <c r="E114" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -6077,7 +6077,7 @@
         <v/>
       </c>
       <c r="I114" t="str">
-        <v>opell-prima-051-main.jpg</v>
+        <v>opell-prima-052-main.jpg</v>
       </c>
       <c r="J114" t="str">
         <v/>
@@ -6106,13 +6106,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B115" t="str">
-        <v>opell-prima-052</v>
+        <v>opell-prima-053</v>
       </c>
       <c r="C115" t="str">
-        <v>OPELL-PRIMA-052</v>
+        <v>OPELL-PRIMA-053</v>
       </c>
       <c r="D115" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Angular Spout</v>
+        <v>Single Lever Sink Mixer Table Mounted Round Spout Side Handle</v>
       </c>
       <c r="E115" t="str">
         <v>Faucets</v>
@@ -6127,7 +6127,7 @@
         <v/>
       </c>
       <c r="I115" t="str">
-        <v>opell-prima-052-main.jpg</v>
+        <v>opell-prima-053-main.jpg</v>
       </c>
       <c r="J115" t="str">
         <v/>
@@ -6156,13 +6156,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B116" t="str">
-        <v>opell-prima-053</v>
+        <v>opell-prima-054</v>
       </c>
       <c r="C116" t="str">
-        <v>OPELL-PRIMA-053</v>
+        <v>OPELL-PRIMA-054</v>
       </c>
       <c r="D116" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Round Spout Side Handle</v>
+        <v>Single Lever Sink Mixer Table Mounted Tall</v>
       </c>
       <c r="E116" t="str">
         <v>Faucets</v>
@@ -6177,7 +6177,7 @@
         <v/>
       </c>
       <c r="I116" t="str">
-        <v>opell-prima-053-main.jpg</v>
+        <v>opell-prima-054-main.jpg</v>
       </c>
       <c r="J116" t="str">
         <v/>
@@ -6206,13 +6206,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B117" t="str">
-        <v>opell-prima-054</v>
+        <v>opell-prima-055</v>
       </c>
       <c r="C117" t="str">
-        <v>OPELL-PRIMA-054</v>
+        <v>OPELL-PRIMA-055</v>
       </c>
       <c r="D117" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Tall</v>
+        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
       </c>
       <c r="E117" t="str">
         <v>Faucets</v>
@@ -6227,7 +6227,7 @@
         <v/>
       </c>
       <c r="I117" t="str">
-        <v>opell-prima-054-main.jpg</v>
+        <v>opell-prima-055-main.jpg</v>
       </c>
       <c r="J117" t="str">
         <v/>
@@ -6256,13 +6256,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B118" t="str">
-        <v>opell-prima-055</v>
+        <v>opell-prima-056</v>
       </c>
       <c r="C118" t="str">
-        <v>OPELL-PRIMA-055</v>
+        <v>OPELL-PRIMA-056</v>
       </c>
       <c r="D118" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
+        <v>Single Lever Sink Mixer Wall Mounted Round Spout</v>
       </c>
       <c r="E118" t="str">
         <v>Faucets</v>
@@ -6277,7 +6277,7 @@
         <v/>
       </c>
       <c r="I118" t="str">
-        <v>opell-prima-055-main.jpg</v>
+        <v>opell-prima-056-main.jpg</v>
       </c>
       <c r="J118" t="str">
         <v/>
@@ -6306,13 +6306,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B119" t="str">
-        <v>opell-prima-056</v>
+        <v>opell-prima-057</v>
       </c>
       <c r="C119" t="str">
-        <v>OPELL-PRIMA-056</v>
+        <v>OPELL-PRIMA-057</v>
       </c>
       <c r="D119" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Round Spout</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E119" t="str">
         <v>Faucets</v>
@@ -6327,7 +6327,7 @@
         <v/>
       </c>
       <c r="I119" t="str">
-        <v>opell-prima-056-main.jpg</v>
+        <v>opell-prima-057-main.jpg</v>
       </c>
       <c r="J119" t="str">
         <v/>
@@ -6356,13 +6356,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B120" t="str">
-        <v>opell-prima-057</v>
+        <v>opell-prima-058</v>
       </c>
       <c r="C120" t="str">
-        <v>OPELL-PRIMA-057</v>
+        <v>OPELL-PRIMA-058</v>
       </c>
       <c r="D120" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Single Lever Wall Mounted Basin Mixer</v>
       </c>
       <c r="E120" t="str">
         <v>Faucets</v>
@@ -6377,7 +6377,7 @@
         <v/>
       </c>
       <c r="I120" t="str">
-        <v>opell-prima-057-main.jpg</v>
+        <v>opell-prima-058-main.jpg</v>
       </c>
       <c r="J120" t="str">
         <v/>
@@ -6406,13 +6406,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B121" t="str">
-        <v>opell-prima-058</v>
+        <v>opell-prima-061</v>
       </c>
       <c r="C121" t="str">
-        <v>OPELL-PRIMA-058</v>
+        <v>OPELL-PRIMA-061</v>
       </c>
       <c r="D121" t="str">
-        <v>Single Lever Wall Mounted Basin Mixer</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E121" t="str">
         <v>Faucets</v>
@@ -6427,7 +6427,7 @@
         <v/>
       </c>
       <c r="I121" t="str">
-        <v>opell-prima-058-main.jpg</v>
+        <v>opell-prima-061-main.jpg</v>
       </c>
       <c r="J121" t="str">
         <v/>
@@ -6453,16 +6453,16 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B122" t="str">
-        <v>opell-prima-059</v>
+        <v>cube-001</v>
       </c>
       <c r="C122" t="str">
-        <v>OPELL-PRIMA-059</v>
+        <v>CUBE-001</v>
       </c>
       <c r="D122" t="str">
-        <v>Single Liver Basin Mixer</v>
+        <v>2 WAY Angle Valve</v>
       </c>
       <c r="E122" t="str">
         <v>Faucets</v>
@@ -6477,7 +6477,7 @@
         <v/>
       </c>
       <c r="I122" t="str">
-        <v>opell-prima-059-main.png</v>
+        <v>cube-001-main.png</v>
       </c>
       <c r="J122" t="str">
         <v/>
@@ -6503,16 +6503,16 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B123" t="str">
-        <v>opell-prima-060</v>
+        <v>cube-002</v>
       </c>
       <c r="C123" t="str">
-        <v>OPELL-PRIMA-060</v>
+        <v>CUBE-002</v>
       </c>
       <c r="D123" t="str">
-        <v>Single Liver Basin Mixer Tall</v>
+        <v>2 WAY BIB Cock</v>
       </c>
       <c r="E123" t="str">
         <v>Faucets</v>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="I123" t="str">
-        <v>opell-prima-060-main.png</v>
+        <v>cube-002-main.png</v>
       </c>
       <c r="J123" t="str">
         <v/>
@@ -6553,16 +6553,16 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B124" t="str">
-        <v>opell-prima-061</v>
+        <v>cube-003</v>
       </c>
       <c r="C124" t="str">
-        <v>OPELL-PRIMA-061</v>
+        <v>CUBE-003</v>
       </c>
       <c r="D124" t="str">
-        <v>Sink Cock</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E124" t="str">
         <v>Faucets</v>
@@ -6577,7 +6577,7 @@
         <v/>
       </c>
       <c r="I124" t="str">
-        <v>opell-prima-061-main.jpg</v>
+        <v>cube-003-main.jpg</v>
       </c>
       <c r="J124" t="str">
         <v/>
@@ -6606,13 +6606,13 @@
         <v>Cube</v>
       </c>
       <c r="B125" t="str">
-        <v>cube-001</v>
+        <v>cube-004</v>
       </c>
       <c r="C125" t="str">
-        <v>CUBE-001</v>
+        <v>CUBE-004</v>
       </c>
       <c r="D125" t="str">
-        <v>2 WAY Angle Valve</v>
+        <v>Basin Mixer Wall Mounted</v>
       </c>
       <c r="E125" t="str">
         <v>Faucets</v>
@@ -6627,7 +6627,7 @@
         <v/>
       </c>
       <c r="I125" t="str">
-        <v>cube-001-main.png</v>
+        <v>cube-004-main.png</v>
       </c>
       <c r="J125" t="str">
         <v/>
@@ -6656,13 +6656,13 @@
         <v>Cube</v>
       </c>
       <c r="B126" t="str">
-        <v>cube-002</v>
+        <v>cube-005</v>
       </c>
       <c r="C126" t="str">
-        <v>CUBE-002</v>
+        <v>CUBE-005</v>
       </c>
       <c r="D126" t="str">
-        <v>2 WAY BIB Cock</v>
+        <v>Bath Tub Spout</v>
       </c>
       <c r="E126" t="str">
         <v>Faucets</v>
@@ -6677,7 +6677,7 @@
         <v/>
       </c>
       <c r="I126" t="str">
-        <v>cube-002-main.png</v>
+        <v>cube-005-main.jpg</v>
       </c>
       <c r="J126" t="str">
         <v/>
@@ -6706,13 +6706,13 @@
         <v>Cube</v>
       </c>
       <c r="B127" t="str">
-        <v>cube-003</v>
+        <v>cube-006</v>
       </c>
       <c r="C127" t="str">
-        <v>CUBE-003</v>
+        <v>CUBE-006</v>
       </c>
       <c r="D127" t="str">
-        <v>Angle Valve</v>
+        <v>Bib Cock Long Body</v>
       </c>
       <c r="E127" t="str">
         <v>Faucets</v>
@@ -6727,7 +6727,7 @@
         <v/>
       </c>
       <c r="I127" t="str">
-        <v>cube-003-main.jpg</v>
+        <v>cube-006-main.jpg</v>
       </c>
       <c r="J127" t="str">
         <v/>
@@ -6756,13 +6756,13 @@
         <v>Cube</v>
       </c>
       <c r="B128" t="str">
-        <v>cube-004</v>
+        <v>cube-007</v>
       </c>
       <c r="C128" t="str">
-        <v>CUBE-004</v>
+        <v>CUBE-007</v>
       </c>
       <c r="D128" t="str">
-        <v>Basin Mixer Wall Mounted</v>
+        <v>Button Spout</v>
       </c>
       <c r="E128" t="str">
         <v>Faucets</v>
@@ -6777,7 +6777,7 @@
         <v/>
       </c>
       <c r="I128" t="str">
-        <v>cube-004-main.png</v>
+        <v>cube-007-main.jpg</v>
       </c>
       <c r="J128" t="str">
         <v/>
@@ -6806,13 +6806,13 @@
         <v>Cube</v>
       </c>
       <c r="B129" t="str">
-        <v>cube-005</v>
+        <v>cube-008</v>
       </c>
       <c r="C129" t="str">
-        <v>CUBE-005</v>
+        <v>CUBE-008</v>
       </c>
       <c r="D129" t="str">
-        <v>Bath Tub Spout</v>
+        <v>Concealed Stop Cock</v>
       </c>
       <c r="E129" t="str">
         <v>Faucets</v>
@@ -6827,7 +6827,7 @@
         <v/>
       </c>
       <c r="I129" t="str">
-        <v>cube-005-main.jpg</v>
+        <v>cube-008-main.jpg</v>
       </c>
       <c r="J129" t="str">
         <v/>
@@ -6856,13 +6856,13 @@
         <v>Cube</v>
       </c>
       <c r="B130" t="str">
-        <v>cube-006</v>
+        <v>cube-009</v>
       </c>
       <c r="C130" t="str">
-        <v>CUBE-006</v>
+        <v>CUBE-009</v>
       </c>
       <c r="D130" t="str">
-        <v>Bib Cock Long Body</v>
+        <v>Diverter Body</v>
       </c>
       <c r="E130" t="str">
         <v>Faucets</v>
@@ -6877,7 +6877,7 @@
         <v/>
       </c>
       <c r="I130" t="str">
-        <v>cube-006-main.jpg</v>
+        <v>cube-009-main.png</v>
       </c>
       <c r="J130" t="str">
         <v/>
@@ -6906,13 +6906,13 @@
         <v>Cube</v>
       </c>
       <c r="B131" t="str">
-        <v>cube-007</v>
+        <v>cube-010</v>
       </c>
       <c r="C131" t="str">
-        <v>CUBE-007</v>
+        <v>CUBE-010</v>
       </c>
       <c r="D131" t="str">
-        <v>Button Spout</v>
+        <v>Diverter Upper Part</v>
       </c>
       <c r="E131" t="str">
         <v>Faucets</v>
@@ -6927,7 +6927,7 @@
         <v/>
       </c>
       <c r="I131" t="str">
-        <v>cube-007-main.jpg</v>
+        <v>cube-010-main.png</v>
       </c>
       <c r="J131" t="str">
         <v/>
@@ -6956,13 +6956,13 @@
         <v>Cube</v>
       </c>
       <c r="B132" t="str">
-        <v>cube-008</v>
+        <v>cube-011</v>
       </c>
       <c r="C132" t="str">
-        <v>CUBE-008</v>
+        <v>CUBE-011</v>
       </c>
       <c r="D132" t="str">
-        <v>Concealed Stop Cock</v>
+        <v>Flush Cock</v>
       </c>
       <c r="E132" t="str">
         <v>Faucets</v>
@@ -6977,7 +6977,7 @@
         <v/>
       </c>
       <c r="I132" t="str">
-        <v>cube-008-main.jpg</v>
+        <v>cube-011-main.jpg</v>
       </c>
       <c r="J132" t="str">
         <v/>
@@ -7006,13 +7006,13 @@
         <v>Cube</v>
       </c>
       <c r="B133" t="str">
-        <v>cube-009</v>
+        <v>cube-012</v>
       </c>
       <c r="C133" t="str">
-        <v>CUBE-009</v>
+        <v>CUBE-012</v>
       </c>
       <c r="D133" t="str">
-        <v>Diverter Body</v>
+        <v>Nozzle Bib Cock</v>
       </c>
       <c r="E133" t="str">
         <v>Faucets</v>
@@ -7027,7 +7027,7 @@
         <v/>
       </c>
       <c r="I133" t="str">
-        <v>cube-009-main.png</v>
+        <v>cube-012-main.jpg</v>
       </c>
       <c r="J133" t="str">
         <v/>
@@ -7056,13 +7056,13 @@
         <v>Cube</v>
       </c>
       <c r="B134" t="str">
-        <v>cube-010</v>
+        <v>cube-013</v>
       </c>
       <c r="C134" t="str">
-        <v>CUBE-010</v>
+        <v>CUBE-013</v>
       </c>
       <c r="D134" t="str">
-        <v>Diverter Upper Part</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E134" t="str">
         <v>Faucets</v>
@@ -7077,7 +7077,7 @@
         <v/>
       </c>
       <c r="I134" t="str">
-        <v>cube-010-main.png</v>
+        <v>cube-013-main.jpg</v>
       </c>
       <c r="J134" t="str">
         <v/>
@@ -7106,13 +7106,13 @@
         <v>Cube</v>
       </c>
       <c r="B135" t="str">
-        <v>cube-011</v>
+        <v>cube-014</v>
       </c>
       <c r="C135" t="str">
-        <v>CUBE-011</v>
+        <v>CUBE-014</v>
       </c>
       <c r="D135" t="str">
-        <v>Flush Cock</v>
+        <v>Pillar Cock Extended</v>
       </c>
       <c r="E135" t="str">
         <v>Faucets</v>
@@ -7127,7 +7127,7 @@
         <v/>
       </c>
       <c r="I135" t="str">
-        <v>cube-011-main.jpg</v>
+        <v>cube-014-main.png</v>
       </c>
       <c r="J135" t="str">
         <v/>
@@ -7156,13 +7156,13 @@
         <v>Cube</v>
       </c>
       <c r="B136" t="str">
-        <v>cube-012</v>
+        <v>cube-015</v>
       </c>
       <c r="C136" t="str">
-        <v>CUBE-012</v>
+        <v>CUBE-015</v>
       </c>
       <c r="D136" t="str">
-        <v>Nozzle Bib Cock</v>
+        <v>Pillar Cock Extended Body</v>
       </c>
       <c r="E136" t="str">
         <v>Faucets</v>
@@ -7177,7 +7177,7 @@
         <v/>
       </c>
       <c r="I136" t="str">
-        <v>cube-012-main.jpg</v>
+        <v>cube-015-main.jpg</v>
       </c>
       <c r="J136" t="str">
         <v/>
@@ -7206,13 +7206,13 @@
         <v>Cube</v>
       </c>
       <c r="B137" t="str">
-        <v>cube-013</v>
+        <v>cube-016</v>
       </c>
       <c r="C137" t="str">
-        <v>CUBE-013</v>
+        <v>CUBE-016</v>
       </c>
       <c r="D137" t="str">
-        <v>Pillar Cock</v>
+        <v>S L Concealed Basin Mixer Exposed Parts</v>
       </c>
       <c r="E137" t="str">
         <v>Faucets</v>
@@ -7227,7 +7227,7 @@
         <v/>
       </c>
       <c r="I137" t="str">
-        <v>cube-013-main.jpg</v>
+        <v>cube-016-main.jpg</v>
       </c>
       <c r="J137" t="str">
         <v/>
@@ -7256,16 +7256,16 @@
         <v>Cube</v>
       </c>
       <c r="B138" t="str">
-        <v>cube-014</v>
+        <v>cube-017</v>
       </c>
       <c r="C138" t="str">
-        <v>CUBE-014</v>
+        <v>CUBE-017</v>
       </c>
       <c r="D138" t="str">
-        <v>Pillar Cock Extended</v>
+        <v>Shower ARM</v>
       </c>
       <c r="E138" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F138" t="str">
         <v/>
@@ -7277,7 +7277,7 @@
         <v/>
       </c>
       <c r="I138" t="str">
-        <v>cube-014-main.png</v>
+        <v>cube-017-main.png</v>
       </c>
       <c r="J138" t="str">
         <v/>
@@ -7306,16 +7306,16 @@
         <v>Cube</v>
       </c>
       <c r="B139" t="str">
-        <v>cube-015</v>
+        <v>cube-018</v>
       </c>
       <c r="C139" t="str">
-        <v>CUBE-015</v>
+        <v>CUBE-018</v>
       </c>
       <c r="D139" t="str">
-        <v>Pillar Cock Extended Body</v>
+        <v>Shower Head</v>
       </c>
       <c r="E139" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -7327,7 +7327,7 @@
         <v/>
       </c>
       <c r="I139" t="str">
-        <v>cube-015-main.jpg</v>
+        <v>cube-018-main.png</v>
       </c>
       <c r="J139" t="str">
         <v/>
@@ -7356,13 +7356,13 @@
         <v>Cube</v>
       </c>
       <c r="B140" t="str">
-        <v>cube-016</v>
+        <v>cube-019</v>
       </c>
       <c r="C140" t="str">
-        <v>CUBE-016</v>
+        <v>CUBE-019</v>
       </c>
       <c r="D140" t="str">
-        <v>S L Concealed Basin Mixer Exposed Parts</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E140" t="str">
         <v>Faucets</v>
@@ -7377,7 +7377,7 @@
         <v/>
       </c>
       <c r="I140" t="str">
-        <v>cube-016-main.jpg</v>
+        <v>cube-019-main.jpg</v>
       </c>
       <c r="J140" t="str">
         <v/>
@@ -7406,16 +7406,16 @@
         <v>Cube</v>
       </c>
       <c r="B141" t="str">
-        <v>cube-017</v>
+        <v>cube-020</v>
       </c>
       <c r="C141" t="str">
-        <v>CUBE-017</v>
+        <v>CUBE-020</v>
       </c>
       <c r="D141" t="str">
-        <v>Shower ARM</v>
+        <v>Single Lever Basin Mixer Extended Body</v>
       </c>
       <c r="E141" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -7427,7 +7427,7 @@
         <v/>
       </c>
       <c r="I141" t="str">
-        <v>cube-017-main.png</v>
+        <v>cube-020-main.png</v>
       </c>
       <c r="J141" t="str">
         <v/>
@@ -7456,16 +7456,16 @@
         <v>Cube</v>
       </c>
       <c r="B142" t="str">
-        <v>cube-018</v>
+        <v>cube-021</v>
       </c>
       <c r="C142" t="str">
-        <v>CUBE-018</v>
+        <v>CUBE-021</v>
       </c>
       <c r="D142" t="str">
-        <v>Shower Head</v>
+        <v>Single Lever Basin Mixer Tall</v>
       </c>
       <c r="E142" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F142" t="str">
         <v/>
@@ -7477,7 +7477,7 @@
         <v/>
       </c>
       <c r="I142" t="str">
-        <v>cube-018-main.png</v>
+        <v>cube-021-main.png</v>
       </c>
       <c r="J142" t="str">
         <v/>
@@ -7506,13 +7506,13 @@
         <v>Cube</v>
       </c>
       <c r="B143" t="str">
-        <v>cube-019</v>
+        <v>cube-022</v>
       </c>
       <c r="C143" t="str">
-        <v>CUBE-019</v>
+        <v>CUBE-022</v>
       </c>
       <c r="D143" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
       </c>
       <c r="E143" t="str">
         <v>Faucets</v>
@@ -7527,7 +7527,7 @@
         <v/>
       </c>
       <c r="I143" t="str">
-        <v>cube-019-main.jpg</v>
+        <v>cube-022-main.jpg</v>
       </c>
       <c r="J143" t="str">
         <v/>
@@ -7556,13 +7556,13 @@
         <v>Cube</v>
       </c>
       <c r="B144" t="str">
-        <v>cube-020</v>
+        <v>cube-023</v>
       </c>
       <c r="C144" t="str">
-        <v>CUBE-020</v>
+        <v>CUBE-023</v>
       </c>
       <c r="D144" t="str">
-        <v>Single Lever Basin Mixer Extended Body</v>
+        <v>Single Lever Diverter</v>
       </c>
       <c r="E144" t="str">
         <v>Faucets</v>
@@ -7577,7 +7577,7 @@
         <v/>
       </c>
       <c r="I144" t="str">
-        <v>cube-020-main.png</v>
+        <v>cube-023-main.jpg</v>
       </c>
       <c r="J144" t="str">
         <v/>
@@ -7606,13 +7606,13 @@
         <v>Cube</v>
       </c>
       <c r="B145" t="str">
-        <v>cube-021</v>
+        <v>cube-024</v>
       </c>
       <c r="C145" t="str">
-        <v>CUBE-021</v>
+        <v>CUBE-024</v>
       </c>
       <c r="D145" t="str">
-        <v>Single Lever Basin Mixer Tall</v>
+        <v>Single Lever Sink Mixer Angular</v>
       </c>
       <c r="E145" t="str">
         <v>Faucets</v>
@@ -7627,7 +7627,7 @@
         <v/>
       </c>
       <c r="I145" t="str">
-        <v>cube-021-main.png</v>
+        <v>cube-024-main.jpg</v>
       </c>
       <c r="J145" t="str">
         <v/>
@@ -7656,13 +7656,13 @@
         <v>Cube</v>
       </c>
       <c r="B146" t="str">
-        <v>cube-022</v>
+        <v>cube-025</v>
       </c>
       <c r="C146" t="str">
-        <v>CUBE-022</v>
+        <v>CUBE-025</v>
       </c>
       <c r="D146" t="str">
-        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
+        <v>Single Lever Sink Mixer Side Handle</v>
       </c>
       <c r="E146" t="str">
         <v>Faucets</v>
@@ -7677,7 +7677,7 @@
         <v/>
       </c>
       <c r="I146" t="str">
-        <v>cube-022-main.jpg</v>
+        <v>cube-025-main.jpg</v>
       </c>
       <c r="J146" t="str">
         <v/>
@@ -7706,13 +7706,13 @@
         <v>Cube</v>
       </c>
       <c r="B147" t="str">
-        <v>cube-023</v>
+        <v>cube-026</v>
       </c>
       <c r="C147" t="str">
-        <v>CUBE-023</v>
+        <v>CUBE-026</v>
       </c>
       <c r="D147" t="str">
-        <v>Single Lever Diverter</v>
+        <v>Single Lever Sink Mixer Wall Mounted</v>
       </c>
       <c r="E147" t="str">
         <v>Faucets</v>
@@ -7727,7 +7727,7 @@
         <v/>
       </c>
       <c r="I147" t="str">
-        <v>cube-023-main.jpg</v>
+        <v>cube-026-main.jpg</v>
       </c>
       <c r="J147" t="str">
         <v/>
@@ -7756,13 +7756,13 @@
         <v>Cube</v>
       </c>
       <c r="B148" t="str">
-        <v>cube-024</v>
+        <v>cube-027</v>
       </c>
       <c r="C148" t="str">
-        <v>CUBE-024</v>
+        <v>CUBE-027</v>
       </c>
       <c r="D148" t="str">
-        <v>Single Lever Sink Mixer Angular</v>
+        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
       </c>
       <c r="E148" t="str">
         <v>Faucets</v>
@@ -7777,7 +7777,7 @@
         <v/>
       </c>
       <c r="I148" t="str">
-        <v>cube-024-main.jpg</v>
+        <v>cube-027-main.jpg</v>
       </c>
       <c r="J148" t="str">
         <v/>
@@ -7806,13 +7806,13 @@
         <v>Cube</v>
       </c>
       <c r="B149" t="str">
-        <v>cube-025</v>
+        <v>cube-028</v>
       </c>
       <c r="C149" t="str">
-        <v>CUBE-025</v>
+        <v>CUBE-028</v>
       </c>
       <c r="D149" t="str">
-        <v>Single Lever Sink Mixer Side Handle</v>
+        <v>Single Lever Table Top</v>
       </c>
       <c r="E149" t="str">
         <v>Faucets</v>
@@ -7827,7 +7827,7 @@
         <v/>
       </c>
       <c r="I149" t="str">
-        <v>cube-025-main.jpg</v>
+        <v>cube-028-main.jpg</v>
       </c>
       <c r="J149" t="str">
         <v/>
@@ -7856,16 +7856,16 @@
         <v>Cube</v>
       </c>
       <c r="B150" t="str">
-        <v>cube-026</v>
+        <v>cube-029</v>
       </c>
       <c r="C150" t="str">
-        <v>CUBE-026</v>
+        <v>CUBE-029</v>
       </c>
       <c r="D150" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted</v>
+        <v>Single Lever Tall Boy</v>
       </c>
       <c r="E150" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F150" t="str">
         <v/>
@@ -7877,7 +7877,7 @@
         <v/>
       </c>
       <c r="I150" t="str">
-        <v>cube-026-main.jpg</v>
+        <v>cube-029-main.jpg</v>
       </c>
       <c r="J150" t="str">
         <v/>
@@ -7906,13 +7906,13 @@
         <v>Cube</v>
       </c>
       <c r="B151" t="str">
-        <v>cube-027</v>
+        <v>cube-030</v>
       </c>
       <c r="C151" t="str">
-        <v>CUBE-027</v>
+        <v>CUBE-030</v>
       </c>
       <c r="D151" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E151" t="str">
         <v>Faucets</v>
@@ -7927,7 +7927,7 @@
         <v/>
       </c>
       <c r="I151" t="str">
-        <v>cube-027-main.jpg</v>
+        <v>cube-030-main.jpg</v>
       </c>
       <c r="J151" t="str">
         <v/>
@@ -7956,13 +7956,13 @@
         <v>Cube</v>
       </c>
       <c r="B152" t="str">
-        <v>cube-028</v>
+        <v>cube-031</v>
       </c>
       <c r="C152" t="str">
-        <v>CUBE-028</v>
+        <v>CUBE-031</v>
       </c>
       <c r="D152" t="str">
-        <v>Single Lever Table Top</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E152" t="str">
         <v>Faucets</v>
@@ -7977,7 +7977,7 @@
         <v/>
       </c>
       <c r="I152" t="str">
-        <v>cube-028-main.jpg</v>
+        <v>cube-031-main.jpg</v>
       </c>
       <c r="J152" t="str">
         <v/>
@@ -8006,16 +8006,16 @@
         <v>Cube</v>
       </c>
       <c r="B153" t="str">
-        <v>cube-029</v>
+        <v>cube-032</v>
       </c>
       <c r="C153" t="str">
-        <v>CUBE-029</v>
+        <v>CUBE-032</v>
       </c>
       <c r="D153" t="str">
-        <v>Single Lever Tall Boy</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E153" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F153" t="str">
         <v/>
@@ -8027,7 +8027,7 @@
         <v/>
       </c>
       <c r="I153" t="str">
-        <v>cube-029-main.jpg</v>
+        <v>cube-032-main.jpg</v>
       </c>
       <c r="J153" t="str">
         <v/>
@@ -8056,13 +8056,13 @@
         <v>Cube</v>
       </c>
       <c r="B154" t="str">
-        <v>cube-030</v>
+        <v>cube-033</v>
       </c>
       <c r="C154" t="str">
-        <v>CUBE-030</v>
+        <v>CUBE-033</v>
       </c>
       <c r="D154" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Two Way Angle Valve</v>
       </c>
       <c r="E154" t="str">
         <v>Faucets</v>
@@ -8077,7 +8077,7 @@
         <v/>
       </c>
       <c r="I154" t="str">
-        <v>cube-030-main.jpg</v>
+        <v>cube-033-main.jpg</v>
       </c>
       <c r="J154" t="str">
         <v/>
@@ -8106,13 +8106,13 @@
         <v>Cube</v>
       </c>
       <c r="B155" t="str">
-        <v>cube-031</v>
+        <v>cube-034</v>
       </c>
       <c r="C155" t="str">
-        <v>CUBE-031</v>
+        <v>CUBE-034</v>
       </c>
       <c r="D155" t="str">
-        <v>Sink Cock</v>
+        <v>Two Way Bib Cock</v>
       </c>
       <c r="E155" t="str">
         <v>Faucets</v>
@@ -8127,7 +8127,7 @@
         <v/>
       </c>
       <c r="I155" t="str">
-        <v>cube-031-main.jpg</v>
+        <v>cube-034-main.jpg</v>
       </c>
       <c r="J155" t="str">
         <v/>
@@ -8156,13 +8156,13 @@
         <v>Cube</v>
       </c>
       <c r="B156" t="str">
-        <v>cube-032</v>
+        <v>cube-035</v>
       </c>
       <c r="C156" t="str">
-        <v>CUBE-032</v>
+        <v>CUBE-035</v>
       </c>
       <c r="D156" t="str">
-        <v>Sink Mixer</v>
+        <v>Wall Mixer Button Spout with Bend</v>
       </c>
       <c r="E156" t="str">
         <v>Faucets</v>
@@ -8177,7 +8177,7 @@
         <v/>
       </c>
       <c r="I156" t="str">
-        <v>cube-032-main.jpg</v>
+        <v>cube-035-main.jpg</v>
       </c>
       <c r="J156" t="str">
         <v/>
@@ -8206,13 +8206,13 @@
         <v>Cube</v>
       </c>
       <c r="B157" t="str">
-        <v>cube-033</v>
+        <v>cube-036</v>
       </c>
       <c r="C157" t="str">
-        <v>CUBE-033</v>
+        <v>CUBE-036</v>
       </c>
       <c r="D157" t="str">
-        <v>Two Way Angle Valve</v>
+        <v>Wall Mixer Telephonic</v>
       </c>
       <c r="E157" t="str">
         <v>Faucets</v>
@@ -8227,7 +8227,7 @@
         <v/>
       </c>
       <c r="I157" t="str">
-        <v>cube-033-main.jpg</v>
+        <v>cube-036-main.jpg</v>
       </c>
       <c r="J157" t="str">
         <v/>
@@ -8256,13 +8256,13 @@
         <v>Cube</v>
       </c>
       <c r="B158" t="str">
-        <v>cube-034</v>
+        <v>cube-037</v>
       </c>
       <c r="C158" t="str">
-        <v>CUBE-034</v>
+        <v>CUBE-037</v>
       </c>
       <c r="D158" t="str">
-        <v>Two Way Bib Cock</v>
+        <v>Wall Mixer with Bend</v>
       </c>
       <c r="E158" t="str">
         <v>Faucets</v>
@@ -8277,7 +8277,7 @@
         <v/>
       </c>
       <c r="I158" t="str">
-        <v>cube-034-main.jpg</v>
+        <v>cube-037-main.jpg</v>
       </c>
       <c r="J158" t="str">
         <v/>
@@ -8306,13 +8306,13 @@
         <v>Cube</v>
       </c>
       <c r="B159" t="str">
-        <v>cube-035</v>
+        <v>cube-038</v>
       </c>
       <c r="C159" t="str">
-        <v>CUBE-035</v>
+        <v>CUBE-038</v>
       </c>
       <c r="D159" t="str">
-        <v>Wall Mixer Button Spout with Bend</v>
+        <v>Wall Mixer with Crutch</v>
       </c>
       <c r="E159" t="str">
         <v>Faucets</v>
@@ -8327,7 +8327,7 @@
         <v/>
       </c>
       <c r="I159" t="str">
-        <v>cube-035-main.jpg</v>
+        <v>cube-038-main.jpg</v>
       </c>
       <c r="J159" t="str">
         <v/>
@@ -8356,16 +8356,16 @@
         <v>Cube</v>
       </c>
       <c r="B160" t="str">
-        <v>cube-036</v>
+        <v>cube-039</v>
       </c>
       <c r="C160" t="str">
-        <v>CUBE-036</v>
+        <v>CUBE-039</v>
       </c>
       <c r="D160" t="str">
-        <v>Wall Mixer Telephonic</v>
+        <v>Waste Coupling</v>
       </c>
       <c r="E160" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F160" t="str">
         <v/>
@@ -8377,7 +8377,7 @@
         <v/>
       </c>
       <c r="I160" t="str">
-        <v>cube-036-main.jpg</v>
+        <v>cube-039-main.png</v>
       </c>
       <c r="J160" t="str">
         <v/>
@@ -8403,16 +8403,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B161" t="str">
-        <v>cube-037</v>
+        <v>cube-prima-001</v>
       </c>
       <c r="C161" t="str">
-        <v>CUBE-037</v>
+        <v>CUBE-PRIMA-001</v>
       </c>
       <c r="D161" t="str">
-        <v>Wall Mixer with Bend</v>
+        <v>2 Way Angle Valve</v>
       </c>
       <c r="E161" t="str">
         <v>Faucets</v>
@@ -8427,7 +8427,7 @@
         <v/>
       </c>
       <c r="I161" t="str">
-        <v>cube-037-main.jpg</v>
+        <v>cube-prima-001-main.jpg</v>
       </c>
       <c r="J161" t="str">
         <v/>
@@ -8453,16 +8453,16 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B162" t="str">
-        <v>cube-038</v>
+        <v>cube-prima-002</v>
       </c>
       <c r="C162" t="str">
-        <v>CUBE-038</v>
+        <v>CUBE-PRIMA-002</v>
       </c>
       <c r="D162" t="str">
-        <v>Wall Mixer with Crutch</v>
+        <v>2 Way Bib Cock</v>
       </c>
       <c r="E162" t="str">
         <v>Faucets</v>
@@ -8477,7 +8477,7 @@
         <v/>
       </c>
       <c r="I162" t="str">
-        <v>cube-038-main.jpg</v>
+        <v>cube-prima-002-main.jpg</v>
       </c>
       <c r="J162" t="str">
         <v/>
@@ -8503,19 +8503,19 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B163" t="str">
-        <v>cube-039</v>
+        <v>cube-prima-003</v>
       </c>
       <c r="C163" t="str">
-        <v>CUBE-039</v>
+        <v>CUBE-PRIMA-003</v>
       </c>
       <c r="D163" t="str">
-        <v>Waste Coupling</v>
+        <v>Bath Tub Spout</v>
       </c>
       <c r="E163" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F163" t="str">
         <v/>
@@ -8527,7 +8527,7 @@
         <v/>
       </c>
       <c r="I163" t="str">
-        <v>cube-039-main.png</v>
+        <v>cube-prima-003-main.jpg</v>
       </c>
       <c r="J163" t="str">
         <v/>
@@ -8556,13 +8556,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B164" t="str">
-        <v>cube-prima-001</v>
+        <v>cube-prima-004</v>
       </c>
       <c r="C164" t="str">
-        <v>CUBE-PRIMA-001</v>
+        <v>CUBE-PRIMA-004</v>
       </c>
       <c r="D164" t="str">
-        <v>2 Way Angle Valve</v>
+        <v>Button Spout</v>
       </c>
       <c r="E164" t="str">
         <v>Faucets</v>
@@ -8577,7 +8577,7 @@
         <v/>
       </c>
       <c r="I164" t="str">
-        <v>cube-prima-001-main.jpg</v>
+        <v>cube-prima-004-main.jpg</v>
       </c>
       <c r="J164" t="str">
         <v/>
@@ -8606,13 +8606,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B165" t="str">
-        <v>cube-prima-002</v>
+        <v>cube-prima-005</v>
       </c>
       <c r="C165" t="str">
-        <v>CUBE-PRIMA-002</v>
+        <v>CUBE-PRIMA-005</v>
       </c>
       <c r="D165" t="str">
-        <v>2 Way Bib Cock</v>
+        <v>Center Hole Basin Mixer</v>
       </c>
       <c r="E165" t="str">
         <v>Faucets</v>
@@ -8627,7 +8627,7 @@
         <v/>
       </c>
       <c r="I165" t="str">
-        <v>cube-prima-002-main.jpg</v>
+        <v>cube-prima-005-main.jpg</v>
       </c>
       <c r="J165" t="str">
         <v/>
@@ -8656,13 +8656,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B166" t="str">
-        <v>cube-prima-003</v>
+        <v>cube-prima-006</v>
       </c>
       <c r="C166" t="str">
-        <v>CUBE-PRIMA-003</v>
+        <v>CUBE-PRIMA-006</v>
       </c>
       <c r="D166" t="str">
-        <v>Bath Tub Spout</v>
+        <v>Concealed Stop Cock 15mm</v>
       </c>
       <c r="E166" t="str">
         <v>Faucets</v>
@@ -8677,7 +8677,7 @@
         <v/>
       </c>
       <c r="I166" t="str">
-        <v>cube-prima-003-main.jpg</v>
+        <v>cube-prima-006-main.jpg</v>
       </c>
       <c r="J166" t="str">
         <v/>
@@ -8706,13 +8706,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B167" t="str">
-        <v>cube-prima-004</v>
+        <v>cube-prima-007</v>
       </c>
       <c r="C167" t="str">
-        <v>CUBE-PRIMA-004</v>
+        <v>CUBE-PRIMA-007</v>
       </c>
       <c r="D167" t="str">
-        <v>Button Spout</v>
+        <v>Concealed Stop Cock 20mm</v>
       </c>
       <c r="E167" t="str">
         <v>Faucets</v>
@@ -8727,7 +8727,7 @@
         <v/>
       </c>
       <c r="I167" t="str">
-        <v>cube-prima-004-main.jpg</v>
+        <v>cube-prima-007-main.jpg</v>
       </c>
       <c r="J167" t="str">
         <v/>
@@ -8756,13 +8756,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B168" t="str">
-        <v>cube-prima-005</v>
+        <v>cube-prima-008</v>
       </c>
       <c r="C168" t="str">
-        <v>CUBE-PRIMA-005</v>
+        <v>CUBE-PRIMA-008</v>
       </c>
       <c r="D168" t="str">
-        <v>Center Hole Basin Mixer</v>
+        <v>High Flow Diverter Complete with Upper Parts</v>
       </c>
       <c r="E168" t="str">
         <v>Faucets</v>
@@ -8777,7 +8777,7 @@
         <v/>
       </c>
       <c r="I168" t="str">
-        <v>cube-prima-005-main.jpg</v>
+        <v>cube-prima-008-main.jpg</v>
       </c>
       <c r="J168" t="str">
         <v/>
@@ -8806,13 +8806,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B169" t="str">
-        <v>cube-prima-006</v>
+        <v>cube-prima-009</v>
       </c>
       <c r="C169" t="str">
-        <v>CUBE-PRIMA-006</v>
+        <v>CUBE-PRIMA-009</v>
       </c>
       <c r="D169" t="str">
-        <v>Concealed Stop Cock 15mm</v>
+        <v>Long Body</v>
       </c>
       <c r="E169" t="str">
         <v>Faucets</v>
@@ -8827,7 +8827,7 @@
         <v/>
       </c>
       <c r="I169" t="str">
-        <v>cube-prima-006-main.jpg</v>
+        <v>cube-prima-009-main.jpg</v>
       </c>
       <c r="J169" t="str">
         <v/>
@@ -8856,13 +8856,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B170" t="str">
-        <v>cube-prima-007</v>
+        <v>cube-prima-010</v>
       </c>
       <c r="C170" t="str">
-        <v>CUBE-PRIMA-007</v>
+        <v>CUBE-PRIMA-010</v>
       </c>
       <c r="D170" t="str">
-        <v>Concealed Stop Cock 20mm</v>
+        <v>Nozzle Bib Cock</v>
       </c>
       <c r="E170" t="str">
         <v>Faucets</v>
@@ -8877,7 +8877,7 @@
         <v/>
       </c>
       <c r="I170" t="str">
-        <v>cube-prima-007-main.jpg</v>
+        <v>cube-prima-010-main.jpg</v>
       </c>
       <c r="J170" t="str">
         <v/>
@@ -8906,13 +8906,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B171" t="str">
-        <v>cube-prima-008</v>
+        <v>cube-prima-011</v>
       </c>
       <c r="C171" t="str">
-        <v>CUBE-PRIMA-008</v>
+        <v>CUBE-PRIMA-011</v>
       </c>
       <c r="D171" t="str">
-        <v>High Flow Diverter Complete with Upper Parts</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E171" t="str">
         <v>Faucets</v>
@@ -8927,7 +8927,7 @@
         <v/>
       </c>
       <c r="I171" t="str">
-        <v>cube-prima-008-main.jpg</v>
+        <v>cube-prima-011-main.jpg</v>
       </c>
       <c r="J171" t="str">
         <v/>
@@ -8956,13 +8956,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B172" t="str">
-        <v>cube-prima-009</v>
+        <v>cube-prima-012</v>
       </c>
       <c r="C172" t="str">
-        <v>CUBE-PRIMA-009</v>
+        <v>CUBE-PRIMA-012</v>
       </c>
       <c r="D172" t="str">
-        <v>Long Body</v>
+        <v>Pillar Cock Extended Body Casted One Piece</v>
       </c>
       <c r="E172" t="str">
         <v>Faucets</v>
@@ -8977,7 +8977,7 @@
         <v/>
       </c>
       <c r="I172" t="str">
-        <v>cube-prima-009-main.jpg</v>
+        <v>cube-prima-012-main.jpg</v>
       </c>
       <c r="J172" t="str">
         <v/>
@@ -9006,13 +9006,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B173" t="str">
-        <v>cube-prima-010</v>
+        <v>cube-prima-013</v>
       </c>
       <c r="C173" t="str">
-        <v>CUBE-PRIMA-010</v>
+        <v>CUBE-PRIMA-013</v>
       </c>
       <c r="D173" t="str">
-        <v>Nozzle Bib Cock</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E173" t="str">
         <v>Faucets</v>
@@ -9027,7 +9027,7 @@
         <v/>
       </c>
       <c r="I173" t="str">
-        <v>cube-prima-010-main.jpg</v>
+        <v>cube-prima-013-main.jpg</v>
       </c>
       <c r="J173" t="str">
         <v/>
@@ -9056,13 +9056,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B174" t="str">
-        <v>cube-prima-011</v>
+        <v>cube-prima-014</v>
       </c>
       <c r="C174" t="str">
-        <v>CUBE-PRIMA-011</v>
+        <v>CUBE-PRIMA-014</v>
       </c>
       <c r="D174" t="str">
-        <v>Pillar Cock</v>
+        <v>Single Lever Basin Mixer Extended Body</v>
       </c>
       <c r="E174" t="str">
         <v>Faucets</v>
@@ -9077,7 +9077,7 @@
         <v/>
       </c>
       <c r="I174" t="str">
-        <v>cube-prima-011-main.jpg</v>
+        <v>cube-prima-014-main.jpg</v>
       </c>
       <c r="J174" t="str">
         <v/>
@@ -9106,13 +9106,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B175" t="str">
-        <v>cube-prima-012</v>
+        <v>cube-prima-015</v>
       </c>
       <c r="C175" t="str">
-        <v>CUBE-PRIMA-012</v>
+        <v>CUBE-PRIMA-015</v>
       </c>
       <c r="D175" t="str">
-        <v>Pillar Cock Extended Body Casted One Piece</v>
+        <v>Single Lever Concealed Basin Mixer Exposed Parts</v>
       </c>
       <c r="E175" t="str">
         <v>Faucets</v>
@@ -9127,7 +9127,7 @@
         <v/>
       </c>
       <c r="I175" t="str">
-        <v>cube-prima-012-main.jpg</v>
+        <v>cube-prima-015-main.jpg</v>
       </c>
       <c r="J175" t="str">
         <v/>
@@ -9156,13 +9156,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B176" t="str">
-        <v>cube-prima-013</v>
+        <v>cube-prima-016</v>
       </c>
       <c r="C176" t="str">
-        <v>CUBE-PRIMA-013</v>
+        <v>CUBE-PRIMA-016</v>
       </c>
       <c r="D176" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Single Lever Sink Mixer Angular</v>
       </c>
       <c r="E176" t="str">
         <v>Faucets</v>
@@ -9177,7 +9177,7 @@
         <v/>
       </c>
       <c r="I176" t="str">
-        <v>cube-prima-013-main.jpg</v>
+        <v>cube-prima-016-main.jpg</v>
       </c>
       <c r="J176" t="str">
         <v/>
@@ -9206,13 +9206,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B177" t="str">
-        <v>cube-prima-014</v>
+        <v>cube-prima-017</v>
       </c>
       <c r="C177" t="str">
-        <v>CUBE-PRIMA-014</v>
+        <v>CUBE-PRIMA-017</v>
       </c>
       <c r="D177" t="str">
-        <v>Single Lever Basin Mixer Extended Body</v>
+        <v>Single Lever Sink Mixer Side Handle</v>
       </c>
       <c r="E177" t="str">
         <v>Faucets</v>
@@ -9227,7 +9227,7 @@
         <v/>
       </c>
       <c r="I177" t="str">
-        <v>cube-prima-014-main.jpg</v>
+        <v>cube-prima-017-main.jpg</v>
       </c>
       <c r="J177" t="str">
         <v/>
@@ -9256,13 +9256,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B178" t="str">
-        <v>cube-prima-015</v>
+        <v>cube-prima-018</v>
       </c>
       <c r="C178" t="str">
-        <v>CUBE-PRIMA-015</v>
+        <v>CUBE-PRIMA-018</v>
       </c>
       <c r="D178" t="str">
-        <v>Single Lever Concealed Basin Mixer Exposed Parts</v>
+        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
       </c>
       <c r="E178" t="str">
         <v>Faucets</v>
@@ -9277,7 +9277,7 @@
         <v/>
       </c>
       <c r="I178" t="str">
-        <v>cube-prima-015-main.jpg</v>
+        <v>cube-prima-018-main.jpg</v>
       </c>
       <c r="J178" t="str">
         <v/>
@@ -9306,13 +9306,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B179" t="str">
-        <v>cube-prima-016</v>
+        <v>cube-prima-019</v>
       </c>
       <c r="C179" t="str">
-        <v>CUBE-PRIMA-016</v>
+        <v>CUBE-PRIMA-019</v>
       </c>
       <c r="D179" t="str">
-        <v>Single Lever Sink Mixer Angular</v>
+        <v>Single Lever Sink Mixer Wall Mounted Cube</v>
       </c>
       <c r="E179" t="str">
         <v>Faucets</v>
@@ -9327,7 +9327,7 @@
         <v/>
       </c>
       <c r="I179" t="str">
-        <v>cube-prima-016-main.jpg</v>
+        <v>cube-prima-019-main.jpg</v>
       </c>
       <c r="J179" t="str">
         <v/>
@@ -9356,13 +9356,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B180" t="str">
-        <v>cube-prima-017</v>
+        <v>cube-prima-020</v>
       </c>
       <c r="C180" t="str">
-        <v>CUBE-PRIMA-017</v>
+        <v>CUBE-PRIMA-020</v>
       </c>
       <c r="D180" t="str">
-        <v>Single Lever Sink Mixer Side Handle</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E180" t="str">
         <v>Faucets</v>
@@ -9377,7 +9377,7 @@
         <v/>
       </c>
       <c r="I180" t="str">
-        <v>cube-prima-017-main.jpg</v>
+        <v>cube-prima-020-main.jpg</v>
       </c>
       <c r="J180" t="str">
         <v/>
@@ -9406,13 +9406,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B181" t="str">
-        <v>cube-prima-018</v>
+        <v>cube-prima-021</v>
       </c>
       <c r="C181" t="str">
-        <v>CUBE-PRIMA-018</v>
+        <v>CUBE-PRIMA-021</v>
       </c>
       <c r="D181" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E181" t="str">
         <v>Faucets</v>
@@ -9427,7 +9427,7 @@
         <v/>
       </c>
       <c r="I181" t="str">
-        <v>cube-prima-018-main.jpg</v>
+        <v>cube-prima-021-main.jpg</v>
       </c>
       <c r="J181" t="str">
         <v/>
@@ -9456,13 +9456,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B182" t="str">
-        <v>cube-prima-019</v>
+        <v>cube-prima-022</v>
       </c>
       <c r="C182" t="str">
-        <v>CUBE-PRIMA-019</v>
+        <v>CUBE-PRIMA-022</v>
       </c>
       <c r="D182" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Cube</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E182" t="str">
         <v>Faucets</v>
@@ -9477,7 +9477,7 @@
         <v/>
       </c>
       <c r="I182" t="str">
-        <v>cube-prima-019-main.jpg</v>
+        <v>cube-prima-022-main.jpg</v>
       </c>
       <c r="J182" t="str">
         <v/>
@@ -9506,16 +9506,16 @@
         <v>Cube Prima</v>
       </c>
       <c r="B183" t="str">
-        <v>cube-prima-020</v>
+        <v>cube-prima-023</v>
       </c>
       <c r="C183" t="str">
-        <v>CUBE-PRIMA-020</v>
+        <v>CUBE-PRIMA-023</v>
       </c>
       <c r="D183" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Swarn Neck</v>
       </c>
       <c r="E183" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F183" t="str">
         <v/>
@@ -9527,7 +9527,7 @@
         <v/>
       </c>
       <c r="I183" t="str">
-        <v>cube-prima-020-main.jpg</v>
+        <v>cube-prima-023-main.jpg</v>
       </c>
       <c r="J183" t="str">
         <v/>
@@ -9556,13 +9556,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B184" t="str">
-        <v>cube-prima-021</v>
+        <v>cube-prima-024</v>
       </c>
       <c r="C184" t="str">
-        <v>CUBE-PRIMA-021</v>
+        <v>CUBE-PRIMA-024</v>
       </c>
       <c r="D184" t="str">
-        <v>Sink Cock</v>
+        <v>Wall Mixer Non Telephonic</v>
       </c>
       <c r="E184" t="str">
         <v>Faucets</v>
@@ -9577,7 +9577,7 @@
         <v/>
       </c>
       <c r="I184" t="str">
-        <v>cube-prima-021-main.jpg</v>
+        <v>cube-prima-024-main.jpg</v>
       </c>
       <c r="J184" t="str">
         <v/>
@@ -9606,13 +9606,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B185" t="str">
-        <v>cube-prima-022</v>
+        <v>cube-prima-025</v>
       </c>
       <c r="C185" t="str">
-        <v>CUBE-PRIMA-022</v>
+        <v>CUBE-PRIMA-025</v>
       </c>
       <c r="D185" t="str">
-        <v>Sink Mixer</v>
+        <v>Wall Mixer with Bend</v>
       </c>
       <c r="E185" t="str">
         <v>Faucets</v>
@@ -9627,7 +9627,7 @@
         <v/>
       </c>
       <c r="I185" t="str">
-        <v>cube-prima-022-main.jpg</v>
+        <v>cube-prima-025-main.jpg</v>
       </c>
       <c r="J185" t="str">
         <v/>
@@ -9656,16 +9656,16 @@
         <v>Cube Prima</v>
       </c>
       <c r="B186" t="str">
-        <v>cube-prima-023</v>
+        <v>cube-prima-026</v>
       </c>
       <c r="C186" t="str">
-        <v>CUBE-PRIMA-023</v>
+        <v>CUBE-PRIMA-026</v>
       </c>
       <c r="D186" t="str">
-        <v>Swarn Neck</v>
+        <v>Wall Mixer with Bend 3-in-1</v>
       </c>
       <c r="E186" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F186" t="str">
         <v/>
@@ -9677,7 +9677,7 @@
         <v/>
       </c>
       <c r="I186" t="str">
-        <v>cube-prima-023-main.jpg</v>
+        <v>cube-prima-026-main.jpg</v>
       </c>
       <c r="J186" t="str">
         <v/>
@@ -9706,13 +9706,13 @@
         <v>Cube Prima</v>
       </c>
       <c r="B187" t="str">
-        <v>cube-prima-024</v>
+        <v>cube-prima-027</v>
       </c>
       <c r="C187" t="str">
-        <v>CUBE-PRIMA-024</v>
+        <v>CUBE-PRIMA-027</v>
       </c>
       <c r="D187" t="str">
-        <v>Wall Mixer Non Telephonic</v>
+        <v>Wall Mixer with Crutch</v>
       </c>
       <c r="E187" t="str">
         <v>Faucets</v>
@@ -9727,7 +9727,7 @@
         <v/>
       </c>
       <c r="I187" t="str">
-        <v>cube-prima-024-main.jpg</v>
+        <v>cube-prima-027-main.jpg</v>
       </c>
       <c r="J187" t="str">
         <v/>
@@ -9753,16 +9753,16 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Cube Prima</v>
+        <v>Fuzone</v>
       </c>
       <c r="B188" t="str">
-        <v>cube-prima-025</v>
+        <v>fuzone-001</v>
       </c>
       <c r="C188" t="str">
-        <v>CUBE-PRIMA-025</v>
+        <v>FUZONE-001</v>
       </c>
       <c r="D188" t="str">
-        <v>Wall Mixer with Bend</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E188" t="str">
         <v>Faucets</v>
@@ -9777,7 +9777,7 @@
         <v/>
       </c>
       <c r="I188" t="str">
-        <v>cube-prima-025-main.jpg</v>
+        <v>fuzone-001-main.jpg</v>
       </c>
       <c r="J188" t="str">
         <v/>
@@ -9803,16 +9803,16 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Cube Prima</v>
+        <v>Fuzone</v>
       </c>
       <c r="B189" t="str">
-        <v>cube-prima-026</v>
+        <v>fuzone-002</v>
       </c>
       <c r="C189" t="str">
-        <v>CUBE-PRIMA-026</v>
+        <v>FUZONE-002</v>
       </c>
       <c r="D189" t="str">
-        <v>Wall Mixer with Bend 3-in-1</v>
+        <v>Bath Tub Spout</v>
       </c>
       <c r="E189" t="str">
         <v>Faucets</v>
@@ -9827,7 +9827,7 @@
         <v/>
       </c>
       <c r="I189" t="str">
-        <v>cube-prima-026-main.jpg</v>
+        <v>fuzone-002-main.jpg</v>
       </c>
       <c r="J189" t="str">
         <v/>
@@ -9853,16 +9853,16 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Cube Prima</v>
+        <v>Fuzone</v>
       </c>
       <c r="B190" t="str">
-        <v>cube-prima-027</v>
+        <v>fuzone-003</v>
       </c>
       <c r="C190" t="str">
-        <v>CUBE-PRIMA-027</v>
+        <v>FUZONE-003</v>
       </c>
       <c r="D190" t="str">
-        <v>Wall Mixer with Crutch</v>
+        <v>Bib Cock</v>
       </c>
       <c r="E190" t="str">
         <v>Faucets</v>
@@ -9877,7 +9877,7 @@
         <v/>
       </c>
       <c r="I190" t="str">
-        <v>cube-prima-027-main.jpg</v>
+        <v>fuzone-003-main.jpg</v>
       </c>
       <c r="J190" t="str">
         <v/>
@@ -9906,13 +9906,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B191" t="str">
-        <v>fuzone-001</v>
+        <v>fuzone-004</v>
       </c>
       <c r="C191" t="str">
-        <v>FUZONE-001</v>
+        <v>FUZONE-004</v>
       </c>
       <c r="D191" t="str">
-        <v>Angle Valve</v>
+        <v>Button Spout</v>
       </c>
       <c r="E191" t="str">
         <v>Faucets</v>
@@ -9927,7 +9927,7 @@
         <v/>
       </c>
       <c r="I191" t="str">
-        <v>fuzone-001-main.jpg</v>
+        <v>fuzone-004-main.jpg</v>
       </c>
       <c r="J191" t="str">
         <v/>
@@ -9956,13 +9956,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B192" t="str">
-        <v>fuzone-002</v>
+        <v>fuzone-005</v>
       </c>
       <c r="C192" t="str">
-        <v>FUZONE-002</v>
+        <v>FUZONE-005</v>
       </c>
       <c r="D192" t="str">
-        <v>Bath Tub Spout</v>
+        <v>Center Hole Mixer</v>
       </c>
       <c r="E192" t="str">
         <v>Faucets</v>
@@ -9977,7 +9977,7 @@
         <v/>
       </c>
       <c r="I192" t="str">
-        <v>fuzone-002-main.jpg</v>
+        <v>fuzone-005-main.jpg</v>
       </c>
       <c r="J192" t="str">
         <v/>
@@ -10006,13 +10006,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B193" t="str">
-        <v>fuzone-003</v>
+        <v>fuzone-006</v>
       </c>
       <c r="C193" t="str">
-        <v>FUZONE-003</v>
+        <v>FUZONE-006</v>
       </c>
       <c r="D193" t="str">
-        <v>Bib Cock</v>
+        <v>Long Body</v>
       </c>
       <c r="E193" t="str">
         <v>Faucets</v>
@@ -10027,7 +10027,7 @@
         <v/>
       </c>
       <c r="I193" t="str">
-        <v>fuzone-003-main.jpg</v>
+        <v>fuzone-006-main.jpg</v>
       </c>
       <c r="J193" t="str">
         <v/>
@@ -10056,13 +10056,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B194" t="str">
-        <v>fuzone-004</v>
+        <v>fuzone-007</v>
       </c>
       <c r="C194" t="str">
-        <v>FUZONE-004</v>
+        <v>FUZONE-007</v>
       </c>
       <c r="D194" t="str">
-        <v>Button Spout</v>
+        <v>New Sink Mixer Wall Mounted Angular Spout Fuzone</v>
       </c>
       <c r="E194" t="str">
         <v>Faucets</v>
@@ -10077,7 +10077,7 @@
         <v/>
       </c>
       <c r="I194" t="str">
-        <v>fuzone-004-main.jpg</v>
+        <v>fuzone-007-main.jpg</v>
       </c>
       <c r="J194" t="str">
         <v/>
@@ -10106,13 +10106,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B195" t="str">
-        <v>fuzone-005</v>
+        <v>fuzone-008</v>
       </c>
       <c r="C195" t="str">
-        <v>FUZONE-005</v>
+        <v>FUZONE-008</v>
       </c>
       <c r="D195" t="str">
-        <v>Center Hole Mixer</v>
+        <v>Nozzle BIB Cock</v>
       </c>
       <c r="E195" t="str">
         <v>Faucets</v>
@@ -10127,7 +10127,7 @@
         <v/>
       </c>
       <c r="I195" t="str">
-        <v>fuzone-005-main.jpg</v>
+        <v>fuzone-008-main.jpg</v>
       </c>
       <c r="J195" t="str">
         <v/>
@@ -10156,13 +10156,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B196" t="str">
-        <v>fuzone-006</v>
+        <v>fuzone-009</v>
       </c>
       <c r="C196" t="str">
-        <v>FUZONE-006</v>
+        <v>FUZONE-009</v>
       </c>
       <c r="D196" t="str">
-        <v>Long Body</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E196" t="str">
         <v>Faucets</v>
@@ -10177,7 +10177,7 @@
         <v/>
       </c>
       <c r="I196" t="str">
-        <v>fuzone-006-main.jpg</v>
+        <v>fuzone-009-main.jpg</v>
       </c>
       <c r="J196" t="str">
         <v/>
@@ -10206,13 +10206,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B197" t="str">
-        <v>fuzone-007</v>
+        <v>fuzone-010</v>
       </c>
       <c r="C197" t="str">
-        <v>FUZONE-007</v>
+        <v>FUZONE-010</v>
       </c>
       <c r="D197" t="str">
-        <v>New Sink Mixer Wall Mounted Angular Spout Fuzone</v>
+        <v>Single Lever Concealed Basin Mixer Upper Parts</v>
       </c>
       <c r="E197" t="str">
         <v>Faucets</v>
@@ -10227,7 +10227,7 @@
         <v/>
       </c>
       <c r="I197" t="str">
-        <v>fuzone-007-main.jpg</v>
+        <v>fuzone-010-main.jpg</v>
       </c>
       <c r="J197" t="str">
         <v/>
@@ -10256,13 +10256,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B198" t="str">
-        <v>fuzone-008</v>
+        <v>fuzone-011</v>
       </c>
       <c r="C198" t="str">
-        <v>FUZONE-008</v>
+        <v>FUZONE-011</v>
       </c>
       <c r="D198" t="str">
-        <v>Nozzle BIB Cock</v>
+        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
       </c>
       <c r="E198" t="str">
         <v>Faucets</v>
@@ -10277,7 +10277,7 @@
         <v/>
       </c>
       <c r="I198" t="str">
-        <v>fuzone-008-main.jpg</v>
+        <v>fuzone-011-main.jpg</v>
       </c>
       <c r="J198" t="str">
         <v/>
@@ -10306,13 +10306,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B199" t="str">
-        <v>fuzone-009</v>
+        <v>fuzone-012</v>
       </c>
       <c r="C199" t="str">
-        <v>FUZONE-009</v>
+        <v>FUZONE-012</v>
       </c>
       <c r="D199" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Single Lever Exposed Parts Kit of High Flow Diverter</v>
       </c>
       <c r="E199" t="str">
         <v>Faucets</v>
@@ -10327,7 +10327,7 @@
         <v/>
       </c>
       <c r="I199" t="str">
-        <v>fuzone-009-main.jpg</v>
+        <v>fuzone-012-main.jpg</v>
       </c>
       <c r="J199" t="str">
         <v/>
@@ -10356,13 +10356,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B200" t="str">
-        <v>fuzone-010</v>
+        <v>fuzone-013</v>
       </c>
       <c r="C200" t="str">
-        <v>FUZONE-010</v>
+        <v>FUZONE-013</v>
       </c>
       <c r="D200" t="str">
-        <v>Single Lever Concealed Basin Mixer Upper Parts</v>
+        <v>Single Lever Mixer All Boy</v>
       </c>
       <c r="E200" t="str">
         <v>Faucets</v>
@@ -10377,7 +10377,7 @@
         <v/>
       </c>
       <c r="I200" t="str">
-        <v>fuzone-010-main.jpg</v>
+        <v>fuzone-013-main.jpg</v>
       </c>
       <c r="J200" t="str">
         <v/>
@@ -10406,13 +10406,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B201" t="str">
-        <v>fuzone-011</v>
+        <v>fuzone-014</v>
       </c>
       <c r="C201" t="str">
-        <v>FUZONE-011</v>
+        <v>FUZONE-014</v>
       </c>
       <c r="D201" t="str">
-        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
+        <v>Single Lever Sink Mixer Angular</v>
       </c>
       <c r="E201" t="str">
         <v>Faucets</v>
@@ -10427,7 +10427,7 @@
         <v/>
       </c>
       <c r="I201" t="str">
-        <v>fuzone-011-main.jpg</v>
+        <v>fuzone-014-main.jpg</v>
       </c>
       <c r="J201" t="str">
         <v/>
@@ -10456,13 +10456,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B202" t="str">
-        <v>fuzone-012</v>
+        <v>fuzone-015</v>
       </c>
       <c r="C202" t="str">
-        <v>FUZONE-012</v>
+        <v>FUZONE-015</v>
       </c>
       <c r="D202" t="str">
-        <v>Single Lever Exposed Parts Kit of High Flow Diverter</v>
+        <v>Single Lever Sink Mixer Side Handle</v>
       </c>
       <c r="E202" t="str">
         <v>Faucets</v>
@@ -10477,7 +10477,7 @@
         <v/>
       </c>
       <c r="I202" t="str">
-        <v>fuzone-012-main.jpg</v>
+        <v>fuzone-015-main.jpg</v>
       </c>
       <c r="J202" t="str">
         <v/>
@@ -10506,13 +10506,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B203" t="str">
-        <v>fuzone-013</v>
+        <v>fuzone-016</v>
       </c>
       <c r="C203" t="str">
-        <v>FUZONE-013</v>
+        <v>FUZONE-016</v>
       </c>
       <c r="D203" t="str">
-        <v>Single Lever Mixer All Boy</v>
+        <v>Single Lever Sink Mixer Wall Mounted</v>
       </c>
       <c r="E203" t="str">
         <v>Faucets</v>
@@ -10527,7 +10527,7 @@
         <v/>
       </c>
       <c r="I203" t="str">
-        <v>fuzone-013-main.jpg</v>
+        <v>fuzone-016-main.jpg</v>
       </c>
       <c r="J203" t="str">
         <v/>
@@ -10556,13 +10556,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B204" t="str">
-        <v>fuzone-014</v>
+        <v>fuzone-017</v>
       </c>
       <c r="C204" t="str">
-        <v>FUZONE-014</v>
+        <v>FUZONE-017</v>
       </c>
       <c r="D204" t="str">
-        <v>Single Lever Sink Mixer Angular</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E204" t="str">
         <v>Faucets</v>
@@ -10577,7 +10577,7 @@
         <v/>
       </c>
       <c r="I204" t="str">
-        <v>fuzone-014-main.jpg</v>
+        <v>fuzone-017-main.jpg</v>
       </c>
       <c r="J204" t="str">
         <v/>
@@ -10606,13 +10606,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B205" t="str">
-        <v>fuzone-015</v>
+        <v>fuzone-018</v>
       </c>
       <c r="C205" t="str">
-        <v>FUZONE-015</v>
+        <v>FUZONE-018</v>
       </c>
       <c r="D205" t="str">
-        <v>Single Lever Sink Mixer Side Handle</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E205" t="str">
         <v>Faucets</v>
@@ -10627,7 +10627,7 @@
         <v/>
       </c>
       <c r="I205" t="str">
-        <v>fuzone-015-main.jpg</v>
+        <v>fuzone-018-main.jpg</v>
       </c>
       <c r="J205" t="str">
         <v/>
@@ -10656,13 +10656,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B206" t="str">
-        <v>fuzone-016</v>
+        <v>fuzone-019</v>
       </c>
       <c r="C206" t="str">
-        <v>FUZONE-016</v>
+        <v>FUZONE-019</v>
       </c>
       <c r="D206" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E206" t="str">
         <v>Faucets</v>
@@ -10677,7 +10677,7 @@
         <v/>
       </c>
       <c r="I206" t="str">
-        <v>fuzone-016-main.jpg</v>
+        <v>fuzone-019-main.jpg</v>
       </c>
       <c r="J206" t="str">
         <v/>
@@ -10706,13 +10706,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B207" t="str">
-        <v>fuzone-017</v>
+        <v>fuzone-020</v>
       </c>
       <c r="C207" t="str">
-        <v>FUZONE-017</v>
+        <v>FUZONE-020</v>
       </c>
       <c r="D207" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Sink Mixer Pillar Mounted Fuzone</v>
       </c>
       <c r="E207" t="str">
         <v>Faucets</v>
@@ -10727,7 +10727,7 @@
         <v/>
       </c>
       <c r="I207" t="str">
-        <v>fuzone-017-main.jpg</v>
+        <v>fuzone-020-main.jpg</v>
       </c>
       <c r="J207" t="str">
         <v/>
@@ -10756,16 +10756,16 @@
         <v>Fuzone</v>
       </c>
       <c r="B208" t="str">
-        <v>fuzone-018</v>
+        <v>fuzone-021</v>
       </c>
       <c r="C208" t="str">
-        <v>FUZONE-018</v>
+        <v>FUZONE-021</v>
       </c>
       <c r="D208" t="str">
-        <v>Sink Cock</v>
+        <v>Swarn Neck</v>
       </c>
       <c r="E208" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F208" t="str">
         <v/>
@@ -10777,7 +10777,7 @@
         <v/>
       </c>
       <c r="I208" t="str">
-        <v>fuzone-018-main.jpg</v>
+        <v>fuzone-021-main.jpg</v>
       </c>
       <c r="J208" t="str">
         <v/>
@@ -10806,13 +10806,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B209" t="str">
-        <v>fuzone-019</v>
+        <v>fuzone-022</v>
       </c>
       <c r="C209" t="str">
-        <v>FUZONE-019</v>
+        <v>FUZONE-022</v>
       </c>
       <c r="D209" t="str">
-        <v>Sink Mixer</v>
+        <v>TWO WAY Angle Valve</v>
       </c>
       <c r="E209" t="str">
         <v>Faucets</v>
@@ -10827,7 +10827,7 @@
         <v/>
       </c>
       <c r="I209" t="str">
-        <v>fuzone-019-main.jpg</v>
+        <v>fuzone-022-main.jpg</v>
       </c>
       <c r="J209" t="str">
         <v/>
@@ -10856,13 +10856,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B210" t="str">
-        <v>fuzone-020</v>
+        <v>fuzone-023</v>
       </c>
       <c r="C210" t="str">
-        <v>FUZONE-020</v>
+        <v>FUZONE-023</v>
       </c>
       <c r="D210" t="str">
-        <v>Sink Mixer Pillar Mounted Fuzone</v>
+        <v>TWO WAY BIB Cock</v>
       </c>
       <c r="E210" t="str">
         <v>Faucets</v>
@@ -10877,7 +10877,7 @@
         <v/>
       </c>
       <c r="I210" t="str">
-        <v>fuzone-020-main.jpg</v>
+        <v>fuzone-023-main.jpg</v>
       </c>
       <c r="J210" t="str">
         <v/>
@@ -10906,16 +10906,16 @@
         <v>Fuzone</v>
       </c>
       <c r="B211" t="str">
-        <v>fuzone-021</v>
+        <v>fuzone-024</v>
       </c>
       <c r="C211" t="str">
-        <v>FUZONE-021</v>
+        <v>FUZONE-024</v>
       </c>
       <c r="D211" t="str">
-        <v>Swarn Neck</v>
+        <v>Wall Mixer Button Spout with Bend</v>
       </c>
       <c r="E211" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F211" t="str">
         <v/>
@@ -10927,7 +10927,7 @@
         <v/>
       </c>
       <c r="I211" t="str">
-        <v>fuzone-021-main.jpg</v>
+        <v>fuzone-024-main.jpg</v>
       </c>
       <c r="J211" t="str">
         <v/>
@@ -10956,13 +10956,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B212" t="str">
-        <v>fuzone-022</v>
+        <v>fuzone-025</v>
       </c>
       <c r="C212" t="str">
-        <v>FUZONE-022</v>
+        <v>FUZONE-025</v>
       </c>
       <c r="D212" t="str">
-        <v>TWO WAY Angle Valve</v>
+        <v>Wall Mixer NON Telephonic</v>
       </c>
       <c r="E212" t="str">
         <v>Faucets</v>
@@ -10977,7 +10977,7 @@
         <v/>
       </c>
       <c r="I212" t="str">
-        <v>fuzone-022-main.jpg</v>
+        <v>fuzone-025-main.jpg</v>
       </c>
       <c r="J212" t="str">
         <v/>
@@ -11006,13 +11006,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B213" t="str">
-        <v>fuzone-023</v>
+        <v>fuzone-026</v>
       </c>
       <c r="C213" t="str">
-        <v>FUZONE-023</v>
+        <v>FUZONE-026</v>
       </c>
       <c r="D213" t="str">
-        <v>TWO WAY BIB Cock</v>
+        <v>Wall Mixer with Bend</v>
       </c>
       <c r="E213" t="str">
         <v>Faucets</v>
@@ -11027,7 +11027,7 @@
         <v/>
       </c>
       <c r="I213" t="str">
-        <v>fuzone-023-main.jpg</v>
+        <v>fuzone-026-main.jpg</v>
       </c>
       <c r="J213" t="str">
         <v/>
@@ -11056,13 +11056,13 @@
         <v>Fuzone</v>
       </c>
       <c r="B214" t="str">
-        <v>fuzone-024</v>
+        <v>fuzone-027</v>
       </c>
       <c r="C214" t="str">
-        <v>FUZONE-024</v>
+        <v>FUZONE-027</v>
       </c>
       <c r="D214" t="str">
-        <v>Wall Mixer Button Spout with Bend</v>
+        <v>Wall Mixer with Crutch</v>
       </c>
       <c r="E214" t="str">
         <v>Faucets</v>
@@ -11077,7 +11077,7 @@
         <v/>
       </c>
       <c r="I214" t="str">
-        <v>fuzone-024-main.jpg</v>
+        <v>fuzone-027-main.jpg</v>
       </c>
       <c r="J214" t="str">
         <v/>
@@ -11103,16 +11103,16 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fuzone</v>
+        <v>JP</v>
       </c>
       <c r="B215" t="str">
-        <v>fuzone-025</v>
+        <v>jp-001</v>
       </c>
       <c r="C215" t="str">
-        <v>FUZONE-025</v>
+        <v>JP-001</v>
       </c>
       <c r="D215" t="str">
-        <v>Wall Mixer NON Telephonic</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E215" t="str">
         <v>Faucets</v>
@@ -11127,7 +11127,7 @@
         <v/>
       </c>
       <c r="I215" t="str">
-        <v>fuzone-025-main.jpg</v>
+        <v>jp-001-main.jpg</v>
       </c>
       <c r="J215" t="str">
         <v/>
@@ -11153,16 +11153,16 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Fuzone</v>
+        <v>JP</v>
       </c>
       <c r="B216" t="str">
-        <v>fuzone-026</v>
+        <v>jp-002</v>
       </c>
       <c r="C216" t="str">
-        <v>FUZONE-026</v>
+        <v>JP-002</v>
       </c>
       <c r="D216" t="str">
-        <v>Wall Mixer with Bend</v>
+        <v>Bib Cock</v>
       </c>
       <c r="E216" t="str">
         <v>Faucets</v>
@@ -11177,7 +11177,7 @@
         <v/>
       </c>
       <c r="I216" t="str">
-        <v>fuzone-026-main.jpg</v>
+        <v>jp-002-main.jpg</v>
       </c>
       <c r="J216" t="str">
         <v/>
@@ -11203,16 +11203,16 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Fuzone</v>
+        <v>JP</v>
       </c>
       <c r="B217" t="str">
-        <v>fuzone-027</v>
+        <v>jp-003</v>
       </c>
       <c r="C217" t="str">
-        <v>FUZONE-027</v>
+        <v>JP-003</v>
       </c>
       <c r="D217" t="str">
-        <v>Wall Mixer with Crutch</v>
+        <v>Bib Cock Long Body</v>
       </c>
       <c r="E217" t="str">
         <v>Faucets</v>
@@ -11227,7 +11227,7 @@
         <v/>
       </c>
       <c r="I217" t="str">
-        <v>fuzone-027-main.jpg</v>
+        <v>jp-003-main.jpg</v>
       </c>
       <c r="J217" t="str">
         <v/>
@@ -11256,13 +11256,13 @@
         <v>JP</v>
       </c>
       <c r="B218" t="str">
-        <v>jp-001</v>
+        <v>jp-004</v>
       </c>
       <c r="C218" t="str">
-        <v>JP-001</v>
+        <v>JP-004</v>
       </c>
       <c r="D218" t="str">
-        <v>Angle Valve</v>
+        <v>Center Hole Mixer</v>
       </c>
       <c r="E218" t="str">
         <v>Faucets</v>
@@ -11277,7 +11277,7 @@
         <v/>
       </c>
       <c r="I218" t="str">
-        <v>jp-001-main.jpg</v>
+        <v>jp-004-main.jpg</v>
       </c>
       <c r="J218" t="str">
         <v/>
@@ -11306,13 +11306,13 @@
         <v>JP</v>
       </c>
       <c r="B219" t="str">
-        <v>jp-002</v>
+        <v>jp-005</v>
       </c>
       <c r="C219" t="str">
-        <v>JP-002</v>
+        <v>JP-005</v>
       </c>
       <c r="D219" t="str">
-        <v>Bib Cock</v>
+        <v>Concealed Stop Cock</v>
       </c>
       <c r="E219" t="str">
         <v>Faucets</v>
@@ -11327,7 +11327,7 @@
         <v/>
       </c>
       <c r="I219" t="str">
-        <v>jp-002-main.jpg</v>
+        <v>jp-005-main.jpg</v>
       </c>
       <c r="J219" t="str">
         <v/>
@@ -11356,13 +11356,13 @@
         <v>JP</v>
       </c>
       <c r="B220" t="str">
-        <v>jp-003</v>
+        <v>jp-006</v>
       </c>
       <c r="C220" t="str">
-        <v>JP-003</v>
+        <v>JP-006</v>
       </c>
       <c r="D220" t="str">
-        <v>Bib Cock Long Body</v>
+        <v>Nozzle Bib Cock</v>
       </c>
       <c r="E220" t="str">
         <v>Faucets</v>
@@ -11377,7 +11377,7 @@
         <v/>
       </c>
       <c r="I220" t="str">
-        <v>jp-003-main.jpg</v>
+        <v>jp-006-main.jpg</v>
       </c>
       <c r="J220" t="str">
         <v/>
@@ -11406,13 +11406,13 @@
         <v>JP</v>
       </c>
       <c r="B221" t="str">
-        <v>jp-004</v>
+        <v>jp-007</v>
       </c>
       <c r="C221" t="str">
-        <v>JP-004</v>
+        <v>JP-007</v>
       </c>
       <c r="D221" t="str">
-        <v>Center Hole Mixer</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E221" t="str">
         <v>Faucets</v>
@@ -11427,7 +11427,7 @@
         <v/>
       </c>
       <c r="I221" t="str">
-        <v>jp-004-main.jpg</v>
+        <v>jp-007-main.jpg</v>
       </c>
       <c r="J221" t="str">
         <v/>
@@ -11456,13 +11456,13 @@
         <v>JP</v>
       </c>
       <c r="B222" t="str">
-        <v>jp-005</v>
+        <v>jp-008</v>
       </c>
       <c r="C222" t="str">
-        <v>JP-005</v>
+        <v>JP-008</v>
       </c>
       <c r="D222" t="str">
-        <v>Concealed Stop Cock</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E222" t="str">
         <v>Faucets</v>
@@ -11477,7 +11477,7 @@
         <v/>
       </c>
       <c r="I222" t="str">
-        <v>jp-005-main.jpg</v>
+        <v>jp-008-main.jpg</v>
       </c>
       <c r="J222" t="str">
         <v/>
@@ -11506,13 +11506,13 @@
         <v>JP</v>
       </c>
       <c r="B223" t="str">
-        <v>jp-006</v>
+        <v>jp-009</v>
       </c>
       <c r="C223" t="str">
-        <v>JP-006</v>
+        <v>JP-009</v>
       </c>
       <c r="D223" t="str">
-        <v>Nozzle Bib Cock</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E223" t="str">
         <v>Faucets</v>
@@ -11527,7 +11527,7 @@
         <v/>
       </c>
       <c r="I223" t="str">
-        <v>jp-006-main.jpg</v>
+        <v>jp-009-main.jpg</v>
       </c>
       <c r="J223" t="str">
         <v/>
@@ -11556,13 +11556,13 @@
         <v>JP</v>
       </c>
       <c r="B224" t="str">
-        <v>jp-007</v>
+        <v>jp-010</v>
       </c>
       <c r="C224" t="str">
-        <v>JP-007</v>
+        <v>JP-010</v>
       </c>
       <c r="D224" t="str">
-        <v>Pillar Cock</v>
+        <v>Swan Neck</v>
       </c>
       <c r="E224" t="str">
         <v>Faucets</v>
@@ -11577,7 +11577,7 @@
         <v/>
       </c>
       <c r="I224" t="str">
-        <v>jp-007-main.jpg</v>
+        <v>jp-010-main.jpg</v>
       </c>
       <c r="J224" t="str">
         <v/>
@@ -11606,13 +11606,13 @@
         <v>JP</v>
       </c>
       <c r="B225" t="str">
-        <v>jp-008</v>
+        <v>jp-011</v>
       </c>
       <c r="C225" t="str">
-        <v>JP-008</v>
+        <v>JP-011</v>
       </c>
       <c r="D225" t="str">
-        <v>Sink Cock</v>
+        <v>Two Way Angle Valve</v>
       </c>
       <c r="E225" t="str">
         <v>Faucets</v>
@@ -11627,7 +11627,7 @@
         <v/>
       </c>
       <c r="I225" t="str">
-        <v>jp-008-main.jpg</v>
+        <v>jp-011-main.jpg</v>
       </c>
       <c r="J225" t="str">
         <v/>
@@ -11656,13 +11656,13 @@
         <v>JP</v>
       </c>
       <c r="B226" t="str">
-        <v>jp-009</v>
+        <v>jp-012</v>
       </c>
       <c r="C226" t="str">
-        <v>JP-009</v>
+        <v>JP-012</v>
       </c>
       <c r="D226" t="str">
-        <v>Sink Mixer</v>
+        <v>Two Way Bib Cock</v>
       </c>
       <c r="E226" t="str">
         <v>Faucets</v>
@@ -11677,7 +11677,7 @@
         <v/>
       </c>
       <c r="I226" t="str">
-        <v>jp-009-main.jpg</v>
+        <v>jp-012-main.jpg</v>
       </c>
       <c r="J226" t="str">
         <v/>
@@ -11706,13 +11706,13 @@
         <v>JP</v>
       </c>
       <c r="B227" t="str">
-        <v>jp-010</v>
+        <v>jp-013</v>
       </c>
       <c r="C227" t="str">
-        <v>JP-010</v>
+        <v>JP-013</v>
       </c>
       <c r="D227" t="str">
-        <v>Swan Neck</v>
+        <v>Wall Mixer 3 in 1 Jp</v>
       </c>
       <c r="E227" t="str">
         <v>Faucets</v>
@@ -11727,7 +11727,7 @@
         <v/>
       </c>
       <c r="I227" t="str">
-        <v>jp-010-main.jpg</v>
+        <v>jp-013-main.jpg</v>
       </c>
       <c r="J227" t="str">
         <v/>
@@ -11756,13 +11756,13 @@
         <v>JP</v>
       </c>
       <c r="B228" t="str">
-        <v>jp-011</v>
+        <v>jp-014</v>
       </c>
       <c r="C228" t="str">
-        <v>JP-011</v>
+        <v>JP-014</v>
       </c>
       <c r="D228" t="str">
-        <v>Two Way Angle Valve</v>
+        <v>Wall Mixer Non Telephonic</v>
       </c>
       <c r="E228" t="str">
         <v>Faucets</v>
@@ -11777,7 +11777,7 @@
         <v/>
       </c>
       <c r="I228" t="str">
-        <v>jp-011-main.jpg</v>
+        <v>jp-014-main.jpg</v>
       </c>
       <c r="J228" t="str">
         <v/>
@@ -11806,13 +11806,13 @@
         <v>JP</v>
       </c>
       <c r="B229" t="str">
-        <v>jp-012</v>
+        <v>jp-015</v>
       </c>
       <c r="C229" t="str">
-        <v>JP-012</v>
+        <v>JP-015</v>
       </c>
       <c r="D229" t="str">
-        <v>Two Way Bib Cock</v>
+        <v>Wall Mixer Telephonic Jp</v>
       </c>
       <c r="E229" t="str">
         <v>Faucets</v>
@@ -11827,7 +11827,7 @@
         <v/>
       </c>
       <c r="I229" t="str">
-        <v>jp-012-main.jpg</v>
+        <v>jp-015-main.jpg</v>
       </c>
       <c r="J229" t="str">
         <v/>
@@ -11856,13 +11856,13 @@
         <v>JP</v>
       </c>
       <c r="B230" t="str">
-        <v>jp-013</v>
+        <v>jp-016</v>
       </c>
       <c r="C230" t="str">
-        <v>JP-013</v>
+        <v>JP-016</v>
       </c>
       <c r="D230" t="str">
-        <v>Wall Mixer 3 in 1 Jp</v>
+        <v>Wall Mixer with Crutch Jp</v>
       </c>
       <c r="E230" t="str">
         <v>Faucets</v>
@@ -11877,7 +11877,7 @@
         <v/>
       </c>
       <c r="I230" t="str">
-        <v>jp-013-main.jpg</v>
+        <v>jp-016-main.jpg</v>
       </c>
       <c r="J230" t="str">
         <v/>
@@ -11903,16 +11903,16 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>JP</v>
+        <v>Premium</v>
       </c>
       <c r="B231" t="str">
-        <v>jp-014</v>
+        <v>premium-001</v>
       </c>
       <c r="C231" t="str">
-        <v>JP-014</v>
+        <v>PREMIUM-001</v>
       </c>
       <c r="D231" t="str">
-        <v>Wall Mixer Non Telephonic</v>
+        <v>2 Way Bib Cock</v>
       </c>
       <c r="E231" t="str">
         <v>Faucets</v>
@@ -11927,7 +11927,7 @@
         <v/>
       </c>
       <c r="I231" t="str">
-        <v>jp-014-main.jpg</v>
+        <v>premium-001-main.jpg</v>
       </c>
       <c r="J231" t="str">
         <v/>
@@ -11953,16 +11953,16 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>JP</v>
+        <v>Premium</v>
       </c>
       <c r="B232" t="str">
-        <v>jp-015</v>
+        <v>premium-002</v>
       </c>
       <c r="C232" t="str">
-        <v>JP-015</v>
+        <v>PREMIUM-002</v>
       </c>
       <c r="D232" t="str">
-        <v>Wall Mixer Telephonic Jp</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E232" t="str">
         <v>Faucets</v>
@@ -11977,7 +11977,7 @@
         <v/>
       </c>
       <c r="I232" t="str">
-        <v>jp-015-main.jpg</v>
+        <v>premium-002-main.jpg</v>
       </c>
       <c r="J232" t="str">
         <v/>
@@ -12003,16 +12003,16 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>JP</v>
+        <v>Premium</v>
       </c>
       <c r="B233" t="str">
-        <v>jp-016</v>
+        <v>premium-003</v>
       </c>
       <c r="C233" t="str">
-        <v>JP-016</v>
+        <v>PREMIUM-003</v>
       </c>
       <c r="D233" t="str">
-        <v>Wall Mixer with Crutch Jp</v>
+        <v>Bib Cock</v>
       </c>
       <c r="E233" t="str">
         <v>Faucets</v>
@@ -12027,7 +12027,7 @@
         <v/>
       </c>
       <c r="I233" t="str">
-        <v>jp-016-main.jpg</v>
+        <v>premium-003-main.jpg</v>
       </c>
       <c r="J233" t="str">
         <v/>
@@ -12056,13 +12056,13 @@
         <v>Premium</v>
       </c>
       <c r="B234" t="str">
-        <v>premium-001</v>
+        <v>premium-004</v>
       </c>
       <c r="C234" t="str">
-        <v>PREMIUM-001</v>
+        <v>PREMIUM-004</v>
       </c>
       <c r="D234" t="str">
-        <v>2 Way Bib Cock</v>
+        <v>Center Hole Mixer</v>
       </c>
       <c r="E234" t="str">
         <v>Faucets</v>
@@ -12077,7 +12077,7 @@
         <v/>
       </c>
       <c r="I234" t="str">
-        <v>premium-001-main.jpg</v>
+        <v>premium-004-main.jpg</v>
       </c>
       <c r="J234" t="str">
         <v/>
@@ -12106,16 +12106,16 @@
         <v>Premium</v>
       </c>
       <c r="B235" t="str">
-        <v>premium-002</v>
+        <v>premium-005</v>
       </c>
       <c r="C235" t="str">
-        <v>PREMIUM-002</v>
+        <v>PREMIUM-005</v>
       </c>
       <c r="D235" t="str">
-        <v>Angle Valve</v>
+        <v>Concealed 15mm Heavy</v>
       </c>
       <c r="E235" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F235" t="str">
         <v/>
@@ -12127,7 +12127,7 @@
         <v/>
       </c>
       <c r="I235" t="str">
-        <v>premium-002-main.jpg</v>
+        <v>premium-005-main.jpg</v>
       </c>
       <c r="J235" t="str">
         <v/>
@@ -12156,13 +12156,13 @@
         <v>Premium</v>
       </c>
       <c r="B236" t="str">
-        <v>premium-003</v>
+        <v>premium-006</v>
       </c>
       <c r="C236" t="str">
-        <v>PREMIUM-003</v>
+        <v>PREMIUM-006</v>
       </c>
       <c r="D236" t="str">
-        <v>Bib Cock</v>
+        <v>Flush Cock</v>
       </c>
       <c r="E236" t="str">
         <v>Faucets</v>
@@ -12177,7 +12177,7 @@
         <v/>
       </c>
       <c r="I236" t="str">
-        <v>premium-003-main.jpg</v>
+        <v>premium-006-main.jpg</v>
       </c>
       <c r="J236" t="str">
         <v/>
@@ -12206,13 +12206,13 @@
         <v>Premium</v>
       </c>
       <c r="B237" t="str">
-        <v>premium-004</v>
+        <v>premium-007</v>
       </c>
       <c r="C237" t="str">
-        <v>PREMIUM-004</v>
+        <v>PREMIUM-007</v>
       </c>
       <c r="D237" t="str">
-        <v>Center Hole Mixer</v>
+        <v>Long Body</v>
       </c>
       <c r="E237" t="str">
         <v>Faucets</v>
@@ -12227,7 +12227,7 @@
         <v/>
       </c>
       <c r="I237" t="str">
-        <v>premium-004-main.jpg</v>
+        <v>premium-007-main.jpg</v>
       </c>
       <c r="J237" t="str">
         <v/>
@@ -12256,16 +12256,16 @@
         <v>Premium</v>
       </c>
       <c r="B238" t="str">
-        <v>premium-005</v>
+        <v>premium-008</v>
       </c>
       <c r="C238" t="str">
-        <v>PREMIUM-005</v>
+        <v>PREMIUM-008</v>
       </c>
       <c r="D238" t="str">
-        <v>Concealed 15mm Heavy</v>
+        <v>Nozzle Bib Cock</v>
       </c>
       <c r="E238" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F238" t="str">
         <v/>
@@ -12277,7 +12277,7 @@
         <v/>
       </c>
       <c r="I238" t="str">
-        <v>premium-005-main.jpg</v>
+        <v>premium-008-main.jpg</v>
       </c>
       <c r="J238" t="str">
         <v/>
@@ -12306,13 +12306,13 @@
         <v>Premium</v>
       </c>
       <c r="B239" t="str">
-        <v>premium-006</v>
+        <v>premium-009</v>
       </c>
       <c r="C239" t="str">
-        <v>PREMIUM-006</v>
+        <v>PREMIUM-009</v>
       </c>
       <c r="D239" t="str">
-        <v>Flush Cock</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E239" t="str">
         <v>Faucets</v>
@@ -12327,7 +12327,7 @@
         <v/>
       </c>
       <c r="I239" t="str">
-        <v>premium-006-main.jpg</v>
+        <v>premium-009-main.jpg</v>
       </c>
       <c r="J239" t="str">
         <v/>
@@ -12356,13 +12356,13 @@
         <v>Premium</v>
       </c>
       <c r="B240" t="str">
-        <v>premium-007</v>
+        <v>premium-010</v>
       </c>
       <c r="C240" t="str">
-        <v>PREMIUM-007</v>
+        <v>PREMIUM-010</v>
       </c>
       <c r="D240" t="str">
-        <v>Long Body</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E240" t="str">
         <v>Faucets</v>
@@ -12377,7 +12377,7 @@
         <v/>
       </c>
       <c r="I240" t="str">
-        <v>premium-007-main.jpg</v>
+        <v>premium-010-main.jpg</v>
       </c>
       <c r="J240" t="str">
         <v/>
@@ -12406,13 +12406,13 @@
         <v>Premium</v>
       </c>
       <c r="B241" t="str">
-        <v>premium-008</v>
+        <v>premium-011</v>
       </c>
       <c r="C241" t="str">
-        <v>PREMIUM-008</v>
+        <v>PREMIUM-011</v>
       </c>
       <c r="D241" t="str">
-        <v>Nozzle Bib Cock</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E241" t="str">
         <v>Faucets</v>
@@ -12427,7 +12427,7 @@
         <v/>
       </c>
       <c r="I241" t="str">
-        <v>premium-008-main.jpg</v>
+        <v>premium-011-main.jpg</v>
       </c>
       <c r="J241" t="str">
         <v/>
@@ -12456,13 +12456,13 @@
         <v>Premium</v>
       </c>
       <c r="B242" t="str">
-        <v>premium-009</v>
+        <v>premium-012</v>
       </c>
       <c r="C242" t="str">
-        <v>PREMIUM-009</v>
+        <v>PREMIUM-012</v>
       </c>
       <c r="D242" t="str">
-        <v>Pillar Cock</v>
+        <v>Swan Neck</v>
       </c>
       <c r="E242" t="str">
         <v>Faucets</v>
@@ -12477,7 +12477,7 @@
         <v/>
       </c>
       <c r="I242" t="str">
-        <v>premium-009-main.jpg</v>
+        <v>premium-012-main.jpg</v>
       </c>
       <c r="J242" t="str">
         <v/>
@@ -12506,13 +12506,13 @@
         <v>Premium</v>
       </c>
       <c r="B243" t="str">
-        <v>premium-010</v>
+        <v>premium-013</v>
       </c>
       <c r="C243" t="str">
-        <v>PREMIUM-010</v>
+        <v>PREMIUM-013</v>
       </c>
       <c r="D243" t="str">
-        <v>Sink Cock</v>
+        <v>Two Way Angle Valve</v>
       </c>
       <c r="E243" t="str">
         <v>Faucets</v>
@@ -12527,7 +12527,7 @@
         <v/>
       </c>
       <c r="I243" t="str">
-        <v>premium-010-main.jpg</v>
+        <v>premium-013-main.jpg</v>
       </c>
       <c r="J243" t="str">
         <v/>
@@ -12556,13 +12556,13 @@
         <v>Premium</v>
       </c>
       <c r="B244" t="str">
-        <v>premium-011</v>
+        <v>premium-014</v>
       </c>
       <c r="C244" t="str">
-        <v>PREMIUM-011</v>
+        <v>PREMIUM-014</v>
       </c>
       <c r="D244" t="str">
-        <v>Sink Mixer</v>
+        <v>Wall Mixer 3 in</v>
       </c>
       <c r="E244" t="str">
         <v>Faucets</v>
@@ -12577,7 +12577,7 @@
         <v/>
       </c>
       <c r="I244" t="str">
-        <v>premium-011-main.jpg</v>
+        <v>premium-014-main.jpg</v>
       </c>
       <c r="J244" t="str">
         <v/>
@@ -12606,13 +12606,13 @@
         <v>Premium</v>
       </c>
       <c r="B245" t="str">
-        <v>premium-012</v>
+        <v>premium-015</v>
       </c>
       <c r="C245" t="str">
-        <v>PREMIUM-012</v>
+        <v>PREMIUM-015</v>
       </c>
       <c r="D245" t="str">
-        <v>Swan Neck</v>
+        <v>Wall Mixer Non Telephonic</v>
       </c>
       <c r="E245" t="str">
         <v>Faucets</v>
@@ -12627,7 +12627,7 @@
         <v/>
       </c>
       <c r="I245" t="str">
-        <v>premium-012-main.jpg</v>
+        <v>premium-015-main.jpg</v>
       </c>
       <c r="J245" t="str">
         <v/>
@@ -12656,13 +12656,13 @@
         <v>Premium</v>
       </c>
       <c r="B246" t="str">
-        <v>premium-013</v>
+        <v>premium-016</v>
       </c>
       <c r="C246" t="str">
-        <v>PREMIUM-013</v>
+        <v>PREMIUM-016</v>
       </c>
       <c r="D246" t="str">
-        <v>Two Way Angle Valve</v>
+        <v>Wall Mixer with Bend</v>
       </c>
       <c r="E246" t="str">
         <v>Faucets</v>
@@ -12677,7 +12677,7 @@
         <v/>
       </c>
       <c r="I246" t="str">
-        <v>premium-013-main.jpg</v>
+        <v>premium-016-main.jpg</v>
       </c>
       <c r="J246" t="str">
         <v/>
@@ -12706,13 +12706,13 @@
         <v>Premium</v>
       </c>
       <c r="B247" t="str">
-        <v>premium-014</v>
+        <v>premium-017</v>
       </c>
       <c r="C247" t="str">
-        <v>PREMIUM-014</v>
+        <v>PREMIUM-017</v>
       </c>
       <c r="D247" t="str">
-        <v>Wall Mixer 3 in</v>
+        <v>Wall Mixer with Crutch</v>
       </c>
       <c r="E247" t="str">
         <v>Faucets</v>
@@ -12727,7 +12727,7 @@
         <v/>
       </c>
       <c r="I247" t="str">
-        <v>premium-014-main.jpg</v>
+        <v>premium-017-main.jpg</v>
       </c>
       <c r="J247" t="str">
         <v/>
@@ -12753,16 +12753,16 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Premium</v>
+        <v>Para Collection</v>
       </c>
       <c r="B248" t="str">
-        <v>premium-015</v>
+        <v>para-collection-001</v>
       </c>
       <c r="C248" t="str">
-        <v>PREMIUM-015</v>
+        <v>PARA-COLLECTION-001</v>
       </c>
       <c r="D248" t="str">
-        <v>Wall Mixer Non Telephonic</v>
+        <v>Angle Valve Para</v>
       </c>
       <c r="E248" t="str">
         <v>Faucets</v>
@@ -12777,7 +12777,7 @@
         <v/>
       </c>
       <c r="I248" t="str">
-        <v>premium-015-main.jpg</v>
+        <v>para-collection-001-main.png</v>
       </c>
       <c r="J248" t="str">
         <v/>
@@ -12803,16 +12803,16 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Premium</v>
+        <v>Para Collection</v>
       </c>
       <c r="B249" t="str">
-        <v>premium-016</v>
+        <v>para-collection-002</v>
       </c>
       <c r="C249" t="str">
-        <v>PREMIUM-016</v>
+        <v>PARA-COLLECTION-002</v>
       </c>
       <c r="D249" t="str">
-        <v>Wall Mixer with Bend</v>
+        <v>Button Spout Para</v>
       </c>
       <c r="E249" t="str">
         <v>Faucets</v>
@@ -12827,7 +12827,7 @@
         <v/>
       </c>
       <c r="I249" t="str">
-        <v>premium-016-main.jpg</v>
+        <v>para-collection-002-main.png</v>
       </c>
       <c r="J249" t="str">
         <v/>
@@ -12853,16 +12853,16 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Premium</v>
+        <v>Para Collection</v>
       </c>
       <c r="B250" t="str">
-        <v>premium-017</v>
+        <v>para-collection-003</v>
       </c>
       <c r="C250" t="str">
-        <v>PREMIUM-017</v>
+        <v>PARA-COLLECTION-003</v>
       </c>
       <c r="D250" t="str">
-        <v>Wall Mixer with Crutch</v>
+        <v>Long Body Para</v>
       </c>
       <c r="E250" t="str">
         <v>Faucets</v>
@@ -12877,7 +12877,7 @@
         <v/>
       </c>
       <c r="I250" t="str">
-        <v>premium-017-main.jpg</v>
+        <v>para-collection-003-main.png</v>
       </c>
       <c r="J250" t="str">
         <v/>
@@ -12906,13 +12906,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B251" t="str">
-        <v>para-collection-001</v>
+        <v>para-collection-004</v>
       </c>
       <c r="C251" t="str">
-        <v>PARA-COLLECTION-001</v>
+        <v>PARA-COLLECTION-004</v>
       </c>
       <c r="D251" t="str">
-        <v>Angle Valve Para</v>
+        <v>Nozzle BIB Cock Para</v>
       </c>
       <c r="E251" t="str">
         <v>Faucets</v>
@@ -12927,7 +12927,7 @@
         <v/>
       </c>
       <c r="I251" t="str">
-        <v>para-collection-001-main.png</v>
+        <v>para-collection-004-main.png</v>
       </c>
       <c r="J251" t="str">
         <v/>
@@ -12956,13 +12956,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B252" t="str">
-        <v>para-collection-002</v>
+        <v>para-collection-005</v>
       </c>
       <c r="C252" t="str">
-        <v>PARA-COLLECTION-002</v>
+        <v>PARA-COLLECTION-005</v>
       </c>
       <c r="D252" t="str">
-        <v>Button Spout Para</v>
+        <v>Pilla Cock Extended Body Para</v>
       </c>
       <c r="E252" t="str">
         <v>Faucets</v>
@@ -12977,7 +12977,7 @@
         <v/>
       </c>
       <c r="I252" t="str">
-        <v>para-collection-002-main.png</v>
+        <v>para-collection-005-main.png</v>
       </c>
       <c r="J252" t="str">
         <v/>
@@ -13006,13 +13006,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B253" t="str">
-        <v>para-collection-003</v>
+        <v>para-collection-006</v>
       </c>
       <c r="C253" t="str">
-        <v>PARA-COLLECTION-003</v>
+        <v>PARA-COLLECTION-006</v>
       </c>
       <c r="D253" t="str">
-        <v>Long Body Para</v>
+        <v>Pillar Cock Para</v>
       </c>
       <c r="E253" t="str">
         <v>Faucets</v>
@@ -13027,7 +13027,7 @@
         <v/>
       </c>
       <c r="I253" t="str">
-        <v>para-collection-003-main.png</v>
+        <v>para-collection-006-main.png</v>
       </c>
       <c r="J253" t="str">
         <v/>
@@ -13056,13 +13056,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B254" t="str">
-        <v>para-collection-004</v>
+        <v>para-collection-007</v>
       </c>
       <c r="C254" t="str">
-        <v>PARA-COLLECTION-004</v>
+        <v>PARA-COLLECTION-007</v>
       </c>
       <c r="D254" t="str">
-        <v>Nozzle BIB Cock Para</v>
+        <v>Plain Spout Para</v>
       </c>
       <c r="E254" t="str">
         <v>Faucets</v>
@@ -13077,7 +13077,7 @@
         <v/>
       </c>
       <c r="I254" t="str">
-        <v>para-collection-004-main.png</v>
+        <v>para-collection-007-main.png</v>
       </c>
       <c r="J254" t="str">
         <v/>
@@ -13106,13 +13106,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B255" t="str">
-        <v>para-collection-005</v>
+        <v>para-collection-008</v>
       </c>
       <c r="C255" t="str">
-        <v>PARA-COLLECTION-005</v>
+        <v>PARA-COLLECTION-008</v>
       </c>
       <c r="D255" t="str">
-        <v>Pilla Cock Extended Body Para</v>
+        <v>Single Lever Basin Mixer Extended Body Para</v>
       </c>
       <c r="E255" t="str">
         <v>Faucets</v>
@@ -13127,7 +13127,7 @@
         <v/>
       </c>
       <c r="I255" t="str">
-        <v>para-collection-005-main.png</v>
+        <v>para-collection-008-main.png</v>
       </c>
       <c r="J255" t="str">
         <v/>
@@ -13156,13 +13156,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B256" t="str">
-        <v>para-collection-006</v>
+        <v>para-collection-009</v>
       </c>
       <c r="C256" t="str">
-        <v>PARA-COLLECTION-006</v>
+        <v>PARA-COLLECTION-009</v>
       </c>
       <c r="D256" t="str">
-        <v>Pillar Cock Para</v>
+        <v>Single Lever Basin Mixer Para</v>
       </c>
       <c r="E256" t="str">
         <v>Faucets</v>
@@ -13177,7 +13177,7 @@
         <v/>
       </c>
       <c r="I256" t="str">
-        <v>para-collection-006-main.png</v>
+        <v>para-collection-009-main.png</v>
       </c>
       <c r="J256" t="str">
         <v/>
@@ -13206,13 +13206,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B257" t="str">
-        <v>para-collection-007</v>
+        <v>para-collection-010</v>
       </c>
       <c r="C257" t="str">
-        <v>PARA-COLLECTION-007</v>
+        <v>PARA-COLLECTION-010</v>
       </c>
       <c r="D257" t="str">
-        <v>Plain Spout Para</v>
+        <v>Single Lever Concealed Basin Mixer Para</v>
       </c>
       <c r="E257" t="str">
         <v>Faucets</v>
@@ -13227,7 +13227,7 @@
         <v/>
       </c>
       <c r="I257" t="str">
-        <v>para-collection-007-main.png</v>
+        <v>para-collection-010-main.png</v>
       </c>
       <c r="J257" t="str">
         <v/>
@@ -13256,13 +13256,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B258" t="str">
-        <v>para-collection-008</v>
+        <v>para-collection-011</v>
       </c>
       <c r="C258" t="str">
-        <v>PARA-COLLECTION-008</v>
+        <v>PARA-COLLECTION-011</v>
       </c>
       <c r="D258" t="str">
-        <v>Single Lever Basin Mixer Extended Body Para</v>
+        <v>Single Lever Concealed Diverter</v>
       </c>
       <c r="E258" t="str">
         <v>Faucets</v>
@@ -13277,7 +13277,7 @@
         <v/>
       </c>
       <c r="I258" t="str">
-        <v>para-collection-008-main.png</v>
+        <v>para-collection-011-main.png</v>
       </c>
       <c r="J258" t="str">
         <v/>
@@ -13306,13 +13306,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B259" t="str">
-        <v>para-collection-009</v>
+        <v>para-collection-012</v>
       </c>
       <c r="C259" t="str">
-        <v>PARA-COLLECTION-009</v>
+        <v>PARA-COLLECTION-012</v>
       </c>
       <c r="D259" t="str">
-        <v>Single Lever Basin Mixer Para</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E259" t="str">
         <v>Faucets</v>
@@ -13327,7 +13327,7 @@
         <v/>
       </c>
       <c r="I259" t="str">
-        <v>para-collection-009-main.png</v>
+        <v>para-collection-012-main.png</v>
       </c>
       <c r="J259" t="str">
         <v/>
@@ -13356,13 +13356,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B260" t="str">
-        <v>para-collection-010</v>
+        <v>para-collection-013</v>
       </c>
       <c r="C260" t="str">
-        <v>PARA-COLLECTION-010</v>
+        <v>PARA-COLLECTION-013</v>
       </c>
       <c r="D260" t="str">
-        <v>Single Lever Concealed Basin Mixer Para</v>
+        <v>Single Lever Wall Mixer with Bend</v>
       </c>
       <c r="E260" t="str">
         <v>Faucets</v>
@@ -13377,7 +13377,7 @@
         <v/>
       </c>
       <c r="I260" t="str">
-        <v>para-collection-010-main.png</v>
+        <v>para-collection-013-main.png</v>
       </c>
       <c r="J260" t="str">
         <v/>
@@ -13406,13 +13406,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B261" t="str">
-        <v>para-collection-011</v>
+        <v>para-collection-014</v>
       </c>
       <c r="C261" t="str">
-        <v>PARA-COLLECTION-011</v>
+        <v>PARA-COLLECTION-014</v>
       </c>
       <c r="D261" t="str">
-        <v>Single Lever Concealed Diverter</v>
+        <v>Table Mounted Single Lever Kitchen Mixer Angular Spout</v>
       </c>
       <c r="E261" t="str">
         <v>Faucets</v>
@@ -13427,7 +13427,7 @@
         <v/>
       </c>
       <c r="I261" t="str">
-        <v>para-collection-011-main.png</v>
+        <v>para-collection-014-main.png</v>
       </c>
       <c r="J261" t="str">
         <v/>
@@ -13456,13 +13456,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B262" t="str">
-        <v>para-collection-012</v>
+        <v>para-collection-015</v>
       </c>
       <c r="C262" t="str">
-        <v>PARA-COLLECTION-012</v>
+        <v>PARA-COLLECTION-015</v>
       </c>
       <c r="D262" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Table Mounted Single Lever Kitchen Mixer Round Spout</v>
       </c>
       <c r="E262" t="str">
         <v>Faucets</v>
@@ -13477,7 +13477,7 @@
         <v/>
       </c>
       <c r="I262" t="str">
-        <v>para-collection-012-main.png</v>
+        <v>para-collection-015-main.png</v>
       </c>
       <c r="J262" t="str">
         <v/>
@@ -13506,13 +13506,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B263" t="str">
-        <v>para-collection-013</v>
+        <v>para-collection-016</v>
       </c>
       <c r="C263" t="str">
-        <v>PARA-COLLECTION-013</v>
+        <v>PARA-COLLECTION-016</v>
       </c>
       <c r="D263" t="str">
-        <v>Single Lever Wall Mixer with Bend</v>
+        <v>Wall Mixer with Bend Para</v>
       </c>
       <c r="E263" t="str">
         <v>Faucets</v>
@@ -13527,7 +13527,7 @@
         <v/>
       </c>
       <c r="I263" t="str">
-        <v>para-collection-013-main.png</v>
+        <v>para-collection-016-main.png</v>
       </c>
       <c r="J263" t="str">
         <v/>
@@ -13556,13 +13556,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B264" t="str">
-        <v>para-collection-014</v>
+        <v>para-collection-017</v>
       </c>
       <c r="C264" t="str">
-        <v>PARA-COLLECTION-014</v>
+        <v>PARA-COLLECTION-017</v>
       </c>
       <c r="D264" t="str">
-        <v>Table Mounted Single Lever Kitchen Mixer Angular Spout</v>
+        <v>Wall Mixer with Crutch Para</v>
       </c>
       <c r="E264" t="str">
         <v>Faucets</v>
@@ -13577,7 +13577,7 @@
         <v/>
       </c>
       <c r="I264" t="str">
-        <v>para-collection-014-main.png</v>
+        <v>para-collection-017-main.png</v>
       </c>
       <c r="J264" t="str">
         <v/>
@@ -13606,13 +13606,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B265" t="str">
-        <v>para-collection-015</v>
+        <v>para-collection-018</v>
       </c>
       <c r="C265" t="str">
-        <v>PARA-COLLECTION-015</v>
+        <v>PARA-COLLECTION-018</v>
       </c>
       <c r="D265" t="str">
-        <v>Table Mounted Single Lever Kitchen Mixer Round Spout</v>
+        <v>Wall Mounted Single Lever Kitchen Mixer Angular Spout</v>
       </c>
       <c r="E265" t="str">
         <v>Faucets</v>
@@ -13627,7 +13627,7 @@
         <v/>
       </c>
       <c r="I265" t="str">
-        <v>para-collection-015-main.png</v>
+        <v>para-collection-018-main.png</v>
       </c>
       <c r="J265" t="str">
         <v/>
@@ -13656,13 +13656,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B266" t="str">
-        <v>para-collection-016</v>
+        <v>para-collection-019</v>
       </c>
       <c r="C266" t="str">
-        <v>PARA-COLLECTION-016</v>
+        <v>PARA-COLLECTION-019</v>
       </c>
       <c r="D266" t="str">
-        <v>Wall Mixer with Bend Para</v>
+        <v>Wall Mounted Single Lever Kitchen Mixer Regular Spout</v>
       </c>
       <c r="E266" t="str">
         <v>Faucets</v>
@@ -13677,7 +13677,7 @@
         <v/>
       </c>
       <c r="I266" t="str">
-        <v>para-collection-016-main.png</v>
+        <v>para-collection-019-main.png</v>
       </c>
       <c r="J266" t="str">
         <v/>
@@ -13706,13 +13706,13 @@
         <v>Para Collection</v>
       </c>
       <c r="B267" t="str">
-        <v>para-collection-017</v>
+        <v>para-collection-020</v>
       </c>
       <c r="C267" t="str">
-        <v>PARA-COLLECTION-017</v>
+        <v>PARA-COLLECTION-020</v>
       </c>
       <c r="D267" t="str">
-        <v>Wall Mixer with Crutch Para</v>
+        <v>Wall Mounted Single Lever Kitchen Mixer Round Spout</v>
       </c>
       <c r="E267" t="str">
         <v>Faucets</v>
@@ -13727,7 +13727,7 @@
         <v/>
       </c>
       <c r="I267" t="str">
-        <v>para-collection-017-main.png</v>
+        <v>para-collection-020-main.png</v>
       </c>
       <c r="J267" t="str">
         <v/>
@@ -13753,19 +13753,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Para Collection</v>
+        <v>Allied</v>
       </c>
       <c r="B268" t="str">
-        <v>para-collection-018</v>
+        <v>allied-001</v>
       </c>
       <c r="C268" t="str">
-        <v>PARA-COLLECTION-018</v>
+        <v>ALLIED-001</v>
       </c>
       <c r="D268" t="str">
-        <v>Wall Mounted Single Lever Kitchen Mixer Angular Spout</v>
+        <v>Abs Round Hand Shower with Brass Tube</v>
       </c>
       <c r="E268" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F268" t="str">
         <v/>
@@ -13777,7 +13777,7 @@
         <v/>
       </c>
       <c r="I268" t="str">
-        <v>para-collection-018-main.png</v>
+        <v>allied-001-main.jpg</v>
       </c>
       <c r="J268" t="str">
         <v/>
@@ -13803,19 +13803,19 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Para Collection</v>
+        <v>Allied</v>
       </c>
       <c r="B269" t="str">
-        <v>para-collection-019</v>
+        <v>allied-002</v>
       </c>
       <c r="C269" t="str">
-        <v>PARA-COLLECTION-019</v>
+        <v>ALLIED-002</v>
       </c>
       <c r="D269" t="str">
-        <v>Wall Mounted Single Lever Kitchen Mixer Regular Spout</v>
+        <v>Abs Square Hand Shower with Brass Tube</v>
       </c>
       <c r="E269" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F269" t="str">
         <v/>
@@ -13827,7 +13827,7 @@
         <v/>
       </c>
       <c r="I269" t="str">
-        <v>para-collection-019-main.png</v>
+        <v>allied-002-main.jpg</v>
       </c>
       <c r="J269" t="str">
         <v/>
@@ -13853,19 +13853,19 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Para Collection</v>
+        <v>Allied</v>
       </c>
       <c r="B270" t="str">
-        <v>para-collection-020</v>
+        <v>allied-003</v>
       </c>
       <c r="C270" t="str">
-        <v>PARA-COLLECTION-020</v>
+        <v>ALLIED-003</v>
       </c>
       <c r="D270" t="str">
-        <v>Wall Mounted Single Lever Kitchen Mixer Round Spout</v>
+        <v>Aliva Maze Over Head Shower</v>
       </c>
       <c r="E270" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F270" t="str">
         <v/>
@@ -13877,7 +13877,7 @@
         <v/>
       </c>
       <c r="I270" t="str">
-        <v>para-collection-020-main.png</v>
+        <v>allied-003-main.png</v>
       </c>
       <c r="J270" t="str">
         <v/>
@@ -13906,16 +13906,16 @@
         <v>Allied</v>
       </c>
       <c r="B271" t="str">
-        <v>allied-001</v>
+        <v>allied-004</v>
       </c>
       <c r="C271" t="str">
-        <v>ALLIED-001</v>
+        <v>ALLIED-004</v>
       </c>
       <c r="D271" t="str">
-        <v>Abs Round Hand Shower with Brass Tube</v>
+        <v>Bottle Trap Full Brass</v>
       </c>
       <c r="E271" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F271" t="str">
         <v/>
@@ -13927,7 +13927,7 @@
         <v/>
       </c>
       <c r="I271" t="str">
-        <v>allied-001-main.jpg</v>
+        <v>allied-004-main.jpg</v>
       </c>
       <c r="J271" t="str">
         <v/>
@@ -13956,16 +13956,16 @@
         <v>Allied</v>
       </c>
       <c r="B272" t="str">
-        <v>allied-002</v>
+        <v>allied-005</v>
       </c>
       <c r="C272" t="str">
-        <v>ALLIED-002</v>
+        <v>ALLIED-005</v>
       </c>
       <c r="D272" t="str">
-        <v>Abs Square Hand Shower with Brass Tube</v>
+        <v>Brass Health Faucet Round Shape with 1.5 Meter Brass Tube</v>
       </c>
       <c r="E272" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F272" t="str">
         <v/>
@@ -13977,7 +13977,7 @@
         <v/>
       </c>
       <c r="I272" t="str">
-        <v>allied-002-main.jpg</v>
+        <v>allied-005-main.jpg</v>
       </c>
       <c r="J272" t="str">
         <v/>
@@ -14006,16 +14006,16 @@
         <v>Allied</v>
       </c>
       <c r="B273" t="str">
-        <v>allied-003</v>
+        <v>allied-006</v>
       </c>
       <c r="C273" t="str">
-        <v>ALLIED-003</v>
+        <v>ALLIED-006</v>
       </c>
       <c r="D273" t="str">
-        <v>Aliva Maze Over Head Shower</v>
+        <v>Brass Health Faucet Sqaure with 1.5 Meter Brass Tube</v>
       </c>
       <c r="E273" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F273" t="str">
         <v/>
@@ -14027,7 +14027,7 @@
         <v/>
       </c>
       <c r="I273" t="str">
-        <v>allied-003-main.png</v>
+        <v>allied-006-main.jpg</v>
       </c>
       <c r="J273" t="str">
         <v/>
@@ -14056,13 +14056,13 @@
         <v>Allied</v>
       </c>
       <c r="B274" t="str">
-        <v>allied-004</v>
+        <v>allied-007</v>
       </c>
       <c r="C274" t="str">
-        <v>ALLIED-004</v>
+        <v>ALLIED-007</v>
       </c>
       <c r="D274" t="str">
-        <v>Bottle Trap Full Brass</v>
+        <v>Concealed Body</v>
       </c>
       <c r="E274" t="str">
         <v>Accessories</v>
@@ -14077,7 +14077,7 @@
         <v/>
       </c>
       <c r="I274" t="str">
-        <v>allied-004-main.jpg</v>
+        <v>allied-007-main.jpg</v>
       </c>
       <c r="J274" t="str">
         <v/>
@@ -14106,13 +14106,13 @@
         <v>Allied</v>
       </c>
       <c r="B275" t="str">
-        <v>allied-005</v>
+        <v>allied-008</v>
       </c>
       <c r="C275" t="str">
-        <v>ALLIED-005</v>
+        <v>ALLIED-008</v>
       </c>
       <c r="D275" t="str">
-        <v>Brass Health Faucet Round Shape with 1.5 Meter Brass Tube</v>
+        <v>Concealed Body 15mm</v>
       </c>
       <c r="E275" t="str">
         <v>Accessories</v>
@@ -14127,7 +14127,7 @@
         <v/>
       </c>
       <c r="I275" t="str">
-        <v>allied-005-main.jpg</v>
+        <v>allied-008-main.jpg</v>
       </c>
       <c r="J275" t="str">
         <v/>
@@ -14156,16 +14156,16 @@
         <v>Allied</v>
       </c>
       <c r="B276" t="str">
-        <v>allied-006</v>
+        <v>allied-009</v>
       </c>
       <c r="C276" t="str">
-        <v>ALLIED-006</v>
+        <v>ALLIED-009</v>
       </c>
       <c r="D276" t="str">
-        <v>Brass Health Faucet Sqaure with 1.5 Meter Brass Tube</v>
+        <v>Cuba Hand Shower with Tube</v>
       </c>
       <c r="E276" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F276" t="str">
         <v/>
@@ -14177,7 +14177,7 @@
         <v/>
       </c>
       <c r="I276" t="str">
-        <v>allied-006-main.jpg</v>
+        <v>allied-009-main.png</v>
       </c>
       <c r="J276" t="str">
         <v/>
@@ -14206,16 +14206,16 @@
         <v>Allied</v>
       </c>
       <c r="B277" t="str">
-        <v>allied-007</v>
+        <v>allied-010</v>
       </c>
       <c r="C277" t="str">
-        <v>ALLIED-007</v>
+        <v>ALLIED-010</v>
       </c>
       <c r="D277" t="str">
-        <v>Concealed Body</v>
+        <v>Donut Hand Shower with Tube</v>
       </c>
       <c r="E277" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F277" t="str">
         <v/>
@@ -14227,7 +14227,7 @@
         <v/>
       </c>
       <c r="I277" t="str">
-        <v>allied-007-main.jpg</v>
+        <v>allied-010-main.png</v>
       </c>
       <c r="J277" t="str">
         <v/>
@@ -14256,16 +14256,16 @@
         <v>Allied</v>
       </c>
       <c r="B278" t="str">
-        <v>allied-008</v>
+        <v>allied-011</v>
       </c>
       <c r="C278" t="str">
-        <v>ALLIED-008</v>
+        <v>ALLIED-011</v>
       </c>
       <c r="D278" t="str">
-        <v>Concealed Body 15mm</v>
+        <v>Donut Shower Head with ARM</v>
       </c>
       <c r="E278" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F278" t="str">
         <v/>
@@ -14277,7 +14277,7 @@
         <v/>
       </c>
       <c r="I278" t="str">
-        <v>allied-008-main.jpg</v>
+        <v>allied-011-main.png</v>
       </c>
       <c r="J278" t="str">
         <v/>
@@ -14306,13 +14306,13 @@
         <v>Allied</v>
       </c>
       <c r="B279" t="str">
-        <v>allied-009</v>
+        <v>allied-012</v>
       </c>
       <c r="C279" t="str">
-        <v>ALLIED-009</v>
+        <v>ALLIED-012</v>
       </c>
       <c r="D279" t="str">
-        <v>Cuba Hand Shower with Tube</v>
+        <v>Glory Hand Shower with Tube</v>
       </c>
       <c r="E279" t="str">
         <v>Showers</v>
@@ -14327,7 +14327,7 @@
         <v/>
       </c>
       <c r="I279" t="str">
-        <v>allied-009-main.png</v>
+        <v>allied-012-main.png</v>
       </c>
       <c r="J279" t="str">
         <v/>
@@ -14356,16 +14356,16 @@
         <v>Allied</v>
       </c>
       <c r="B280" t="str">
-        <v>allied-010</v>
+        <v>allied-013</v>
       </c>
       <c r="C280" t="str">
-        <v>ALLIED-010</v>
+        <v>ALLIED-013</v>
       </c>
       <c r="D280" t="str">
-        <v>Donut Hand Shower with Tube</v>
+        <v>Health Faucet with Tube</v>
       </c>
       <c r="E280" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F280" t="str">
         <v/>
@@ -14377,7 +14377,7 @@
         <v/>
       </c>
       <c r="I280" t="str">
-        <v>allied-010-main.png</v>
+        <v>allied-013-main.png</v>
       </c>
       <c r="J280" t="str">
         <v/>
@@ -14406,16 +14406,16 @@
         <v>Allied</v>
       </c>
       <c r="B281" t="str">
-        <v>allied-011</v>
+        <v>allied-014</v>
       </c>
       <c r="C281" t="str">
-        <v>ALLIED-011</v>
+        <v>ALLIED-014</v>
       </c>
       <c r="D281" t="str">
-        <v>Donut Shower Head with ARM</v>
+        <v>High Flow Diverter Body Three in Let</v>
       </c>
       <c r="E281" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F281" t="str">
         <v/>
@@ -14427,7 +14427,7 @@
         <v/>
       </c>
       <c r="I281" t="str">
-        <v>allied-011-main.png</v>
+        <v>allied-014-main.jpg</v>
       </c>
       <c r="J281" t="str">
         <v/>
@@ -14456,13 +14456,13 @@
         <v>Allied</v>
       </c>
       <c r="B282" t="str">
-        <v>allied-012</v>
+        <v>allied-015</v>
       </c>
       <c r="C282" t="str">
-        <v>ALLIED-012</v>
+        <v>ALLIED-015</v>
       </c>
       <c r="D282" t="str">
-        <v>Glory Hand Shower with Tube</v>
+        <v>Maze Square Shower Head</v>
       </c>
       <c r="E282" t="str">
         <v>Showers</v>
@@ -14477,7 +14477,7 @@
         <v/>
       </c>
       <c r="I282" t="str">
-        <v>allied-012-main.png</v>
+        <v>allied-015-main.png</v>
       </c>
       <c r="J282" t="str">
         <v/>
@@ -14506,16 +14506,16 @@
         <v>Allied</v>
       </c>
       <c r="B283" t="str">
-        <v>allied-013</v>
+        <v>allied-016</v>
       </c>
       <c r="C283" t="str">
-        <v>ALLIED-013</v>
+        <v>ALLIED-016</v>
       </c>
       <c r="D283" t="str">
-        <v>Health Faucet with Tube</v>
+        <v>Oval Maze Overhead Shower</v>
       </c>
       <c r="E283" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F283" t="str">
         <v/>
@@ -14527,7 +14527,7 @@
         <v/>
       </c>
       <c r="I283" t="str">
-        <v>allied-013-main.png</v>
+        <v>allied-016-main.png</v>
       </c>
       <c r="J283" t="str">
         <v/>
@@ -14556,13 +14556,13 @@
         <v>Allied</v>
       </c>
       <c r="B284" t="str">
-        <v>allied-014</v>
+        <v>allied-017</v>
       </c>
       <c r="C284" t="str">
-        <v>ALLIED-014</v>
+        <v>ALLIED-017</v>
       </c>
       <c r="D284" t="str">
-        <v>High Flow Diverter Body Three in Let</v>
+        <v>Pressmatic Pillar Cock</v>
       </c>
       <c r="E284" t="str">
         <v>Faucets</v>
@@ -14577,7 +14577,7 @@
         <v/>
       </c>
       <c r="I284" t="str">
-        <v>allied-014-main.jpg</v>
+        <v>allied-017-main.png</v>
       </c>
       <c r="J284" t="str">
         <v/>
@@ -14606,13 +14606,13 @@
         <v>Allied</v>
       </c>
       <c r="B285" t="str">
-        <v>allied-015</v>
+        <v>allied-018</v>
       </c>
       <c r="C285" t="str">
-        <v>ALLIED-015</v>
+        <v>ALLIED-018</v>
       </c>
       <c r="D285" t="str">
-        <v>Maze Square Shower Head</v>
+        <v>Round 4 Inch Shower Head with ARM</v>
       </c>
       <c r="E285" t="str">
         <v>Showers</v>
@@ -14627,7 +14627,7 @@
         <v/>
       </c>
       <c r="I285" t="str">
-        <v>allied-015-main.png</v>
+        <v>allied-018-main.png</v>
       </c>
       <c r="J285" t="str">
         <v/>
@@ -14656,13 +14656,13 @@
         <v>Allied</v>
       </c>
       <c r="B286" t="str">
-        <v>allied-016</v>
+        <v>allied-019</v>
       </c>
       <c r="C286" t="str">
-        <v>ALLIED-016</v>
+        <v>ALLIED-019</v>
       </c>
       <c r="D286" t="str">
-        <v>Oval Maze Overhead Shower</v>
+        <v>Round Hand Shower with Tube</v>
       </c>
       <c r="E286" t="str">
         <v>Showers</v>
@@ -14677,7 +14677,7 @@
         <v/>
       </c>
       <c r="I286" t="str">
-        <v>allied-016-main.png</v>
+        <v>allied-019-main.png</v>
       </c>
       <c r="J286" t="str">
         <v/>
@@ -14706,16 +14706,16 @@
         <v>Allied</v>
       </c>
       <c r="B287" t="str">
-        <v>allied-017</v>
+        <v>allied-020</v>
       </c>
       <c r="C287" t="str">
-        <v>ALLIED-017</v>
+        <v>ALLIED-020</v>
       </c>
       <c r="D287" t="str">
-        <v>Pressmatic Pillar Cock</v>
+        <v>Shower Head Round Maze</v>
       </c>
       <c r="E287" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F287" t="str">
         <v/>
@@ -14727,7 +14727,7 @@
         <v/>
       </c>
       <c r="I287" t="str">
-        <v>allied-017-main.png</v>
+        <v>allied-020-main.png</v>
       </c>
       <c r="J287" t="str">
         <v/>
@@ -14756,13 +14756,13 @@
         <v>Allied</v>
       </c>
       <c r="B288" t="str">
-        <v>allied-018</v>
+        <v>allied-021</v>
       </c>
       <c r="C288" t="str">
-        <v>ALLIED-018</v>
+        <v>ALLIED-021</v>
       </c>
       <c r="D288" t="str">
-        <v>Round 4 Inch Shower Head with ARM</v>
+        <v>Shower Rail</v>
       </c>
       <c r="E288" t="str">
         <v>Showers</v>
@@ -14777,7 +14777,7 @@
         <v/>
       </c>
       <c r="I288" t="str">
-        <v>allied-018-main.png</v>
+        <v>allied-021-main.png</v>
       </c>
       <c r="J288" t="str">
         <v/>
@@ -14806,13 +14806,13 @@
         <v>Allied</v>
       </c>
       <c r="B289" t="str">
-        <v>allied-019</v>
+        <v>allied-022</v>
       </c>
       <c r="C289" t="str">
-        <v>ALLIED-019</v>
+        <v>ALLIED-022</v>
       </c>
       <c r="D289" t="str">
-        <v>Round Hand Shower with Tube</v>
+        <v>Shower Arm Round 450mm Brass</v>
       </c>
       <c r="E289" t="str">
         <v>Showers</v>
@@ -14827,7 +14827,7 @@
         <v/>
       </c>
       <c r="I289" t="str">
-        <v>allied-019-main.png</v>
+        <v>allied-022-main.jpg</v>
       </c>
       <c r="J289" t="str">
         <v/>
@@ -14856,13 +14856,13 @@
         <v>Allied</v>
       </c>
       <c r="B290" t="str">
-        <v>allied-020</v>
+        <v>allied-023</v>
       </c>
       <c r="C290" t="str">
-        <v>ALLIED-020</v>
+        <v>ALLIED-023</v>
       </c>
       <c r="D290" t="str">
-        <v>Shower Head Round Maze</v>
+        <v>Shower Arm Square 400mm Brass</v>
       </c>
       <c r="E290" t="str">
         <v>Showers</v>
@@ -14877,7 +14877,7 @@
         <v/>
       </c>
       <c r="I290" t="str">
-        <v>allied-020-main.png</v>
+        <v>allied-023-main.jpg</v>
       </c>
       <c r="J290" t="str">
         <v/>
@@ -14906,16 +14906,16 @@
         <v>Allied</v>
       </c>
       <c r="B291" t="str">
-        <v>allied-021</v>
+        <v>allied-024</v>
       </c>
       <c r="C291" t="str">
-        <v>ALLIED-021</v>
+        <v>ALLIED-024</v>
       </c>
       <c r="D291" t="str">
-        <v>Shower Rail</v>
+        <v>Single Lever Concealed Basin Mixer High Flow Body</v>
       </c>
       <c r="E291" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F291" t="str">
         <v/>
@@ -14927,7 +14927,7 @@
         <v/>
       </c>
       <c r="I291" t="str">
-        <v>allied-021-main.png</v>
+        <v>allied-024-main.jpg</v>
       </c>
       <c r="J291" t="str">
         <v/>
@@ -14956,16 +14956,16 @@
         <v>Allied</v>
       </c>
       <c r="B292" t="str">
-        <v>allied-022</v>
+        <v>allied-025</v>
       </c>
       <c r="C292" t="str">
-        <v>ALLIED-022</v>
+        <v>ALLIED-025</v>
       </c>
       <c r="D292" t="str">
-        <v>Shower Arm Round 450mm Brass</v>
+        <v>Single Lever Concealed Deusch Mixer Body</v>
       </c>
       <c r="E292" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F292" t="str">
         <v/>
@@ -14977,7 +14977,7 @@
         <v/>
       </c>
       <c r="I292" t="str">
-        <v>allied-022-main.jpg</v>
+        <v>allied-025-main.jpg</v>
       </c>
       <c r="J292" t="str">
         <v/>
@@ -15006,16 +15006,16 @@
         <v>Allied</v>
       </c>
       <c r="B293" t="str">
-        <v>allied-023</v>
+        <v>allied-026</v>
       </c>
       <c r="C293" t="str">
-        <v>ALLIED-023</v>
+        <v>ALLIED-026</v>
       </c>
       <c r="D293" t="str">
-        <v>Shower Arm Square 400mm Brass</v>
+        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
       </c>
       <c r="E293" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F293" t="str">
         <v/>
@@ -15027,7 +15027,7 @@
         <v/>
       </c>
       <c r="I293" t="str">
-        <v>allied-023-main.jpg</v>
+        <v>allied-026-main.jpg</v>
       </c>
       <c r="J293" t="str">
         <v/>
@@ -15056,13 +15056,13 @@
         <v>Allied</v>
       </c>
       <c r="B294" t="str">
-        <v>allied-024</v>
+        <v>allied-027</v>
       </c>
       <c r="C294" t="str">
-        <v>ALLIED-024</v>
+        <v>ALLIED-027</v>
       </c>
       <c r="D294" t="str">
-        <v>Single Lever Concealed Basin Mixer High Flow Body</v>
+        <v>Single Lever Concealed High Flow Diverter Body</v>
       </c>
       <c r="E294" t="str">
         <v>Faucets</v>
@@ -15077,7 +15077,7 @@
         <v/>
       </c>
       <c r="I294" t="str">
-        <v>allied-024-main.jpg</v>
+        <v>allied-027-main.jpg</v>
       </c>
       <c r="J294" t="str">
         <v/>
@@ -15106,16 +15106,16 @@
         <v>Allied</v>
       </c>
       <c r="B295" t="str">
-        <v>allied-025</v>
+        <v>allied-028</v>
       </c>
       <c r="C295" t="str">
-        <v>ALLIED-025</v>
+        <v>ALLIED-028</v>
       </c>
       <c r="D295" t="str">
-        <v>Single Lever Concealed Deusch Mixer Body</v>
+        <v>Wall Outlet Round with 15mm Thread to Connect Hand Shower Pipe Flange</v>
       </c>
       <c r="E295" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F295" t="str">
         <v/>
@@ -15127,7 +15127,7 @@
         <v/>
       </c>
       <c r="I295" t="str">
-        <v>allied-025-main.jpg</v>
+        <v>allied-028-main.jpg</v>
       </c>
       <c r="J295" t="str">
         <v/>
@@ -15156,16 +15156,16 @@
         <v>Allied</v>
       </c>
       <c r="B296" t="str">
-        <v>allied-026</v>
+        <v>allied-029</v>
       </c>
       <c r="C296" t="str">
-        <v>ALLIED-026</v>
+        <v>ALLIED-029</v>
       </c>
       <c r="D296" t="str">
-        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
+        <v>Wall Outlet Square with 15mm Thread to Connect Hand Shower Pipe Flange</v>
       </c>
       <c r="E296" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F296" t="str">
         <v/>
@@ -15177,7 +15177,7 @@
         <v/>
       </c>
       <c r="I296" t="str">
-        <v>allied-026-main.jpg</v>
+        <v>allied-029-main.jpg</v>
       </c>
       <c r="J296" t="str">
         <v/>
@@ -15206,16 +15206,16 @@
         <v>Allied</v>
       </c>
       <c r="B297" t="str">
-        <v>allied-027</v>
+        <v>allied-030</v>
       </c>
       <c r="C297" t="str">
-        <v>ALLIED-027</v>
+        <v>ALLIED-030</v>
       </c>
       <c r="D297" t="str">
-        <v>Single Lever Concealed High Flow Diverter Body</v>
+        <v>Waste Coupling 3 Inch with Thread CAP</v>
       </c>
       <c r="E297" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F297" t="str">
         <v/>
@@ -15227,7 +15227,7 @@
         <v/>
       </c>
       <c r="I297" t="str">
-        <v>allied-027-main.jpg</v>
+        <v>allied-030-main.png</v>
       </c>
       <c r="J297" t="str">
         <v/>
@@ -15256,16 +15256,16 @@
         <v>Allied</v>
       </c>
       <c r="B298" t="str">
-        <v>allied-028</v>
+        <v>allied-031</v>
       </c>
       <c r="C298" t="str">
-        <v>ALLIED-028</v>
+        <v>ALLIED-031</v>
       </c>
       <c r="D298" t="str">
-        <v>Wall Outlet Round with 15mm Thread to Connect Hand Shower Pipe Flange</v>
+        <v>Waste Coupling 5 Inch with Thread CAP</v>
       </c>
       <c r="E298" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F298" t="str">
         <v/>
@@ -15277,7 +15277,7 @@
         <v/>
       </c>
       <c r="I298" t="str">
-        <v>allied-028-main.jpg</v>
+        <v>allied-031-main.png</v>
       </c>
       <c r="J298" t="str">
         <v/>
@@ -15306,16 +15306,16 @@
         <v>Allied</v>
       </c>
       <c r="B299" t="str">
-        <v>allied-029</v>
+        <v>allied-032</v>
       </c>
       <c r="C299" t="str">
-        <v>ALLIED-029</v>
+        <v>ALLIED-032</v>
       </c>
       <c r="D299" t="str">
-        <v>Wall Outlet Square with 15mm Thread to Connect Hand Shower Pipe Flange</v>
+        <v>Waste Full Thread</v>
       </c>
       <c r="E299" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F299" t="str">
         <v/>
@@ -15327,7 +15327,7 @@
         <v/>
       </c>
       <c r="I299" t="str">
-        <v>allied-029-main.jpg</v>
+        <v>allied-032-main.jpg</v>
       </c>
       <c r="J299" t="str">
         <v/>
@@ -15353,19 +15353,19 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Allied</v>
+        <v>Zenith Collections</v>
       </c>
       <c r="B300" t="str">
-        <v>allied-030</v>
+        <v>zenith-collections-001</v>
       </c>
       <c r="C300" t="str">
-        <v>ALLIED-030</v>
+        <v>ZENITH-COLLECTIONS-001</v>
       </c>
       <c r="D300" t="str">
-        <v>Waste Coupling 3 Inch with Thread CAP</v>
+        <v>Single Lever Basin Mixer Chrome</v>
       </c>
       <c r="E300" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F300" t="str">
         <v/>
@@ -15377,7 +15377,7 @@
         <v/>
       </c>
       <c r="I300" t="str">
-        <v>allied-030-main.png</v>
+        <v/>
       </c>
       <c r="J300" t="str">
         <v/>
@@ -15403,19 +15403,19 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Allied</v>
+        <v>Zenith Collections</v>
       </c>
       <c r="B301" t="str">
-        <v>allied-031</v>
+        <v>zenith-collections-002</v>
       </c>
       <c r="C301" t="str">
-        <v>ALLIED-031</v>
+        <v>ZENITH-COLLECTIONS-002</v>
       </c>
       <c r="D301" t="str">
-        <v>Waste Coupling 5 Inch with Thread CAP</v>
+        <v>Single Lever Basin Mixer Matt Beige</v>
       </c>
       <c r="E301" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F301" t="str">
         <v/>
@@ -15427,7 +15427,7 @@
         <v/>
       </c>
       <c r="I301" t="str">
-        <v>allied-031-main.png</v>
+        <v/>
       </c>
       <c r="J301" t="str">
         <v/>
@@ -15453,19 +15453,19 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Allied</v>
+        <v>Zenith Collections</v>
       </c>
       <c r="B302" t="str">
-        <v>allied-032</v>
+        <v>zenith-collections-003</v>
       </c>
       <c r="C302" t="str">
-        <v>ALLIED-032</v>
+        <v>ZENITH-COLLECTIONS-003</v>
       </c>
       <c r="D302" t="str">
-        <v>Waste Full Thread</v>
+        <v>Single Lever Basin Mixer Matt Black</v>
       </c>
       <c r="E302" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F302" t="str">
         <v/>
@@ -15477,7 +15477,7 @@
         <v/>
       </c>
       <c r="I302" t="str">
-        <v>allied-032-main.jpg</v>
+        <v/>
       </c>
       <c r="J302" t="str">
         <v/>
@@ -15503,19 +15503,19 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Zenith Collections</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B303" t="str">
-        <v>zenith-collections-001</v>
+        <v>square-brass-accessories-001</v>
       </c>
       <c r="C303" t="str">
-        <v>ZENITH-COLLECTIONS-001</v>
+        <v>SQUARE-BRASS-ACCESSORIES-001</v>
       </c>
       <c r="D303" t="str">
-        <v>Single Lever Basin Mixer Chrome</v>
+        <v>Bath Rob Double Hook</v>
       </c>
       <c r="E303" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F303" t="str">
         <v/>
@@ -15527,7 +15527,7 @@
         <v/>
       </c>
       <c r="I303" t="str">
-        <v/>
+        <v>square-brass-accessories-001-main.jpg</v>
       </c>
       <c r="J303" t="str">
         <v/>
@@ -15553,19 +15553,19 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Zenith Collections</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B304" t="str">
-        <v>zenith-collections-002</v>
+        <v>square-brass-accessories-002</v>
       </c>
       <c r="C304" t="str">
-        <v>ZENITH-COLLECTIONS-002</v>
+        <v>SQUARE-BRASS-ACCESSORIES-002</v>
       </c>
       <c r="D304" t="str">
-        <v>Single Lever Basin Mixer Matt Beige</v>
+        <v>Single Towel Rail</v>
       </c>
       <c r="E304" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F304" t="str">
         <v/>
@@ -15577,7 +15577,7 @@
         <v/>
       </c>
       <c r="I304" t="str">
-        <v/>
+        <v>square-brass-accessories-002-main.jpg</v>
       </c>
       <c r="J304" t="str">
         <v/>
@@ -15603,19 +15603,19 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Zenith Collections</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B305" t="str">
-        <v>zenith-collections-003</v>
+        <v>square-brass-accessories-003</v>
       </c>
       <c r="C305" t="str">
-        <v>ZENITH-COLLECTIONS-003</v>
+        <v>SQUARE-BRASS-ACCESSORIES-003</v>
       </c>
       <c r="D305" t="str">
-        <v>Single Lever Basin Mixer Matt Black</v>
+        <v>Soap Dish</v>
       </c>
       <c r="E305" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F305" t="str">
         <v/>
@@ -15627,7 +15627,7 @@
         <v/>
       </c>
       <c r="I305" t="str">
-        <v/>
+        <v>square-brass-accessories-003-main.jpg</v>
       </c>
       <c r="J305" t="str">
         <v/>
@@ -15656,13 +15656,13 @@
         <v>Square Brass Accessories</v>
       </c>
       <c r="B306" t="str">
-        <v>square-brass-accessories-001</v>
+        <v>square-brass-accessories-004</v>
       </c>
       <c r="C306" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-001</v>
+        <v>SQUARE-BRASS-ACCESSORIES-004</v>
       </c>
       <c r="D306" t="str">
-        <v>Bath Rob Double Hook</v>
+        <v>Toilet Paper Holder Without Flap</v>
       </c>
       <c r="E306" t="str">
         <v>Accessories</v>
@@ -15677,7 +15677,7 @@
         <v/>
       </c>
       <c r="I306" t="str">
-        <v>square-brass-accessories-001-main.jpg</v>
+        <v>square-brass-accessories-004-main.jpg</v>
       </c>
       <c r="J306" t="str">
         <v/>
@@ -15706,13 +15706,13 @@
         <v>Square Brass Accessories</v>
       </c>
       <c r="B307" t="str">
-        <v>square-brass-accessories-002</v>
+        <v>square-brass-accessories-005</v>
       </c>
       <c r="C307" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-002</v>
+        <v>SQUARE-BRASS-ACCESSORIES-005</v>
       </c>
       <c r="D307" t="str">
-        <v>Single Towel Rail</v>
+        <v>Toilet Roll Holder with Flap</v>
       </c>
       <c r="E307" t="str">
         <v>Accessories</v>
@@ -15727,7 +15727,7 @@
         <v/>
       </c>
       <c r="I307" t="str">
-        <v>square-brass-accessories-002-main.jpg</v>
+        <v>square-brass-accessories-005-main.jpg</v>
       </c>
       <c r="J307" t="str">
         <v/>
@@ -15756,13 +15756,13 @@
         <v>Square Brass Accessories</v>
       </c>
       <c r="B308" t="str">
-        <v>square-brass-accessories-003</v>
+        <v>square-brass-accessories-006</v>
       </c>
       <c r="C308" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-003</v>
+        <v>SQUARE-BRASS-ACCESSORIES-006</v>
       </c>
       <c r="D308" t="str">
-        <v>Soap Dish</v>
+        <v>Towel Rack</v>
       </c>
       <c r="E308" t="str">
         <v>Accessories</v>
@@ -15777,7 +15777,7 @@
         <v/>
       </c>
       <c r="I308" t="str">
-        <v>square-brass-accessories-003-main.jpg</v>
+        <v>square-brass-accessories-006-main.jpg</v>
       </c>
       <c r="J308" t="str">
         <v/>
@@ -15806,13 +15806,13 @@
         <v>Square Brass Accessories</v>
       </c>
       <c r="B309" t="str">
-        <v>square-brass-accessories-004</v>
+        <v>square-brass-accessories-007</v>
       </c>
       <c r="C309" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-004</v>
+        <v>SQUARE-BRASS-ACCESSORIES-007</v>
       </c>
       <c r="D309" t="str">
-        <v>Toilet Paper Holder Without Flap</v>
+        <v>Tower Ring</v>
       </c>
       <c r="E309" t="str">
         <v>Accessories</v>
@@ -15827,7 +15827,7 @@
         <v/>
       </c>
       <c r="I309" t="str">
-        <v>square-brass-accessories-004-main.jpg</v>
+        <v>square-brass-accessories-007-main.jpg</v>
       </c>
       <c r="J309" t="str">
         <v/>
@@ -15856,13 +15856,13 @@
         <v>Square Brass Accessories</v>
       </c>
       <c r="B310" t="str">
-        <v>square-brass-accessories-005</v>
+        <v>square-brass-accessories-008</v>
       </c>
       <c r="C310" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-005</v>
+        <v>SQUARE-BRASS-ACCESSORIES-008</v>
       </c>
       <c r="D310" t="str">
-        <v>Toilet Roll Holder with Flap</v>
+        <v>Tumbler Holder</v>
       </c>
       <c r="E310" t="str">
         <v>Accessories</v>
@@ -15877,7 +15877,7 @@
         <v/>
       </c>
       <c r="I310" t="str">
-        <v>square-brass-accessories-005-main.jpg</v>
+        <v>square-brass-accessories-008-main.jpg</v>
       </c>
       <c r="J310" t="str">
         <v/>
@@ -15903,16 +15903,16 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B311" t="str">
-        <v>square-brass-accessories-006</v>
+        <v>round-brass-accessories-001</v>
       </c>
       <c r="C311" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-006</v>
+        <v>ROUND-BRASS-ACCESSORIES-001</v>
       </c>
       <c r="D311" t="str">
-        <v>Towel Rack</v>
+        <v>Paper Holder Round</v>
       </c>
       <c r="E311" t="str">
         <v>Accessories</v>
@@ -15927,7 +15927,7 @@
         <v/>
       </c>
       <c r="I311" t="str">
-        <v>square-brass-accessories-006-main.jpg</v>
+        <v>round-brass-accessories-001-main.jpg</v>
       </c>
       <c r="J311" t="str">
         <v/>
@@ -15953,16 +15953,16 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B312" t="str">
-        <v>square-brass-accessories-007</v>
+        <v>round-brass-accessories-002</v>
       </c>
       <c r="C312" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-007</v>
+        <v>ROUND-BRASS-ACCESSORIES-002</v>
       </c>
       <c r="D312" t="str">
-        <v>Tower Ring</v>
+        <v>Round Soap Dish</v>
       </c>
       <c r="E312" t="str">
         <v>Accessories</v>
@@ -15977,7 +15977,7 @@
         <v/>
       </c>
       <c r="I312" t="str">
-        <v>square-brass-accessories-007-main.jpg</v>
+        <v>round-brass-accessories-002-main.jpg</v>
       </c>
       <c r="J312" t="str">
         <v/>
@@ -16003,16 +16003,16 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B313" t="str">
-        <v>square-brass-accessories-008</v>
+        <v>round-brass-accessories-003</v>
       </c>
       <c r="C313" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-008</v>
+        <v>ROUND-BRASS-ACCESSORIES-003</v>
       </c>
       <c r="D313" t="str">
-        <v>Tumbler Holder</v>
+        <v>Round Tumbler</v>
       </c>
       <c r="E313" t="str">
         <v>Accessories</v>
@@ -16027,7 +16027,7 @@
         <v/>
       </c>
       <c r="I313" t="str">
-        <v>square-brass-accessories-008-main.jpg</v>
+        <v>round-brass-accessories-003-main.jpg</v>
       </c>
       <c r="J313" t="str">
         <v/>
@@ -16056,13 +16056,13 @@
         <v>Round Brass Accessories</v>
       </c>
       <c r="B314" t="str">
-        <v>round-brass-accessories-001</v>
+        <v>round-brass-accessories-004</v>
       </c>
       <c r="C314" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-001</v>
+        <v>ROUND-BRASS-ACCESSORIES-004</v>
       </c>
       <c r="D314" t="str">
-        <v>Paper Holder Round</v>
+        <v>Towel Rack Round</v>
       </c>
       <c r="E314" t="str">
         <v>Accessories</v>
@@ -16077,7 +16077,7 @@
         <v/>
       </c>
       <c r="I314" t="str">
-        <v>round-brass-accessories-001-main.jpg</v>
+        <v>round-brass-accessories-004-main.jpg</v>
       </c>
       <c r="J314" t="str">
         <v/>
@@ -16106,13 +16106,13 @@
         <v>Round Brass Accessories</v>
       </c>
       <c r="B315" t="str">
-        <v>round-brass-accessories-002</v>
+        <v>round-brass-accessories-005</v>
       </c>
       <c r="C315" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-002</v>
+        <v>ROUND-BRASS-ACCESSORIES-005</v>
       </c>
       <c r="D315" t="str">
-        <v>Round Soap Dish</v>
+        <v>Towel Rail</v>
       </c>
       <c r="E315" t="str">
         <v>Accessories</v>
@@ -16127,7 +16127,7 @@
         <v/>
       </c>
       <c r="I315" t="str">
-        <v>round-brass-accessories-002-main.jpg</v>
+        <v>round-brass-accessories-005-main.jpg</v>
       </c>
       <c r="J315" t="str">
         <v/>
@@ -16156,13 +16156,13 @@
         <v>Round Brass Accessories</v>
       </c>
       <c r="B316" t="str">
-        <v>round-brass-accessories-003</v>
+        <v>round-brass-accessories-006</v>
       </c>
       <c r="C316" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-003</v>
+        <v>ROUND-BRASS-ACCESSORIES-006</v>
       </c>
       <c r="D316" t="str">
-        <v>Round Tumbler</v>
+        <v>Towel Ring Round</v>
       </c>
       <c r="E316" t="str">
         <v>Accessories</v>
@@ -16177,7 +16177,7 @@
         <v/>
       </c>
       <c r="I316" t="str">
-        <v>round-brass-accessories-003-main.jpg</v>
+        <v>round-brass-accessories-006-main.jpg</v>
       </c>
       <c r="J316" t="str">
         <v/>
@@ -16198,162 +16198,12 @@
         <v/>
       </c>
       <c r="P316" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="str">
-        <v>Round Brass Accessories</v>
-      </c>
-      <c r="B317" t="str">
-        <v>round-brass-accessories-004</v>
-      </c>
-      <c r="C317" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-004</v>
-      </c>
-      <c r="D317" t="str">
-        <v>Towel Rack Round</v>
-      </c>
-      <c r="E317" t="str">
-        <v>Accessories</v>
-      </c>
-      <c r="F317" t="str">
-        <v/>
-      </c>
-      <c r="G317" t="str">
-        <v/>
-      </c>
-      <c r="H317" t="str">
-        <v/>
-      </c>
-      <c r="I317" t="str">
-        <v>round-brass-accessories-004-main.jpg</v>
-      </c>
-      <c r="J317" t="str">
-        <v/>
-      </c>
-      <c r="K317" t="str">
-        <v/>
-      </c>
-      <c r="L317" t="str">
-        <v/>
-      </c>
-      <c r="M317" t="str">
-        <v/>
-      </c>
-      <c r="N317" t="str">
-        <v/>
-      </c>
-      <c r="O317" t="str">
-        <v/>
-      </c>
-      <c r="P317" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="str">
-        <v>Round Brass Accessories</v>
-      </c>
-      <c r="B318" t="str">
-        <v>round-brass-accessories-005</v>
-      </c>
-      <c r="C318" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-005</v>
-      </c>
-      <c r="D318" t="str">
-        <v>Towel Rail</v>
-      </c>
-      <c r="E318" t="str">
-        <v>Accessories</v>
-      </c>
-      <c r="F318" t="str">
-        <v/>
-      </c>
-      <c r="G318" t="str">
-        <v/>
-      </c>
-      <c r="H318" t="str">
-        <v/>
-      </c>
-      <c r="I318" t="str">
-        <v>round-brass-accessories-005-main.jpg</v>
-      </c>
-      <c r="J318" t="str">
-        <v/>
-      </c>
-      <c r="K318" t="str">
-        <v/>
-      </c>
-      <c r="L318" t="str">
-        <v/>
-      </c>
-      <c r="M318" t="str">
-        <v/>
-      </c>
-      <c r="N318" t="str">
-        <v/>
-      </c>
-      <c r="O318" t="str">
-        <v/>
-      </c>
-      <c r="P318" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="str">
-        <v>Round Brass Accessories</v>
-      </c>
-      <c r="B319" t="str">
-        <v>round-brass-accessories-006</v>
-      </c>
-      <c r="C319" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-006</v>
-      </c>
-      <c r="D319" t="str">
-        <v>Towel Ring Round</v>
-      </c>
-      <c r="E319" t="str">
-        <v>Accessories</v>
-      </c>
-      <c r="F319" t="str">
-        <v/>
-      </c>
-      <c r="G319" t="str">
-        <v/>
-      </c>
-      <c r="H319" t="str">
-        <v/>
-      </c>
-      <c r="I319" t="str">
-        <v>round-brass-accessories-006-main.jpg</v>
-      </c>
-      <c r="J319" t="str">
-        <v/>
-      </c>
-      <c r="K319" t="str">
-        <v/>
-      </c>
-      <c r="L319" t="str">
-        <v/>
-      </c>
-      <c r="M319" t="str">
-        <v/>
-      </c>
-      <c r="N319" t="str">
-        <v/>
-      </c>
-      <c r="O319" t="str">
-        <v/>
-      </c>
-      <c r="P319" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P316"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/product catalogue.xlsx
+++ b/product catalogue.xlsx
@@ -15362,13 +15362,13 @@
         <v>ZENITH-COLLECTIONS-001</v>
       </c>
       <c r="D300" t="str">
-        <v>Single Lever Basin Mixer Chrome</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E300" t="str">
         <v>Faucets</v>
       </c>
       <c r="F300" t="str">
-        <v/>
+        <v>Chrome</v>
       </c>
       <c r="G300" t="str">
         <v/>
@@ -15406,19 +15406,19 @@
         <v>Zenith Collections</v>
       </c>
       <c r="B301" t="str">
-        <v>zenith-collections-002</v>
+        <v>zenith-collections-001</v>
       </c>
       <c r="C301" t="str">
         <v>ZENITH-COLLECTIONS-002</v>
       </c>
       <c r="D301" t="str">
-        <v>Single Lever Basin Mixer Matt Beige</v>
+        <v/>
       </c>
       <c r="E301" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F301" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G301" t="str">
         <v/>
@@ -15456,19 +15456,19 @@
         <v>Zenith Collections</v>
       </c>
       <c r="B302" t="str">
-        <v>zenith-collections-003</v>
+        <v>zenith-collections-001</v>
       </c>
       <c r="C302" t="str">
         <v>ZENITH-COLLECTIONS-003</v>
       </c>
       <c r="D302" t="str">
-        <v>Single Lever Basin Mixer Matt Black</v>
+        <v/>
       </c>
       <c r="E302" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F302" t="str">
-        <v/>
+        <v>Matt Black</v>
       </c>
       <c r="G302" t="str">
         <v/>

--- a/product catalogue.xlsx
+++ b/product catalogue.xlsx
@@ -3762,13 +3762,13 @@
         <v>OPELL-PRIMA-006</v>
       </c>
       <c r="D68" t="str">
-        <v>Basin Mixer Upper Part</v>
+        <v>Basin Mixer Wall Mounted Upper Parts</v>
       </c>
       <c r="E68" t="str">
         <v>Faucets</v>
       </c>
       <c r="F68" t="str">
-        <v/>
+        <v>Matt Black Gold</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3806,19 +3806,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B69" t="str">
-        <v>opell-prima-007</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C69" t="str">
         <v>OPELL-PRIMA-007</v>
       </c>
       <c r="D69" t="str">
-        <v>Basin Mixer Upper Parts</v>
+        <v/>
       </c>
       <c r="E69" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F69" t="str">
-        <v/>
+        <v>Matt White Gold</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3856,19 +3856,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B70" t="str">
-        <v>opell-prima-008</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C70" t="str">
         <v>OPELL-PRIMA-008</v>
       </c>
       <c r="D70" t="str">
-        <v>Basin Mixer Wall Mounted</v>
+        <v/>
       </c>
       <c r="E70" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F70" t="str">
-        <v/>
+        <v>Matt Beige Gold</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3906,19 +3906,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B71" t="str">
-        <v>opell-prima-009</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C71" t="str">
         <v>OPELL-PRIMA-009</v>
       </c>
       <c r="D71" t="str">
-        <v>Basin Mixer Wall Mounted Upper Parts</v>
+        <v/>
       </c>
       <c r="E71" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F71" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G71" t="str">
         <v/>

--- a/product catalogue.xlsx
+++ b/product catalogue.xlsx
@@ -3759,7 +3759,7 @@
         <v>opell-prima-006</v>
       </c>
       <c r="C68" t="str">
-        <v>OPELL-PRIMA-006</v>
+        <v>OPELL-PRIMA-058</v>
       </c>
       <c r="D68" t="str">
         <v>Basin Mixer Wall Mounted Upper Parts</v>
@@ -3768,7 +3768,7 @@
         <v>Faucets</v>
       </c>
       <c r="F68" t="str">
-        <v>Matt Black Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3777,7 +3777,7 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>opell-prima-006-main.png</v>
+        <v>opell-prima-058-main.jpg</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3809,7 +3809,7 @@
         <v>opell-prima-006</v>
       </c>
       <c r="C69" t="str">
-        <v>OPELL-PRIMA-007</v>
+        <v>OPELL-PRIMA-006</v>
       </c>
       <c r="D69" t="str">
         <v/>
@@ -3818,7 +3818,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Matt White Gold</v>
+        <v>Matt Black Gold</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>opell-prima-007-main.png</v>
+        <v>opell-prima-006-main.png</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>opell-prima-006</v>
       </c>
       <c r="C70" t="str">
-        <v>OPELL-PRIMA-008</v>
+        <v>OPELL-PRIMA-007</v>
       </c>
       <c r="D70" t="str">
         <v/>
@@ -3868,7 +3868,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Matt Beige Gold</v>
+        <v>Matt White Gold</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>opell-prima-008-main.png</v>
+        <v>opell-prima-007-main.png</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3909,7 +3909,7 @@
         <v>opell-prima-006</v>
       </c>
       <c r="C71" t="str">
-        <v>OPELL-PRIMA-009</v>
+        <v>OPELL-PRIMA-008</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -3918,7 +3918,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Matt White</v>
+        <v>Matt Beige Gold</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3927,7 +3927,7 @@
         <v/>
       </c>
       <c r="I71" t="str">
-        <v>opell-prima-009-main.png</v>
+        <v>opell-prima-008-main.png</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -3956,19 +3956,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B72" t="str">
-        <v>opell-prima-010</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C72" t="str">
-        <v>OPELL-PRIMA-010</v>
+        <v>OPELL-PRIMA-009</v>
       </c>
       <c r="D72" t="str">
-        <v>Bath TUB Spout</v>
+        <v/>
       </c>
       <c r="E72" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>opell-prima-010-main.jpg</v>
+        <v>opell-prima-009-main.png</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -4006,16 +4006,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B73" t="str">
-        <v>opell-prima-015</v>
+        <v>opell-prima-010</v>
       </c>
       <c r="C73" t="str">
-        <v>OPELL-PRIMA-015</v>
+        <v>OPELL-PRIMA-010</v>
       </c>
       <c r="D73" t="str">
-        <v>Bottle Trap</v>
+        <v>Bath TUB Spout</v>
       </c>
       <c r="E73" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F73" t="str">
         <v/>
@@ -4027,7 +4027,7 @@
         <v/>
       </c>
       <c r="I73" t="str">
-        <v>opell-prima-015-main.png</v>
+        <v>opell-prima-010-main.jpg</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -4059,16 +4059,16 @@
         <v>opell-prima-015</v>
       </c>
       <c r="C74" t="str">
-        <v>OPELL-PRIMA-011</v>
+        <v>OPELL-PRIMA-015</v>
       </c>
       <c r="D74" t="str">
-        <v/>
+        <v>Bottle Trap</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>Accessories</v>
       </c>
       <c r="F74" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4077,7 +4077,7 @@
         <v/>
       </c>
       <c r="I74" t="str">
-        <v>opell-prima-011-main.png</v>
+        <v>opell-prima-015-main.png</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -4109,7 +4109,7 @@
         <v>opell-prima-015</v>
       </c>
       <c r="C75" t="str">
-        <v>OPELL-PRIMA-014</v>
+        <v>OPELL-PRIMA-011</v>
       </c>
       <c r="D75" t="str">
         <v/>
@@ -4118,7 +4118,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Matt Black</v>
+        <v>Matt Beige</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4127,7 +4127,7 @@
         <v/>
       </c>
       <c r="I75" t="str">
-        <v>opell-prima-014-main.png</v>
+        <v>opell-prima-011-main.png</v>
       </c>
       <c r="J75" t="str">
         <v/>
@@ -4159,7 +4159,7 @@
         <v>opell-prima-015</v>
       </c>
       <c r="C76" t="str">
-        <v>OPELL-PRIMA-016</v>
+        <v>OPELL-PRIMA-014</v>
       </c>
       <c r="D76" t="str">
         <v/>
@@ -4168,7 +4168,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Matt White</v>
+        <v>Matt Black</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I76" t="str">
-        <v>opell-prima-016-main.png</v>
+        <v>opell-prima-014-main.png</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -4206,19 +4206,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B77" t="str">
-        <v>opell-prima-012</v>
+        <v>opell-prima-015</v>
       </c>
       <c r="C77" t="str">
-        <v>OPELL-PRIMA-012</v>
+        <v>OPELL-PRIMA-016</v>
       </c>
       <c r="D77" t="str">
-        <v>Beige Gold Alive</v>
+        <v/>
       </c>
       <c r="E77" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F77" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4227,7 +4227,7 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>opell-prima-012-main.png</v>
+        <v>opell-prima-016-main.png</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4256,16 +4256,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B78" t="str">
-        <v>opell-prima-013</v>
+        <v>opell-prima-012</v>
       </c>
       <c r="C78" t="str">
-        <v>OPELL-PRIMA-013</v>
+        <v>OPELL-PRIMA-012</v>
       </c>
       <c r="D78" t="str">
-        <v>Beige Gold Shower</v>
+        <v>Beige Gold Alive</v>
       </c>
       <c r="E78" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F78" t="str">
         <v/>
@@ -4277,7 +4277,7 @@
         <v/>
       </c>
       <c r="I78" t="str">
-        <v>opell-prima-013-main.png</v>
+        <v>opell-prima-012-main.png</v>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -4306,16 +4306,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B79" t="str">
-        <v>opell-prima-017</v>
+        <v>opell-prima-013</v>
       </c>
       <c r="C79" t="str">
-        <v>OPELL-PRIMA-017</v>
+        <v>OPELL-PRIMA-013</v>
       </c>
       <c r="D79" t="str">
-        <v>Button Spout</v>
+        <v>Beige Gold Shower</v>
       </c>
       <c r="E79" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F79" t="str">
         <v/>
@@ -4327,7 +4327,7 @@
         <v/>
       </c>
       <c r="I79" t="str">
-        <v>opell-prima-017-main.jpg</v>
+        <v>opell-prima-013-main.png</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -4356,16 +4356,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B80" t="str">
-        <v>opell-prima-018</v>
+        <v>opell-prima-017</v>
       </c>
       <c r="C80" t="str">
-        <v>OPELL-PRIMA-018</v>
+        <v>OPELL-PRIMA-017</v>
       </c>
       <c r="D80" t="str">
-        <v>Center Hole</v>
+        <v>Button Spout</v>
       </c>
       <c r="E80" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F80" t="str">
         <v/>
@@ -4377,7 +4377,7 @@
         <v/>
       </c>
       <c r="I80" t="str">
-        <v>opell-prima-018-main.jpg</v>
+        <v>opell-prima-017-main.jpg</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -4406,16 +4406,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B81" t="str">
-        <v>opell-prima-019</v>
+        <v>opell-prima-018</v>
       </c>
       <c r="C81" t="str">
-        <v>OPELL-PRIMA-019</v>
+        <v>OPELL-PRIMA-018</v>
       </c>
       <c r="D81" t="str">
-        <v>Concealed Stop Cock</v>
+        <v>Center Hole</v>
       </c>
       <c r="E81" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -4427,7 +4427,7 @@
         <v/>
       </c>
       <c r="I81" t="str">
-        <v>opell-prima-019-main.jpg</v>
+        <v>opell-prima-018-main.jpg</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -4456,13 +4456,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B82" t="str">
-        <v>opell-prima-020</v>
+        <v>opell-prima-019</v>
       </c>
       <c r="C82" t="str">
-        <v>OPELL-PRIMA-020</v>
+        <v>OPELL-PRIMA-019</v>
       </c>
       <c r="D82" t="str">
-        <v>Diverter Body</v>
+        <v>Concealed Stop Cock</v>
       </c>
       <c r="E82" t="str">
         <v>Faucets</v>
@@ -4477,7 +4477,7 @@
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>opell-prima-020-main.png</v>
+        <v>opell-prima-019-main.jpg</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -4509,16 +4509,16 @@
         <v>opell-prima-020</v>
       </c>
       <c r="C83" t="str">
-        <v>OPELL-PRIMA-022</v>
+        <v>OPELL-PRIMA-020</v>
       </c>
       <c r="D83" t="str">
-        <v/>
+        <v>Diverter Body</v>
       </c>
       <c r="E83" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F83" t="str">
-        <v>Rich Gold</v>
+        <v/>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>opell-prima-022-main.png</v>
+        <v>opell-prima-020-main.png</v>
       </c>
       <c r="J83" t="str">
         <v/>
@@ -4559,7 +4559,7 @@
         <v>opell-prima-020</v>
       </c>
       <c r="C84" t="str">
-        <v>OPELL-PRIMA-023</v>
+        <v>OPELL-PRIMA-022</v>
       </c>
       <c r="D84" t="str">
         <v/>
@@ -4568,7 +4568,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Matt Beige</v>
+        <v>Rich Gold</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -4577,7 +4577,7 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>opell-prima-023-main.png</v>
+        <v>opell-prima-022-main.png</v>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -4606,19 +4606,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B85" t="str">
-        <v>opell-prima-021</v>
+        <v>opell-prima-020</v>
       </c>
       <c r="C85" t="str">
-        <v>OPELL-PRIMA-021</v>
+        <v>OPELL-PRIMA-023</v>
       </c>
       <c r="D85" t="str">
-        <v>Diverter Body for ALL Colour and Gold Combination</v>
+        <v/>
       </c>
       <c r="E85" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -4627,7 +4627,7 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>opell-prima-021-main.png</v>
+        <v>opell-prima-023-main.png</v>
       </c>
       <c r="J85" t="str">
         <v/>
@@ -4656,13 +4656,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B86" t="str">
-        <v>opell-prima-024</v>
+        <v>opell-prima-021</v>
       </c>
       <c r="C86" t="str">
-        <v>OPELL-PRIMA-024</v>
+        <v>OPELL-PRIMA-021</v>
       </c>
       <c r="D86" t="str">
-        <v>Diverter Upper Part</v>
+        <v>Diverter Body for ALL Colour and Gold Combination</v>
       </c>
       <c r="E86" t="str">
         <v>Faucets</v>
@@ -4677,7 +4677,7 @@
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>opell-prima-024-main.png</v>
+        <v>opell-prima-021-main.png</v>
       </c>
       <c r="J86" t="str">
         <v/>
@@ -4706,13 +4706,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B87" t="str">
-        <v>opell-prima-025</v>
+        <v>opell-prima-024</v>
       </c>
       <c r="C87" t="str">
-        <v>OPELL-PRIMA-025</v>
+        <v>OPELL-PRIMA-024</v>
       </c>
       <c r="D87" t="str">
-        <v>Diverter Upper Parts</v>
+        <v>Diverter Upper Part</v>
       </c>
       <c r="E87" t="str">
         <v>Faucets</v>
@@ -4727,7 +4727,7 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>opell-prima-025-main.png</v>
+        <v>opell-prima-024-main.png</v>
       </c>
       <c r="J87" t="str">
         <v/>
@@ -4756,13 +4756,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B88" t="str">
-        <v>opell-prima-026</v>
+        <v>opell-prima-025</v>
       </c>
       <c r="C88" t="str">
-        <v>OPELL-PRIMA-026</v>
+        <v>OPELL-PRIMA-025</v>
       </c>
       <c r="D88" t="str">
-        <v>Exposed Parts for Single Lever High Flow Diverter Body</v>
+        <v>Diverter Upper Parts</v>
       </c>
       <c r="E88" t="str">
         <v>Faucets</v>
@@ -4777,7 +4777,7 @@
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>opell-prima-026-main.jpg</v>
+        <v>opell-prima-025-main.png</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -4806,16 +4806,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B89" t="str">
-        <v>opell-prima-027</v>
+        <v>opell-prima-026</v>
       </c>
       <c r="C89" t="str">
-        <v>OPELL-PRIMA-027</v>
+        <v>OPELL-PRIMA-026</v>
       </c>
       <c r="D89" t="str">
-        <v>Gold</v>
+        <v>Exposed Parts for Single Lever High Flow Diverter Body</v>
       </c>
       <c r="E89" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F89" t="str">
         <v/>
@@ -4827,7 +4827,7 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>opell-prima-027-main.png</v>
+        <v>opell-prima-026-main.jpg</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4856,16 +4856,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B90" t="str">
-        <v>opell-prima-029</v>
+        <v>opell-prima-027</v>
       </c>
       <c r="C90" t="str">
-        <v>OPELL-PRIMA-029</v>
+        <v>OPELL-PRIMA-027</v>
       </c>
       <c r="D90" t="str">
-        <v>Hand Shower</v>
+        <v>Gold</v>
       </c>
       <c r="E90" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F90" t="str">
         <v/>
@@ -4877,7 +4877,7 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>opell-prima-029-main.png</v>
+        <v>opell-prima-027-main.png</v>
       </c>
       <c r="J90" t="str">
         <v/>
@@ -4909,16 +4909,16 @@
         <v>opell-prima-029</v>
       </c>
       <c r="C91" t="str">
-        <v>OPELL-PRIMA-028</v>
+        <v>OPELL-PRIMA-029</v>
       </c>
       <c r="D91" t="str">
-        <v/>
+        <v>Hand Shower</v>
       </c>
       <c r="E91" t="str">
-        <v/>
+        <v>Showers</v>
       </c>
       <c r="F91" t="str">
-        <v>Rose Gold</v>
+        <v/>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -4927,7 +4927,7 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>opell-prima-028-main.png</v>
+        <v>opell-prima-029-main.png</v>
       </c>
       <c r="J91" t="str">
         <v/>
@@ -4959,7 +4959,7 @@
         <v>opell-prima-029</v>
       </c>
       <c r="C92" t="str">
-        <v>OPELL-PRIMA-030</v>
+        <v>OPELL-PRIMA-028</v>
       </c>
       <c r="D92" t="str">
         <v/>
@@ -4968,7 +4968,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Rich Gold</v>
+        <v>Rose Gold</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -4977,7 +4977,7 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v>opell-prima-030-main.png</v>
+        <v>opell-prima-028-main.png</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -5006,19 +5006,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B93" t="str">
-        <v>opell-prima-031</v>
+        <v>opell-prima-029</v>
       </c>
       <c r="C93" t="str">
-        <v>OPELL-PRIMA-031</v>
+        <v>OPELL-PRIMA-030</v>
       </c>
       <c r="D93" t="str">
-        <v>Health Faucet</v>
+        <v/>
       </c>
       <c r="E93" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F93" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5027,7 +5027,7 @@
         <v/>
       </c>
       <c r="I93" t="str">
-        <v>opell-prima-031-main.png</v>
+        <v>opell-prima-030-main.png</v>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -5056,16 +5056,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B94" t="str">
-        <v>opell-prima-032</v>
+        <v>opell-prima-031</v>
       </c>
       <c r="C94" t="str">
-        <v>OPELL-PRIMA-032</v>
+        <v>OPELL-PRIMA-031</v>
       </c>
       <c r="D94" t="str">
-        <v>Long Body</v>
+        <v>Health Faucet</v>
       </c>
       <c r="E94" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F94" t="str">
         <v/>
@@ -5077,7 +5077,7 @@
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>opell-prima-032-main.jpg</v>
+        <v>opell-prima-031-main.png</v>
       </c>
       <c r="J94" t="str">
         <v/>
@@ -5106,16 +5106,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B95" t="str">
-        <v>opell-prima-033</v>
+        <v>opell-prima-032</v>
       </c>
       <c r="C95" t="str">
-        <v>OPELL-PRIMA-033</v>
+        <v>OPELL-PRIMA-032</v>
       </c>
       <c r="D95" t="str">
-        <v>Matte Beige Alive</v>
+        <v>Long Body</v>
       </c>
       <c r="E95" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F95" t="str">
         <v/>
@@ -5127,7 +5127,7 @@
         <v/>
       </c>
       <c r="I95" t="str">
-        <v>opell-prima-033-main.png</v>
+        <v>opell-prima-032-main.jpg</v>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -5156,16 +5156,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B96" t="str">
-        <v>opell-prima-034</v>
+        <v>opell-prima-033</v>
       </c>
       <c r="C96" t="str">
-        <v>OPELL-PRIMA-034</v>
+        <v>OPELL-PRIMA-033</v>
       </c>
       <c r="D96" t="str">
-        <v>Matte White Shower Head</v>
+        <v>Matte Beige Alive</v>
       </c>
       <c r="E96" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F96" t="str">
         <v/>
@@ -5177,7 +5177,7 @@
         <v/>
       </c>
       <c r="I96" t="str">
-        <v>opell-prima-034-main.png</v>
+        <v>opell-prima-033-main.png</v>
       </c>
       <c r="J96" t="str">
         <v/>
@@ -5206,16 +5206,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B97" t="str">
-        <v>opell-prima-035</v>
+        <v>opell-prima-034</v>
       </c>
       <c r="C97" t="str">
-        <v>OPELL-PRIMA-035</v>
+        <v>OPELL-PRIMA-034</v>
       </c>
       <c r="D97" t="str">
-        <v>NON Telephonic</v>
+        <v>Matte White Shower Head</v>
       </c>
       <c r="E97" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F97" t="str">
         <v/>
@@ -5227,7 +5227,7 @@
         <v/>
       </c>
       <c r="I97" t="str">
-        <v>opell-prima-035-main.jpg</v>
+        <v>opell-prima-034-main.png</v>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -5256,16 +5256,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B98" t="str">
-        <v>opell-prima-036</v>
+        <v>opell-prima-035</v>
       </c>
       <c r="C98" t="str">
-        <v>OPELL-PRIMA-036</v>
+        <v>OPELL-PRIMA-035</v>
       </c>
       <c r="D98" t="str">
-        <v>Nozzle BIB Cock</v>
+        <v>NON Telephonic</v>
       </c>
       <c r="E98" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F98" t="str">
         <v/>
@@ -5277,7 +5277,7 @@
         <v/>
       </c>
       <c r="I98" t="str">
-        <v>opell-prima-036-main.jpg</v>
+        <v>opell-prima-035-main.jpg</v>
       </c>
       <c r="J98" t="str">
         <v/>
@@ -5306,13 +5306,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B99" t="str">
-        <v>opell-prima-037</v>
+        <v>opell-prima-036</v>
       </c>
       <c r="C99" t="str">
-        <v>OPELL-PRIMA-037</v>
+        <v>OPELL-PRIMA-036</v>
       </c>
       <c r="D99" t="str">
-        <v>Pillar Cock</v>
+        <v>Nozzle BIB Cock</v>
       </c>
       <c r="E99" t="str">
         <v>Faucets</v>
@@ -5327,7 +5327,7 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v>opell-prima-037-main.jpg</v>
+        <v>opell-prima-036-main.jpg</v>
       </c>
       <c r="J99" t="str">
         <v/>
@@ -5356,13 +5356,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B100" t="str">
-        <v>opell-prima-038</v>
+        <v>opell-prima-037</v>
       </c>
       <c r="C100" t="str">
-        <v>OPELL-PRIMA-038</v>
+        <v>OPELL-PRIMA-037</v>
       </c>
       <c r="D100" t="str">
-        <v>Pillar Cock Extend</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E100" t="str">
         <v>Faucets</v>
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="I100" t="str">
-        <v>opell-prima-038-main.png</v>
+        <v>opell-prima-037-main.jpg</v>
       </c>
       <c r="J100" t="str">
         <v/>
@@ -5406,13 +5406,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B101" t="str">
-        <v>opell-prima-039</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C101" t="str">
-        <v>OPELL-PRIMA-039</v>
+        <v>OPELL-PRIMA-038</v>
       </c>
       <c r="D101" t="str">
-        <v>Pillar Cock Extended</v>
+        <v>Pillar Cock Extend</v>
       </c>
       <c r="E101" t="str">
         <v>Faucets</v>
@@ -5427,7 +5427,7 @@
         <v/>
       </c>
       <c r="I101" t="str">
-        <v>opell-prima-039-main.png</v>
+        <v>opell-prima-038-main.png</v>
       </c>
       <c r="J101" t="str">
         <v/>
@@ -5456,13 +5456,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B102" t="str">
-        <v>opell-prima-040</v>
+        <v>opell-prima-039</v>
       </c>
       <c r="C102" t="str">
-        <v>OPELL-PRIMA-040</v>
+        <v>OPELL-PRIMA-039</v>
       </c>
       <c r="D102" t="str">
-        <v>Pillar Cock Extended Body</v>
+        <v>Pillar Cock Extended</v>
       </c>
       <c r="E102" t="str">
         <v>Faucets</v>
@@ -5477,7 +5477,7 @@
         <v/>
       </c>
       <c r="I102" t="str">
-        <v>opell-prima-040-main.jpg</v>
+        <v>opell-prima-039-main.png</v>
       </c>
       <c r="J102" t="str">
         <v/>
@@ -5506,13 +5506,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B103" t="str">
-        <v>opell-prima-041</v>
+        <v>opell-prima-040</v>
       </c>
       <c r="C103" t="str">
-        <v>OPELL-PRIMA-041</v>
+        <v>OPELL-PRIMA-040</v>
       </c>
       <c r="D103" t="str">
-        <v>Plain Spout</v>
+        <v>Pillar Cock Extended Body</v>
       </c>
       <c r="E103" t="str">
         <v>Faucets</v>
@@ -5527,7 +5527,7 @@
         <v/>
       </c>
       <c r="I103" t="str">
-        <v>opell-prima-041-main.png</v>
+        <v>opell-prima-040-main.jpg</v>
       </c>
       <c r="J103" t="str">
         <v/>
@@ -5556,16 +5556,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B104" t="str">
-        <v>opell-prima-042</v>
+        <v>opell-prima-041</v>
       </c>
       <c r="C104" t="str">
-        <v>OPELL-PRIMA-042</v>
+        <v>OPELL-PRIMA-041</v>
       </c>
       <c r="D104" t="str">
-        <v>Shower ARM</v>
+        <v>Plain Spout</v>
       </c>
       <c r="E104" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F104" t="str">
         <v/>
@@ -5577,7 +5577,7 @@
         <v/>
       </c>
       <c r="I104" t="str">
-        <v>opell-prima-042-main.png</v>
+        <v>opell-prima-041-main.png</v>
       </c>
       <c r="J104" t="str">
         <v/>
@@ -5609,16 +5609,16 @@
         <v>opell-prima-042</v>
       </c>
       <c r="C105" t="str">
-        <v>OPELL-PRIMA-043</v>
+        <v>OPELL-PRIMA-042</v>
       </c>
       <c r="D105" t="str">
-        <v/>
+        <v>Shower ARM</v>
       </c>
       <c r="E105" t="str">
-        <v/>
+        <v>Showers</v>
       </c>
       <c r="F105" t="str">
-        <v>Matt Black Gold</v>
+        <v/>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -5627,7 +5627,7 @@
         <v/>
       </c>
       <c r="I105" t="str">
-        <v>opell-prima-043-main.png</v>
+        <v>opell-prima-042-main.png</v>
       </c>
       <c r="J105" t="str">
         <v/>
@@ -5656,19 +5656,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B106" t="str">
-        <v>opell-prima-044</v>
+        <v>opell-prima-042</v>
       </c>
       <c r="C106" t="str">
-        <v>OPELL-PRIMA-044</v>
+        <v>OPELL-PRIMA-043</v>
       </c>
       <c r="D106" t="str">
-        <v>Shower Head</v>
+        <v/>
       </c>
       <c r="E106" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F106" t="str">
-        <v/>
+        <v>Matt Black Gold</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="I106" t="str">
-        <v>opell-prima-044-main.png</v>
+        <v>opell-prima-043-main.png</v>
       </c>
       <c r="J106" t="str">
         <v/>
@@ -5709,16 +5709,16 @@
         <v>opell-prima-044</v>
       </c>
       <c r="C107" t="str">
-        <v>OPELL-PRIMA-045</v>
+        <v>OPELL-PRIMA-044</v>
       </c>
       <c r="D107" t="str">
-        <v/>
+        <v>Shower Head</v>
       </c>
       <c r="E107" t="str">
-        <v/>
+        <v>Showers</v>
       </c>
       <c r="F107" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v/>
       </c>
       <c r="I107" t="str">
-        <v>opell-prima-045-main.png</v>
+        <v>opell-prima-044-main.png</v>
       </c>
       <c r="J107" t="str">
         <v/>
@@ -5756,19 +5756,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B108" t="str">
-        <v>opell-prima-046</v>
+        <v>opell-prima-044</v>
       </c>
       <c r="C108" t="str">
-        <v>OPELL-PRIMA-046</v>
+        <v>OPELL-PRIMA-045</v>
       </c>
       <c r="D108" t="str">
-        <v>Shower Mixer for Spout Only</v>
+        <v/>
       </c>
       <c r="E108" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F108" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -5777,7 +5777,7 @@
         <v/>
       </c>
       <c r="I108" t="str">
-        <v>opell-prima-046-main.jpg</v>
+        <v>opell-prima-045-main.png</v>
       </c>
       <c r="J108" t="str">
         <v/>
@@ -5806,16 +5806,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B109" t="str">
-        <v>opell-prima-047</v>
+        <v>opell-prima-046</v>
       </c>
       <c r="C109" t="str">
-        <v>OPELL-PRIMA-047</v>
+        <v>OPELL-PRIMA-046</v>
       </c>
       <c r="D109" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Shower Mixer for Spout Only</v>
       </c>
       <c r="E109" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F109" t="str">
         <v/>
@@ -5827,10 +5827,10 @@
         <v/>
       </c>
       <c r="I109" t="str">
-        <v>opell-prima-047-main.jpg</v>
+        <v>opell-prima-046-main.jpg</v>
       </c>
       <c r="J109" t="str">
-        <v>opell-prima-047-main.jpg,opell-prima-059-main.png</v>
+        <v/>
       </c>
       <c r="K109" t="str">
         <v/>
@@ -5856,13 +5856,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B110" t="str">
-        <v>opell-prima-048</v>
+        <v>opell-prima-047</v>
       </c>
       <c r="C110" t="str">
-        <v>OPELL-PRIMA-048</v>
+        <v>OPELL-PRIMA-047</v>
       </c>
       <c r="D110" t="str">
-        <v>Single Lever Basin Mixer Extended Body</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E110" t="str">
         <v>Faucets</v>
@@ -5877,10 +5877,10 @@
         <v/>
       </c>
       <c r="I110" t="str">
-        <v>opell-prima-048-main.jpg</v>
+        <v>opell-prima-047-main.jpg</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>opell-prima-047-main.jpg,opell-prima-059-main.png</v>
       </c>
       <c r="K110" t="str">
         <v/>
@@ -5906,13 +5906,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B111" t="str">
-        <v>opell-prima-049</v>
+        <v>opell-prima-048</v>
       </c>
       <c r="C111" t="str">
-        <v>OPELL-PRIMA-049</v>
+        <v>OPELL-PRIMA-048</v>
       </c>
       <c r="D111" t="str">
-        <v>Single Lever Basin Mixer Tall</v>
+        <v>Single Lever Basin Mixer Extended Body</v>
       </c>
       <c r="E111" t="str">
         <v>Faucets</v>
@@ -5927,10 +5927,10 @@
         <v/>
       </c>
       <c r="I111" t="str">
-        <v>opell-prima-049-main.png</v>
+        <v>opell-prima-048-main.jpg</v>
       </c>
       <c r="J111" t="str">
-        <v>opell-prima-049-main.png,opell-prima-060-main.png</v>
+        <v/>
       </c>
       <c r="K111" t="str">
         <v/>
@@ -5956,16 +5956,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B112" t="str">
-        <v>opell-prima-050</v>
+        <v>opell-prima-049</v>
       </c>
       <c r="C112" t="str">
-        <v>OPELL-PRIMA-050</v>
+        <v>OPELL-PRIMA-049</v>
       </c>
       <c r="D112" t="str">
-        <v>Single Lever Basin Tall</v>
+        <v>Single Lever Basin Mixer Tall</v>
       </c>
       <c r="E112" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -5977,10 +5977,10 @@
         <v/>
       </c>
       <c r="I112" t="str">
-        <v>opell-prima-050-main.png</v>
+        <v>opell-prima-049-main.png</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>opell-prima-049-main.png,opell-prima-060-main.png</v>
       </c>
       <c r="K112" t="str">
         <v/>
@@ -6006,16 +6006,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B113" t="str">
-        <v>opell-prima-051</v>
+        <v>opell-prima-050</v>
       </c>
       <c r="C113" t="str">
-        <v>OPELL-PRIMA-051</v>
+        <v>OPELL-PRIMA-050</v>
       </c>
       <c r="D113" t="str">
-        <v>Single Lever Exposed Shower Mixer</v>
+        <v>Single Lever Basin Tall</v>
       </c>
       <c r="E113" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="I113" t="str">
-        <v>opell-prima-051-main.jpg</v>
+        <v>opell-prima-050-main.png</v>
       </c>
       <c r="J113" t="str">
         <v/>
@@ -6056,16 +6056,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B114" t="str">
-        <v>opell-prima-052</v>
+        <v>opell-prima-051</v>
       </c>
       <c r="C114" t="str">
-        <v>OPELL-PRIMA-052</v>
+        <v>OPELL-PRIMA-051</v>
       </c>
       <c r="D114" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Angular Spout</v>
+        <v>Single Lever Exposed Shower Mixer</v>
       </c>
       <c r="E114" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -6077,7 +6077,7 @@
         <v/>
       </c>
       <c r="I114" t="str">
-        <v>opell-prima-052-main.jpg</v>
+        <v>opell-prima-051-main.jpg</v>
       </c>
       <c r="J114" t="str">
         <v/>
@@ -6106,13 +6106,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B115" t="str">
-        <v>opell-prima-053</v>
+        <v>opell-prima-052</v>
       </c>
       <c r="C115" t="str">
-        <v>OPELL-PRIMA-053</v>
+        <v>OPELL-PRIMA-052</v>
       </c>
       <c r="D115" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Round Spout Side Handle</v>
+        <v>Single Lever Sink Mixer Table Mounted Angular Spout</v>
       </c>
       <c r="E115" t="str">
         <v>Faucets</v>
@@ -6127,7 +6127,7 @@
         <v/>
       </c>
       <c r="I115" t="str">
-        <v>opell-prima-053-main.jpg</v>
+        <v>opell-prima-052-main.jpg</v>
       </c>
       <c r="J115" t="str">
         <v/>
@@ -6156,13 +6156,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B116" t="str">
-        <v>opell-prima-054</v>
+        <v>opell-prima-053</v>
       </c>
       <c r="C116" t="str">
-        <v>OPELL-PRIMA-054</v>
+        <v>OPELL-PRIMA-053</v>
       </c>
       <c r="D116" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Tall</v>
+        <v>Single Lever Sink Mixer Table Mounted Round Spout Side Handle</v>
       </c>
       <c r="E116" t="str">
         <v>Faucets</v>
@@ -6177,7 +6177,7 @@
         <v/>
       </c>
       <c r="I116" t="str">
-        <v>opell-prima-054-main.jpg</v>
+        <v>opell-prima-053-main.jpg</v>
       </c>
       <c r="J116" t="str">
         <v/>
@@ -6206,13 +6206,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B117" t="str">
-        <v>opell-prima-055</v>
+        <v>opell-prima-054</v>
       </c>
       <c r="C117" t="str">
-        <v>OPELL-PRIMA-055</v>
+        <v>OPELL-PRIMA-054</v>
       </c>
       <c r="D117" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
+        <v>Single Lever Sink Mixer Table Mounted Tall</v>
       </c>
       <c r="E117" t="str">
         <v>Faucets</v>
@@ -6227,7 +6227,7 @@
         <v/>
       </c>
       <c r="I117" t="str">
-        <v>opell-prima-055-main.jpg</v>
+        <v>opell-prima-054-main.jpg</v>
       </c>
       <c r="J117" t="str">
         <v/>
@@ -6256,13 +6256,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B118" t="str">
-        <v>opell-prima-056</v>
+        <v>opell-prima-055</v>
       </c>
       <c r="C118" t="str">
-        <v>OPELL-PRIMA-056</v>
+        <v>OPELL-PRIMA-055</v>
       </c>
       <c r="D118" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Round Spout</v>
+        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
       </c>
       <c r="E118" t="str">
         <v>Faucets</v>
@@ -6277,7 +6277,7 @@
         <v/>
       </c>
       <c r="I118" t="str">
-        <v>opell-prima-056-main.jpg</v>
+        <v>opell-prima-055-main.jpg</v>
       </c>
       <c r="J118" t="str">
         <v/>
@@ -6306,13 +6306,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B119" t="str">
-        <v>opell-prima-057</v>
+        <v>opell-prima-056</v>
       </c>
       <c r="C119" t="str">
-        <v>OPELL-PRIMA-057</v>
+        <v>OPELL-PRIMA-056</v>
       </c>
       <c r="D119" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Single Lever Sink Mixer Wall Mounted Round Spout</v>
       </c>
       <c r="E119" t="str">
         <v>Faucets</v>
@@ -6327,7 +6327,7 @@
         <v/>
       </c>
       <c r="I119" t="str">
-        <v>opell-prima-057-main.jpg</v>
+        <v>opell-prima-056-main.jpg</v>
       </c>
       <c r="J119" t="str">
         <v/>
@@ -6356,13 +6356,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B120" t="str">
-        <v>opell-prima-058</v>
+        <v>opell-prima-057</v>
       </c>
       <c r="C120" t="str">
-        <v>OPELL-PRIMA-058</v>
+        <v>OPELL-PRIMA-057</v>
       </c>
       <c r="D120" t="str">
-        <v>Single Lever Wall Mounted Basin Mixer</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E120" t="str">
         <v>Faucets</v>
@@ -6377,7 +6377,7 @@
         <v/>
       </c>
       <c r="I120" t="str">
-        <v>opell-prima-058-main.jpg</v>
+        <v>opell-prima-057-main.jpg</v>
       </c>
       <c r="J120" t="str">
         <v/>

--- a/product catalogue.xlsx
+++ b/product catalogue.xlsx
@@ -3668,7 +3668,7 @@
         <v>Showers</v>
       </c>
       <c r="F66" t="str">
-        <v/>
+        <v>Chrome</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -3706,19 +3706,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B67" t="str">
-        <v>opell-prima-005</v>
+        <v>opell-prima-003</v>
       </c>
       <c r="C67" t="str">
-        <v>OPELL-PRIMA-005</v>
+        <v>OPELL-PRIMA-012</v>
       </c>
       <c r="D67" t="str">
-        <v>Angle Valve</v>
+        <v/>
       </c>
       <c r="E67" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F67" t="str">
-        <v/>
+        <v>Profile Beige Gold</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -3727,7 +3727,7 @@
         <v/>
       </c>
       <c r="I67" t="str">
-        <v>opell-prima-005-main.jpg</v>
+        <v>opell-prima-012-main.png</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -3756,19 +3756,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B68" t="str">
-        <v>opell-prima-006</v>
+        <v>opell-prima-003</v>
       </c>
       <c r="C68" t="str">
-        <v>OPELL-PRIMA-058</v>
+        <v>OPELL-PRIMA-033</v>
       </c>
       <c r="D68" t="str">
-        <v>Basin Mixer Wall Mounted Upper Parts</v>
+        <v/>
       </c>
       <c r="E68" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F68" t="str">
-        <v>Chrome</v>
+        <v>Matt Beige</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3777,7 +3777,7 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>opell-prima-058-main.jpg</v>
+        <v>opell-prima-033-main.png</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3806,19 +3806,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B69" t="str">
-        <v>opell-prima-006</v>
+        <v>opell-prima-005</v>
       </c>
       <c r="C69" t="str">
-        <v>OPELL-PRIMA-006</v>
+        <v>OPELL-PRIMA-005</v>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>Angle Valve</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F69" t="str">
-        <v>Matt Black Gold</v>
+        <v/>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>opell-prima-006-main.png</v>
+        <v>opell-prima-005-main.jpg</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3859,16 +3859,16 @@
         <v>opell-prima-006</v>
       </c>
       <c r="C70" t="str">
-        <v>OPELL-PRIMA-007</v>
+        <v>OPELL-PRIMA-058</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>Basin Mixer Wall Mounted Upper Parts</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F70" t="str">
-        <v>Matt White Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>opell-prima-007-main.png</v>
+        <v>opell-prima-058-main.jpg</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3909,7 +3909,7 @@
         <v>opell-prima-006</v>
       </c>
       <c r="C71" t="str">
-        <v>OPELL-PRIMA-008</v>
+        <v>OPELL-PRIMA-006</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -3918,7 +3918,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Matt Beige Gold</v>
+        <v>Matt Black Gold</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3927,7 +3927,7 @@
         <v/>
       </c>
       <c r="I71" t="str">
-        <v>opell-prima-008-main.png</v>
+        <v>opell-prima-006-main.png</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -3959,7 +3959,7 @@
         <v>opell-prima-006</v>
       </c>
       <c r="C72" t="str">
-        <v>OPELL-PRIMA-009</v>
+        <v>OPELL-PRIMA-007</v>
       </c>
       <c r="D72" t="str">
         <v/>
@@ -3968,7 +3968,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Matt White</v>
+        <v>Matt White Gold</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>opell-prima-009-main.png</v>
+        <v>opell-prima-007-main.png</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -4006,19 +4006,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B73" t="str">
-        <v>opell-prima-010</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C73" t="str">
-        <v>OPELL-PRIMA-010</v>
+        <v>OPELL-PRIMA-008</v>
       </c>
       <c r="D73" t="str">
-        <v>Bath TUB Spout</v>
+        <v/>
       </c>
       <c r="E73" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F73" t="str">
-        <v/>
+        <v>Matt Beige Gold</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4027,7 +4027,7 @@
         <v/>
       </c>
       <c r="I73" t="str">
-        <v>opell-prima-010-main.jpg</v>
+        <v>opell-prima-008-main.png</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -4056,19 +4056,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B74" t="str">
-        <v>opell-prima-015</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C74" t="str">
-        <v>OPELL-PRIMA-015</v>
+        <v>OPELL-PRIMA-009</v>
       </c>
       <c r="D74" t="str">
-        <v>Bottle Trap</v>
+        <v/>
       </c>
       <c r="E74" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F74" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4077,7 +4077,7 @@
         <v/>
       </c>
       <c r="I74" t="str">
-        <v>opell-prima-015-main.png</v>
+        <v>opell-prima-009-main.png</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -4106,19 +4106,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B75" t="str">
-        <v>opell-prima-015</v>
+        <v>opell-prima-010</v>
       </c>
       <c r="C75" t="str">
-        <v>OPELL-PRIMA-011</v>
+        <v>OPELL-PRIMA-010</v>
       </c>
       <c r="D75" t="str">
-        <v/>
+        <v>Bath TUB Spout</v>
       </c>
       <c r="E75" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F75" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4127,7 +4127,7 @@
         <v/>
       </c>
       <c r="I75" t="str">
-        <v>opell-prima-011-main.png</v>
+        <v>opell-prima-010-main.jpg</v>
       </c>
       <c r="J75" t="str">
         <v/>
@@ -4159,16 +4159,16 @@
         <v>opell-prima-015</v>
       </c>
       <c r="C76" t="str">
-        <v>OPELL-PRIMA-014</v>
+        <v>OPELL-PRIMA-015</v>
       </c>
       <c r="D76" t="str">
-        <v/>
+        <v>Bottle Trap</v>
       </c>
       <c r="E76" t="str">
-        <v/>
+        <v>Accessories</v>
       </c>
       <c r="F76" t="str">
-        <v>Matt Black</v>
+        <v/>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I76" t="str">
-        <v>opell-prima-014-main.png</v>
+        <v>opell-prima-015-main.png</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -4209,7 +4209,7 @@
         <v>opell-prima-015</v>
       </c>
       <c r="C77" t="str">
-        <v>OPELL-PRIMA-016</v>
+        <v>OPELL-PRIMA-011</v>
       </c>
       <c r="D77" t="str">
         <v/>
@@ -4218,7 +4218,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Matt White</v>
+        <v>Matt Beige</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4227,7 +4227,7 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>opell-prima-016-main.png</v>
+        <v>opell-prima-011-main.png</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4256,19 +4256,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B78" t="str">
-        <v>opell-prima-012</v>
+        <v>opell-prima-015</v>
       </c>
       <c r="C78" t="str">
-        <v>OPELL-PRIMA-012</v>
+        <v>OPELL-PRIMA-014</v>
       </c>
       <c r="D78" t="str">
-        <v>Beige Gold Alive</v>
+        <v/>
       </c>
       <c r="E78" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F78" t="str">
-        <v/>
+        <v>Matt Black</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -4277,7 +4277,7 @@
         <v/>
       </c>
       <c r="I78" t="str">
-        <v>opell-prima-012-main.png</v>
+        <v>opell-prima-014-main.png</v>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -4306,19 +4306,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B79" t="str">
-        <v>opell-prima-013</v>
+        <v>opell-prima-015</v>
       </c>
       <c r="C79" t="str">
-        <v>OPELL-PRIMA-013</v>
+        <v>OPELL-PRIMA-016</v>
       </c>
       <c r="D79" t="str">
-        <v>Beige Gold Shower</v>
+        <v/>
       </c>
       <c r="E79" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F79" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -4327,7 +4327,7 @@
         <v/>
       </c>
       <c r="I79" t="str">
-        <v>opell-prima-013-main.png</v>
+        <v>opell-prima-016-main.png</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -4356,16 +4356,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B80" t="str">
-        <v>opell-prima-017</v>
+        <v>opell-prima-013</v>
       </c>
       <c r="C80" t="str">
-        <v>OPELL-PRIMA-017</v>
+        <v>OPELL-PRIMA-013</v>
       </c>
       <c r="D80" t="str">
-        <v>Button Spout</v>
+        <v>Beige Gold Shower</v>
       </c>
       <c r="E80" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F80" t="str">
         <v/>
@@ -4377,7 +4377,7 @@
         <v/>
       </c>
       <c r="I80" t="str">
-        <v>opell-prima-017-main.jpg</v>
+        <v>opell-prima-013-main.png</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -4406,16 +4406,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B81" t="str">
-        <v>opell-prima-018</v>
+        <v>opell-prima-017</v>
       </c>
       <c r="C81" t="str">
-        <v>OPELL-PRIMA-018</v>
+        <v>OPELL-PRIMA-017</v>
       </c>
       <c r="D81" t="str">
-        <v>Center Hole</v>
+        <v>Button Spout</v>
       </c>
       <c r="E81" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -4427,7 +4427,7 @@
         <v/>
       </c>
       <c r="I81" t="str">
-        <v>opell-prima-018-main.jpg</v>
+        <v>opell-prima-017-main.jpg</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -4456,16 +4456,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B82" t="str">
-        <v>opell-prima-019</v>
+        <v>opell-prima-018</v>
       </c>
       <c r="C82" t="str">
-        <v>OPELL-PRIMA-019</v>
+        <v>OPELL-PRIMA-018</v>
       </c>
       <c r="D82" t="str">
-        <v>Concealed Stop Cock</v>
+        <v>Center Hole</v>
       </c>
       <c r="E82" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F82" t="str">
         <v/>
@@ -4477,7 +4477,7 @@
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>opell-prima-019-main.jpg</v>
+        <v>opell-prima-018-main.jpg</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -4506,13 +4506,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B83" t="str">
-        <v>opell-prima-020</v>
+        <v>opell-prima-019</v>
       </c>
       <c r="C83" t="str">
-        <v>OPELL-PRIMA-020</v>
+        <v>OPELL-PRIMA-019</v>
       </c>
       <c r="D83" t="str">
-        <v>Diverter Body</v>
+        <v>Concealed Stop Cock</v>
       </c>
       <c r="E83" t="str">
         <v>Faucets</v>
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>opell-prima-020-main.png</v>
+        <v>opell-prima-019-main.jpg</v>
       </c>
       <c r="J83" t="str">
         <v/>
@@ -4559,16 +4559,16 @@
         <v>opell-prima-020</v>
       </c>
       <c r="C84" t="str">
-        <v>OPELL-PRIMA-022</v>
+        <v>OPELL-PRIMA-020</v>
       </c>
       <c r="D84" t="str">
-        <v/>
+        <v>Diverter Body</v>
       </c>
       <c r="E84" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F84" t="str">
-        <v>Rich Gold</v>
+        <v/>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -4577,7 +4577,7 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>opell-prima-022-main.png</v>
+        <v>opell-prima-020-main.png</v>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -4609,7 +4609,7 @@
         <v>opell-prima-020</v>
       </c>
       <c r="C85" t="str">
-        <v>OPELL-PRIMA-023</v>
+        <v>OPELL-PRIMA-022</v>
       </c>
       <c r="D85" t="str">
         <v/>
@@ -4618,7 +4618,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Matt Beige</v>
+        <v>Rich Gold</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -4627,7 +4627,7 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>opell-prima-023-main.png</v>
+        <v>opell-prima-022-main.png</v>
       </c>
       <c r="J85" t="str">
         <v/>
@@ -4656,19 +4656,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B86" t="str">
-        <v>opell-prima-021</v>
+        <v>opell-prima-020</v>
       </c>
       <c r="C86" t="str">
-        <v>OPELL-PRIMA-021</v>
+        <v>OPELL-PRIMA-023</v>
       </c>
       <c r="D86" t="str">
-        <v>Diverter Body for ALL Colour and Gold Combination</v>
+        <v/>
       </c>
       <c r="E86" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F86" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -4677,7 +4677,7 @@
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>opell-prima-021-main.png</v>
+        <v>opell-prima-023-main.png</v>
       </c>
       <c r="J86" t="str">
         <v/>
@@ -4706,13 +4706,13 @@
         <v>Opell Prima</v>
       </c>
       <c r="B87" t="str">
-        <v>opell-prima-024</v>
+        <v>opell-prima-021</v>
       </c>
       <c r="C87" t="str">
-        <v>OPELL-PRIMA-024</v>
+        <v>OPELL-PRIMA-021</v>
       </c>
       <c r="D87" t="str">
-        <v>Diverter Upper Part</v>
+        <v>Diverter Body for ALL Colour and Gold Combination</v>
       </c>
       <c r="E87" t="str">
         <v>Faucets</v>
@@ -4727,7 +4727,7 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>opell-prima-024-main.png</v>
+        <v>opell-prima-021-main.png</v>
       </c>
       <c r="J87" t="str">
         <v/>
@@ -4756,19 +4756,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B88" t="str">
-        <v>opell-prima-025</v>
+        <v>opell-prima-024</v>
       </c>
       <c r="C88" t="str">
-        <v>OPELL-PRIMA-025</v>
+        <v>OPELL-PRIMA-024</v>
       </c>
       <c r="D88" t="str">
-        <v>Diverter Upper Parts</v>
+        <v>Exposed Parts for Single Lever High Flow Diverter Body</v>
       </c>
       <c r="E88" t="str">
         <v>Faucets</v>
       </c>
       <c r="F88" t="str">
-        <v/>
+        <v>Matt Black</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>opell-prima-025-main.png</v>
+        <v>opell-prima-024-main.png</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -4806,19 +4806,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B89" t="str">
-        <v>opell-prima-026</v>
+        <v>opell-prima-024</v>
       </c>
       <c r="C89" t="str">
-        <v>OPELL-PRIMA-026</v>
+        <v>OPELL-PRIMA-025</v>
       </c>
       <c r="D89" t="str">
-        <v>Exposed Parts for Single Lever High Flow Diverter Body</v>
+        <v/>
       </c>
       <c r="E89" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F89" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4827,7 +4827,7 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>opell-prima-026-main.jpg</v>
+        <v>opell-prima-025-main.png</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4856,19 +4856,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B90" t="str">
-        <v>opell-prima-027</v>
+        <v>opell-prima-024</v>
       </c>
       <c r="C90" t="str">
-        <v>OPELL-PRIMA-027</v>
+        <v>OPELL-PRIMA-026</v>
       </c>
       <c r="D90" t="str">
-        <v>Gold</v>
+        <v/>
       </c>
       <c r="E90" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F90" t="str">
-        <v/>
+        <v>Chrome</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4877,7 +4877,7 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>opell-prima-027-main.png</v>
+        <v>opell-prima-026-main.jpg</v>
       </c>
       <c r="J90" t="str">
         <v/>
@@ -4906,16 +4906,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B91" t="str">
-        <v>opell-prima-029</v>
+        <v>opell-prima-027</v>
       </c>
       <c r="C91" t="str">
-        <v>OPELL-PRIMA-029</v>
+        <v>OPELL-PRIMA-027</v>
       </c>
       <c r="D91" t="str">
-        <v>Hand Shower</v>
+        <v>Gold</v>
       </c>
       <c r="E91" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F91" t="str">
         <v/>
@@ -4927,7 +4927,7 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>opell-prima-029-main.png</v>
+        <v>opell-prima-027-main.png</v>
       </c>
       <c r="J91" t="str">
         <v/>
@@ -4959,16 +4959,16 @@
         <v>opell-prima-029</v>
       </c>
       <c r="C92" t="str">
-        <v>OPELL-PRIMA-028</v>
+        <v>OPELL-PRIMA-029</v>
       </c>
       <c r="D92" t="str">
-        <v/>
+        <v>Hand Shower</v>
       </c>
       <c r="E92" t="str">
-        <v/>
+        <v>Showers</v>
       </c>
       <c r="F92" t="str">
-        <v>Rose Gold</v>
+        <v/>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -4977,7 +4977,7 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v>opell-prima-028-main.png</v>
+        <v>opell-prima-029-main.png</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -5009,7 +5009,7 @@
         <v>opell-prima-029</v>
       </c>
       <c r="C93" t="str">
-        <v>OPELL-PRIMA-030</v>
+        <v>OPELL-PRIMA-028</v>
       </c>
       <c r="D93" t="str">
         <v/>
@@ -5018,7 +5018,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Rich Gold</v>
+        <v>Rose Gold</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5027,7 +5027,7 @@
         <v/>
       </c>
       <c r="I93" t="str">
-        <v>opell-prima-030-main.png</v>
+        <v>opell-prima-028-main.png</v>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -5056,19 +5056,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B94" t="str">
-        <v>opell-prima-031</v>
+        <v>opell-prima-029</v>
       </c>
       <c r="C94" t="str">
-        <v>OPELL-PRIMA-031</v>
+        <v>OPELL-PRIMA-030</v>
       </c>
       <c r="D94" t="str">
-        <v>Health Faucet</v>
+        <v/>
       </c>
       <c r="E94" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F94" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5077,7 +5077,7 @@
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>opell-prima-031-main.png</v>
+        <v>opell-prima-030-main.png</v>
       </c>
       <c r="J94" t="str">
         <v/>
@@ -5106,16 +5106,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B95" t="str">
-        <v>opell-prima-032</v>
+        <v>opell-prima-031</v>
       </c>
       <c r="C95" t="str">
-        <v>OPELL-PRIMA-032</v>
+        <v>OPELL-PRIMA-031</v>
       </c>
       <c r="D95" t="str">
-        <v>Long Body</v>
+        <v>Health Faucet</v>
       </c>
       <c r="E95" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F95" t="str">
         <v/>
@@ -5127,7 +5127,7 @@
         <v/>
       </c>
       <c r="I95" t="str">
-        <v>opell-prima-032-main.jpg</v>
+        <v>opell-prima-031-main.png</v>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -5156,16 +5156,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B96" t="str">
-        <v>opell-prima-033</v>
+        <v>opell-prima-032</v>
       </c>
       <c r="C96" t="str">
-        <v>OPELL-PRIMA-033</v>
+        <v>OPELL-PRIMA-032</v>
       </c>
       <c r="D96" t="str">
-        <v>Matte Beige Alive</v>
+        <v>Long Body</v>
       </c>
       <c r="E96" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F96" t="str">
         <v/>
@@ -5177,7 +5177,7 @@
         <v/>
       </c>
       <c r="I96" t="str">
-        <v>opell-prima-033-main.png</v>
+        <v>opell-prima-032-main.jpg</v>
       </c>
       <c r="J96" t="str">
         <v/>
@@ -5412,13 +5412,13 @@
         <v>OPELL-PRIMA-038</v>
       </c>
       <c r="D101" t="str">
-        <v>Pillar Cock Extend</v>
+        <v>Single Lever Basin Mixer Tall</v>
       </c>
       <c r="E101" t="str">
         <v>Faucets</v>
       </c>
       <c r="F101" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -5456,19 +5456,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B102" t="str">
-        <v>opell-prima-039</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C102" t="str">
         <v>OPELL-PRIMA-039</v>
       </c>
       <c r="D102" t="str">
-        <v>Pillar Cock Extended</v>
+        <v/>
       </c>
       <c r="E102" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F102" t="str">
-        <v/>
+        <v>Rose Gold</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -5506,19 +5506,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B103" t="str">
-        <v>opell-prima-040</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C103" t="str">
-        <v>OPELL-PRIMA-040</v>
+        <v>OPELL-PRIMA-048</v>
       </c>
       <c r="D103" t="str">
-        <v>Pillar Cock Extended Body</v>
+        <v/>
       </c>
       <c r="E103" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F103" t="str">
-        <v/>
+        <v>Chrome</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -5527,7 +5527,7 @@
         <v/>
       </c>
       <c r="I103" t="str">
-        <v>opell-prima-040-main.jpg</v>
+        <v>opell-prima-048-main.jpg</v>
       </c>
       <c r="J103" t="str">
         <v/>
@@ -5556,19 +5556,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B104" t="str">
-        <v>opell-prima-041</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C104" t="str">
-        <v>OPELL-PRIMA-041</v>
+        <v>OPELL-PRIMA-049</v>
       </c>
       <c r="D104" t="str">
-        <v>Plain Spout</v>
+        <v/>
       </c>
       <c r="E104" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F104" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -5577,7 +5577,7 @@
         <v/>
       </c>
       <c r="I104" t="str">
-        <v>opell-prima-041-main.png</v>
+        <v>opell-prima-049-main.png</v>
       </c>
       <c r="J104" t="str">
         <v/>
@@ -5606,19 +5606,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B105" t="str">
-        <v>opell-prima-042</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C105" t="str">
-        <v>OPELL-PRIMA-042</v>
+        <v>OPELL-PRIMA-050</v>
       </c>
       <c r="D105" t="str">
-        <v>Shower ARM</v>
+        <v/>
       </c>
       <c r="E105" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F105" t="str">
-        <v/>
+        <v>Matt Beige Gold</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -5627,7 +5627,7 @@
         <v/>
       </c>
       <c r="I105" t="str">
-        <v>opell-prima-042-main.png</v>
+        <v>opell-prima-050-main.png</v>
       </c>
       <c r="J105" t="str">
         <v/>
@@ -5656,19 +5656,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B106" t="str">
-        <v>opell-prima-042</v>
+        <v>opell-prima-040</v>
       </c>
       <c r="C106" t="str">
-        <v>OPELL-PRIMA-043</v>
+        <v>OPELL-PRIMA-040</v>
       </c>
       <c r="D106" t="str">
-        <v/>
+        <v>Pillar Cock Extended Body</v>
       </c>
       <c r="E106" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F106" t="str">
-        <v>Matt Black Gold</v>
+        <v/>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="I106" t="str">
-        <v>opell-prima-043-main.png</v>
+        <v>opell-prima-040-main.jpg</v>
       </c>
       <c r="J106" t="str">
         <v/>
@@ -5706,16 +5706,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B107" t="str">
-        <v>opell-prima-044</v>
+        <v>opell-prima-041</v>
       </c>
       <c r="C107" t="str">
-        <v>OPELL-PRIMA-044</v>
+        <v>OPELL-PRIMA-041</v>
       </c>
       <c r="D107" t="str">
-        <v>Shower Head</v>
+        <v>Plain Spout</v>
       </c>
       <c r="E107" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v/>
       </c>
       <c r="I107" t="str">
-        <v>opell-prima-044-main.png</v>
+        <v>opell-prima-041-main.png</v>
       </c>
       <c r="J107" t="str">
         <v/>
@@ -5756,19 +5756,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B108" t="str">
-        <v>opell-prima-044</v>
+        <v>opell-prima-042</v>
       </c>
       <c r="C108" t="str">
-        <v>OPELL-PRIMA-045</v>
+        <v>OPELL-PRIMA-042</v>
       </c>
       <c r="D108" t="str">
-        <v/>
+        <v>Shower ARM</v>
       </c>
       <c r="E108" t="str">
-        <v/>
+        <v>Showers</v>
       </c>
       <c r="F108" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -5777,7 +5777,7 @@
         <v/>
       </c>
       <c r="I108" t="str">
-        <v>opell-prima-045-main.png</v>
+        <v>opell-prima-042-main.png</v>
       </c>
       <c r="J108" t="str">
         <v/>
@@ -5806,19 +5806,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B109" t="str">
-        <v>opell-prima-046</v>
+        <v>opell-prima-042</v>
       </c>
       <c r="C109" t="str">
-        <v>OPELL-PRIMA-046</v>
+        <v>OPELL-PRIMA-043</v>
       </c>
       <c r="D109" t="str">
-        <v>Shower Mixer for Spout Only</v>
+        <v/>
       </c>
       <c r="E109" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F109" t="str">
-        <v/>
+        <v>Matt Black Gold</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -5827,7 +5827,7 @@
         <v/>
       </c>
       <c r="I109" t="str">
-        <v>opell-prima-046-main.jpg</v>
+        <v>opell-prima-043-main.png</v>
       </c>
       <c r="J109" t="str">
         <v/>
@@ -5856,16 +5856,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B110" t="str">
-        <v>opell-prima-047</v>
+        <v>opell-prima-044</v>
       </c>
       <c r="C110" t="str">
-        <v>OPELL-PRIMA-047</v>
+        <v>OPELL-PRIMA-044</v>
       </c>
       <c r="D110" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Shower Head</v>
       </c>
       <c r="E110" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F110" t="str">
         <v/>
@@ -5877,10 +5877,10 @@
         <v/>
       </c>
       <c r="I110" t="str">
-        <v>opell-prima-047-main.jpg</v>
+        <v>opell-prima-044-main.png</v>
       </c>
       <c r="J110" t="str">
-        <v>opell-prima-047-main.jpg,opell-prima-059-main.png</v>
+        <v/>
       </c>
       <c r="K110" t="str">
         <v/>
@@ -5906,19 +5906,19 @@
         <v>Opell Prima</v>
       </c>
       <c r="B111" t="str">
-        <v>opell-prima-048</v>
+        <v>opell-prima-044</v>
       </c>
       <c r="C111" t="str">
-        <v>OPELL-PRIMA-048</v>
+        <v>OPELL-PRIMA-045</v>
       </c>
       <c r="D111" t="str">
-        <v>Single Lever Basin Mixer Extended Body</v>
+        <v/>
       </c>
       <c r="E111" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F111" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -5927,7 +5927,7 @@
         <v/>
       </c>
       <c r="I111" t="str">
-        <v>opell-prima-048-main.jpg</v>
+        <v>opell-prima-045-main.png</v>
       </c>
       <c r="J111" t="str">
         <v/>
@@ -5956,16 +5956,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B112" t="str">
-        <v>opell-prima-049</v>
+        <v>opell-prima-046</v>
       </c>
       <c r="C112" t="str">
-        <v>OPELL-PRIMA-049</v>
+        <v>OPELL-PRIMA-046</v>
       </c>
       <c r="D112" t="str">
-        <v>Single Lever Basin Mixer Tall</v>
+        <v>Shower Mixer for Spout Only</v>
       </c>
       <c r="E112" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -5977,10 +5977,10 @@
         <v/>
       </c>
       <c r="I112" t="str">
-        <v>opell-prima-049-main.png</v>
+        <v>opell-prima-046-main.jpg</v>
       </c>
       <c r="J112" t="str">
-        <v>opell-prima-049-main.png,opell-prima-060-main.png</v>
+        <v/>
       </c>
       <c r="K112" t="str">
         <v/>
@@ -6006,16 +6006,16 @@
         <v>Opell Prima</v>
       </c>
       <c r="B113" t="str">
-        <v>opell-prima-050</v>
+        <v>opell-prima-047</v>
       </c>
       <c r="C113" t="str">
-        <v>OPELL-PRIMA-050</v>
+        <v>OPELL-PRIMA-047</v>
       </c>
       <c r="D113" t="str">
-        <v>Single Lever Basin Tall</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E113" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -6027,10 +6027,10 @@
         <v/>
       </c>
       <c r="I113" t="str">
-        <v>opell-prima-050-main.png</v>
+        <v>opell-prima-047-main.jpg</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>opell-prima-047-main.jpg,opell-prima-059-main.png</v>
       </c>
       <c r="K113" t="str">
         <v/>

--- a/product catalogue.xlsx
+++ b/product catalogue.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P316"/>
+  <dimension ref="A1:P329"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3553,13 +3553,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B64" t="str">
-        <v>opell-prima-001</v>
+        <v>cube-001</v>
       </c>
       <c r="C64" t="str">
-        <v>OPELL-PRIMA-001</v>
+        <v>CUBE-001</v>
       </c>
       <c r="D64" t="str">
         <v>2 WAY Angle Valve</v>
@@ -3577,7 +3577,7 @@
         <v/>
       </c>
       <c r="I64" t="str">
-        <v>opell-prima-001-main.jpg</v>
+        <v>cube-001-main.png</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -3603,13 +3603,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B65" t="str">
-        <v>opell-prima-002</v>
+        <v>cube-002</v>
       </c>
       <c r="C65" t="str">
-        <v>OPELL-PRIMA-002</v>
+        <v>CUBE-002</v>
       </c>
       <c r="D65" t="str">
         <v>2 WAY BIB Cock</v>
@@ -3627,7 +3627,7 @@
         <v/>
       </c>
       <c r="I65" t="str">
-        <v>opell-prima-002-main.png</v>
+        <v>cube-002-main.png</v>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -3653,22 +3653,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B66" t="str">
-        <v>opell-prima-003</v>
+        <v>cube-003</v>
       </c>
       <c r="C66" t="str">
-        <v>OPELL-PRIMA-003</v>
+        <v>CUBE-003</v>
       </c>
       <c r="D66" t="str">
-        <v>Aliva Shower Head</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E66" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F66" t="str">
-        <v>Chrome</v>
+        <v/>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -3677,10 +3677,10 @@
         <v/>
       </c>
       <c r="I66" t="str">
-        <v>opell-prima-003-main.png</v>
+        <v>cube-003-main.jpg</v>
       </c>
       <c r="J66" t="str">
-        <v>opell-prima-003-main.png,opell-prima-004-main.png</v>
+        <v/>
       </c>
       <c r="K66" t="str">
         <v/>
@@ -3703,22 +3703,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B67" t="str">
-        <v>opell-prima-003</v>
+        <v>cube-004</v>
       </c>
       <c r="C67" t="str">
-        <v>OPELL-PRIMA-012</v>
+        <v>CUBE-004</v>
       </c>
       <c r="D67" t="str">
-        <v/>
+        <v>Basin Mixer Wall Mounted</v>
       </c>
       <c r="E67" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F67" t="str">
-        <v>Profile Beige Gold</v>
+        <v/>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -3727,7 +3727,7 @@
         <v/>
       </c>
       <c r="I67" t="str">
-        <v>opell-prima-012-main.png</v>
+        <v>cube-004-main.png</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -3753,22 +3753,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B68" t="str">
-        <v>opell-prima-003</v>
+        <v>cube-005</v>
       </c>
       <c r="C68" t="str">
-        <v>OPELL-PRIMA-033</v>
+        <v>CUBE-005</v>
       </c>
       <c r="D68" t="str">
-        <v/>
+        <v>Bath Tub Spout</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F68" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3777,7 +3777,7 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>opell-prima-033-main.png</v>
+        <v>cube-005-main.jpg</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3803,16 +3803,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B69" t="str">
-        <v>opell-prima-005</v>
+        <v>cube-006</v>
       </c>
       <c r="C69" t="str">
-        <v>OPELL-PRIMA-005</v>
+        <v>CUBE-006</v>
       </c>
       <c r="D69" t="str">
-        <v>Angle Valve</v>
+        <v>Bib Cock Long Body</v>
       </c>
       <c r="E69" t="str">
         <v>Faucets</v>
@@ -3827,7 +3827,7 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>opell-prima-005-main.jpg</v>
+        <v>cube-006-main.jpg</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3853,22 +3853,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B70" t="str">
-        <v>opell-prima-006</v>
+        <v>cube-007</v>
       </c>
       <c r="C70" t="str">
-        <v>OPELL-PRIMA-058</v>
+        <v>CUBE-007</v>
       </c>
       <c r="D70" t="str">
-        <v>Basin Mixer Wall Mounted Upper Parts</v>
+        <v>Button Spout</v>
       </c>
       <c r="E70" t="str">
         <v>Faucets</v>
       </c>
       <c r="F70" t="str">
-        <v>Chrome</v>
+        <v/>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>opell-prima-058-main.jpg</v>
+        <v>cube-007-main.jpg</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B71" t="str">
-        <v>opell-prima-006</v>
+        <v>cube-008</v>
       </c>
       <c r="C71" t="str">
-        <v>OPELL-PRIMA-006</v>
+        <v>CUBE-008</v>
       </c>
       <c r="D71" t="str">
-        <v/>
+        <v>Concealed Stop Cock</v>
       </c>
       <c r="E71" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F71" t="str">
-        <v>Matt Black Gold</v>
+        <v/>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3927,7 +3927,7 @@
         <v/>
       </c>
       <c r="I71" t="str">
-        <v>opell-prima-006-main.png</v>
+        <v>cube-008-main.jpg</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B72" t="str">
-        <v>opell-prima-006</v>
+        <v>cube-009</v>
       </c>
       <c r="C72" t="str">
-        <v>OPELL-PRIMA-007</v>
+        <v>CUBE-009</v>
       </c>
       <c r="D72" t="str">
-        <v/>
+        <v>Diverter Body</v>
       </c>
       <c r="E72" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F72" t="str">
-        <v>Matt White Gold</v>
+        <v/>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>opell-prima-007-main.png</v>
+        <v>cube-009-main.png</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B73" t="str">
-        <v>opell-prima-006</v>
+        <v>cube-010</v>
       </c>
       <c r="C73" t="str">
-        <v>OPELL-PRIMA-008</v>
+        <v>CUBE-010</v>
       </c>
       <c r="D73" t="str">
-        <v/>
+        <v>Diverter Upper Part</v>
       </c>
       <c r="E73" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F73" t="str">
-        <v>Matt Beige Gold</v>
+        <v/>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4027,7 +4027,7 @@
         <v/>
       </c>
       <c r="I73" t="str">
-        <v>opell-prima-008-main.png</v>
+        <v>cube-010-main.png</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -4053,22 +4053,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B74" t="str">
-        <v>opell-prima-006</v>
+        <v>cube-011</v>
       </c>
       <c r="C74" t="str">
-        <v>OPELL-PRIMA-009</v>
+        <v>CUBE-011</v>
       </c>
       <c r="D74" t="str">
-        <v/>
+        <v>Flush Cock</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F74" t="str">
-        <v>Matt White</v>
+        <v/>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4077,7 +4077,7 @@
         <v/>
       </c>
       <c r="I74" t="str">
-        <v>opell-prima-009-main.png</v>
+        <v>cube-011-main.jpg</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -4103,16 +4103,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B75" t="str">
-        <v>opell-prima-010</v>
+        <v>cube-012</v>
       </c>
       <c r="C75" t="str">
-        <v>OPELL-PRIMA-010</v>
+        <v>CUBE-012</v>
       </c>
       <c r="D75" t="str">
-        <v>Bath TUB Spout</v>
+        <v>Nozzle Bib Cock</v>
       </c>
       <c r="E75" t="str">
         <v>Faucets</v>
@@ -4127,7 +4127,7 @@
         <v/>
       </c>
       <c r="I75" t="str">
-        <v>opell-prima-010-main.jpg</v>
+        <v>cube-012-main.jpg</v>
       </c>
       <c r="J75" t="str">
         <v/>
@@ -4153,19 +4153,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B76" t="str">
-        <v>opell-prima-015</v>
+        <v>cube-013</v>
       </c>
       <c r="C76" t="str">
-        <v>OPELL-PRIMA-015</v>
+        <v>CUBE-013</v>
       </c>
       <c r="D76" t="str">
-        <v>Bottle Trap</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E76" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F76" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I76" t="str">
-        <v>opell-prima-015-main.png</v>
+        <v>cube-013-main.jpg</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B77" t="str">
-        <v>opell-prima-015</v>
+        <v>cube-014</v>
       </c>
       <c r="C77" t="str">
-        <v>OPELL-PRIMA-011</v>
+        <v>CUBE-014</v>
       </c>
       <c r="D77" t="str">
-        <v/>
+        <v>Pillar Cock Extended</v>
       </c>
       <c r="E77" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F77" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4227,7 +4227,7 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>opell-prima-011-main.png</v>
+        <v>cube-014-main.png</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4253,22 +4253,22 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B78" t="str">
-        <v>opell-prima-015</v>
+        <v>cube-015</v>
       </c>
       <c r="C78" t="str">
-        <v>OPELL-PRIMA-014</v>
+        <v>CUBE-015</v>
       </c>
       <c r="D78" t="str">
-        <v/>
+        <v>Pillar Cock Extended Body</v>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F78" t="str">
-        <v>Matt Black</v>
+        <v/>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -4277,7 +4277,7 @@
         <v/>
       </c>
       <c r="I78" t="str">
-        <v>opell-prima-014-main.png</v>
+        <v>cube-015-main.jpg</v>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -4303,22 +4303,22 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B79" t="str">
-        <v>opell-prima-015</v>
+        <v>cube-016</v>
       </c>
       <c r="C79" t="str">
-        <v>OPELL-PRIMA-016</v>
+        <v>CUBE-016</v>
       </c>
       <c r="D79" t="str">
-        <v/>
+        <v>S L Concealed Basin Mixer Exposed Parts</v>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F79" t="str">
-        <v>Matt White</v>
+        <v/>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -4327,7 +4327,7 @@
         <v/>
       </c>
       <c r="I79" t="str">
-        <v>opell-prima-016-main.png</v>
+        <v>cube-016-main.jpg</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -4353,16 +4353,16 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B80" t="str">
-        <v>opell-prima-013</v>
+        <v>cube-017</v>
       </c>
       <c r="C80" t="str">
-        <v>OPELL-PRIMA-013</v>
+        <v>CUBE-017</v>
       </c>
       <c r="D80" t="str">
-        <v>Beige Gold Shower</v>
+        <v>Shower ARM</v>
       </c>
       <c r="E80" t="str">
         <v>Showers</v>
@@ -4377,7 +4377,7 @@
         <v/>
       </c>
       <c r="I80" t="str">
-        <v>opell-prima-013-main.png</v>
+        <v>cube-017-main.png</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -4403,19 +4403,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B81" t="str">
-        <v>opell-prima-017</v>
+        <v>cube-018</v>
       </c>
       <c r="C81" t="str">
-        <v>OPELL-PRIMA-017</v>
+        <v>CUBE-018</v>
       </c>
       <c r="D81" t="str">
-        <v>Button Spout</v>
+        <v>Shower Head</v>
       </c>
       <c r="E81" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -4427,7 +4427,7 @@
         <v/>
       </c>
       <c r="I81" t="str">
-        <v>opell-prima-017-main.jpg</v>
+        <v>cube-018-main.png</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -4453,19 +4453,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B82" t="str">
-        <v>opell-prima-018</v>
+        <v>cube-019</v>
       </c>
       <c r="C82" t="str">
-        <v>OPELL-PRIMA-018</v>
+        <v>CUBE-019</v>
       </c>
       <c r="D82" t="str">
-        <v>Center Hole</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E82" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F82" t="str">
         <v/>
@@ -4477,7 +4477,7 @@
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>opell-prima-018-main.jpg</v>
+        <v>cube-019-main.jpg</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -4503,16 +4503,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B83" t="str">
-        <v>opell-prima-019</v>
+        <v>cube-020</v>
       </c>
       <c r="C83" t="str">
-        <v>OPELL-PRIMA-019</v>
+        <v>CUBE-020</v>
       </c>
       <c r="D83" t="str">
-        <v>Concealed Stop Cock</v>
+        <v>Single Lever Basin Mixer Extended Body</v>
       </c>
       <c r="E83" t="str">
         <v>Faucets</v>
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v>opell-prima-019-main.jpg</v>
+        <v>cube-020-main.png</v>
       </c>
       <c r="J83" t="str">
         <v/>
@@ -4553,16 +4553,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B84" t="str">
-        <v>opell-prima-020</v>
+        <v>cube-021</v>
       </c>
       <c r="C84" t="str">
-        <v>OPELL-PRIMA-020</v>
+        <v>CUBE-021</v>
       </c>
       <c r="D84" t="str">
-        <v>Diverter Body</v>
+        <v>Single Lever Basin Mixer Tall</v>
       </c>
       <c r="E84" t="str">
         <v>Faucets</v>
@@ -4577,7 +4577,7 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>opell-prima-020-main.png</v>
+        <v>cube-021-main.png</v>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B85" t="str">
-        <v>opell-prima-020</v>
+        <v>cube-022</v>
       </c>
       <c r="C85" t="str">
-        <v>OPELL-PRIMA-022</v>
+        <v>CUBE-022</v>
       </c>
       <c r="D85" t="str">
-        <v/>
+        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
       </c>
       <c r="E85" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F85" t="str">
-        <v>Rich Gold</v>
+        <v/>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -4627,7 +4627,7 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v>opell-prima-022-main.png</v>
+        <v>cube-022-main.jpg</v>
       </c>
       <c r="J85" t="str">
         <v/>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B86" t="str">
-        <v>opell-prima-020</v>
+        <v>cube-023</v>
       </c>
       <c r="C86" t="str">
-        <v>OPELL-PRIMA-023</v>
+        <v>CUBE-023</v>
       </c>
       <c r="D86" t="str">
-        <v/>
+        <v>Single Lever Diverter</v>
       </c>
       <c r="E86" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F86" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -4677,7 +4677,7 @@
         <v/>
       </c>
       <c r="I86" t="str">
-        <v>opell-prima-023-main.png</v>
+        <v>cube-023-main.jpg</v>
       </c>
       <c r="J86" t="str">
         <v/>
@@ -4703,16 +4703,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B87" t="str">
-        <v>opell-prima-021</v>
+        <v>cube-024</v>
       </c>
       <c r="C87" t="str">
-        <v>OPELL-PRIMA-021</v>
+        <v>CUBE-024</v>
       </c>
       <c r="D87" t="str">
-        <v>Diverter Body for ALL Colour and Gold Combination</v>
+        <v>Single Lever Sink Mixer Angular</v>
       </c>
       <c r="E87" t="str">
         <v>Faucets</v>
@@ -4727,7 +4727,7 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>opell-prima-021-main.png</v>
+        <v>cube-024-main.jpg</v>
       </c>
       <c r="J87" t="str">
         <v/>
@@ -4753,22 +4753,22 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B88" t="str">
-        <v>opell-prima-024</v>
+        <v>cube-025</v>
       </c>
       <c r="C88" t="str">
-        <v>OPELL-PRIMA-024</v>
+        <v>CUBE-025</v>
       </c>
       <c r="D88" t="str">
-        <v>Exposed Parts for Single Lever High Flow Diverter Body</v>
+        <v>Single Lever Sink Mixer Side Handle</v>
       </c>
       <c r="E88" t="str">
         <v>Faucets</v>
       </c>
       <c r="F88" t="str">
-        <v>Matt Black</v>
+        <v/>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v/>
       </c>
       <c r="I88" t="str">
-        <v>opell-prima-024-main.png</v>
+        <v>cube-025-main.jpg</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -4803,22 +4803,22 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B89" t="str">
-        <v>opell-prima-024</v>
+        <v>cube-026</v>
       </c>
       <c r="C89" t="str">
-        <v>OPELL-PRIMA-025</v>
+        <v>CUBE-026</v>
       </c>
       <c r="D89" t="str">
-        <v/>
+        <v>Single Lever Sink Mixer Wall Mounted</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F89" t="str">
-        <v>Rich Gold</v>
+        <v/>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -4827,7 +4827,7 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>opell-prima-025-main.png</v>
+        <v>cube-026-main.jpg</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B90" t="str">
-        <v>opell-prima-024</v>
+        <v>cube-027</v>
       </c>
       <c r="C90" t="str">
-        <v>OPELL-PRIMA-026</v>
+        <v>CUBE-027</v>
       </c>
       <c r="D90" t="str">
-        <v/>
+        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
       </c>
       <c r="E90" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F90" t="str">
-        <v>Chrome</v>
+        <v/>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4877,7 +4877,7 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>opell-prima-026-main.jpg</v>
+        <v>cube-027-main.jpg</v>
       </c>
       <c r="J90" t="str">
         <v/>
@@ -4903,19 +4903,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B91" t="str">
-        <v>opell-prima-027</v>
+        <v>cube-028</v>
       </c>
       <c r="C91" t="str">
-        <v>OPELL-PRIMA-027</v>
+        <v>CUBE-028</v>
       </c>
       <c r="D91" t="str">
-        <v>Gold</v>
+        <v>Single Lever Table Top</v>
       </c>
       <c r="E91" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F91" t="str">
         <v/>
@@ -4927,7 +4927,7 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>opell-prima-027-main.png</v>
+        <v>cube-028-main.jpg</v>
       </c>
       <c r="J91" t="str">
         <v/>
@@ -4953,19 +4953,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B92" t="str">
-        <v>opell-prima-029</v>
+        <v>cube-029</v>
       </c>
       <c r="C92" t="str">
-        <v>OPELL-PRIMA-029</v>
+        <v>CUBE-029</v>
       </c>
       <c r="D92" t="str">
-        <v>Hand Shower</v>
+        <v>Single Lever Tall Boy</v>
       </c>
       <c r="E92" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F92" t="str">
         <v/>
@@ -4977,7 +4977,7 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v>opell-prima-029-main.png</v>
+        <v>cube-029-main.jpg</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -5003,22 +5003,22 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B93" t="str">
-        <v>opell-prima-029</v>
+        <v>cube-030</v>
       </c>
       <c r="C93" t="str">
-        <v>OPELL-PRIMA-028</v>
+        <v>CUBE-030</v>
       </c>
       <c r="D93" t="str">
-        <v/>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E93" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F93" t="str">
-        <v>Rose Gold</v>
+        <v/>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5027,7 +5027,7 @@
         <v/>
       </c>
       <c r="I93" t="str">
-        <v>opell-prima-028-main.png</v>
+        <v>cube-030-main.jpg</v>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -5053,22 +5053,22 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B94" t="str">
-        <v>opell-prima-029</v>
+        <v>cube-031</v>
       </c>
       <c r="C94" t="str">
-        <v>OPELL-PRIMA-030</v>
+        <v>CUBE-031</v>
       </c>
       <c r="D94" t="str">
-        <v/>
+        <v>Sink Cock</v>
       </c>
       <c r="E94" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F94" t="str">
-        <v>Rich Gold</v>
+        <v/>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5077,7 +5077,7 @@
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>opell-prima-030-main.png</v>
+        <v>cube-031-main.jpg</v>
       </c>
       <c r="J94" t="str">
         <v/>
@@ -5103,19 +5103,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B95" t="str">
-        <v>opell-prima-031</v>
+        <v>cube-032</v>
       </c>
       <c r="C95" t="str">
-        <v>OPELL-PRIMA-031</v>
+        <v>CUBE-032</v>
       </c>
       <c r="D95" t="str">
-        <v>Health Faucet</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E95" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F95" t="str">
         <v/>
@@ -5127,7 +5127,7 @@
         <v/>
       </c>
       <c r="I95" t="str">
-        <v>opell-prima-031-main.png</v>
+        <v>cube-032-main.jpg</v>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -5153,16 +5153,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B96" t="str">
-        <v>opell-prima-032</v>
+        <v>cube-033</v>
       </c>
       <c r="C96" t="str">
-        <v>OPELL-PRIMA-032</v>
+        <v>CUBE-033</v>
       </c>
       <c r="D96" t="str">
-        <v>Long Body</v>
+        <v>Two Way Angle Valve</v>
       </c>
       <c r="E96" t="str">
         <v>Faucets</v>
@@ -5177,7 +5177,7 @@
         <v/>
       </c>
       <c r="I96" t="str">
-        <v>opell-prima-032-main.jpg</v>
+        <v>cube-033-main.jpg</v>
       </c>
       <c r="J96" t="str">
         <v/>
@@ -5203,19 +5203,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B97" t="str">
-        <v>opell-prima-034</v>
+        <v>cube-034</v>
       </c>
       <c r="C97" t="str">
-        <v>OPELL-PRIMA-034</v>
+        <v>CUBE-034</v>
       </c>
       <c r="D97" t="str">
-        <v>Matte White Shower Head</v>
+        <v>Two Way Bib Cock</v>
       </c>
       <c r="E97" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F97" t="str">
         <v/>
@@ -5227,7 +5227,7 @@
         <v/>
       </c>
       <c r="I97" t="str">
-        <v>opell-prima-034-main.png</v>
+        <v>cube-034-main.jpg</v>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -5253,19 +5253,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B98" t="str">
-        <v>opell-prima-035</v>
+        <v>cube-035</v>
       </c>
       <c r="C98" t="str">
-        <v>OPELL-PRIMA-035</v>
+        <v>CUBE-035</v>
       </c>
       <c r="D98" t="str">
-        <v>NON Telephonic</v>
+        <v>Wall Mixer Button Spout with Bend</v>
       </c>
       <c r="E98" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F98" t="str">
         <v/>
@@ -5277,7 +5277,7 @@
         <v/>
       </c>
       <c r="I98" t="str">
-        <v>opell-prima-035-main.jpg</v>
+        <v>cube-035-main.jpg</v>
       </c>
       <c r="J98" t="str">
         <v/>
@@ -5303,16 +5303,16 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B99" t="str">
-        <v>opell-prima-036</v>
+        <v>cube-036</v>
       </c>
       <c r="C99" t="str">
-        <v>OPELL-PRIMA-036</v>
+        <v>CUBE-036</v>
       </c>
       <c r="D99" t="str">
-        <v>Nozzle BIB Cock</v>
+        <v>Wall Mixer Telephonic</v>
       </c>
       <c r="E99" t="str">
         <v>Faucets</v>
@@ -5327,7 +5327,7 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v>opell-prima-036-main.jpg</v>
+        <v>cube-036-main.jpg</v>
       </c>
       <c r="J99" t="str">
         <v/>
@@ -5353,16 +5353,16 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B100" t="str">
-        <v>opell-prima-037</v>
+        <v>cube-037</v>
       </c>
       <c r="C100" t="str">
-        <v>OPELL-PRIMA-037</v>
+        <v>CUBE-037</v>
       </c>
       <c r="D100" t="str">
-        <v>Pillar Cock</v>
+        <v>Wall Mixer with Bend</v>
       </c>
       <c r="E100" t="str">
         <v>Faucets</v>
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="I100" t="str">
-        <v>opell-prima-037-main.jpg</v>
+        <v>cube-037-main.jpg</v>
       </c>
       <c r="J100" t="str">
         <v/>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B101" t="str">
-        <v>opell-prima-038</v>
+        <v>cube-038</v>
       </c>
       <c r="C101" t="str">
-        <v>OPELL-PRIMA-038</v>
+        <v>CUBE-038</v>
       </c>
       <c r="D101" t="str">
-        <v>Single Lever Basin Mixer Tall</v>
+        <v>Wall Mixer with Crutch</v>
       </c>
       <c r="E101" t="str">
         <v>Faucets</v>
       </c>
       <c r="F101" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -5427,7 +5427,7 @@
         <v/>
       </c>
       <c r="I101" t="str">
-        <v>opell-prima-038-main.png</v>
+        <v>cube-038-main.jpg</v>
       </c>
       <c r="J101" t="str">
         <v/>
@@ -5453,22 +5453,22 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Opell Prima</v>
+        <v>Cube</v>
       </c>
       <c r="B102" t="str">
-        <v>opell-prima-038</v>
+        <v>cube-039</v>
       </c>
       <c r="C102" t="str">
-        <v>OPELL-PRIMA-039</v>
+        <v>CUBE-039</v>
       </c>
       <c r="D102" t="str">
-        <v/>
+        <v>Waste Coupling</v>
       </c>
       <c r="E102" t="str">
-        <v/>
+        <v>Accessories</v>
       </c>
       <c r="F102" t="str">
-        <v>Rose Gold</v>
+        <v/>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -5477,7 +5477,7 @@
         <v/>
       </c>
       <c r="I102" t="str">
-        <v>opell-prima-039-main.png</v>
+        <v>cube-039-main.png</v>
       </c>
       <c r="J102" t="str">
         <v/>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B103" t="str">
-        <v>opell-prima-038</v>
+        <v>cube-prima-001</v>
       </c>
       <c r="C103" t="str">
-        <v>OPELL-PRIMA-048</v>
+        <v>CUBE-PRIMA-001</v>
       </c>
       <c r="D103" t="str">
-        <v/>
+        <v>2 Way Angle Valve</v>
       </c>
       <c r="E103" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F103" t="str">
-        <v>Chrome</v>
+        <v/>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -5527,7 +5527,7 @@
         <v/>
       </c>
       <c r="I103" t="str">
-        <v>opell-prima-048-main.jpg</v>
+        <v>cube-prima-001-main.jpg</v>
       </c>
       <c r="J103" t="str">
         <v/>
@@ -5553,22 +5553,22 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B104" t="str">
-        <v>opell-prima-038</v>
+        <v>cube-prima-002</v>
       </c>
       <c r="C104" t="str">
-        <v>OPELL-PRIMA-049</v>
+        <v>CUBE-PRIMA-002</v>
       </c>
       <c r="D104" t="str">
-        <v/>
+        <v>2 Way Bib Cock</v>
       </c>
       <c r="E104" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F104" t="str">
-        <v>Matt White</v>
+        <v/>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -5577,7 +5577,7 @@
         <v/>
       </c>
       <c r="I104" t="str">
-        <v>opell-prima-049-main.png</v>
+        <v>cube-prima-002-main.jpg</v>
       </c>
       <c r="J104" t="str">
         <v/>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B105" t="str">
-        <v>opell-prima-038</v>
+        <v>cube-prima-003</v>
       </c>
       <c r="C105" t="str">
-        <v>OPELL-PRIMA-050</v>
+        <v>CUBE-PRIMA-003</v>
       </c>
       <c r="D105" t="str">
-        <v/>
+        <v>Bath Tub Spout</v>
       </c>
       <c r="E105" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F105" t="str">
-        <v>Matt Beige Gold</v>
+        <v/>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -5627,7 +5627,7 @@
         <v/>
       </c>
       <c r="I105" t="str">
-        <v>opell-prima-050-main.png</v>
+        <v>cube-prima-003-main.jpg</v>
       </c>
       <c r="J105" t="str">
         <v/>
@@ -5653,16 +5653,16 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B106" t="str">
-        <v>opell-prima-040</v>
+        <v>cube-prima-004</v>
       </c>
       <c r="C106" t="str">
-        <v>OPELL-PRIMA-040</v>
+        <v>CUBE-PRIMA-004</v>
       </c>
       <c r="D106" t="str">
-        <v>Pillar Cock Extended Body</v>
+        <v>Button Spout</v>
       </c>
       <c r="E106" t="str">
         <v>Faucets</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="I106" t="str">
-        <v>opell-prima-040-main.jpg</v>
+        <v>cube-prima-004-main.jpg</v>
       </c>
       <c r="J106" t="str">
         <v/>
@@ -5703,16 +5703,16 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B107" t="str">
-        <v>opell-prima-041</v>
+        <v>cube-prima-005</v>
       </c>
       <c r="C107" t="str">
-        <v>OPELL-PRIMA-041</v>
+        <v>CUBE-PRIMA-005</v>
       </c>
       <c r="D107" t="str">
-        <v>Plain Spout</v>
+        <v>Center Hole Basin Mixer</v>
       </c>
       <c r="E107" t="str">
         <v>Faucets</v>
@@ -5727,7 +5727,7 @@
         <v/>
       </c>
       <c r="I107" t="str">
-        <v>opell-prima-041-main.png</v>
+        <v>cube-prima-005-main.jpg</v>
       </c>
       <c r="J107" t="str">
         <v/>
@@ -5753,19 +5753,19 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B108" t="str">
-        <v>opell-prima-042</v>
+        <v>cube-prima-006</v>
       </c>
       <c r="C108" t="str">
-        <v>OPELL-PRIMA-042</v>
+        <v>CUBE-PRIMA-006</v>
       </c>
       <c r="D108" t="str">
-        <v>Shower ARM</v>
+        <v>Concealed Stop Cock 15mm</v>
       </c>
       <c r="E108" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F108" t="str">
         <v/>
@@ -5777,7 +5777,7 @@
         <v/>
       </c>
       <c r="I108" t="str">
-        <v>opell-prima-042-main.png</v>
+        <v>cube-prima-006-main.jpg</v>
       </c>
       <c r="J108" t="str">
         <v/>
@@ -5803,22 +5803,22 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B109" t="str">
-        <v>opell-prima-042</v>
+        <v>cube-prima-007</v>
       </c>
       <c r="C109" t="str">
-        <v>OPELL-PRIMA-043</v>
+        <v>CUBE-PRIMA-007</v>
       </c>
       <c r="D109" t="str">
-        <v/>
+        <v>Concealed Stop Cock 20mm</v>
       </c>
       <c r="E109" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F109" t="str">
-        <v>Matt Black Gold</v>
+        <v/>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -5827,7 +5827,7 @@
         <v/>
       </c>
       <c r="I109" t="str">
-        <v>opell-prima-043-main.png</v>
+        <v>cube-prima-007-main.jpg</v>
       </c>
       <c r="J109" t="str">
         <v/>
@@ -5853,19 +5853,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B110" t="str">
-        <v>opell-prima-044</v>
+        <v>cube-prima-008</v>
       </c>
       <c r="C110" t="str">
-        <v>OPELL-PRIMA-044</v>
+        <v>CUBE-PRIMA-008</v>
       </c>
       <c r="D110" t="str">
-        <v>Shower Head</v>
+        <v>High Flow Diverter Complete with Upper Parts</v>
       </c>
       <c r="E110" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F110" t="str">
         <v/>
@@ -5877,7 +5877,7 @@
         <v/>
       </c>
       <c r="I110" t="str">
-        <v>opell-prima-044-main.png</v>
+        <v>cube-prima-008-main.jpg</v>
       </c>
       <c r="J110" t="str">
         <v/>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B111" t="str">
-        <v>opell-prima-044</v>
+        <v>cube-prima-009</v>
       </c>
       <c r="C111" t="str">
-        <v>OPELL-PRIMA-045</v>
+        <v>CUBE-PRIMA-009</v>
       </c>
       <c r="D111" t="str">
-        <v/>
+        <v>Long Body</v>
       </c>
       <c r="E111" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F111" t="str">
-        <v>Matt Beige</v>
+        <v/>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -5927,7 +5927,7 @@
         <v/>
       </c>
       <c r="I111" t="str">
-        <v>opell-prima-045-main.png</v>
+        <v>cube-prima-009-main.jpg</v>
       </c>
       <c r="J111" t="str">
         <v/>
@@ -5953,19 +5953,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B112" t="str">
-        <v>opell-prima-046</v>
+        <v>cube-prima-010</v>
       </c>
       <c r="C112" t="str">
-        <v>OPELL-PRIMA-046</v>
+        <v>CUBE-PRIMA-010</v>
       </c>
       <c r="D112" t="str">
-        <v>Shower Mixer for Spout Only</v>
+        <v>Nozzle Bib Cock</v>
       </c>
       <c r="E112" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -5977,7 +5977,7 @@
         <v/>
       </c>
       <c r="I112" t="str">
-        <v>opell-prima-046-main.jpg</v>
+        <v>cube-prima-010-main.jpg</v>
       </c>
       <c r="J112" t="str">
         <v/>
@@ -6003,16 +6003,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B113" t="str">
-        <v>opell-prima-047</v>
+        <v>cube-prima-011</v>
       </c>
       <c r="C113" t="str">
-        <v>OPELL-PRIMA-047</v>
+        <v>CUBE-PRIMA-011</v>
       </c>
       <c r="D113" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E113" t="str">
         <v>Faucets</v>
@@ -6027,10 +6027,10 @@
         <v/>
       </c>
       <c r="I113" t="str">
-        <v>opell-prima-047-main.jpg</v>
+        <v>cube-prima-011-main.jpg</v>
       </c>
       <c r="J113" t="str">
-        <v>opell-prima-047-main.jpg,opell-prima-059-main.png</v>
+        <v/>
       </c>
       <c r="K113" t="str">
         <v/>
@@ -6053,19 +6053,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B114" t="str">
-        <v>opell-prima-051</v>
+        <v>cube-prima-012</v>
       </c>
       <c r="C114" t="str">
-        <v>OPELL-PRIMA-051</v>
+        <v>CUBE-PRIMA-012</v>
       </c>
       <c r="D114" t="str">
-        <v>Single Lever Exposed Shower Mixer</v>
+        <v>Pillar Cock Extended Body Casted One Piece</v>
       </c>
       <c r="E114" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -6077,7 +6077,7 @@
         <v/>
       </c>
       <c r="I114" t="str">
-        <v>opell-prima-051-main.jpg</v>
+        <v>cube-prima-012-main.jpg</v>
       </c>
       <c r="J114" t="str">
         <v/>
@@ -6103,16 +6103,16 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B115" t="str">
-        <v>opell-prima-052</v>
+        <v>cube-prima-013</v>
       </c>
       <c r="C115" t="str">
-        <v>OPELL-PRIMA-052</v>
+        <v>CUBE-PRIMA-013</v>
       </c>
       <c r="D115" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Angular Spout</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E115" t="str">
         <v>Faucets</v>
@@ -6127,7 +6127,7 @@
         <v/>
       </c>
       <c r="I115" t="str">
-        <v>opell-prima-052-main.jpg</v>
+        <v>cube-prima-013-main.jpg</v>
       </c>
       <c r="J115" t="str">
         <v/>
@@ -6153,16 +6153,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B116" t="str">
-        <v>opell-prima-053</v>
+        <v>cube-prima-014</v>
       </c>
       <c r="C116" t="str">
-        <v>OPELL-PRIMA-053</v>
+        <v>CUBE-PRIMA-014</v>
       </c>
       <c r="D116" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Round Spout Side Handle</v>
+        <v>Single Lever Basin Mixer Extended Body</v>
       </c>
       <c r="E116" t="str">
         <v>Faucets</v>
@@ -6177,7 +6177,7 @@
         <v/>
       </c>
       <c r="I116" t="str">
-        <v>opell-prima-053-main.jpg</v>
+        <v>cube-prima-014-main.jpg</v>
       </c>
       <c r="J116" t="str">
         <v/>
@@ -6203,16 +6203,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B117" t="str">
-        <v>opell-prima-054</v>
+        <v>cube-prima-015</v>
       </c>
       <c r="C117" t="str">
-        <v>OPELL-PRIMA-054</v>
+        <v>CUBE-PRIMA-015</v>
       </c>
       <c r="D117" t="str">
-        <v>Single Lever Sink Mixer Table Mounted Tall</v>
+        <v>Single Lever Concealed Basin Mixer Exposed Parts</v>
       </c>
       <c r="E117" t="str">
         <v>Faucets</v>
@@ -6227,7 +6227,7 @@
         <v/>
       </c>
       <c r="I117" t="str">
-        <v>opell-prima-054-main.jpg</v>
+        <v>cube-prima-015-main.jpg</v>
       </c>
       <c r="J117" t="str">
         <v/>
@@ -6253,16 +6253,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B118" t="str">
-        <v>opell-prima-055</v>
+        <v>cube-prima-016</v>
       </c>
       <c r="C118" t="str">
-        <v>OPELL-PRIMA-055</v>
+        <v>CUBE-PRIMA-016</v>
       </c>
       <c r="D118" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
+        <v>Single Lever Sink Mixer Angular</v>
       </c>
       <c r="E118" t="str">
         <v>Faucets</v>
@@ -6277,7 +6277,7 @@
         <v/>
       </c>
       <c r="I118" t="str">
-        <v>opell-prima-055-main.jpg</v>
+        <v>cube-prima-016-main.jpg</v>
       </c>
       <c r="J118" t="str">
         <v/>
@@ -6303,16 +6303,16 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B119" t="str">
-        <v>opell-prima-056</v>
+        <v>cube-prima-017</v>
       </c>
       <c r="C119" t="str">
-        <v>OPELL-PRIMA-056</v>
+        <v>CUBE-PRIMA-017</v>
       </c>
       <c r="D119" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Round Spout</v>
+        <v>Single Lever Sink Mixer Side Handle</v>
       </c>
       <c r="E119" t="str">
         <v>Faucets</v>
@@ -6327,7 +6327,7 @@
         <v/>
       </c>
       <c r="I119" t="str">
-        <v>opell-prima-056-main.jpg</v>
+        <v>cube-prima-017-main.jpg</v>
       </c>
       <c r="J119" t="str">
         <v/>
@@ -6353,16 +6353,16 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B120" t="str">
-        <v>opell-prima-057</v>
+        <v>cube-prima-018</v>
       </c>
       <c r="C120" t="str">
-        <v>OPELL-PRIMA-057</v>
+        <v>CUBE-PRIMA-018</v>
       </c>
       <c r="D120" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
       </c>
       <c r="E120" t="str">
         <v>Faucets</v>
@@ -6377,7 +6377,7 @@
         <v/>
       </c>
       <c r="I120" t="str">
-        <v>opell-prima-057-main.jpg</v>
+        <v>cube-prima-018-main.jpg</v>
       </c>
       <c r="J120" t="str">
         <v/>
@@ -6403,16 +6403,16 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B121" t="str">
-        <v>opell-prima-061</v>
+        <v>cube-prima-019</v>
       </c>
       <c r="C121" t="str">
-        <v>OPELL-PRIMA-061</v>
+        <v>CUBE-PRIMA-019</v>
       </c>
       <c r="D121" t="str">
-        <v>Sink Cock</v>
+        <v>Single Lever Sink Mixer Wall Mounted Cube</v>
       </c>
       <c r="E121" t="str">
         <v>Faucets</v>
@@ -6427,7 +6427,7 @@
         <v/>
       </c>
       <c r="I121" t="str">
-        <v>opell-prima-061-main.jpg</v>
+        <v>cube-prima-019-main.jpg</v>
       </c>
       <c r="J121" t="str">
         <v/>
@@ -6453,16 +6453,16 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B122" t="str">
-        <v>cube-001</v>
+        <v>cube-prima-020</v>
       </c>
       <c r="C122" t="str">
-        <v>CUBE-001</v>
+        <v>CUBE-PRIMA-020</v>
       </c>
       <c r="D122" t="str">
-        <v>2 WAY Angle Valve</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E122" t="str">
         <v>Faucets</v>
@@ -6477,7 +6477,7 @@
         <v/>
       </c>
       <c r="I122" t="str">
-        <v>cube-001-main.png</v>
+        <v>cube-prima-020-main.jpg</v>
       </c>
       <c r="J122" t="str">
         <v/>
@@ -6503,16 +6503,16 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B123" t="str">
-        <v>cube-002</v>
+        <v>cube-prima-021</v>
       </c>
       <c r="C123" t="str">
-        <v>CUBE-002</v>
+        <v>CUBE-PRIMA-021</v>
       </c>
       <c r="D123" t="str">
-        <v>2 WAY BIB Cock</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E123" t="str">
         <v>Faucets</v>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="I123" t="str">
-        <v>cube-002-main.png</v>
+        <v>cube-prima-021-main.jpg</v>
       </c>
       <c r="J123" t="str">
         <v/>
@@ -6553,16 +6553,16 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B124" t="str">
-        <v>cube-003</v>
+        <v>cube-prima-022</v>
       </c>
       <c r="C124" t="str">
-        <v>CUBE-003</v>
+        <v>CUBE-PRIMA-022</v>
       </c>
       <c r="D124" t="str">
-        <v>Angle Valve</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E124" t="str">
         <v>Faucets</v>
@@ -6577,7 +6577,7 @@
         <v/>
       </c>
       <c r="I124" t="str">
-        <v>cube-003-main.jpg</v>
+        <v>cube-prima-022-main.jpg</v>
       </c>
       <c r="J124" t="str">
         <v/>
@@ -6603,19 +6603,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B125" t="str">
-        <v>cube-004</v>
+        <v>cube-prima-023</v>
       </c>
       <c r="C125" t="str">
-        <v>CUBE-004</v>
+        <v>CUBE-PRIMA-023</v>
       </c>
       <c r="D125" t="str">
-        <v>Basin Mixer Wall Mounted</v>
+        <v>Swarn Neck</v>
       </c>
       <c r="E125" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F125" t="str">
         <v/>
@@ -6627,7 +6627,7 @@
         <v/>
       </c>
       <c r="I125" t="str">
-        <v>cube-004-main.png</v>
+        <v>cube-prima-023-main.jpg</v>
       </c>
       <c r="J125" t="str">
         <v/>
@@ -6653,16 +6653,16 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B126" t="str">
-        <v>cube-005</v>
+        <v>cube-prima-024</v>
       </c>
       <c r="C126" t="str">
-        <v>CUBE-005</v>
+        <v>CUBE-PRIMA-024</v>
       </c>
       <c r="D126" t="str">
-        <v>Bath Tub Spout</v>
+        <v>Wall Mixer Non Telephonic</v>
       </c>
       <c r="E126" t="str">
         <v>Faucets</v>
@@ -6677,7 +6677,7 @@
         <v/>
       </c>
       <c r="I126" t="str">
-        <v>cube-005-main.jpg</v>
+        <v>cube-prima-024-main.jpg</v>
       </c>
       <c r="J126" t="str">
         <v/>
@@ -6703,16 +6703,16 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B127" t="str">
-        <v>cube-006</v>
+        <v>cube-prima-025</v>
       </c>
       <c r="C127" t="str">
-        <v>CUBE-006</v>
+        <v>CUBE-PRIMA-025</v>
       </c>
       <c r="D127" t="str">
-        <v>Bib Cock Long Body</v>
+        <v>Wall Mixer with Bend</v>
       </c>
       <c r="E127" t="str">
         <v>Faucets</v>
@@ -6727,7 +6727,7 @@
         <v/>
       </c>
       <c r="I127" t="str">
-        <v>cube-006-main.jpg</v>
+        <v>cube-prima-025-main.jpg</v>
       </c>
       <c r="J127" t="str">
         <v/>
@@ -6753,16 +6753,16 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B128" t="str">
-        <v>cube-007</v>
+        <v>cube-prima-026</v>
       </c>
       <c r="C128" t="str">
-        <v>CUBE-007</v>
+        <v>CUBE-PRIMA-026</v>
       </c>
       <c r="D128" t="str">
-        <v>Button Spout</v>
+        <v>Wall Mixer with Bend 3-in-1</v>
       </c>
       <c r="E128" t="str">
         <v>Faucets</v>
@@ -6777,7 +6777,7 @@
         <v/>
       </c>
       <c r="I128" t="str">
-        <v>cube-007-main.jpg</v>
+        <v>cube-prima-026-main.jpg</v>
       </c>
       <c r="J128" t="str">
         <v/>
@@ -6803,16 +6803,16 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Cube</v>
+        <v>Cube Prima</v>
       </c>
       <c r="B129" t="str">
-        <v>cube-008</v>
+        <v>cube-prima-027</v>
       </c>
       <c r="C129" t="str">
-        <v>CUBE-008</v>
+        <v>CUBE-PRIMA-027</v>
       </c>
       <c r="D129" t="str">
-        <v>Concealed Stop Cock</v>
+        <v>Wall Mixer with Crutch</v>
       </c>
       <c r="E129" t="str">
         <v>Faucets</v>
@@ -6827,7 +6827,7 @@
         <v/>
       </c>
       <c r="I129" t="str">
-        <v>cube-008-main.jpg</v>
+        <v>cube-prima-027-main.jpg</v>
       </c>
       <c r="J129" t="str">
         <v/>
@@ -6853,16 +6853,16 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B130" t="str">
-        <v>cube-009</v>
+        <v>fuzone-001</v>
       </c>
       <c r="C130" t="str">
-        <v>CUBE-009</v>
+        <v>FUZONE-001</v>
       </c>
       <c r="D130" t="str">
-        <v>Diverter Body</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E130" t="str">
         <v>Faucets</v>
@@ -6877,7 +6877,7 @@
         <v/>
       </c>
       <c r="I130" t="str">
-        <v>cube-009-main.png</v>
+        <v>fuzone-001-main.jpg</v>
       </c>
       <c r="J130" t="str">
         <v/>
@@ -6903,16 +6903,16 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B131" t="str">
-        <v>cube-010</v>
+        <v>fuzone-002</v>
       </c>
       <c r="C131" t="str">
-        <v>CUBE-010</v>
+        <v>FUZONE-002</v>
       </c>
       <c r="D131" t="str">
-        <v>Diverter Upper Part</v>
+        <v>Bath Tub Spout</v>
       </c>
       <c r="E131" t="str">
         <v>Faucets</v>
@@ -6927,7 +6927,7 @@
         <v/>
       </c>
       <c r="I131" t="str">
-        <v>cube-010-main.png</v>
+        <v>fuzone-002-main.jpg</v>
       </c>
       <c r="J131" t="str">
         <v/>
@@ -6953,16 +6953,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B132" t="str">
-        <v>cube-011</v>
+        <v>fuzone-003</v>
       </c>
       <c r="C132" t="str">
-        <v>CUBE-011</v>
+        <v>FUZONE-003</v>
       </c>
       <c r="D132" t="str">
-        <v>Flush Cock</v>
+        <v>Bib Cock</v>
       </c>
       <c r="E132" t="str">
         <v>Faucets</v>
@@ -6977,7 +6977,7 @@
         <v/>
       </c>
       <c r="I132" t="str">
-        <v>cube-011-main.jpg</v>
+        <v>fuzone-003-main.jpg</v>
       </c>
       <c r="J132" t="str">
         <v/>
@@ -7003,16 +7003,16 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B133" t="str">
-        <v>cube-012</v>
+        <v>fuzone-004</v>
       </c>
       <c r="C133" t="str">
-        <v>CUBE-012</v>
+        <v>FUZONE-004</v>
       </c>
       <c r="D133" t="str">
-        <v>Nozzle Bib Cock</v>
+        <v>Button Spout</v>
       </c>
       <c r="E133" t="str">
         <v>Faucets</v>
@@ -7027,7 +7027,7 @@
         <v/>
       </c>
       <c r="I133" t="str">
-        <v>cube-012-main.jpg</v>
+        <v>fuzone-004-main.jpg</v>
       </c>
       <c r="J133" t="str">
         <v/>
@@ -7053,16 +7053,16 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B134" t="str">
-        <v>cube-013</v>
+        <v>fuzone-005</v>
       </c>
       <c r="C134" t="str">
-        <v>CUBE-013</v>
+        <v>FUZONE-005</v>
       </c>
       <c r="D134" t="str">
-        <v>Pillar Cock</v>
+        <v>Center Hole Mixer</v>
       </c>
       <c r="E134" t="str">
         <v>Faucets</v>
@@ -7077,7 +7077,7 @@
         <v/>
       </c>
       <c r="I134" t="str">
-        <v>cube-013-main.jpg</v>
+        <v>fuzone-005-main.jpg</v>
       </c>
       <c r="J134" t="str">
         <v/>
@@ -7103,16 +7103,16 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B135" t="str">
-        <v>cube-014</v>
+        <v>fuzone-006</v>
       </c>
       <c r="C135" t="str">
-        <v>CUBE-014</v>
+        <v>FUZONE-006</v>
       </c>
       <c r="D135" t="str">
-        <v>Pillar Cock Extended</v>
+        <v>Long Body</v>
       </c>
       <c r="E135" t="str">
         <v>Faucets</v>
@@ -7127,7 +7127,7 @@
         <v/>
       </c>
       <c r="I135" t="str">
-        <v>cube-014-main.png</v>
+        <v>fuzone-006-main.jpg</v>
       </c>
       <c r="J135" t="str">
         <v/>
@@ -7153,16 +7153,16 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B136" t="str">
-        <v>cube-015</v>
+        <v>fuzone-007</v>
       </c>
       <c r="C136" t="str">
-        <v>CUBE-015</v>
+        <v>FUZONE-007</v>
       </c>
       <c r="D136" t="str">
-        <v>Pillar Cock Extended Body</v>
+        <v>New Sink Mixer Wall Mounted Angular Spout Fuzone</v>
       </c>
       <c r="E136" t="str">
         <v>Faucets</v>
@@ -7177,7 +7177,7 @@
         <v/>
       </c>
       <c r="I136" t="str">
-        <v>cube-015-main.jpg</v>
+        <v>fuzone-007-main.jpg</v>
       </c>
       <c r="J136" t="str">
         <v/>
@@ -7203,16 +7203,16 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B137" t="str">
-        <v>cube-016</v>
+        <v>fuzone-008</v>
       </c>
       <c r="C137" t="str">
-        <v>CUBE-016</v>
+        <v>FUZONE-008</v>
       </c>
       <c r="D137" t="str">
-        <v>S L Concealed Basin Mixer Exposed Parts</v>
+        <v>Nozzle BIB Cock</v>
       </c>
       <c r="E137" t="str">
         <v>Faucets</v>
@@ -7227,7 +7227,7 @@
         <v/>
       </c>
       <c r="I137" t="str">
-        <v>cube-016-main.jpg</v>
+        <v>fuzone-008-main.jpg</v>
       </c>
       <c r="J137" t="str">
         <v/>
@@ -7253,19 +7253,19 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B138" t="str">
-        <v>cube-017</v>
+        <v>fuzone-009</v>
       </c>
       <c r="C138" t="str">
-        <v>CUBE-017</v>
+        <v>FUZONE-009</v>
       </c>
       <c r="D138" t="str">
-        <v>Shower ARM</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E138" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F138" t="str">
         <v/>
@@ -7277,7 +7277,7 @@
         <v/>
       </c>
       <c r="I138" t="str">
-        <v>cube-017-main.png</v>
+        <v>fuzone-009-main.jpg</v>
       </c>
       <c r="J138" t="str">
         <v/>
@@ -7303,19 +7303,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B139" t="str">
-        <v>cube-018</v>
+        <v>fuzone-010</v>
       </c>
       <c r="C139" t="str">
-        <v>CUBE-018</v>
+        <v>FUZONE-010</v>
       </c>
       <c r="D139" t="str">
-        <v>Shower Head</v>
+        <v>Single Lever Concealed Basin Mixer Upper Parts</v>
       </c>
       <c r="E139" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -7327,7 +7327,7 @@
         <v/>
       </c>
       <c r="I139" t="str">
-        <v>cube-018-main.png</v>
+        <v>fuzone-010-main.jpg</v>
       </c>
       <c r="J139" t="str">
         <v/>
@@ -7353,16 +7353,16 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B140" t="str">
-        <v>cube-019</v>
+        <v>fuzone-011</v>
       </c>
       <c r="C140" t="str">
-        <v>CUBE-019</v>
+        <v>FUZONE-011</v>
       </c>
       <c r="D140" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
       </c>
       <c r="E140" t="str">
         <v>Faucets</v>
@@ -7377,7 +7377,7 @@
         <v/>
       </c>
       <c r="I140" t="str">
-        <v>cube-019-main.jpg</v>
+        <v>fuzone-011-main.jpg</v>
       </c>
       <c r="J140" t="str">
         <v/>
@@ -7403,16 +7403,16 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B141" t="str">
-        <v>cube-020</v>
+        <v>fuzone-012</v>
       </c>
       <c r="C141" t="str">
-        <v>CUBE-020</v>
+        <v>FUZONE-012</v>
       </c>
       <c r="D141" t="str">
-        <v>Single Lever Basin Mixer Extended Body</v>
+        <v>Single Lever Exposed Parts Kit of High Flow Diverter</v>
       </c>
       <c r="E141" t="str">
         <v>Faucets</v>
@@ -7427,7 +7427,7 @@
         <v/>
       </c>
       <c r="I141" t="str">
-        <v>cube-020-main.png</v>
+        <v>fuzone-012-main.jpg</v>
       </c>
       <c r="J141" t="str">
         <v/>
@@ -7453,16 +7453,16 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B142" t="str">
-        <v>cube-021</v>
+        <v>fuzone-013</v>
       </c>
       <c r="C142" t="str">
-        <v>CUBE-021</v>
+        <v>FUZONE-013</v>
       </c>
       <c r="D142" t="str">
-        <v>Single Lever Basin Mixer Tall</v>
+        <v>Single Lever Mixer All Boy</v>
       </c>
       <c r="E142" t="str">
         <v>Faucets</v>
@@ -7477,7 +7477,7 @@
         <v/>
       </c>
       <c r="I142" t="str">
-        <v>cube-021-main.png</v>
+        <v>fuzone-013-main.jpg</v>
       </c>
       <c r="J142" t="str">
         <v/>
@@ -7503,16 +7503,16 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B143" t="str">
-        <v>cube-022</v>
+        <v>fuzone-014</v>
       </c>
       <c r="C143" t="str">
-        <v>CUBE-022</v>
+        <v>FUZONE-014</v>
       </c>
       <c r="D143" t="str">
-        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
+        <v>Single Lever Sink Mixer Angular</v>
       </c>
       <c r="E143" t="str">
         <v>Faucets</v>
@@ -7527,7 +7527,7 @@
         <v/>
       </c>
       <c r="I143" t="str">
-        <v>cube-022-main.jpg</v>
+        <v>fuzone-014-main.jpg</v>
       </c>
       <c r="J143" t="str">
         <v/>
@@ -7553,16 +7553,16 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B144" t="str">
-        <v>cube-023</v>
+        <v>fuzone-015</v>
       </c>
       <c r="C144" t="str">
-        <v>CUBE-023</v>
+        <v>FUZONE-015</v>
       </c>
       <c r="D144" t="str">
-        <v>Single Lever Diverter</v>
+        <v>Single Lever Sink Mixer Side Handle</v>
       </c>
       <c r="E144" t="str">
         <v>Faucets</v>
@@ -7577,7 +7577,7 @@
         <v/>
       </c>
       <c r="I144" t="str">
-        <v>cube-023-main.jpg</v>
+        <v>fuzone-015-main.jpg</v>
       </c>
       <c r="J144" t="str">
         <v/>
@@ -7603,16 +7603,16 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B145" t="str">
-        <v>cube-024</v>
+        <v>fuzone-016</v>
       </c>
       <c r="C145" t="str">
-        <v>CUBE-024</v>
+        <v>FUZONE-016</v>
       </c>
       <c r="D145" t="str">
-        <v>Single Lever Sink Mixer Angular</v>
+        <v>Single Lever Sink Mixer Wall Mounted</v>
       </c>
       <c r="E145" t="str">
         <v>Faucets</v>
@@ -7627,7 +7627,7 @@
         <v/>
       </c>
       <c r="I145" t="str">
-        <v>cube-024-main.jpg</v>
+        <v>fuzone-016-main.jpg</v>
       </c>
       <c r="J145" t="str">
         <v/>
@@ -7653,16 +7653,16 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B146" t="str">
-        <v>cube-025</v>
+        <v>fuzone-017</v>
       </c>
       <c r="C146" t="str">
-        <v>CUBE-025</v>
+        <v>FUZONE-017</v>
       </c>
       <c r="D146" t="str">
-        <v>Single Lever Sink Mixer Side Handle</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E146" t="str">
         <v>Faucets</v>
@@ -7677,7 +7677,7 @@
         <v/>
       </c>
       <c r="I146" t="str">
-        <v>cube-025-main.jpg</v>
+        <v>fuzone-017-main.jpg</v>
       </c>
       <c r="J146" t="str">
         <v/>
@@ -7703,16 +7703,16 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B147" t="str">
-        <v>cube-026</v>
+        <v>fuzone-018</v>
       </c>
       <c r="C147" t="str">
-        <v>CUBE-026</v>
+        <v>FUZONE-018</v>
       </c>
       <c r="D147" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E147" t="str">
         <v>Faucets</v>
@@ -7727,7 +7727,7 @@
         <v/>
       </c>
       <c r="I147" t="str">
-        <v>cube-026-main.jpg</v>
+        <v>fuzone-018-main.jpg</v>
       </c>
       <c r="J147" t="str">
         <v/>
@@ -7753,16 +7753,16 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B148" t="str">
-        <v>cube-027</v>
+        <v>fuzone-019</v>
       </c>
       <c r="C148" t="str">
-        <v>CUBE-027</v>
+        <v>FUZONE-019</v>
       </c>
       <c r="D148" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E148" t="str">
         <v>Faucets</v>
@@ -7777,7 +7777,7 @@
         <v/>
       </c>
       <c r="I148" t="str">
-        <v>cube-027-main.jpg</v>
+        <v>fuzone-019-main.jpg</v>
       </c>
       <c r="J148" t="str">
         <v/>
@@ -7803,16 +7803,16 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B149" t="str">
-        <v>cube-028</v>
+        <v>fuzone-020</v>
       </c>
       <c r="C149" t="str">
-        <v>CUBE-028</v>
+        <v>FUZONE-020</v>
       </c>
       <c r="D149" t="str">
-        <v>Single Lever Table Top</v>
+        <v>Sink Mixer Pillar Mounted Fuzone</v>
       </c>
       <c r="E149" t="str">
         <v>Faucets</v>
@@ -7827,7 +7827,7 @@
         <v/>
       </c>
       <c r="I149" t="str">
-        <v>cube-028-main.jpg</v>
+        <v>fuzone-020-main.jpg</v>
       </c>
       <c r="J149" t="str">
         <v/>
@@ -7853,16 +7853,16 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B150" t="str">
-        <v>cube-029</v>
+        <v>fuzone-021</v>
       </c>
       <c r="C150" t="str">
-        <v>CUBE-029</v>
+        <v>FUZONE-021</v>
       </c>
       <c r="D150" t="str">
-        <v>Single Lever Tall Boy</v>
+        <v>Swarn Neck</v>
       </c>
       <c r="E150" t="str">
         <v>Accessories</v>
@@ -7877,7 +7877,7 @@
         <v/>
       </c>
       <c r="I150" t="str">
-        <v>cube-029-main.jpg</v>
+        <v>fuzone-021-main.jpg</v>
       </c>
       <c r="J150" t="str">
         <v/>
@@ -7903,16 +7903,16 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B151" t="str">
-        <v>cube-030</v>
+        <v>fuzone-022</v>
       </c>
       <c r="C151" t="str">
-        <v>CUBE-030</v>
+        <v>FUZONE-022</v>
       </c>
       <c r="D151" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>TWO WAY Angle Valve</v>
       </c>
       <c r="E151" t="str">
         <v>Faucets</v>
@@ -7927,7 +7927,7 @@
         <v/>
       </c>
       <c r="I151" t="str">
-        <v>cube-030-main.jpg</v>
+        <v>fuzone-022-main.jpg</v>
       </c>
       <c r="J151" t="str">
         <v/>
@@ -7953,16 +7953,16 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B152" t="str">
-        <v>cube-031</v>
+        <v>fuzone-023</v>
       </c>
       <c r="C152" t="str">
-        <v>CUBE-031</v>
+        <v>FUZONE-023</v>
       </c>
       <c r="D152" t="str">
-        <v>Sink Cock</v>
+        <v>TWO WAY BIB Cock</v>
       </c>
       <c r="E152" t="str">
         <v>Faucets</v>
@@ -7977,7 +7977,7 @@
         <v/>
       </c>
       <c r="I152" t="str">
-        <v>cube-031-main.jpg</v>
+        <v>fuzone-023-main.jpg</v>
       </c>
       <c r="J152" t="str">
         <v/>
@@ -8003,16 +8003,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B153" t="str">
-        <v>cube-032</v>
+        <v>fuzone-024</v>
       </c>
       <c r="C153" t="str">
-        <v>CUBE-032</v>
+        <v>FUZONE-024</v>
       </c>
       <c r="D153" t="str">
-        <v>Sink Mixer</v>
+        <v>Wall Mixer Button Spout with Bend</v>
       </c>
       <c r="E153" t="str">
         <v>Faucets</v>
@@ -8027,7 +8027,7 @@
         <v/>
       </c>
       <c r="I153" t="str">
-        <v>cube-032-main.jpg</v>
+        <v>fuzone-024-main.jpg</v>
       </c>
       <c r="J153" t="str">
         <v/>
@@ -8053,16 +8053,16 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B154" t="str">
-        <v>cube-033</v>
+        <v>fuzone-025</v>
       </c>
       <c r="C154" t="str">
-        <v>CUBE-033</v>
+        <v>FUZONE-025</v>
       </c>
       <c r="D154" t="str">
-        <v>Two Way Angle Valve</v>
+        <v>Wall Mixer NON Telephonic</v>
       </c>
       <c r="E154" t="str">
         <v>Faucets</v>
@@ -8077,7 +8077,7 @@
         <v/>
       </c>
       <c r="I154" t="str">
-        <v>cube-033-main.jpg</v>
+        <v>fuzone-025-main.jpg</v>
       </c>
       <c r="J154" t="str">
         <v/>
@@ -8103,16 +8103,16 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B155" t="str">
-        <v>cube-034</v>
+        <v>fuzone-026</v>
       </c>
       <c r="C155" t="str">
-        <v>CUBE-034</v>
+        <v>FUZONE-026</v>
       </c>
       <c r="D155" t="str">
-        <v>Two Way Bib Cock</v>
+        <v>Wall Mixer with Bend</v>
       </c>
       <c r="E155" t="str">
         <v>Faucets</v>
@@ -8127,7 +8127,7 @@
         <v/>
       </c>
       <c r="I155" t="str">
-        <v>cube-034-main.jpg</v>
+        <v>fuzone-026-main.jpg</v>
       </c>
       <c r="J155" t="str">
         <v/>
@@ -8153,16 +8153,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Cube</v>
+        <v>Fuzone</v>
       </c>
       <c r="B156" t="str">
-        <v>cube-035</v>
+        <v>fuzone-027</v>
       </c>
       <c r="C156" t="str">
-        <v>CUBE-035</v>
+        <v>FUZONE-027</v>
       </c>
       <c r="D156" t="str">
-        <v>Wall Mixer Button Spout with Bend</v>
+        <v>Wall Mixer with Crutch</v>
       </c>
       <c r="E156" t="str">
         <v>Faucets</v>
@@ -8177,7 +8177,7 @@
         <v/>
       </c>
       <c r="I156" t="str">
-        <v>cube-035-main.jpg</v>
+        <v>fuzone-027-main.jpg</v>
       </c>
       <c r="J156" t="str">
         <v/>
@@ -8203,16 +8203,16 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Cube</v>
+        <v>JP</v>
       </c>
       <c r="B157" t="str">
-        <v>cube-036</v>
+        <v>jp-001</v>
       </c>
       <c r="C157" t="str">
-        <v>CUBE-036</v>
+        <v>JP-001</v>
       </c>
       <c r="D157" t="str">
-        <v>Wall Mixer Telephonic</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E157" t="str">
         <v>Faucets</v>
@@ -8227,7 +8227,7 @@
         <v/>
       </c>
       <c r="I157" t="str">
-        <v>cube-036-main.jpg</v>
+        <v>jp-001-main.jpg</v>
       </c>
       <c r="J157" t="str">
         <v/>
@@ -8253,16 +8253,16 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Cube</v>
+        <v>JP</v>
       </c>
       <c r="B158" t="str">
-        <v>cube-037</v>
+        <v>jp-002</v>
       </c>
       <c r="C158" t="str">
-        <v>CUBE-037</v>
+        <v>JP-002</v>
       </c>
       <c r="D158" t="str">
-        <v>Wall Mixer with Bend</v>
+        <v>Bib Cock</v>
       </c>
       <c r="E158" t="str">
         <v>Faucets</v>
@@ -8277,7 +8277,7 @@
         <v/>
       </c>
       <c r="I158" t="str">
-        <v>cube-037-main.jpg</v>
+        <v>jp-002-main.jpg</v>
       </c>
       <c r="J158" t="str">
         <v/>
@@ -8303,16 +8303,16 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cube</v>
+        <v>JP</v>
       </c>
       <c r="B159" t="str">
-        <v>cube-038</v>
+        <v>jp-003</v>
       </c>
       <c r="C159" t="str">
-        <v>CUBE-038</v>
+        <v>JP-003</v>
       </c>
       <c r="D159" t="str">
-        <v>Wall Mixer with Crutch</v>
+        <v>Bib Cock Long Body</v>
       </c>
       <c r="E159" t="str">
         <v>Faucets</v>
@@ -8327,7 +8327,7 @@
         <v/>
       </c>
       <c r="I159" t="str">
-        <v>cube-038-main.jpg</v>
+        <v>jp-003-main.jpg</v>
       </c>
       <c r="J159" t="str">
         <v/>
@@ -8353,19 +8353,19 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Cube</v>
+        <v>JP</v>
       </c>
       <c r="B160" t="str">
-        <v>cube-039</v>
+        <v>jp-004</v>
       </c>
       <c r="C160" t="str">
-        <v>CUBE-039</v>
+        <v>JP-004</v>
       </c>
       <c r="D160" t="str">
-        <v>Waste Coupling</v>
+        <v>Center Hole Mixer</v>
       </c>
       <c r="E160" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F160" t="str">
         <v/>
@@ -8377,7 +8377,7 @@
         <v/>
       </c>
       <c r="I160" t="str">
-        <v>cube-039-main.png</v>
+        <v>jp-004-main.jpg</v>
       </c>
       <c r="J160" t="str">
         <v/>
@@ -8403,16 +8403,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B161" t="str">
-        <v>cube-prima-001</v>
+        <v>jp-005</v>
       </c>
       <c r="C161" t="str">
-        <v>CUBE-PRIMA-001</v>
+        <v>JP-005</v>
       </c>
       <c r="D161" t="str">
-        <v>2 Way Angle Valve</v>
+        <v>Concealed Stop Cock</v>
       </c>
       <c r="E161" t="str">
         <v>Faucets</v>
@@ -8427,7 +8427,7 @@
         <v/>
       </c>
       <c r="I161" t="str">
-        <v>cube-prima-001-main.jpg</v>
+        <v>jp-005-main.jpg</v>
       </c>
       <c r="J161" t="str">
         <v/>
@@ -8453,16 +8453,16 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B162" t="str">
-        <v>cube-prima-002</v>
+        <v>jp-006</v>
       </c>
       <c r="C162" t="str">
-        <v>CUBE-PRIMA-002</v>
+        <v>JP-006</v>
       </c>
       <c r="D162" t="str">
-        <v>2 Way Bib Cock</v>
+        <v>Nozzle Bib Cock</v>
       </c>
       <c r="E162" t="str">
         <v>Faucets</v>
@@ -8477,7 +8477,7 @@
         <v/>
       </c>
       <c r="I162" t="str">
-        <v>cube-prima-002-main.jpg</v>
+        <v>jp-006-main.jpg</v>
       </c>
       <c r="J162" t="str">
         <v/>
@@ -8503,16 +8503,16 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B163" t="str">
-        <v>cube-prima-003</v>
+        <v>jp-007</v>
       </c>
       <c r="C163" t="str">
-        <v>CUBE-PRIMA-003</v>
+        <v>JP-007</v>
       </c>
       <c r="D163" t="str">
-        <v>Bath Tub Spout</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E163" t="str">
         <v>Faucets</v>
@@ -8527,7 +8527,7 @@
         <v/>
       </c>
       <c r="I163" t="str">
-        <v>cube-prima-003-main.jpg</v>
+        <v>jp-007-main.jpg</v>
       </c>
       <c r="J163" t="str">
         <v/>
@@ -8553,16 +8553,16 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B164" t="str">
-        <v>cube-prima-004</v>
+        <v>jp-008</v>
       </c>
       <c r="C164" t="str">
-        <v>CUBE-PRIMA-004</v>
+        <v>JP-008</v>
       </c>
       <c r="D164" t="str">
-        <v>Button Spout</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E164" t="str">
         <v>Faucets</v>
@@ -8577,7 +8577,7 @@
         <v/>
       </c>
       <c r="I164" t="str">
-        <v>cube-prima-004-main.jpg</v>
+        <v>jp-008-main.jpg</v>
       </c>
       <c r="J164" t="str">
         <v/>
@@ -8603,16 +8603,16 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B165" t="str">
-        <v>cube-prima-005</v>
+        <v>jp-009</v>
       </c>
       <c r="C165" t="str">
-        <v>CUBE-PRIMA-005</v>
+        <v>JP-009</v>
       </c>
       <c r="D165" t="str">
-        <v>Center Hole Basin Mixer</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E165" t="str">
         <v>Faucets</v>
@@ -8627,7 +8627,7 @@
         <v/>
       </c>
       <c r="I165" t="str">
-        <v>cube-prima-005-main.jpg</v>
+        <v>jp-009-main.jpg</v>
       </c>
       <c r="J165" t="str">
         <v/>
@@ -8653,16 +8653,16 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B166" t="str">
-        <v>cube-prima-006</v>
+        <v>jp-010</v>
       </c>
       <c r="C166" t="str">
-        <v>CUBE-PRIMA-006</v>
+        <v>JP-010</v>
       </c>
       <c r="D166" t="str">
-        <v>Concealed Stop Cock 15mm</v>
+        <v>Swan Neck</v>
       </c>
       <c r="E166" t="str">
         <v>Faucets</v>
@@ -8677,7 +8677,7 @@
         <v/>
       </c>
       <c r="I166" t="str">
-        <v>cube-prima-006-main.jpg</v>
+        <v>jp-010-main.jpg</v>
       </c>
       <c r="J166" t="str">
         <v/>
@@ -8703,16 +8703,16 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B167" t="str">
-        <v>cube-prima-007</v>
+        <v>jp-011</v>
       </c>
       <c r="C167" t="str">
-        <v>CUBE-PRIMA-007</v>
+        <v>JP-011</v>
       </c>
       <c r="D167" t="str">
-        <v>Concealed Stop Cock 20mm</v>
+        <v>Two Way Angle Valve</v>
       </c>
       <c r="E167" t="str">
         <v>Faucets</v>
@@ -8727,7 +8727,7 @@
         <v/>
       </c>
       <c r="I167" t="str">
-        <v>cube-prima-007-main.jpg</v>
+        <v>jp-011-main.jpg</v>
       </c>
       <c r="J167" t="str">
         <v/>
@@ -8753,16 +8753,16 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B168" t="str">
-        <v>cube-prima-008</v>
+        <v>jp-012</v>
       </c>
       <c r="C168" t="str">
-        <v>CUBE-PRIMA-008</v>
+        <v>JP-012</v>
       </c>
       <c r="D168" t="str">
-        <v>High Flow Diverter Complete with Upper Parts</v>
+        <v>Two Way Bib Cock</v>
       </c>
       <c r="E168" t="str">
         <v>Faucets</v>
@@ -8777,7 +8777,7 @@
         <v/>
       </c>
       <c r="I168" t="str">
-        <v>cube-prima-008-main.jpg</v>
+        <v>jp-012-main.jpg</v>
       </c>
       <c r="J168" t="str">
         <v/>
@@ -8803,16 +8803,16 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B169" t="str">
-        <v>cube-prima-009</v>
+        <v>jp-013</v>
       </c>
       <c r="C169" t="str">
-        <v>CUBE-PRIMA-009</v>
+        <v>JP-013</v>
       </c>
       <c r="D169" t="str">
-        <v>Long Body</v>
+        <v>Wall Mixer 3 in 1 Jp</v>
       </c>
       <c r="E169" t="str">
         <v>Faucets</v>
@@ -8827,7 +8827,7 @@
         <v/>
       </c>
       <c r="I169" t="str">
-        <v>cube-prima-009-main.jpg</v>
+        <v>jp-013-main.jpg</v>
       </c>
       <c r="J169" t="str">
         <v/>
@@ -8853,16 +8853,16 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B170" t="str">
-        <v>cube-prima-010</v>
+        <v>jp-014</v>
       </c>
       <c r="C170" t="str">
-        <v>CUBE-PRIMA-010</v>
+        <v>JP-014</v>
       </c>
       <c r="D170" t="str">
-        <v>Nozzle Bib Cock</v>
+        <v>Wall Mixer Non Telephonic</v>
       </c>
       <c r="E170" t="str">
         <v>Faucets</v>
@@ -8877,7 +8877,7 @@
         <v/>
       </c>
       <c r="I170" t="str">
-        <v>cube-prima-010-main.jpg</v>
+        <v>jp-014-main.jpg</v>
       </c>
       <c r="J170" t="str">
         <v/>
@@ -8903,16 +8903,16 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B171" t="str">
-        <v>cube-prima-011</v>
+        <v>jp-015</v>
       </c>
       <c r="C171" t="str">
-        <v>CUBE-PRIMA-011</v>
+        <v>JP-015</v>
       </c>
       <c r="D171" t="str">
-        <v>Pillar Cock</v>
+        <v>Wall Mixer Telephonic Jp</v>
       </c>
       <c r="E171" t="str">
         <v>Faucets</v>
@@ -8927,7 +8927,7 @@
         <v/>
       </c>
       <c r="I171" t="str">
-        <v>cube-prima-011-main.jpg</v>
+        <v>jp-015-main.jpg</v>
       </c>
       <c r="J171" t="str">
         <v/>
@@ -8953,16 +8953,16 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Cube Prima</v>
+        <v>JP</v>
       </c>
       <c r="B172" t="str">
-        <v>cube-prima-012</v>
+        <v>jp-016</v>
       </c>
       <c r="C172" t="str">
-        <v>CUBE-PRIMA-012</v>
+        <v>JP-016</v>
       </c>
       <c r="D172" t="str">
-        <v>Pillar Cock Extended Body Casted One Piece</v>
+        <v>Wall Mixer with Crutch Jp</v>
       </c>
       <c r="E172" t="str">
         <v>Faucets</v>
@@ -8977,7 +8977,7 @@
         <v/>
       </c>
       <c r="I172" t="str">
-        <v>cube-prima-012-main.jpg</v>
+        <v>jp-016-main.jpg</v>
       </c>
       <c r="J172" t="str">
         <v/>
@@ -9003,16 +9003,16 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B173" t="str">
-        <v>cube-prima-013</v>
+        <v>premium-001</v>
       </c>
       <c r="C173" t="str">
-        <v>CUBE-PRIMA-013</v>
+        <v>PREMIUM-001</v>
       </c>
       <c r="D173" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>2 Way Bib Cock</v>
       </c>
       <c r="E173" t="str">
         <v>Faucets</v>
@@ -9027,7 +9027,7 @@
         <v/>
       </c>
       <c r="I173" t="str">
-        <v>cube-prima-013-main.jpg</v>
+        <v>premium-001-main.jpg</v>
       </c>
       <c r="J173" t="str">
         <v/>
@@ -9053,16 +9053,16 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B174" t="str">
-        <v>cube-prima-014</v>
+        <v>premium-002</v>
       </c>
       <c r="C174" t="str">
-        <v>CUBE-PRIMA-014</v>
+        <v>PREMIUM-002</v>
       </c>
       <c r="D174" t="str">
-        <v>Single Lever Basin Mixer Extended Body</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E174" t="str">
         <v>Faucets</v>
@@ -9077,7 +9077,7 @@
         <v/>
       </c>
       <c r="I174" t="str">
-        <v>cube-prima-014-main.jpg</v>
+        <v>premium-002-main.jpg</v>
       </c>
       <c r="J174" t="str">
         <v/>
@@ -9103,16 +9103,16 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B175" t="str">
-        <v>cube-prima-015</v>
+        <v>premium-003</v>
       </c>
       <c r="C175" t="str">
-        <v>CUBE-PRIMA-015</v>
+        <v>PREMIUM-003</v>
       </c>
       <c r="D175" t="str">
-        <v>Single Lever Concealed Basin Mixer Exposed Parts</v>
+        <v>Bib Cock</v>
       </c>
       <c r="E175" t="str">
         <v>Faucets</v>
@@ -9127,7 +9127,7 @@
         <v/>
       </c>
       <c r="I175" t="str">
-        <v>cube-prima-015-main.jpg</v>
+        <v>premium-003-main.jpg</v>
       </c>
       <c r="J175" t="str">
         <v/>
@@ -9153,16 +9153,16 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B176" t="str">
-        <v>cube-prima-016</v>
+        <v>premium-004</v>
       </c>
       <c r="C176" t="str">
-        <v>CUBE-PRIMA-016</v>
+        <v>PREMIUM-004</v>
       </c>
       <c r="D176" t="str">
-        <v>Single Lever Sink Mixer Angular</v>
+        <v>Center Hole Mixer</v>
       </c>
       <c r="E176" t="str">
         <v>Faucets</v>
@@ -9177,7 +9177,7 @@
         <v/>
       </c>
       <c r="I176" t="str">
-        <v>cube-prima-016-main.jpg</v>
+        <v>premium-004-main.jpg</v>
       </c>
       <c r="J176" t="str">
         <v/>
@@ -9203,19 +9203,19 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B177" t="str">
-        <v>cube-prima-017</v>
+        <v>premium-005</v>
       </c>
       <c r="C177" t="str">
-        <v>CUBE-PRIMA-017</v>
+        <v>PREMIUM-005</v>
       </c>
       <c r="D177" t="str">
-        <v>Single Lever Sink Mixer Side Handle</v>
+        <v>Concealed 15mm Heavy</v>
       </c>
       <c r="E177" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F177" t="str">
         <v/>
@@ -9227,7 +9227,7 @@
         <v/>
       </c>
       <c r="I177" t="str">
-        <v>cube-prima-017-main.jpg</v>
+        <v>premium-005-main.jpg</v>
       </c>
       <c r="J177" t="str">
         <v/>
@@ -9253,16 +9253,16 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B178" t="str">
-        <v>cube-prima-018</v>
+        <v>premium-006</v>
       </c>
       <c r="C178" t="str">
-        <v>CUBE-PRIMA-018</v>
+        <v>PREMIUM-006</v>
       </c>
       <c r="D178" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
+        <v>Flush Cock</v>
       </c>
       <c r="E178" t="str">
         <v>Faucets</v>
@@ -9277,7 +9277,7 @@
         <v/>
       </c>
       <c r="I178" t="str">
-        <v>cube-prima-018-main.jpg</v>
+        <v>premium-006-main.jpg</v>
       </c>
       <c r="J178" t="str">
         <v/>
@@ -9303,16 +9303,16 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B179" t="str">
-        <v>cube-prima-019</v>
+        <v>premium-007</v>
       </c>
       <c r="C179" t="str">
-        <v>CUBE-PRIMA-019</v>
+        <v>PREMIUM-007</v>
       </c>
       <c r="D179" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted Cube</v>
+        <v>Long Body</v>
       </c>
       <c r="E179" t="str">
         <v>Faucets</v>
@@ -9327,7 +9327,7 @@
         <v/>
       </c>
       <c r="I179" t="str">
-        <v>cube-prima-019-main.jpg</v>
+        <v>premium-007-main.jpg</v>
       </c>
       <c r="J179" t="str">
         <v/>
@@ -9353,16 +9353,16 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B180" t="str">
-        <v>cube-prima-020</v>
+        <v>premium-008</v>
       </c>
       <c r="C180" t="str">
-        <v>CUBE-PRIMA-020</v>
+        <v>PREMIUM-008</v>
       </c>
       <c r="D180" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Nozzle Bib Cock</v>
       </c>
       <c r="E180" t="str">
         <v>Faucets</v>
@@ -9377,7 +9377,7 @@
         <v/>
       </c>
       <c r="I180" t="str">
-        <v>cube-prima-020-main.jpg</v>
+        <v>premium-008-main.jpg</v>
       </c>
       <c r="J180" t="str">
         <v/>
@@ -9403,16 +9403,16 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B181" t="str">
-        <v>cube-prima-021</v>
+        <v>premium-009</v>
       </c>
       <c r="C181" t="str">
-        <v>CUBE-PRIMA-021</v>
+        <v>PREMIUM-009</v>
       </c>
       <c r="D181" t="str">
-        <v>Sink Cock</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E181" t="str">
         <v>Faucets</v>
@@ -9427,7 +9427,7 @@
         <v/>
       </c>
       <c r="I181" t="str">
-        <v>cube-prima-021-main.jpg</v>
+        <v>premium-009-main.jpg</v>
       </c>
       <c r="J181" t="str">
         <v/>
@@ -9453,16 +9453,16 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B182" t="str">
-        <v>cube-prima-022</v>
+        <v>premium-010</v>
       </c>
       <c r="C182" t="str">
-        <v>CUBE-PRIMA-022</v>
+        <v>PREMIUM-010</v>
       </c>
       <c r="D182" t="str">
-        <v>Sink Mixer</v>
+        <v>Sink Cock</v>
       </c>
       <c r="E182" t="str">
         <v>Faucets</v>
@@ -9477,7 +9477,7 @@
         <v/>
       </c>
       <c r="I182" t="str">
-        <v>cube-prima-022-main.jpg</v>
+        <v>premium-010-main.jpg</v>
       </c>
       <c r="J182" t="str">
         <v/>
@@ -9503,19 +9503,19 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B183" t="str">
-        <v>cube-prima-023</v>
+        <v>premium-011</v>
       </c>
       <c r="C183" t="str">
-        <v>CUBE-PRIMA-023</v>
+        <v>PREMIUM-011</v>
       </c>
       <c r="D183" t="str">
-        <v>Swarn Neck</v>
+        <v>Sink Mixer</v>
       </c>
       <c r="E183" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F183" t="str">
         <v/>
@@ -9527,7 +9527,7 @@
         <v/>
       </c>
       <c r="I183" t="str">
-        <v>cube-prima-023-main.jpg</v>
+        <v>premium-011-main.jpg</v>
       </c>
       <c r="J183" t="str">
         <v/>
@@ -9553,16 +9553,16 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B184" t="str">
-        <v>cube-prima-024</v>
+        <v>premium-012</v>
       </c>
       <c r="C184" t="str">
-        <v>CUBE-PRIMA-024</v>
+        <v>PREMIUM-012</v>
       </c>
       <c r="D184" t="str">
-        <v>Wall Mixer Non Telephonic</v>
+        <v>Swan Neck</v>
       </c>
       <c r="E184" t="str">
         <v>Faucets</v>
@@ -9577,7 +9577,7 @@
         <v/>
       </c>
       <c r="I184" t="str">
-        <v>cube-prima-024-main.jpg</v>
+        <v>premium-012-main.jpg</v>
       </c>
       <c r="J184" t="str">
         <v/>
@@ -9603,16 +9603,16 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B185" t="str">
-        <v>cube-prima-025</v>
+        <v>premium-013</v>
       </c>
       <c r="C185" t="str">
-        <v>CUBE-PRIMA-025</v>
+        <v>PREMIUM-013</v>
       </c>
       <c r="D185" t="str">
-        <v>Wall Mixer with Bend</v>
+        <v>Two Way Angle Valve</v>
       </c>
       <c r="E185" t="str">
         <v>Faucets</v>
@@ -9627,7 +9627,7 @@
         <v/>
       </c>
       <c r="I185" t="str">
-        <v>cube-prima-025-main.jpg</v>
+        <v>premium-013-main.jpg</v>
       </c>
       <c r="J185" t="str">
         <v/>
@@ -9653,16 +9653,16 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B186" t="str">
-        <v>cube-prima-026</v>
+        <v>premium-014</v>
       </c>
       <c r="C186" t="str">
-        <v>CUBE-PRIMA-026</v>
+        <v>PREMIUM-014</v>
       </c>
       <c r="D186" t="str">
-        <v>Wall Mixer with Bend 3-in-1</v>
+        <v>Wall Mixer 3 in</v>
       </c>
       <c r="E186" t="str">
         <v>Faucets</v>
@@ -9677,7 +9677,7 @@
         <v/>
       </c>
       <c r="I186" t="str">
-        <v>cube-prima-026-main.jpg</v>
+        <v>premium-014-main.jpg</v>
       </c>
       <c r="J186" t="str">
         <v/>
@@ -9703,16 +9703,16 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Cube Prima</v>
+        <v>Premium</v>
       </c>
       <c r="B187" t="str">
-        <v>cube-prima-027</v>
+        <v>premium-015</v>
       </c>
       <c r="C187" t="str">
-        <v>CUBE-PRIMA-027</v>
+        <v>PREMIUM-015</v>
       </c>
       <c r="D187" t="str">
-        <v>Wall Mixer with Crutch</v>
+        <v>Wall Mixer Non Telephonic</v>
       </c>
       <c r="E187" t="str">
         <v>Faucets</v>
@@ -9727,7 +9727,7 @@
         <v/>
       </c>
       <c r="I187" t="str">
-        <v>cube-prima-027-main.jpg</v>
+        <v>premium-015-main.jpg</v>
       </c>
       <c r="J187" t="str">
         <v/>
@@ -9753,16 +9753,16 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fuzone</v>
+        <v>Premium</v>
       </c>
       <c r="B188" t="str">
-        <v>fuzone-001</v>
+        <v>premium-016</v>
       </c>
       <c r="C188" t="str">
-        <v>FUZONE-001</v>
+        <v>PREMIUM-016</v>
       </c>
       <c r="D188" t="str">
-        <v>Angle Valve</v>
+        <v>Wall Mixer with Bend</v>
       </c>
       <c r="E188" t="str">
         <v>Faucets</v>
@@ -9777,7 +9777,7 @@
         <v/>
       </c>
       <c r="I188" t="str">
-        <v>fuzone-001-main.jpg</v>
+        <v>premium-016-main.jpg</v>
       </c>
       <c r="J188" t="str">
         <v/>
@@ -9803,16 +9803,16 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Fuzone</v>
+        <v>Premium</v>
       </c>
       <c r="B189" t="str">
-        <v>fuzone-002</v>
+        <v>premium-017</v>
       </c>
       <c r="C189" t="str">
-        <v>FUZONE-002</v>
+        <v>PREMIUM-017</v>
       </c>
       <c r="D189" t="str">
-        <v>Bath Tub Spout</v>
+        <v>Wall Mixer with Crutch</v>
       </c>
       <c r="E189" t="str">
         <v>Faucets</v>
@@ -9827,7 +9827,7 @@
         <v/>
       </c>
       <c r="I189" t="str">
-        <v>fuzone-002-main.jpg</v>
+        <v>premium-017-main.jpg</v>
       </c>
       <c r="J189" t="str">
         <v/>
@@ -9853,16 +9853,16 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B190" t="str">
-        <v>fuzone-003</v>
+        <v>para-collection-001</v>
       </c>
       <c r="C190" t="str">
-        <v>FUZONE-003</v>
+        <v>PARA-COLLECTION-001</v>
       </c>
       <c r="D190" t="str">
-        <v>Bib Cock</v>
+        <v>Angle Valve Para</v>
       </c>
       <c r="E190" t="str">
         <v>Faucets</v>
@@ -9877,7 +9877,7 @@
         <v/>
       </c>
       <c r="I190" t="str">
-        <v>fuzone-003-main.jpg</v>
+        <v>para-collection-001-main.png</v>
       </c>
       <c r="J190" t="str">
         <v/>
@@ -9903,16 +9903,16 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B191" t="str">
-        <v>fuzone-004</v>
+        <v>para-collection-002</v>
       </c>
       <c r="C191" t="str">
-        <v>FUZONE-004</v>
+        <v>PARA-COLLECTION-002</v>
       </c>
       <c r="D191" t="str">
-        <v>Button Spout</v>
+        <v>Button Spout Para</v>
       </c>
       <c r="E191" t="str">
         <v>Faucets</v>
@@ -9927,7 +9927,7 @@
         <v/>
       </c>
       <c r="I191" t="str">
-        <v>fuzone-004-main.jpg</v>
+        <v>para-collection-002-main.png</v>
       </c>
       <c r="J191" t="str">
         <v/>
@@ -9953,16 +9953,16 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B192" t="str">
-        <v>fuzone-005</v>
+        <v>para-collection-003</v>
       </c>
       <c r="C192" t="str">
-        <v>FUZONE-005</v>
+        <v>PARA-COLLECTION-003</v>
       </c>
       <c r="D192" t="str">
-        <v>Center Hole Mixer</v>
+        <v>Long Body Para</v>
       </c>
       <c r="E192" t="str">
         <v>Faucets</v>
@@ -9977,7 +9977,7 @@
         <v/>
       </c>
       <c r="I192" t="str">
-        <v>fuzone-005-main.jpg</v>
+        <v>para-collection-003-main.png</v>
       </c>
       <c r="J192" t="str">
         <v/>
@@ -10003,16 +10003,16 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B193" t="str">
-        <v>fuzone-006</v>
+        <v>para-collection-004</v>
       </c>
       <c r="C193" t="str">
-        <v>FUZONE-006</v>
+        <v>PARA-COLLECTION-004</v>
       </c>
       <c r="D193" t="str">
-        <v>Long Body</v>
+        <v>Nozzle BIB Cock Para</v>
       </c>
       <c r="E193" t="str">
         <v>Faucets</v>
@@ -10027,7 +10027,7 @@
         <v/>
       </c>
       <c r="I193" t="str">
-        <v>fuzone-006-main.jpg</v>
+        <v>para-collection-004-main.png</v>
       </c>
       <c r="J193" t="str">
         <v/>
@@ -10053,16 +10053,16 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B194" t="str">
-        <v>fuzone-007</v>
+        <v>para-collection-005</v>
       </c>
       <c r="C194" t="str">
-        <v>FUZONE-007</v>
+        <v>PARA-COLLECTION-005</v>
       </c>
       <c r="D194" t="str">
-        <v>New Sink Mixer Wall Mounted Angular Spout Fuzone</v>
+        <v>Pilla Cock Extended Body Para</v>
       </c>
       <c r="E194" t="str">
         <v>Faucets</v>
@@ -10077,7 +10077,7 @@
         <v/>
       </c>
       <c r="I194" t="str">
-        <v>fuzone-007-main.jpg</v>
+        <v>para-collection-005-main.png</v>
       </c>
       <c r="J194" t="str">
         <v/>
@@ -10103,16 +10103,16 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B195" t="str">
-        <v>fuzone-008</v>
+        <v>para-collection-006</v>
       </c>
       <c r="C195" t="str">
-        <v>FUZONE-008</v>
+        <v>PARA-COLLECTION-006</v>
       </c>
       <c r="D195" t="str">
-        <v>Nozzle BIB Cock</v>
+        <v>Pillar Cock Para</v>
       </c>
       <c r="E195" t="str">
         <v>Faucets</v>
@@ -10127,7 +10127,7 @@
         <v/>
       </c>
       <c r="I195" t="str">
-        <v>fuzone-008-main.jpg</v>
+        <v>para-collection-006-main.png</v>
       </c>
       <c r="J195" t="str">
         <v/>
@@ -10153,16 +10153,16 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B196" t="str">
-        <v>fuzone-009</v>
+        <v>para-collection-007</v>
       </c>
       <c r="C196" t="str">
-        <v>FUZONE-009</v>
+        <v>PARA-COLLECTION-007</v>
       </c>
       <c r="D196" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v>Plain Spout Para</v>
       </c>
       <c r="E196" t="str">
         <v>Faucets</v>
@@ -10177,7 +10177,7 @@
         <v/>
       </c>
       <c r="I196" t="str">
-        <v>fuzone-009-main.jpg</v>
+        <v>para-collection-007-main.png</v>
       </c>
       <c r="J196" t="str">
         <v/>
@@ -10203,16 +10203,16 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B197" t="str">
-        <v>fuzone-010</v>
+        <v>para-collection-008</v>
       </c>
       <c r="C197" t="str">
-        <v>FUZONE-010</v>
+        <v>PARA-COLLECTION-008</v>
       </c>
       <c r="D197" t="str">
-        <v>Single Lever Concealed Basin Mixer Upper Parts</v>
+        <v>Single Lever Basin Mixer Extended Body Para</v>
       </c>
       <c r="E197" t="str">
         <v>Faucets</v>
@@ -10227,7 +10227,7 @@
         <v/>
       </c>
       <c r="I197" t="str">
-        <v>fuzone-010-main.jpg</v>
+        <v>para-collection-008-main.png</v>
       </c>
       <c r="J197" t="str">
         <v/>
@@ -10253,16 +10253,16 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B198" t="str">
-        <v>fuzone-011</v>
+        <v>para-collection-009</v>
       </c>
       <c r="C198" t="str">
-        <v>FUZONE-011</v>
+        <v>PARA-COLLECTION-009</v>
       </c>
       <c r="D198" t="str">
-        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
+        <v>Single Lever Basin Mixer Para</v>
       </c>
       <c r="E198" t="str">
         <v>Faucets</v>
@@ -10277,7 +10277,7 @@
         <v/>
       </c>
       <c r="I198" t="str">
-        <v>fuzone-011-main.jpg</v>
+        <v>para-collection-009-main.png</v>
       </c>
       <c r="J198" t="str">
         <v/>
@@ -10303,16 +10303,16 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B199" t="str">
-        <v>fuzone-012</v>
+        <v>para-collection-010</v>
       </c>
       <c r="C199" t="str">
-        <v>FUZONE-012</v>
+        <v>PARA-COLLECTION-010</v>
       </c>
       <c r="D199" t="str">
-        <v>Single Lever Exposed Parts Kit of High Flow Diverter</v>
+        <v>Single Lever Concealed Basin Mixer Para</v>
       </c>
       <c r="E199" t="str">
         <v>Faucets</v>
@@ -10327,7 +10327,7 @@
         <v/>
       </c>
       <c r="I199" t="str">
-        <v>fuzone-012-main.jpg</v>
+        <v>para-collection-010-main.png</v>
       </c>
       <c r="J199" t="str">
         <v/>
@@ -10353,16 +10353,16 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B200" t="str">
-        <v>fuzone-013</v>
+        <v>para-collection-011</v>
       </c>
       <c r="C200" t="str">
-        <v>FUZONE-013</v>
+        <v>PARA-COLLECTION-011</v>
       </c>
       <c r="D200" t="str">
-        <v>Single Lever Mixer All Boy</v>
+        <v>Single Lever Concealed Diverter</v>
       </c>
       <c r="E200" t="str">
         <v>Faucets</v>
@@ -10377,7 +10377,7 @@
         <v/>
       </c>
       <c r="I200" t="str">
-        <v>fuzone-013-main.jpg</v>
+        <v>para-collection-011-main.png</v>
       </c>
       <c r="J200" t="str">
         <v/>
@@ -10403,16 +10403,16 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B201" t="str">
-        <v>fuzone-014</v>
+        <v>para-collection-012</v>
       </c>
       <c r="C201" t="str">
-        <v>FUZONE-014</v>
+        <v>PARA-COLLECTION-012</v>
       </c>
       <c r="D201" t="str">
-        <v>Single Lever Sink Mixer Angular</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E201" t="str">
         <v>Faucets</v>
@@ -10427,7 +10427,7 @@
         <v/>
       </c>
       <c r="I201" t="str">
-        <v>fuzone-014-main.jpg</v>
+        <v>para-collection-012-main.png</v>
       </c>
       <c r="J201" t="str">
         <v/>
@@ -10453,16 +10453,16 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B202" t="str">
-        <v>fuzone-015</v>
+        <v>para-collection-013</v>
       </c>
       <c r="C202" t="str">
-        <v>FUZONE-015</v>
+        <v>PARA-COLLECTION-013</v>
       </c>
       <c r="D202" t="str">
-        <v>Single Lever Sink Mixer Side Handle</v>
+        <v>Single Lever Wall Mixer with Bend</v>
       </c>
       <c r="E202" t="str">
         <v>Faucets</v>
@@ -10477,7 +10477,7 @@
         <v/>
       </c>
       <c r="I202" t="str">
-        <v>fuzone-015-main.jpg</v>
+        <v>para-collection-013-main.png</v>
       </c>
       <c r="J202" t="str">
         <v/>
@@ -10503,16 +10503,16 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B203" t="str">
-        <v>fuzone-016</v>
+        <v>para-collection-014</v>
       </c>
       <c r="C203" t="str">
-        <v>FUZONE-016</v>
+        <v>PARA-COLLECTION-014</v>
       </c>
       <c r="D203" t="str">
-        <v>Single Lever Sink Mixer Wall Mounted</v>
+        <v>Table Mounted Single Lever Kitchen Mixer Angular Spout</v>
       </c>
       <c r="E203" t="str">
         <v>Faucets</v>
@@ -10527,7 +10527,7 @@
         <v/>
       </c>
       <c r="I203" t="str">
-        <v>fuzone-016-main.jpg</v>
+        <v>para-collection-014-main.png</v>
       </c>
       <c r="J203" t="str">
         <v/>
@@ -10553,16 +10553,16 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B204" t="str">
-        <v>fuzone-017</v>
+        <v>para-collection-015</v>
       </c>
       <c r="C204" t="str">
-        <v>FUZONE-017</v>
+        <v>PARA-COLLECTION-015</v>
       </c>
       <c r="D204" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>Table Mounted Single Lever Kitchen Mixer Round Spout</v>
       </c>
       <c r="E204" t="str">
         <v>Faucets</v>
@@ -10577,7 +10577,7 @@
         <v/>
       </c>
       <c r="I204" t="str">
-        <v>fuzone-017-main.jpg</v>
+        <v>para-collection-015-main.png</v>
       </c>
       <c r="J204" t="str">
         <v/>
@@ -10603,16 +10603,16 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B205" t="str">
-        <v>fuzone-018</v>
+        <v>para-collection-016</v>
       </c>
       <c r="C205" t="str">
-        <v>FUZONE-018</v>
+        <v>PARA-COLLECTION-016</v>
       </c>
       <c r="D205" t="str">
-        <v>Sink Cock</v>
+        <v>Wall Mixer with Bend Para</v>
       </c>
       <c r="E205" t="str">
         <v>Faucets</v>
@@ -10627,7 +10627,7 @@
         <v/>
       </c>
       <c r="I205" t="str">
-        <v>fuzone-018-main.jpg</v>
+        <v>para-collection-016-main.png</v>
       </c>
       <c r="J205" t="str">
         <v/>
@@ -10653,16 +10653,16 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B206" t="str">
-        <v>fuzone-019</v>
+        <v>para-collection-017</v>
       </c>
       <c r="C206" t="str">
-        <v>FUZONE-019</v>
+        <v>PARA-COLLECTION-017</v>
       </c>
       <c r="D206" t="str">
-        <v>Sink Mixer</v>
+        <v>Wall Mixer with Crutch Para</v>
       </c>
       <c r="E206" t="str">
         <v>Faucets</v>
@@ -10677,7 +10677,7 @@
         <v/>
       </c>
       <c r="I206" t="str">
-        <v>fuzone-019-main.jpg</v>
+        <v>para-collection-017-main.png</v>
       </c>
       <c r="J206" t="str">
         <v/>
@@ -10703,16 +10703,16 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B207" t="str">
-        <v>fuzone-020</v>
+        <v>para-collection-018</v>
       </c>
       <c r="C207" t="str">
-        <v>FUZONE-020</v>
+        <v>PARA-COLLECTION-018</v>
       </c>
       <c r="D207" t="str">
-        <v>Sink Mixer Pillar Mounted Fuzone</v>
+        <v>Wall Mounted Single Lever Kitchen Mixer Angular Spout</v>
       </c>
       <c r="E207" t="str">
         <v>Faucets</v>
@@ -10727,7 +10727,7 @@
         <v/>
       </c>
       <c r="I207" t="str">
-        <v>fuzone-020-main.jpg</v>
+        <v>para-collection-018-main.png</v>
       </c>
       <c r="J207" t="str">
         <v/>
@@ -10753,19 +10753,19 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B208" t="str">
-        <v>fuzone-021</v>
+        <v>para-collection-019</v>
       </c>
       <c r="C208" t="str">
-        <v>FUZONE-021</v>
+        <v>PARA-COLLECTION-019</v>
       </c>
       <c r="D208" t="str">
-        <v>Swarn Neck</v>
+        <v>Wall Mounted Single Lever Kitchen Mixer Regular Spout</v>
       </c>
       <c r="E208" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F208" t="str">
         <v/>
@@ -10777,7 +10777,7 @@
         <v/>
       </c>
       <c r="I208" t="str">
-        <v>fuzone-021-main.jpg</v>
+        <v>para-collection-019-main.png</v>
       </c>
       <c r="J208" t="str">
         <v/>
@@ -10803,16 +10803,16 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Fuzone</v>
+        <v>Para Collection</v>
       </c>
       <c r="B209" t="str">
-        <v>fuzone-022</v>
+        <v>para-collection-020</v>
       </c>
       <c r="C209" t="str">
-        <v>FUZONE-022</v>
+        <v>PARA-COLLECTION-020</v>
       </c>
       <c r="D209" t="str">
-        <v>TWO WAY Angle Valve</v>
+        <v>Wall Mounted Single Lever Kitchen Mixer Round Spout</v>
       </c>
       <c r="E209" t="str">
         <v>Faucets</v>
@@ -10827,7 +10827,7 @@
         <v/>
       </c>
       <c r="I209" t="str">
-        <v>fuzone-022-main.jpg</v>
+        <v>para-collection-020-main.png</v>
       </c>
       <c r="J209" t="str">
         <v/>
@@ -10853,19 +10853,19 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Fuzone</v>
+        <v>Allied</v>
       </c>
       <c r="B210" t="str">
-        <v>fuzone-023</v>
+        <v>allied-001</v>
       </c>
       <c r="C210" t="str">
-        <v>FUZONE-023</v>
+        <v>ALLIED-001</v>
       </c>
       <c r="D210" t="str">
-        <v>TWO WAY BIB Cock</v>
+        <v>Abs Round Hand Shower with Brass Tube</v>
       </c>
       <c r="E210" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F210" t="str">
         <v/>
@@ -10877,7 +10877,7 @@
         <v/>
       </c>
       <c r="I210" t="str">
-        <v>fuzone-023-main.jpg</v>
+        <v>allied-001-main.jpg</v>
       </c>
       <c r="J210" t="str">
         <v/>
@@ -10903,19 +10903,19 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Fuzone</v>
+        <v>Allied</v>
       </c>
       <c r="B211" t="str">
-        <v>fuzone-024</v>
+        <v>allied-002</v>
       </c>
       <c r="C211" t="str">
-        <v>FUZONE-024</v>
+        <v>ALLIED-002</v>
       </c>
       <c r="D211" t="str">
-        <v>Wall Mixer Button Spout with Bend</v>
+        <v>Abs Square Hand Shower with Brass Tube</v>
       </c>
       <c r="E211" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F211" t="str">
         <v/>
@@ -10927,7 +10927,7 @@
         <v/>
       </c>
       <c r="I211" t="str">
-        <v>fuzone-024-main.jpg</v>
+        <v>allied-002-main.jpg</v>
       </c>
       <c r="J211" t="str">
         <v/>
@@ -10953,19 +10953,19 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Fuzone</v>
+        <v>Allied</v>
       </c>
       <c r="B212" t="str">
-        <v>fuzone-025</v>
+        <v>allied-003</v>
       </c>
       <c r="C212" t="str">
-        <v>FUZONE-025</v>
+        <v>ALLIED-003</v>
       </c>
       <c r="D212" t="str">
-        <v>Wall Mixer NON Telephonic</v>
+        <v>Aliva Maze Over Head Shower</v>
       </c>
       <c r="E212" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F212" t="str">
         <v/>
@@ -10977,7 +10977,7 @@
         <v/>
       </c>
       <c r="I212" t="str">
-        <v>fuzone-025-main.jpg</v>
+        <v>allied-003-main.png</v>
       </c>
       <c r="J212" t="str">
         <v/>
@@ -11003,19 +11003,19 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Fuzone</v>
+        <v>Allied</v>
       </c>
       <c r="B213" t="str">
-        <v>fuzone-026</v>
+        <v>allied-004</v>
       </c>
       <c r="C213" t="str">
-        <v>FUZONE-026</v>
+        <v>ALLIED-004</v>
       </c>
       <c r="D213" t="str">
-        <v>Wall Mixer with Bend</v>
+        <v>Bottle Trap Full Brass</v>
       </c>
       <c r="E213" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F213" t="str">
         <v/>
@@ -11027,7 +11027,7 @@
         <v/>
       </c>
       <c r="I213" t="str">
-        <v>fuzone-026-main.jpg</v>
+        <v>allied-004-main.jpg</v>
       </c>
       <c r="J213" t="str">
         <v/>
@@ -11053,19 +11053,19 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Fuzone</v>
+        <v>Allied</v>
       </c>
       <c r="B214" t="str">
-        <v>fuzone-027</v>
+        <v>allied-005</v>
       </c>
       <c r="C214" t="str">
-        <v>FUZONE-027</v>
+        <v>ALLIED-005</v>
       </c>
       <c r="D214" t="str">
-        <v>Wall Mixer with Crutch</v>
+        <v>Brass Health Faucet Round Shape with 1.5 Meter Brass Tube</v>
       </c>
       <c r="E214" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F214" t="str">
         <v/>
@@ -11077,7 +11077,7 @@
         <v/>
       </c>
       <c r="I214" t="str">
-        <v>fuzone-027-main.jpg</v>
+        <v>allied-005-main.jpg</v>
       </c>
       <c r="J214" t="str">
         <v/>
@@ -11103,19 +11103,19 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B215" t="str">
-        <v>jp-001</v>
+        <v>allied-006</v>
       </c>
       <c r="C215" t="str">
-        <v>JP-001</v>
+        <v>ALLIED-006</v>
       </c>
       <c r="D215" t="str">
-        <v>Angle Valve</v>
+        <v>Brass Health Faucet Sqaure with 1.5 Meter Brass Tube</v>
       </c>
       <c r="E215" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F215" t="str">
         <v/>
@@ -11127,7 +11127,7 @@
         <v/>
       </c>
       <c r="I215" t="str">
-        <v>jp-001-main.jpg</v>
+        <v>allied-006-main.jpg</v>
       </c>
       <c r="J215" t="str">
         <v/>
@@ -11153,19 +11153,19 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B216" t="str">
-        <v>jp-002</v>
+        <v>allied-007</v>
       </c>
       <c r="C216" t="str">
-        <v>JP-002</v>
+        <v>ALLIED-007</v>
       </c>
       <c r="D216" t="str">
-        <v>Bib Cock</v>
+        <v>Concealed Body</v>
       </c>
       <c r="E216" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F216" t="str">
         <v/>
@@ -11177,7 +11177,7 @@
         <v/>
       </c>
       <c r="I216" t="str">
-        <v>jp-002-main.jpg</v>
+        <v>allied-007-main.jpg</v>
       </c>
       <c r="J216" t="str">
         <v/>
@@ -11203,19 +11203,19 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B217" t="str">
-        <v>jp-003</v>
+        <v>allied-008</v>
       </c>
       <c r="C217" t="str">
-        <v>JP-003</v>
+        <v>ALLIED-008</v>
       </c>
       <c r="D217" t="str">
-        <v>Bib Cock Long Body</v>
+        <v>Concealed Body 15mm</v>
       </c>
       <c r="E217" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F217" t="str">
         <v/>
@@ -11227,7 +11227,7 @@
         <v/>
       </c>
       <c r="I217" t="str">
-        <v>jp-003-main.jpg</v>
+        <v>allied-008-main.jpg</v>
       </c>
       <c r="J217" t="str">
         <v/>
@@ -11253,19 +11253,19 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B218" t="str">
-        <v>jp-004</v>
+        <v>allied-009</v>
       </c>
       <c r="C218" t="str">
-        <v>JP-004</v>
+        <v>ALLIED-009</v>
       </c>
       <c r="D218" t="str">
-        <v>Center Hole Mixer</v>
+        <v>Cuba Hand Shower with Tube</v>
       </c>
       <c r="E218" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F218" t="str">
         <v/>
@@ -11277,7 +11277,7 @@
         <v/>
       </c>
       <c r="I218" t="str">
-        <v>jp-004-main.jpg</v>
+        <v>allied-009-main.png</v>
       </c>
       <c r="J218" t="str">
         <v/>
@@ -11303,19 +11303,19 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B219" t="str">
-        <v>jp-005</v>
+        <v>allied-010</v>
       </c>
       <c r="C219" t="str">
-        <v>JP-005</v>
+        <v>ALLIED-010</v>
       </c>
       <c r="D219" t="str">
-        <v>Concealed Stop Cock</v>
+        <v>Donut Hand Shower with Tube</v>
       </c>
       <c r="E219" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F219" t="str">
         <v/>
@@ -11327,7 +11327,7 @@
         <v/>
       </c>
       <c r="I219" t="str">
-        <v>jp-005-main.jpg</v>
+        <v>allied-010-main.png</v>
       </c>
       <c r="J219" t="str">
         <v/>
@@ -11353,19 +11353,19 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B220" t="str">
-        <v>jp-006</v>
+        <v>allied-011</v>
       </c>
       <c r="C220" t="str">
-        <v>JP-006</v>
+        <v>ALLIED-011</v>
       </c>
       <c r="D220" t="str">
-        <v>Nozzle Bib Cock</v>
+        <v>Donut Shower Head with ARM</v>
       </c>
       <c r="E220" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F220" t="str">
         <v/>
@@ -11377,7 +11377,7 @@
         <v/>
       </c>
       <c r="I220" t="str">
-        <v>jp-006-main.jpg</v>
+        <v>allied-011-main.png</v>
       </c>
       <c r="J220" t="str">
         <v/>
@@ -11403,19 +11403,19 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B221" t="str">
-        <v>jp-007</v>
+        <v>allied-012</v>
       </c>
       <c r="C221" t="str">
-        <v>JP-007</v>
+        <v>ALLIED-012</v>
       </c>
       <c r="D221" t="str">
-        <v>Pillar Cock</v>
+        <v>Glory Hand Shower with Tube</v>
       </c>
       <c r="E221" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F221" t="str">
         <v/>
@@ -11427,7 +11427,7 @@
         <v/>
       </c>
       <c r="I221" t="str">
-        <v>jp-007-main.jpg</v>
+        <v>allied-012-main.png</v>
       </c>
       <c r="J221" t="str">
         <v/>
@@ -11453,19 +11453,19 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B222" t="str">
-        <v>jp-008</v>
+        <v>allied-013</v>
       </c>
       <c r="C222" t="str">
-        <v>JP-008</v>
+        <v>ALLIED-013</v>
       </c>
       <c r="D222" t="str">
-        <v>Sink Cock</v>
+        <v>Health Faucet with Tube</v>
       </c>
       <c r="E222" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F222" t="str">
         <v/>
@@ -11477,7 +11477,7 @@
         <v/>
       </c>
       <c r="I222" t="str">
-        <v>jp-008-main.jpg</v>
+        <v>allied-013-main.png</v>
       </c>
       <c r="J222" t="str">
         <v/>
@@ -11503,16 +11503,16 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B223" t="str">
-        <v>jp-009</v>
+        <v>allied-014</v>
       </c>
       <c r="C223" t="str">
-        <v>JP-009</v>
+        <v>ALLIED-014</v>
       </c>
       <c r="D223" t="str">
-        <v>Sink Mixer</v>
+        <v>High Flow Diverter Body Three in Let</v>
       </c>
       <c r="E223" t="str">
         <v>Faucets</v>
@@ -11527,7 +11527,7 @@
         <v/>
       </c>
       <c r="I223" t="str">
-        <v>jp-009-main.jpg</v>
+        <v>allied-014-main.jpg</v>
       </c>
       <c r="J223" t="str">
         <v/>
@@ -11553,19 +11553,19 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B224" t="str">
-        <v>jp-010</v>
+        <v>allied-015</v>
       </c>
       <c r="C224" t="str">
-        <v>JP-010</v>
+        <v>ALLIED-015</v>
       </c>
       <c r="D224" t="str">
-        <v>Swan Neck</v>
+        <v>Maze Square Shower Head</v>
       </c>
       <c r="E224" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F224" t="str">
         <v/>
@@ -11577,7 +11577,7 @@
         <v/>
       </c>
       <c r="I224" t="str">
-        <v>jp-010-main.jpg</v>
+        <v>allied-015-main.png</v>
       </c>
       <c r="J224" t="str">
         <v/>
@@ -11603,19 +11603,19 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B225" t="str">
-        <v>jp-011</v>
+        <v>allied-016</v>
       </c>
       <c r="C225" t="str">
-        <v>JP-011</v>
+        <v>ALLIED-016</v>
       </c>
       <c r="D225" t="str">
-        <v>Two Way Angle Valve</v>
+        <v>Oval Maze Overhead Shower</v>
       </c>
       <c r="E225" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F225" t="str">
         <v/>
@@ -11627,7 +11627,7 @@
         <v/>
       </c>
       <c r="I225" t="str">
-        <v>jp-011-main.jpg</v>
+        <v>allied-016-main.png</v>
       </c>
       <c r="J225" t="str">
         <v/>
@@ -11653,16 +11653,16 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B226" t="str">
-        <v>jp-012</v>
+        <v>allied-017</v>
       </c>
       <c r="C226" t="str">
-        <v>JP-012</v>
+        <v>ALLIED-017</v>
       </c>
       <c r="D226" t="str">
-        <v>Two Way Bib Cock</v>
+        <v>Pressmatic Pillar Cock</v>
       </c>
       <c r="E226" t="str">
         <v>Faucets</v>
@@ -11677,7 +11677,7 @@
         <v/>
       </c>
       <c r="I226" t="str">
-        <v>jp-012-main.jpg</v>
+        <v>allied-017-main.png</v>
       </c>
       <c r="J226" t="str">
         <v/>
@@ -11703,19 +11703,19 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B227" t="str">
-        <v>jp-013</v>
+        <v>allied-018</v>
       </c>
       <c r="C227" t="str">
-        <v>JP-013</v>
+        <v>ALLIED-018</v>
       </c>
       <c r="D227" t="str">
-        <v>Wall Mixer 3 in 1 Jp</v>
+        <v>Round 4 Inch Shower Head with ARM</v>
       </c>
       <c r="E227" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F227" t="str">
         <v/>
@@ -11727,7 +11727,7 @@
         <v/>
       </c>
       <c r="I227" t="str">
-        <v>jp-013-main.jpg</v>
+        <v>allied-018-main.png</v>
       </c>
       <c r="J227" t="str">
         <v/>
@@ -11753,19 +11753,19 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B228" t="str">
-        <v>jp-014</v>
+        <v>allied-019</v>
       </c>
       <c r="C228" t="str">
-        <v>JP-014</v>
+        <v>ALLIED-019</v>
       </c>
       <c r="D228" t="str">
-        <v>Wall Mixer Non Telephonic</v>
+        <v>Round Hand Shower with Tube</v>
       </c>
       <c r="E228" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F228" t="str">
         <v/>
@@ -11777,7 +11777,7 @@
         <v/>
       </c>
       <c r="I228" t="str">
-        <v>jp-014-main.jpg</v>
+        <v>allied-019-main.png</v>
       </c>
       <c r="J228" t="str">
         <v/>
@@ -11803,19 +11803,19 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B229" t="str">
-        <v>jp-015</v>
+        <v>allied-020</v>
       </c>
       <c r="C229" t="str">
-        <v>JP-015</v>
+        <v>ALLIED-020</v>
       </c>
       <c r="D229" t="str">
-        <v>Wall Mixer Telephonic Jp</v>
+        <v>Shower Head Round Maze</v>
       </c>
       <c r="E229" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F229" t="str">
         <v/>
@@ -11827,7 +11827,7 @@
         <v/>
       </c>
       <c r="I229" t="str">
-        <v>jp-015-main.jpg</v>
+        <v>allied-020-main.png</v>
       </c>
       <c r="J229" t="str">
         <v/>
@@ -11853,19 +11853,19 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="B230" t="str">
-        <v>jp-016</v>
+        <v>allied-021</v>
       </c>
       <c r="C230" t="str">
-        <v>JP-016</v>
+        <v>ALLIED-021</v>
       </c>
       <c r="D230" t="str">
-        <v>Wall Mixer with Crutch Jp</v>
+        <v>Shower Rail</v>
       </c>
       <c r="E230" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F230" t="str">
         <v/>
@@ -11877,7 +11877,7 @@
         <v/>
       </c>
       <c r="I230" t="str">
-        <v>jp-016-main.jpg</v>
+        <v>allied-021-main.png</v>
       </c>
       <c r="J230" t="str">
         <v/>
@@ -11903,19 +11903,19 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B231" t="str">
-        <v>premium-001</v>
+        <v>allied-022</v>
       </c>
       <c r="C231" t="str">
-        <v>PREMIUM-001</v>
+        <v>ALLIED-022</v>
       </c>
       <c r="D231" t="str">
-        <v>2 Way Bib Cock</v>
+        <v>Shower Arm Round 450mm Brass</v>
       </c>
       <c r="E231" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F231" t="str">
         <v/>
@@ -11927,7 +11927,7 @@
         <v/>
       </c>
       <c r="I231" t="str">
-        <v>premium-001-main.jpg</v>
+        <v>allied-022-main.jpg</v>
       </c>
       <c r="J231" t="str">
         <v/>
@@ -11953,19 +11953,19 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B232" t="str">
-        <v>premium-002</v>
+        <v>allied-023</v>
       </c>
       <c r="C232" t="str">
-        <v>PREMIUM-002</v>
+        <v>ALLIED-023</v>
       </c>
       <c r="D232" t="str">
-        <v>Angle Valve</v>
+        <v>Shower Arm Square 400mm Brass</v>
       </c>
       <c r="E232" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F232" t="str">
         <v/>
@@ -11977,7 +11977,7 @@
         <v/>
       </c>
       <c r="I232" t="str">
-        <v>premium-002-main.jpg</v>
+        <v>allied-023-main.jpg</v>
       </c>
       <c r="J232" t="str">
         <v/>
@@ -12003,16 +12003,16 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B233" t="str">
-        <v>premium-003</v>
+        <v>allied-024</v>
       </c>
       <c r="C233" t="str">
-        <v>PREMIUM-003</v>
+        <v>ALLIED-024</v>
       </c>
       <c r="D233" t="str">
-        <v>Bib Cock</v>
+        <v>Single Lever Concealed Basin Mixer High Flow Body</v>
       </c>
       <c r="E233" t="str">
         <v>Faucets</v>
@@ -12027,7 +12027,7 @@
         <v/>
       </c>
       <c r="I233" t="str">
-        <v>premium-003-main.jpg</v>
+        <v>allied-024-main.jpg</v>
       </c>
       <c r="J233" t="str">
         <v/>
@@ -12053,16 +12053,16 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B234" t="str">
-        <v>premium-004</v>
+        <v>allied-025</v>
       </c>
       <c r="C234" t="str">
-        <v>PREMIUM-004</v>
+        <v>ALLIED-025</v>
       </c>
       <c r="D234" t="str">
-        <v>Center Hole Mixer</v>
+        <v>Single Lever Concealed Deusch Mixer Body</v>
       </c>
       <c r="E234" t="str">
         <v>Faucets</v>
@@ -12077,7 +12077,7 @@
         <v/>
       </c>
       <c r="I234" t="str">
-        <v>premium-004-main.jpg</v>
+        <v>allied-025-main.jpg</v>
       </c>
       <c r="J234" t="str">
         <v/>
@@ -12103,19 +12103,19 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B235" t="str">
-        <v>premium-005</v>
+        <v>allied-026</v>
       </c>
       <c r="C235" t="str">
-        <v>PREMIUM-005</v>
+        <v>ALLIED-026</v>
       </c>
       <c r="D235" t="str">
-        <v>Concealed 15mm Heavy</v>
+        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
       </c>
       <c r="E235" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F235" t="str">
         <v/>
@@ -12127,7 +12127,7 @@
         <v/>
       </c>
       <c r="I235" t="str">
-        <v>premium-005-main.jpg</v>
+        <v>allied-026-main.jpg</v>
       </c>
       <c r="J235" t="str">
         <v/>
@@ -12153,16 +12153,16 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B236" t="str">
-        <v>premium-006</v>
+        <v>allied-027</v>
       </c>
       <c r="C236" t="str">
-        <v>PREMIUM-006</v>
+        <v>ALLIED-027</v>
       </c>
       <c r="D236" t="str">
-        <v>Flush Cock</v>
+        <v>Single Lever Concealed High Flow Diverter Body</v>
       </c>
       <c r="E236" t="str">
         <v>Faucets</v>
@@ -12177,7 +12177,7 @@
         <v/>
       </c>
       <c r="I236" t="str">
-        <v>premium-006-main.jpg</v>
+        <v>allied-027-main.jpg</v>
       </c>
       <c r="J236" t="str">
         <v/>
@@ -12203,19 +12203,19 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B237" t="str">
-        <v>premium-007</v>
+        <v>allied-028</v>
       </c>
       <c r="C237" t="str">
-        <v>PREMIUM-007</v>
+        <v>ALLIED-028</v>
       </c>
       <c r="D237" t="str">
-        <v>Long Body</v>
+        <v>Wall Outlet Round with 15mm Thread to Connect Hand Shower Pipe Flange</v>
       </c>
       <c r="E237" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F237" t="str">
         <v/>
@@ -12227,7 +12227,7 @@
         <v/>
       </c>
       <c r="I237" t="str">
-        <v>premium-007-main.jpg</v>
+        <v>allied-028-main.jpg</v>
       </c>
       <c r="J237" t="str">
         <v/>
@@ -12253,19 +12253,19 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B238" t="str">
-        <v>premium-008</v>
+        <v>allied-029</v>
       </c>
       <c r="C238" t="str">
-        <v>PREMIUM-008</v>
+        <v>ALLIED-029</v>
       </c>
       <c r="D238" t="str">
-        <v>Nozzle Bib Cock</v>
+        <v>Wall Outlet Square with 15mm Thread to Connect Hand Shower Pipe Flange</v>
       </c>
       <c r="E238" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F238" t="str">
         <v/>
@@ -12277,7 +12277,7 @@
         <v/>
       </c>
       <c r="I238" t="str">
-        <v>premium-008-main.jpg</v>
+        <v>allied-029-main.jpg</v>
       </c>
       <c r="J238" t="str">
         <v/>
@@ -12303,19 +12303,19 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B239" t="str">
-        <v>premium-009</v>
+        <v>allied-030</v>
       </c>
       <c r="C239" t="str">
-        <v>PREMIUM-009</v>
+        <v>ALLIED-030</v>
       </c>
       <c r="D239" t="str">
-        <v>Pillar Cock</v>
+        <v>Waste Coupling 3 Inch with Thread CAP</v>
       </c>
       <c r="E239" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F239" t="str">
         <v/>
@@ -12327,7 +12327,7 @@
         <v/>
       </c>
       <c r="I239" t="str">
-        <v>premium-009-main.jpg</v>
+        <v>allied-030-main.png</v>
       </c>
       <c r="J239" t="str">
         <v/>
@@ -12353,19 +12353,19 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B240" t="str">
-        <v>premium-010</v>
+        <v>allied-031</v>
       </c>
       <c r="C240" t="str">
-        <v>PREMIUM-010</v>
+        <v>ALLIED-031</v>
       </c>
       <c r="D240" t="str">
-        <v>Sink Cock</v>
+        <v>Waste Coupling 5 Inch with Thread CAP</v>
       </c>
       <c r="E240" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F240" t="str">
         <v/>
@@ -12377,7 +12377,7 @@
         <v/>
       </c>
       <c r="I240" t="str">
-        <v>premium-010-main.jpg</v>
+        <v>allied-031-main.png</v>
       </c>
       <c r="J240" t="str">
         <v/>
@@ -12403,19 +12403,19 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Premium</v>
+        <v>Allied</v>
       </c>
       <c r="B241" t="str">
-        <v>premium-011</v>
+        <v>allied-032</v>
       </c>
       <c r="C241" t="str">
-        <v>PREMIUM-011</v>
+        <v>ALLIED-032</v>
       </c>
       <c r="D241" t="str">
-        <v>Sink Mixer</v>
+        <v>Waste Full Thread</v>
       </c>
       <c r="E241" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F241" t="str">
         <v/>
@@ -12427,7 +12427,7 @@
         <v/>
       </c>
       <c r="I241" t="str">
-        <v>premium-011-main.jpg</v>
+        <v>allied-032-main.jpg</v>
       </c>
       <c r="J241" t="str">
         <v/>
@@ -12453,22 +12453,22 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Premium</v>
+        <v>Zenith Collections</v>
       </c>
       <c r="B242" t="str">
-        <v>premium-012</v>
+        <v>zenith-collections-001</v>
       </c>
       <c r="C242" t="str">
-        <v>PREMIUM-012</v>
+        <v>ZENITH-COLLECTIONS-001</v>
       </c>
       <c r="D242" t="str">
-        <v>Swan Neck</v>
+        <v>Single Lever Basin Mixer</v>
       </c>
       <c r="E242" t="str">
         <v>Faucets</v>
       </c>
       <c r="F242" t="str">
-        <v/>
+        <v>Chrome</v>
       </c>
       <c r="G242" t="str">
         <v/>
@@ -12477,7 +12477,7 @@
         <v/>
       </c>
       <c r="I242" t="str">
-        <v>premium-012-main.jpg</v>
+        <v/>
       </c>
       <c r="J242" t="str">
         <v/>
@@ -12503,22 +12503,22 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Premium</v>
+        <v>Zenith Collections</v>
       </c>
       <c r="B243" t="str">
-        <v>premium-013</v>
+        <v>zenith-collections-001</v>
       </c>
       <c r="C243" t="str">
-        <v>PREMIUM-013</v>
+        <v>ZENITH-COLLECTIONS-002</v>
       </c>
       <c r="D243" t="str">
-        <v>Two Way Angle Valve</v>
+        <v/>
       </c>
       <c r="E243" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F243" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G243" t="str">
         <v/>
@@ -12527,7 +12527,7 @@
         <v/>
       </c>
       <c r="I243" t="str">
-        <v>premium-013-main.jpg</v>
+        <v/>
       </c>
       <c r="J243" t="str">
         <v/>
@@ -12553,22 +12553,22 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Premium</v>
+        <v>Zenith Collections</v>
       </c>
       <c r="B244" t="str">
-        <v>premium-014</v>
+        <v>zenith-collections-001</v>
       </c>
       <c r="C244" t="str">
-        <v>PREMIUM-014</v>
+        <v>ZENITH-COLLECTIONS-003</v>
       </c>
       <c r="D244" t="str">
-        <v>Wall Mixer 3 in</v>
+        <v/>
       </c>
       <c r="E244" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F244" t="str">
-        <v/>
+        <v>Matt Black</v>
       </c>
       <c r="G244" t="str">
         <v/>
@@ -12577,7 +12577,7 @@
         <v/>
       </c>
       <c r="I244" t="str">
-        <v>premium-014-main.jpg</v>
+        <v/>
       </c>
       <c r="J244" t="str">
         <v/>
@@ -12603,19 +12603,19 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Premium</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B245" t="str">
-        <v>premium-015</v>
+        <v>square-brass-accessories-001</v>
       </c>
       <c r="C245" t="str">
-        <v>PREMIUM-015</v>
+        <v>SQUARE-BRASS-ACCESSORIES-001</v>
       </c>
       <c r="D245" t="str">
-        <v>Wall Mixer Non Telephonic</v>
+        <v>Bath Rob Double Hook</v>
       </c>
       <c r="E245" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F245" t="str">
         <v/>
@@ -12627,7 +12627,7 @@
         <v/>
       </c>
       <c r="I245" t="str">
-        <v>premium-015-main.jpg</v>
+        <v>square-brass-accessories-001-main.jpg</v>
       </c>
       <c r="J245" t="str">
         <v/>
@@ -12653,19 +12653,19 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Premium</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B246" t="str">
-        <v>premium-016</v>
+        <v>square-brass-accessories-002</v>
       </c>
       <c r="C246" t="str">
-        <v>PREMIUM-016</v>
+        <v>SQUARE-BRASS-ACCESSORIES-002</v>
       </c>
       <c r="D246" t="str">
-        <v>Wall Mixer with Bend</v>
+        <v>Single Towel Rail</v>
       </c>
       <c r="E246" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F246" t="str">
         <v/>
@@ -12677,7 +12677,7 @@
         <v/>
       </c>
       <c r="I246" t="str">
-        <v>premium-016-main.jpg</v>
+        <v>square-brass-accessories-002-main.jpg</v>
       </c>
       <c r="J246" t="str">
         <v/>
@@ -12703,19 +12703,19 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Premium</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B247" t="str">
-        <v>premium-017</v>
+        <v>square-brass-accessories-003</v>
       </c>
       <c r="C247" t="str">
-        <v>PREMIUM-017</v>
+        <v>SQUARE-BRASS-ACCESSORIES-003</v>
       </c>
       <c r="D247" t="str">
-        <v>Wall Mixer with Crutch</v>
+        <v>Soap Dish</v>
       </c>
       <c r="E247" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F247" t="str">
         <v/>
@@ -12727,7 +12727,7 @@
         <v/>
       </c>
       <c r="I247" t="str">
-        <v>premium-017-main.jpg</v>
+        <v>square-brass-accessories-003-main.jpg</v>
       </c>
       <c r="J247" t="str">
         <v/>
@@ -12753,19 +12753,19 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Para Collection</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B248" t="str">
-        <v>para-collection-001</v>
+        <v>square-brass-accessories-004</v>
       </c>
       <c r="C248" t="str">
-        <v>PARA-COLLECTION-001</v>
+        <v>SQUARE-BRASS-ACCESSORIES-004</v>
       </c>
       <c r="D248" t="str">
-        <v>Angle Valve Para</v>
+        <v>Toilet Paper Holder Without Flap</v>
       </c>
       <c r="E248" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F248" t="str">
         <v/>
@@ -12777,7 +12777,7 @@
         <v/>
       </c>
       <c r="I248" t="str">
-        <v>para-collection-001-main.png</v>
+        <v>square-brass-accessories-004-main.jpg</v>
       </c>
       <c r="J248" t="str">
         <v/>
@@ -12803,19 +12803,19 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Para Collection</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B249" t="str">
-        <v>para-collection-002</v>
+        <v>square-brass-accessories-005</v>
       </c>
       <c r="C249" t="str">
-        <v>PARA-COLLECTION-002</v>
+        <v>SQUARE-BRASS-ACCESSORIES-005</v>
       </c>
       <c r="D249" t="str">
-        <v>Button Spout Para</v>
+        <v>Toilet Roll Holder with Flap</v>
       </c>
       <c r="E249" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F249" t="str">
         <v/>
@@ -12827,7 +12827,7 @@
         <v/>
       </c>
       <c r="I249" t="str">
-        <v>para-collection-002-main.png</v>
+        <v>square-brass-accessories-005-main.jpg</v>
       </c>
       <c r="J249" t="str">
         <v/>
@@ -12853,19 +12853,19 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Para Collection</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B250" t="str">
-        <v>para-collection-003</v>
+        <v>square-brass-accessories-006</v>
       </c>
       <c r="C250" t="str">
-        <v>PARA-COLLECTION-003</v>
+        <v>SQUARE-BRASS-ACCESSORIES-006</v>
       </c>
       <c r="D250" t="str">
-        <v>Long Body Para</v>
+        <v>Towel Rack</v>
       </c>
       <c r="E250" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F250" t="str">
         <v/>
@@ -12877,7 +12877,7 @@
         <v/>
       </c>
       <c r="I250" t="str">
-        <v>para-collection-003-main.png</v>
+        <v>square-brass-accessories-006-main.jpg</v>
       </c>
       <c r="J250" t="str">
         <v/>
@@ -12903,19 +12903,19 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Para Collection</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B251" t="str">
-        <v>para-collection-004</v>
+        <v>square-brass-accessories-007</v>
       </c>
       <c r="C251" t="str">
-        <v>PARA-COLLECTION-004</v>
+        <v>SQUARE-BRASS-ACCESSORIES-007</v>
       </c>
       <c r="D251" t="str">
-        <v>Nozzle BIB Cock Para</v>
+        <v>Tower Ring</v>
       </c>
       <c r="E251" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F251" t="str">
         <v/>
@@ -12927,7 +12927,7 @@
         <v/>
       </c>
       <c r="I251" t="str">
-        <v>para-collection-004-main.png</v>
+        <v>square-brass-accessories-007-main.jpg</v>
       </c>
       <c r="J251" t="str">
         <v/>
@@ -12953,19 +12953,19 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Para Collection</v>
+        <v>Square Brass Accessories</v>
       </c>
       <c r="B252" t="str">
-        <v>para-collection-005</v>
+        <v>square-brass-accessories-008</v>
       </c>
       <c r="C252" t="str">
-        <v>PARA-COLLECTION-005</v>
+        <v>SQUARE-BRASS-ACCESSORIES-008</v>
       </c>
       <c r="D252" t="str">
-        <v>Pilla Cock Extended Body Para</v>
+        <v>Tumbler Holder</v>
       </c>
       <c r="E252" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F252" t="str">
         <v/>
@@ -12977,7 +12977,7 @@
         <v/>
       </c>
       <c r="I252" t="str">
-        <v>para-collection-005-main.png</v>
+        <v>square-brass-accessories-008-main.jpg</v>
       </c>
       <c r="J252" t="str">
         <v/>
@@ -13003,19 +13003,19 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Para Collection</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B253" t="str">
-        <v>para-collection-006</v>
+        <v>round-brass-accessories-001</v>
       </c>
       <c r="C253" t="str">
-        <v>PARA-COLLECTION-006</v>
+        <v>ROUND-BRASS-ACCESSORIES-001</v>
       </c>
       <c r="D253" t="str">
-        <v>Pillar Cock Para</v>
+        <v>Paper Holder Round</v>
       </c>
       <c r="E253" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F253" t="str">
         <v/>
@@ -13027,7 +13027,7 @@
         <v/>
       </c>
       <c r="I253" t="str">
-        <v>para-collection-006-main.png</v>
+        <v>round-brass-accessories-001-main.jpg</v>
       </c>
       <c r="J253" t="str">
         <v/>
@@ -13053,19 +13053,19 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Para Collection</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B254" t="str">
-        <v>para-collection-007</v>
+        <v>round-brass-accessories-002</v>
       </c>
       <c r="C254" t="str">
-        <v>PARA-COLLECTION-007</v>
+        <v>ROUND-BRASS-ACCESSORIES-002</v>
       </c>
       <c r="D254" t="str">
-        <v>Plain Spout Para</v>
+        <v>Round Soap Dish</v>
       </c>
       <c r="E254" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F254" t="str">
         <v/>
@@ -13077,7 +13077,7 @@
         <v/>
       </c>
       <c r="I254" t="str">
-        <v>para-collection-007-main.png</v>
+        <v>round-brass-accessories-002-main.jpg</v>
       </c>
       <c r="J254" t="str">
         <v/>
@@ -13103,19 +13103,19 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Para Collection</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B255" t="str">
-        <v>para-collection-008</v>
+        <v>round-brass-accessories-003</v>
       </c>
       <c r="C255" t="str">
-        <v>PARA-COLLECTION-008</v>
+        <v>ROUND-BRASS-ACCESSORIES-003</v>
       </c>
       <c r="D255" t="str">
-        <v>Single Lever Basin Mixer Extended Body Para</v>
+        <v>Round Tumbler</v>
       </c>
       <c r="E255" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F255" t="str">
         <v/>
@@ -13127,7 +13127,7 @@
         <v/>
       </c>
       <c r="I255" t="str">
-        <v>para-collection-008-main.png</v>
+        <v>round-brass-accessories-003-main.jpg</v>
       </c>
       <c r="J255" t="str">
         <v/>
@@ -13153,19 +13153,19 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Para Collection</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B256" t="str">
-        <v>para-collection-009</v>
+        <v>round-brass-accessories-004</v>
       </c>
       <c r="C256" t="str">
-        <v>PARA-COLLECTION-009</v>
+        <v>ROUND-BRASS-ACCESSORIES-004</v>
       </c>
       <c r="D256" t="str">
-        <v>Single Lever Basin Mixer Para</v>
+        <v>Towel Rack Round</v>
       </c>
       <c r="E256" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F256" t="str">
         <v/>
@@ -13177,7 +13177,7 @@
         <v/>
       </c>
       <c r="I256" t="str">
-        <v>para-collection-009-main.png</v>
+        <v>round-brass-accessories-004-main.jpg</v>
       </c>
       <c r="J256" t="str">
         <v/>
@@ -13203,19 +13203,19 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Para Collection</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B257" t="str">
-        <v>para-collection-010</v>
+        <v>round-brass-accessories-005</v>
       </c>
       <c r="C257" t="str">
-        <v>PARA-COLLECTION-010</v>
+        <v>ROUND-BRASS-ACCESSORIES-005</v>
       </c>
       <c r="D257" t="str">
-        <v>Single Lever Concealed Basin Mixer Para</v>
+        <v>Towel Rail</v>
       </c>
       <c r="E257" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F257" t="str">
         <v/>
@@ -13227,7 +13227,7 @@
         <v/>
       </c>
       <c r="I257" t="str">
-        <v>para-collection-010-main.png</v>
+        <v>round-brass-accessories-005-main.jpg</v>
       </c>
       <c r="J257" t="str">
         <v/>
@@ -13253,19 +13253,19 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Para Collection</v>
+        <v>Round Brass Accessories</v>
       </c>
       <c r="B258" t="str">
-        <v>para-collection-011</v>
+        <v>round-brass-accessories-006</v>
       </c>
       <c r="C258" t="str">
-        <v>PARA-COLLECTION-011</v>
+        <v>ROUND-BRASS-ACCESSORIES-006</v>
       </c>
       <c r="D258" t="str">
-        <v>Single Lever Concealed Diverter</v>
+        <v>Towel Ring Round</v>
       </c>
       <c r="E258" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F258" t="str">
         <v/>
@@ -13277,7 +13277,7 @@
         <v/>
       </c>
       <c r="I258" t="str">
-        <v>para-collection-011-main.png</v>
+        <v>round-brass-accessories-006-main.jpg</v>
       </c>
       <c r="J258" t="str">
         <v/>
@@ -13303,16 +13303,16 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B259" t="str">
-        <v>para-collection-012</v>
+        <v>opell-prima-001</v>
       </c>
       <c r="C259" t="str">
-        <v>PARA-COLLECTION-012</v>
+        <v>OPELL-PRIMA-001</v>
       </c>
       <c r="D259" t="str">
-        <v>Single Lever Wall Mixer</v>
+        <v>2 WAY Angle Valve</v>
       </c>
       <c r="E259" t="str">
         <v>Faucets</v>
@@ -13327,7 +13327,7 @@
         <v/>
       </c>
       <c r="I259" t="str">
-        <v>para-collection-012-main.png</v>
+        <v>opell-prima-001-main.jpg</v>
       </c>
       <c r="J259" t="str">
         <v/>
@@ -13353,16 +13353,16 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B260" t="str">
-        <v>para-collection-013</v>
+        <v>opell-prima-002</v>
       </c>
       <c r="C260" t="str">
-        <v>PARA-COLLECTION-013</v>
+        <v>OPELL-PRIMA-002</v>
       </c>
       <c r="D260" t="str">
-        <v>Single Lever Wall Mixer with Bend</v>
+        <v>2 WAY BIB Cock</v>
       </c>
       <c r="E260" t="str">
         <v>Faucets</v>
@@ -13377,7 +13377,7 @@
         <v/>
       </c>
       <c r="I260" t="str">
-        <v>para-collection-013-main.png</v>
+        <v>opell-prima-002-main.png</v>
       </c>
       <c r="J260" t="str">
         <v/>
@@ -13403,22 +13403,22 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B261" t="str">
-        <v>para-collection-014</v>
+        <v>opell-prima-003</v>
       </c>
       <c r="C261" t="str">
-        <v>PARA-COLLECTION-014</v>
+        <v>OPELL-PRIMA-003</v>
       </c>
       <c r="D261" t="str">
-        <v>Table Mounted Single Lever Kitchen Mixer Angular Spout</v>
+        <v>Aliva Shower Head</v>
       </c>
       <c r="E261" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F261" t="str">
-        <v/>
+        <v>Chrome</v>
       </c>
       <c r="G261" t="str">
         <v/>
@@ -13427,7 +13427,7 @@
         <v/>
       </c>
       <c r="I261" t="str">
-        <v>para-collection-014-main.png</v>
+        <v>opell-prima-003-main.png</v>
       </c>
       <c r="J261" t="str">
         <v/>
@@ -13453,22 +13453,22 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B262" t="str">
-        <v>para-collection-015</v>
+        <v>opell-prima-003</v>
       </c>
       <c r="C262" t="str">
-        <v>PARA-COLLECTION-015</v>
+        <v>OPELL-PRIMA-004</v>
       </c>
       <c r="D262" t="str">
-        <v>Table Mounted Single Lever Kitchen Mixer Round Spout</v>
+        <v/>
       </c>
       <c r="E262" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F262" t="str">
-        <v/>
+        <v>Profile White Gold</v>
       </c>
       <c r="G262" t="str">
         <v/>
@@ -13477,7 +13477,7 @@
         <v/>
       </c>
       <c r="I262" t="str">
-        <v>para-collection-015-main.png</v>
+        <v>opell-prima-004-main.png</v>
       </c>
       <c r="J262" t="str">
         <v/>
@@ -13503,22 +13503,22 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B263" t="str">
-        <v>para-collection-016</v>
+        <v>opell-prima-003</v>
       </c>
       <c r="C263" t="str">
-        <v>PARA-COLLECTION-016</v>
+        <v>OPELL-PRIMA-012</v>
       </c>
       <c r="D263" t="str">
-        <v>Wall Mixer with Bend Para</v>
+        <v/>
       </c>
       <c r="E263" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F263" t="str">
-        <v/>
+        <v>Profile Beige Gold</v>
       </c>
       <c r="G263" t="str">
         <v/>
@@ -13527,7 +13527,7 @@
         <v/>
       </c>
       <c r="I263" t="str">
-        <v>para-collection-016-main.png</v>
+        <v>opell-prima-012-main.png</v>
       </c>
       <c r="J263" t="str">
         <v/>
@@ -13553,22 +13553,22 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B264" t="str">
-        <v>para-collection-017</v>
+        <v>opell-prima-003</v>
       </c>
       <c r="C264" t="str">
-        <v>PARA-COLLECTION-017</v>
+        <v>OPELL-PRIMA-033</v>
       </c>
       <c r="D264" t="str">
-        <v>Wall Mixer with Crutch Para</v>
+        <v/>
       </c>
       <c r="E264" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F264" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G264" t="str">
         <v/>
@@ -13577,7 +13577,7 @@
         <v/>
       </c>
       <c r="I264" t="str">
-        <v>para-collection-017-main.png</v>
+        <v>opell-prima-033-main.png</v>
       </c>
       <c r="J264" t="str">
         <v/>
@@ -13603,16 +13603,16 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B265" t="str">
-        <v>para-collection-018</v>
+        <v>opell-prima-005</v>
       </c>
       <c r="C265" t="str">
-        <v>PARA-COLLECTION-018</v>
+        <v>OPELL-PRIMA-005</v>
       </c>
       <c r="D265" t="str">
-        <v>Wall Mounted Single Lever Kitchen Mixer Angular Spout</v>
+        <v>Angle Valve</v>
       </c>
       <c r="E265" t="str">
         <v>Faucets</v>
@@ -13627,7 +13627,7 @@
         <v/>
       </c>
       <c r="I265" t="str">
-        <v>para-collection-018-main.png</v>
+        <v>opell-prima-005-main.jpg</v>
       </c>
       <c r="J265" t="str">
         <v/>
@@ -13653,22 +13653,22 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B266" t="str">
-        <v>para-collection-019</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C266" t="str">
-        <v>PARA-COLLECTION-019</v>
+        <v>OPELL-PRIMA-006</v>
       </c>
       <c r="D266" t="str">
-        <v>Wall Mounted Single Lever Kitchen Mixer Regular Spout</v>
+        <v>Basin Mixer Wall Mounted Upper Parts</v>
       </c>
       <c r="E266" t="str">
         <v>Faucets</v>
       </c>
       <c r="F266" t="str">
-        <v/>
+        <v>Matt Black Gold</v>
       </c>
       <c r="G266" t="str">
         <v/>
@@ -13677,7 +13677,7 @@
         <v/>
       </c>
       <c r="I266" t="str">
-        <v>para-collection-019-main.png</v>
+        <v>opell-prima-006-main.png</v>
       </c>
       <c r="J266" t="str">
         <v/>
@@ -13703,22 +13703,22 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Para Collection</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B267" t="str">
-        <v>para-collection-020</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C267" t="str">
-        <v>PARA-COLLECTION-020</v>
+        <v>OPELL-PRIMA-007</v>
       </c>
       <c r="D267" t="str">
-        <v>Wall Mounted Single Lever Kitchen Mixer Round Spout</v>
+        <v/>
       </c>
       <c r="E267" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F267" t="str">
-        <v/>
+        <v>Matt White Gold</v>
       </c>
       <c r="G267" t="str">
         <v/>
@@ -13727,7 +13727,7 @@
         <v/>
       </c>
       <c r="I267" t="str">
-        <v>para-collection-020-main.png</v>
+        <v>opell-prima-007-main.png</v>
       </c>
       <c r="J267" t="str">
         <v/>
@@ -13753,22 +13753,22 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B268" t="str">
-        <v>allied-001</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C268" t="str">
-        <v>ALLIED-001</v>
+        <v>OPELL-PRIMA-008</v>
       </c>
       <c r="D268" t="str">
-        <v>Abs Round Hand Shower with Brass Tube</v>
+        <v/>
       </c>
       <c r="E268" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F268" t="str">
-        <v/>
+        <v>Matt Beige Gold</v>
       </c>
       <c r="G268" t="str">
         <v/>
@@ -13777,7 +13777,7 @@
         <v/>
       </c>
       <c r="I268" t="str">
-        <v>allied-001-main.jpg</v>
+        <v>opell-prima-008-main.png</v>
       </c>
       <c r="J268" t="str">
         <v/>
@@ -13803,22 +13803,22 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B269" t="str">
-        <v>allied-002</v>
+        <v>opell-prima-006</v>
       </c>
       <c r="C269" t="str">
-        <v>ALLIED-002</v>
+        <v>OPELL-PRIMA-009</v>
       </c>
       <c r="D269" t="str">
-        <v>Abs Square Hand Shower with Brass Tube</v>
+        <v/>
       </c>
       <c r="E269" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F269" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G269" t="str">
         <v/>
@@ -13827,7 +13827,7 @@
         <v/>
       </c>
       <c r="I269" t="str">
-        <v>allied-002-main.jpg</v>
+        <v>opell-prima-009-main.png</v>
       </c>
       <c r="J269" t="str">
         <v/>
@@ -13853,19 +13853,19 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B270" t="str">
-        <v>allied-003</v>
+        <v>opell-prima-010</v>
       </c>
       <c r="C270" t="str">
-        <v>ALLIED-003</v>
+        <v>OPELL-PRIMA-010</v>
       </c>
       <c r="D270" t="str">
-        <v>Aliva Maze Over Head Shower</v>
+        <v>Bath TUB Spout</v>
       </c>
       <c r="E270" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F270" t="str">
         <v/>
@@ -13877,7 +13877,7 @@
         <v/>
       </c>
       <c r="I270" t="str">
-        <v>allied-003-main.png</v>
+        <v>opell-prima-010-main.jpg</v>
       </c>
       <c r="J270" t="str">
         <v/>
@@ -13903,22 +13903,22 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B271" t="str">
-        <v>allied-004</v>
+        <v>opell-prima-011</v>
       </c>
       <c r="C271" t="str">
-        <v>ALLIED-004</v>
+        <v>OPELL-PRIMA-011</v>
       </c>
       <c r="D271" t="str">
-        <v>Bottle Trap Full Brass</v>
+        <v>Bottle Trap</v>
       </c>
       <c r="E271" t="str">
         <v>Accessories</v>
       </c>
       <c r="F271" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G271" t="str">
         <v/>
@@ -13927,7 +13927,7 @@
         <v/>
       </c>
       <c r="I271" t="str">
-        <v>allied-004-main.jpg</v>
+        <v>opell-prima-011-main.png</v>
       </c>
       <c r="J271" t="str">
         <v/>
@@ -13953,22 +13953,22 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B272" t="str">
-        <v>allied-005</v>
+        <v>opell-prima-011</v>
       </c>
       <c r="C272" t="str">
-        <v>ALLIED-005</v>
+        <v>OPELL-PRIMA-014</v>
       </c>
       <c r="D272" t="str">
-        <v>Brass Health Faucet Round Shape with 1.5 Meter Brass Tube</v>
+        <v/>
       </c>
       <c r="E272" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F272" t="str">
-        <v/>
+        <v>Matt Black</v>
       </c>
       <c r="G272" t="str">
         <v/>
@@ -13977,7 +13977,7 @@
         <v/>
       </c>
       <c r="I272" t="str">
-        <v>allied-005-main.jpg</v>
+        <v>opell-prima-014-main.png</v>
       </c>
       <c r="J272" t="str">
         <v/>
@@ -14003,22 +14003,22 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B273" t="str">
-        <v>allied-006</v>
+        <v>opell-prima-011</v>
       </c>
       <c r="C273" t="str">
-        <v>ALLIED-006</v>
+        <v>OPELL-PRIMA-015</v>
       </c>
       <c r="D273" t="str">
-        <v>Brass Health Faucet Sqaure with 1.5 Meter Brass Tube</v>
+        <v/>
       </c>
       <c r="E273" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F273" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G273" t="str">
         <v/>
@@ -14027,7 +14027,7 @@
         <v/>
       </c>
       <c r="I273" t="str">
-        <v>allied-006-main.jpg</v>
+        <v>opell-prima-015-main.png</v>
       </c>
       <c r="J273" t="str">
         <v/>
@@ -14053,22 +14053,22 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B274" t="str">
-        <v>allied-007</v>
+        <v>opell-prima-011</v>
       </c>
       <c r="C274" t="str">
-        <v>ALLIED-007</v>
+        <v>OPELL-PRIMA-016</v>
       </c>
       <c r="D274" t="str">
-        <v>Concealed Body</v>
+        <v/>
       </c>
       <c r="E274" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F274" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G274" t="str">
         <v/>
@@ -14077,7 +14077,7 @@
         <v/>
       </c>
       <c r="I274" t="str">
-        <v>allied-007-main.jpg</v>
+        <v>opell-prima-016-main.png</v>
       </c>
       <c r="J274" t="str">
         <v/>
@@ -14103,22 +14103,22 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B275" t="str">
-        <v>allied-008</v>
+        <v>opell-prima-027</v>
       </c>
       <c r="C275" t="str">
-        <v>ALLIED-008</v>
+        <v>OPELL-PRIMA-027</v>
       </c>
       <c r="D275" t="str">
-        <v>Concealed Body 15mm</v>
+        <v>Square Shower Head</v>
       </c>
       <c r="E275" t="str">
         <v>Accessories</v>
       </c>
       <c r="F275" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G275" t="str">
         <v/>
@@ -14127,7 +14127,7 @@
         <v/>
       </c>
       <c r="I275" t="str">
-        <v>allied-008-main.jpg</v>
+        <v>opell-prima-027-main.png</v>
       </c>
       <c r="J275" t="str">
         <v/>
@@ -14153,22 +14153,22 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B276" t="str">
-        <v>allied-009</v>
+        <v>opell-prima-027</v>
       </c>
       <c r="C276" t="str">
-        <v>ALLIED-009</v>
+        <v>OPELL-PRIMA-013</v>
       </c>
       <c r="D276" t="str">
-        <v>Cuba Hand Shower with Tube</v>
+        <v/>
       </c>
       <c r="E276" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F276" t="str">
-        <v/>
+        <v>Profile Beige Gold</v>
       </c>
       <c r="G276" t="str">
         <v/>
@@ -14177,7 +14177,7 @@
         <v/>
       </c>
       <c r="I276" t="str">
-        <v>allied-009-main.png</v>
+        <v>opell-prima-013-main.png</v>
       </c>
       <c r="J276" t="str">
         <v/>
@@ -14203,22 +14203,22 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B277" t="str">
-        <v>allied-010</v>
+        <v>opell-prima-027</v>
       </c>
       <c r="C277" t="str">
-        <v>ALLIED-010</v>
+        <v>OPELL-PRIMA-074</v>
       </c>
       <c r="D277" t="str">
-        <v>Donut Hand Shower with Tube</v>
+        <v/>
       </c>
       <c r="E277" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F277" t="str">
-        <v/>
+        <v>Profile White Gold</v>
       </c>
       <c r="G277" t="str">
         <v/>
@@ -14227,7 +14227,7 @@
         <v/>
       </c>
       <c r="I277" t="str">
-        <v>allied-010-main.png</v>
+        <v>opell-prima-074-main.png</v>
       </c>
       <c r="J277" t="str">
         <v/>
@@ -14253,19 +14253,19 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B278" t="str">
-        <v>allied-011</v>
+        <v>opell-prima-017</v>
       </c>
       <c r="C278" t="str">
-        <v>ALLIED-011</v>
+        <v>OPELL-PRIMA-017</v>
       </c>
       <c r="D278" t="str">
-        <v>Donut Shower Head with ARM</v>
+        <v>Button Spout</v>
       </c>
       <c r="E278" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F278" t="str">
         <v/>
@@ -14277,7 +14277,7 @@
         <v/>
       </c>
       <c r="I278" t="str">
-        <v>allied-011-main.png</v>
+        <v>opell-prima-017-main.jpg</v>
       </c>
       <c r="J278" t="str">
         <v/>
@@ -14303,19 +14303,19 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B279" t="str">
-        <v>allied-012</v>
+        <v>opell-prima-018</v>
       </c>
       <c r="C279" t="str">
-        <v>ALLIED-012</v>
+        <v>OPELL-PRIMA-018</v>
       </c>
       <c r="D279" t="str">
-        <v>Glory Hand Shower with Tube</v>
+        <v>Center Hole</v>
       </c>
       <c r="E279" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F279" t="str">
         <v/>
@@ -14327,7 +14327,7 @@
         <v/>
       </c>
       <c r="I279" t="str">
-        <v>allied-012-main.png</v>
+        <v>opell-prima-018-main.jpg</v>
       </c>
       <c r="J279" t="str">
         <v/>
@@ -14353,19 +14353,19 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B280" t="str">
-        <v>allied-013</v>
+        <v>opell-prima-019</v>
       </c>
       <c r="C280" t="str">
-        <v>ALLIED-013</v>
+        <v>OPELL-PRIMA-019</v>
       </c>
       <c r="D280" t="str">
-        <v>Health Faucet with Tube</v>
+        <v>Concealed Stop Cock</v>
       </c>
       <c r="E280" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F280" t="str">
         <v/>
@@ -14377,7 +14377,7 @@
         <v/>
       </c>
       <c r="I280" t="str">
-        <v>allied-013-main.png</v>
+        <v>opell-prima-019-main.jpg</v>
       </c>
       <c r="J280" t="str">
         <v/>
@@ -14403,22 +14403,22 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B281" t="str">
-        <v>allied-014</v>
+        <v>opell-prima-020</v>
       </c>
       <c r="C281" t="str">
-        <v>ALLIED-014</v>
+        <v>OPELL-PRIMA-020</v>
       </c>
       <c r="D281" t="str">
-        <v>High Flow Diverter Body Three in Let</v>
+        <v>Diverter Body</v>
       </c>
       <c r="E281" t="str">
         <v>Faucets</v>
       </c>
       <c r="F281" t="str">
-        <v/>
+        <v>Rose Gold</v>
       </c>
       <c r="G281" t="str">
         <v/>
@@ -14427,7 +14427,7 @@
         <v/>
       </c>
       <c r="I281" t="str">
-        <v>allied-014-main.jpg</v>
+        <v>opell-prima-020-main.png</v>
       </c>
       <c r="J281" t="str">
         <v/>
@@ -14453,22 +14453,22 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B282" t="str">
-        <v>allied-015</v>
+        <v>opell-prima-020</v>
       </c>
       <c r="C282" t="str">
-        <v>ALLIED-015</v>
+        <v>OPELL-PRIMA-021</v>
       </c>
       <c r="D282" t="str">
-        <v>Maze Square Shower Head</v>
+        <v/>
       </c>
       <c r="E282" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F282" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G282" t="str">
         <v/>
@@ -14477,7 +14477,7 @@
         <v/>
       </c>
       <c r="I282" t="str">
-        <v>allied-015-main.png</v>
+        <v>opell-prima-021-main.png</v>
       </c>
       <c r="J282" t="str">
         <v/>
@@ -14503,22 +14503,22 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B283" t="str">
-        <v>allied-016</v>
+        <v>opell-prima-020</v>
       </c>
       <c r="C283" t="str">
-        <v>ALLIED-016</v>
+        <v>OPELL-PRIMA-023</v>
       </c>
       <c r="D283" t="str">
-        <v>Oval Maze Overhead Shower</v>
+        <v/>
       </c>
       <c r="E283" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F283" t="str">
-        <v/>
+        <v>Matt Beige Gold</v>
       </c>
       <c r="G283" t="str">
         <v/>
@@ -14527,7 +14527,7 @@
         <v/>
       </c>
       <c r="I283" t="str">
-        <v>allied-016-main.png</v>
+        <v>opell-prima-023-main.png</v>
       </c>
       <c r="J283" t="str">
         <v/>
@@ -14553,22 +14553,22 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B284" t="str">
-        <v>allied-017</v>
+        <v>opell-prima-024</v>
       </c>
       <c r="C284" t="str">
-        <v>ALLIED-017</v>
+        <v>OPELL-PRIMA-024</v>
       </c>
       <c r="D284" t="str">
-        <v>Pressmatic Pillar Cock</v>
+        <v>Diverter Upper Parts</v>
       </c>
       <c r="E284" t="str">
         <v>Faucets</v>
       </c>
       <c r="F284" t="str">
-        <v/>
+        <v>Matt Black</v>
       </c>
       <c r="G284" t="str">
         <v/>
@@ -14577,7 +14577,7 @@
         <v/>
       </c>
       <c r="I284" t="str">
-        <v>allied-017-main.png</v>
+        <v>opell-prima-024-main.png</v>
       </c>
       <c r="J284" t="str">
         <v/>
@@ -14603,22 +14603,22 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B285" t="str">
-        <v>allied-018</v>
+        <v>opell-prima-024</v>
       </c>
       <c r="C285" t="str">
-        <v>ALLIED-018</v>
+        <v>OPELL-PRIMA-025</v>
       </c>
       <c r="D285" t="str">
-        <v>Round 4 Inch Shower Head with ARM</v>
+        <v/>
       </c>
       <c r="E285" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F285" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G285" t="str">
         <v/>
@@ -14627,7 +14627,7 @@
         <v/>
       </c>
       <c r="I285" t="str">
-        <v>allied-018-main.png</v>
+        <v>opell-prima-025-main.png</v>
       </c>
       <c r="J285" t="str">
         <v/>
@@ -14653,22 +14653,22 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B286" t="str">
-        <v>allied-019</v>
+        <v>opell-prima-024</v>
       </c>
       <c r="C286" t="str">
-        <v>ALLIED-019</v>
+        <v>OPELL-PRIMA-026</v>
       </c>
       <c r="D286" t="str">
-        <v>Round Hand Shower with Tube</v>
+        <v/>
       </c>
       <c r="E286" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F286" t="str">
-        <v/>
+        <v>Chrome</v>
       </c>
       <c r="G286" t="str">
         <v/>
@@ -14677,7 +14677,7 @@
         <v/>
       </c>
       <c r="I286" t="str">
-        <v>allied-019-main.png</v>
+        <v>opell-prima-026-main.jpg</v>
       </c>
       <c r="J286" t="str">
         <v/>
@@ -14703,22 +14703,22 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B287" t="str">
-        <v>allied-020</v>
+        <v>opell-prima-028</v>
       </c>
       <c r="C287" t="str">
-        <v>ALLIED-020</v>
+        <v>OPELL-PRIMA-028</v>
       </c>
       <c r="D287" t="str">
-        <v>Shower Head Round Maze</v>
+        <v>Hand Shower</v>
       </c>
       <c r="E287" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F287" t="str">
-        <v/>
+        <v>Rose Gold</v>
       </c>
       <c r="G287" t="str">
         <v/>
@@ -14727,7 +14727,7 @@
         <v/>
       </c>
       <c r="I287" t="str">
-        <v>allied-020-main.png</v>
+        <v>opell-prima-028-main.png</v>
       </c>
       <c r="J287" t="str">
         <v/>
@@ -14753,22 +14753,22 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B288" t="str">
-        <v>allied-021</v>
+        <v>opell-prima-028</v>
       </c>
       <c r="C288" t="str">
-        <v>ALLIED-021</v>
+        <v>OPELL-PRIMA-029</v>
       </c>
       <c r="D288" t="str">
-        <v>Shower Rail</v>
+        <v/>
       </c>
       <c r="E288" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F288" t="str">
-        <v/>
+        <v>Matt Black</v>
       </c>
       <c r="G288" t="str">
         <v/>
@@ -14777,7 +14777,7 @@
         <v/>
       </c>
       <c r="I288" t="str">
-        <v>allied-021-main.png</v>
+        <v>opell-prima-029-main.png</v>
       </c>
       <c r="J288" t="str">
         <v/>
@@ -14803,22 +14803,22 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B289" t="str">
-        <v>allied-022</v>
+        <v>opell-prima-028</v>
       </c>
       <c r="C289" t="str">
-        <v>ALLIED-022</v>
+        <v>OPELL-PRIMA-030</v>
       </c>
       <c r="D289" t="str">
-        <v>Shower Arm Round 450mm Brass</v>
+        <v/>
       </c>
       <c r="E289" t="str">
-        <v>Showers</v>
+        <v/>
       </c>
       <c r="F289" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G289" t="str">
         <v/>
@@ -14827,7 +14827,7 @@
         <v/>
       </c>
       <c r="I289" t="str">
-        <v>allied-022-main.jpg</v>
+        <v>opell-prima-030-main.png</v>
       </c>
       <c r="J289" t="str">
         <v/>
@@ -14853,19 +14853,19 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B290" t="str">
-        <v>allied-023</v>
+        <v>opell-prima-031</v>
       </c>
       <c r="C290" t="str">
-        <v>ALLIED-023</v>
+        <v>OPELL-PRIMA-031</v>
       </c>
       <c r="D290" t="str">
-        <v>Shower Arm Square 400mm Brass</v>
+        <v>Health Faucet</v>
       </c>
       <c r="E290" t="str">
-        <v>Showers</v>
+        <v>Accessories</v>
       </c>
       <c r="F290" t="str">
         <v/>
@@ -14877,7 +14877,7 @@
         <v/>
       </c>
       <c r="I290" t="str">
-        <v>allied-023-main.jpg</v>
+        <v>opell-prima-031-main.png</v>
       </c>
       <c r="J290" t="str">
         <v/>
@@ -14903,16 +14903,16 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B291" t="str">
-        <v>allied-024</v>
+        <v>opell-prima-032</v>
       </c>
       <c r="C291" t="str">
-        <v>ALLIED-024</v>
+        <v>OPELL-PRIMA-032</v>
       </c>
       <c r="D291" t="str">
-        <v>Single Lever Concealed Basin Mixer High Flow Body</v>
+        <v>Long Body</v>
       </c>
       <c r="E291" t="str">
         <v>Faucets</v>
@@ -14927,7 +14927,7 @@
         <v/>
       </c>
       <c r="I291" t="str">
-        <v>allied-024-main.jpg</v>
+        <v>opell-prima-032-main.jpg</v>
       </c>
       <c r="J291" t="str">
         <v/>
@@ -14953,19 +14953,19 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B292" t="str">
-        <v>allied-025</v>
+        <v>opell-prima-034</v>
       </c>
       <c r="C292" t="str">
-        <v>ALLIED-025</v>
+        <v>OPELL-PRIMA-034</v>
       </c>
       <c r="D292" t="str">
-        <v>Single Lever Concealed Deusch Mixer Body</v>
+        <v>Matte White Shower Head</v>
       </c>
       <c r="E292" t="str">
-        <v>Faucets</v>
+        <v>Showers</v>
       </c>
       <c r="F292" t="str">
         <v/>
@@ -14977,7 +14977,7 @@
         <v/>
       </c>
       <c r="I292" t="str">
-        <v>allied-025-main.jpg</v>
+        <v>opell-prima-034-main.png</v>
       </c>
       <c r="J292" t="str">
         <v/>
@@ -15003,19 +15003,19 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B293" t="str">
-        <v>allied-026</v>
+        <v>opell-prima-035</v>
       </c>
       <c r="C293" t="str">
-        <v>ALLIED-026</v>
+        <v>OPELL-PRIMA-035</v>
       </c>
       <c r="D293" t="str">
-        <v>Single Lever Concealed Deusch Mixer Upper Parts</v>
+        <v>NON Telephonic</v>
       </c>
       <c r="E293" t="str">
-        <v>Faucets</v>
+        <v>Accessories</v>
       </c>
       <c r="F293" t="str">
         <v/>
@@ -15027,7 +15027,7 @@
         <v/>
       </c>
       <c r="I293" t="str">
-        <v>allied-026-main.jpg</v>
+        <v>opell-prima-035-main.jpg</v>
       </c>
       <c r="J293" t="str">
         <v/>
@@ -15053,16 +15053,16 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B294" t="str">
-        <v>allied-027</v>
+        <v>opell-prima-036</v>
       </c>
       <c r="C294" t="str">
-        <v>ALLIED-027</v>
+        <v>OPELL-PRIMA-036</v>
       </c>
       <c r="D294" t="str">
-        <v>Single Lever Concealed High Flow Diverter Body</v>
+        <v>Nozzle BIB Cock</v>
       </c>
       <c r="E294" t="str">
         <v>Faucets</v>
@@ -15077,7 +15077,7 @@
         <v/>
       </c>
       <c r="I294" t="str">
-        <v>allied-027-main.jpg</v>
+        <v>opell-prima-036-main.jpg</v>
       </c>
       <c r="J294" t="str">
         <v/>
@@ -15103,19 +15103,19 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B295" t="str">
-        <v>allied-028</v>
+        <v>opell-prima-037</v>
       </c>
       <c r="C295" t="str">
-        <v>ALLIED-028</v>
+        <v>OPELL-PRIMA-037</v>
       </c>
       <c r="D295" t="str">
-        <v>Wall Outlet Round with 15mm Thread to Connect Hand Shower Pipe Flange</v>
+        <v>Pillar Cock</v>
       </c>
       <c r="E295" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F295" t="str">
         <v/>
@@ -15127,7 +15127,7 @@
         <v/>
       </c>
       <c r="I295" t="str">
-        <v>allied-028-main.jpg</v>
+        <v>opell-prima-037-main.jpg</v>
       </c>
       <c r="J295" t="str">
         <v/>
@@ -15153,22 +15153,22 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B296" t="str">
-        <v>allied-029</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C296" t="str">
-        <v>ALLIED-029</v>
+        <v>OPELL-PRIMA-038</v>
       </c>
       <c r="D296" t="str">
-        <v>Wall Outlet Square with 15mm Thread to Connect Hand Shower Pipe Flange</v>
+        <v>Single Lever Basin Mixer Tall</v>
       </c>
       <c r="E296" t="str">
-        <v>Showers</v>
+        <v>Faucets</v>
       </c>
       <c r="F296" t="str">
-        <v/>
+        <v>Matt Beige</v>
       </c>
       <c r="G296" t="str">
         <v/>
@@ -15177,7 +15177,7 @@
         <v/>
       </c>
       <c r="I296" t="str">
-        <v>allied-029-main.jpg</v>
+        <v>opell-prima-038-main.png</v>
       </c>
       <c r="J296" t="str">
         <v/>
@@ -15203,22 +15203,22 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B297" t="str">
-        <v>allied-030</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C297" t="str">
-        <v>ALLIED-030</v>
+        <v>OPELL-PRIMA-039</v>
       </c>
       <c r="D297" t="str">
-        <v>Waste Coupling 3 Inch with Thread CAP</v>
+        <v/>
       </c>
       <c r="E297" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F297" t="str">
-        <v/>
+        <v>Rose Gold</v>
       </c>
       <c r="G297" t="str">
         <v/>
@@ -15227,7 +15227,7 @@
         <v/>
       </c>
       <c r="I297" t="str">
-        <v>allied-030-main.png</v>
+        <v>opell-prima-039-main.png</v>
       </c>
       <c r="J297" t="str">
         <v/>
@@ -15253,22 +15253,22 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B298" t="str">
-        <v>allied-031</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C298" t="str">
-        <v>ALLIED-031</v>
+        <v>OPELL-PRIMA-049</v>
       </c>
       <c r="D298" t="str">
-        <v>Waste Coupling 5 Inch with Thread CAP</v>
+        <v/>
       </c>
       <c r="E298" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F298" t="str">
-        <v/>
+        <v>Matt White</v>
       </c>
       <c r="G298" t="str">
         <v/>
@@ -15277,7 +15277,7 @@
         <v/>
       </c>
       <c r="I298" t="str">
-        <v>allied-031-main.png</v>
+        <v>opell-prima-049-main.png</v>
       </c>
       <c r="J298" t="str">
         <v/>
@@ -15303,22 +15303,22 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Allied</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B299" t="str">
-        <v>allied-032</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C299" t="str">
-        <v>ALLIED-032</v>
+        <v>OPELL-PRIMA-050</v>
       </c>
       <c r="D299" t="str">
-        <v>Waste Full Thread</v>
+        <v/>
       </c>
       <c r="E299" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F299" t="str">
-        <v/>
+        <v>Matt Beige Gold</v>
       </c>
       <c r="G299" t="str">
         <v/>
@@ -15327,7 +15327,7 @@
         <v/>
       </c>
       <c r="I299" t="str">
-        <v>allied-032-main.jpg</v>
+        <v>opell-prima-050-main.png</v>
       </c>
       <c r="J299" t="str">
         <v/>
@@ -15353,22 +15353,22 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Zenith Collections</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B300" t="str">
-        <v>zenith-collections-001</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C300" t="str">
-        <v>ZENITH-COLLECTIONS-001</v>
+        <v>OPELL-PRIMA-059</v>
       </c>
       <c r="D300" t="str">
-        <v>Single Lever Basin Mixer</v>
+        <v/>
       </c>
       <c r="E300" t="str">
-        <v>Faucets</v>
+        <v/>
       </c>
       <c r="F300" t="str">
-        <v>Chrome</v>
+        <v>Profile White Gold</v>
       </c>
       <c r="G300" t="str">
         <v/>
@@ -15377,7 +15377,7 @@
         <v/>
       </c>
       <c r="I300" t="str">
-        <v/>
+        <v>opell-prima-059-main.png</v>
       </c>
       <c r="J300" t="str">
         <v/>
@@ -15403,13 +15403,13 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Zenith Collections</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B301" t="str">
-        <v>zenith-collections-001</v>
+        <v>opell-prima-038</v>
       </c>
       <c r="C301" t="str">
-        <v>ZENITH-COLLECTIONS-002</v>
+        <v>OPELL-PRIMA-060</v>
       </c>
       <c r="D301" t="str">
         <v/>
@@ -15418,7 +15418,7 @@
         <v/>
       </c>
       <c r="F301" t="str">
-        <v>Matt Beige</v>
+        <v>Rich Gold</v>
       </c>
       <c r="G301" t="str">
         <v/>
@@ -15427,7 +15427,7 @@
         <v/>
       </c>
       <c r="I301" t="str">
-        <v/>
+        <v>opell-prima-060-main.png</v>
       </c>
       <c r="J301" t="str">
         <v/>
@@ -15453,22 +15453,22 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Zenith Collections</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B302" t="str">
-        <v>zenith-collections-001</v>
+        <v>opell-prima-040</v>
       </c>
       <c r="C302" t="str">
-        <v>ZENITH-COLLECTIONS-003</v>
+        <v>OPELL-PRIMA-040</v>
       </c>
       <c r="D302" t="str">
-        <v/>
+        <v>Pillar Cock Extended Body</v>
       </c>
       <c r="E302" t="str">
-        <v/>
+        <v>Faucets</v>
       </c>
       <c r="F302" t="str">
-        <v>Matt Black</v>
+        <v/>
       </c>
       <c r="G302" t="str">
         <v/>
@@ -15477,7 +15477,7 @@
         <v/>
       </c>
       <c r="I302" t="str">
-        <v/>
+        <v>opell-prima-040-main.jpg</v>
       </c>
       <c r="J302" t="str">
         <v/>
@@ -15503,19 +15503,19 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B303" t="str">
-        <v>square-brass-accessories-001</v>
+        <v>opell-prima-041</v>
       </c>
       <c r="C303" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-001</v>
+        <v>OPELL-PRIMA-041</v>
       </c>
       <c r="D303" t="str">
-        <v>Bath Rob Double Hook</v>
+        <v>Plain Spout</v>
       </c>
       <c r="E303" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F303" t="str">
         <v/>
@@ -15527,7 +15527,7 @@
         <v/>
       </c>
       <c r="I303" t="str">
-        <v>square-brass-accessories-001-main.jpg</v>
+        <v>opell-prima-041-main.png</v>
       </c>
       <c r="J303" t="str">
         <v/>
@@ -15553,22 +15553,22 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B304" t="str">
-        <v>square-brass-accessories-002</v>
+        <v>opell-prima-042</v>
       </c>
       <c r="C304" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-002</v>
+        <v>OPELL-PRIMA-042</v>
       </c>
       <c r="D304" t="str">
-        <v>Single Towel Rail</v>
+        <v>Shower Arm</v>
       </c>
       <c r="E304" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F304" t="str">
-        <v/>
+        <v>Rich Gold</v>
       </c>
       <c r="G304" t="str">
         <v/>
@@ -15577,7 +15577,7 @@
         <v/>
       </c>
       <c r="I304" t="str">
-        <v>square-brass-accessories-002-main.jpg</v>
+        <v>opell-prima-042-main.png</v>
       </c>
       <c r="J304" t="str">
         <v/>
@@ -15603,22 +15603,22 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B305" t="str">
-        <v>square-brass-accessories-003</v>
+        <v>opell-prima-042</v>
       </c>
       <c r="C305" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-003</v>
+        <v>OPELL-PRIMA-043</v>
       </c>
       <c r="D305" t="str">
-        <v>Soap Dish</v>
+        <v/>
       </c>
       <c r="E305" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="F305" t="str">
-        <v/>
+        <v>Matt Black Gold</v>
       </c>
       <c r="G305" t="str">
         <v/>
@@ -15627,7 +15627,7 @@
         <v/>
       </c>
       <c r="I305" t="str">
-        <v>square-brass-accessories-003-main.jpg</v>
+        <v>opell-prima-043-main.png</v>
       </c>
       <c r="J305" t="str">
         <v/>
@@ -15653,19 +15653,19 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B306" t="str">
-        <v>square-brass-accessories-004</v>
+        <v>opell-prima-044</v>
       </c>
       <c r="C306" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-004</v>
+        <v>OPELL-PRIMA-044</v>
       </c>
       <c r="D306" t="str">
-        <v>Toilet Paper Holder Without Flap</v>
+        <v>Shower Head</v>
       </c>
       <c r="E306" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F306" t="str">
         <v/>
@@ -15677,7 +15677,7 @@
         <v/>
       </c>
       <c r="I306" t="str">
-        <v>square-brass-accessories-004-main.jpg</v>
+        <v>opell-prima-044-main.png</v>
       </c>
       <c r="J306" t="str">
         <v/>
@@ -15703,19 +15703,19 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B307" t="str">
-        <v>square-brass-accessories-005</v>
+        <v>opell-prima-045</v>
       </c>
       <c r="C307" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-005</v>
+        <v>OPELL-PRIMA-045</v>
       </c>
       <c r="D307" t="str">
-        <v>Toilet Roll Holder with Flap</v>
+        <v>Shower Head Beige</v>
       </c>
       <c r="E307" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F307" t="str">
         <v/>
@@ -15727,7 +15727,7 @@
         <v/>
       </c>
       <c r="I307" t="str">
-        <v>square-brass-accessories-005-main.jpg</v>
+        <v>opell-prima-045-main.png</v>
       </c>
       <c r="J307" t="str">
         <v/>
@@ -15753,19 +15753,19 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B308" t="str">
-        <v>square-brass-accessories-006</v>
+        <v>opell-prima-046</v>
       </c>
       <c r="C308" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-006</v>
+        <v>OPELL-PRIMA-046</v>
       </c>
       <c r="D308" t="str">
-        <v>Towel Rack</v>
+        <v>Shower Mixer for Spout Only</v>
       </c>
       <c r="E308" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F308" t="str">
         <v/>
@@ -15777,7 +15777,7 @@
         <v/>
       </c>
       <c r="I308" t="str">
-        <v>square-brass-accessories-006-main.jpg</v>
+        <v>opell-prima-046-main.jpg</v>
       </c>
       <c r="J308" t="str">
         <v/>
@@ -15803,19 +15803,19 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B309" t="str">
-        <v>square-brass-accessories-007</v>
+        <v>opell-prima-051</v>
       </c>
       <c r="C309" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-007</v>
+        <v>OPELL-PRIMA-051</v>
       </c>
       <c r="D309" t="str">
-        <v>Tower Ring</v>
+        <v>Single Lever Exposed Shower Mixer</v>
       </c>
       <c r="E309" t="str">
-        <v>Accessories</v>
+        <v>Showers</v>
       </c>
       <c r="F309" t="str">
         <v/>
@@ -15827,7 +15827,7 @@
         <v/>
       </c>
       <c r="I309" t="str">
-        <v>square-brass-accessories-007-main.jpg</v>
+        <v>opell-prima-051-main.jpg</v>
       </c>
       <c r="J309" t="str">
         <v/>
@@ -15853,19 +15853,19 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Square Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B310" t="str">
-        <v>square-brass-accessories-008</v>
+        <v>opell-prima-052</v>
       </c>
       <c r="C310" t="str">
-        <v>SQUARE-BRASS-ACCESSORIES-008</v>
+        <v>OPELL-PRIMA-052</v>
       </c>
       <c r="D310" t="str">
-        <v>Tumbler Holder</v>
+        <v>Single Lever Sink Mixer Table Mounted Angular Spout</v>
       </c>
       <c r="E310" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F310" t="str">
         <v/>
@@ -15877,7 +15877,7 @@
         <v/>
       </c>
       <c r="I310" t="str">
-        <v>square-brass-accessories-008-main.jpg</v>
+        <v>opell-prima-052-main.jpg</v>
       </c>
       <c r="J310" t="str">
         <v/>
@@ -15903,19 +15903,19 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Round Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B311" t="str">
-        <v>round-brass-accessories-001</v>
+        <v>opell-prima-053</v>
       </c>
       <c r="C311" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-001</v>
+        <v>OPELL-PRIMA-053</v>
       </c>
       <c r="D311" t="str">
-        <v>Paper Holder Round</v>
+        <v>Single Lever Sink Mixer Table Mounted Round Spout Side Handle</v>
       </c>
       <c r="E311" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F311" t="str">
         <v/>
@@ -15927,7 +15927,7 @@
         <v/>
       </c>
       <c r="I311" t="str">
-        <v>round-brass-accessories-001-main.jpg</v>
+        <v>opell-prima-053-main.jpg</v>
       </c>
       <c r="J311" t="str">
         <v/>
@@ -15953,19 +15953,19 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B312" t="str">
-        <v>round-brass-accessories-002</v>
+        <v>opell-prima-054</v>
       </c>
       <c r="C312" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-002</v>
+        <v>OPELL-PRIMA-054</v>
       </c>
       <c r="D312" t="str">
-        <v>Round Soap Dish</v>
+        <v>Single Lever Sink Mixer Table Mounted Tall</v>
       </c>
       <c r="E312" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F312" t="str">
         <v/>
@@ -15977,7 +15977,7 @@
         <v/>
       </c>
       <c r="I312" t="str">
-        <v>round-brass-accessories-002-main.jpg</v>
+        <v>opell-prima-054-main.jpg</v>
       </c>
       <c r="J312" t="str">
         <v/>
@@ -16003,19 +16003,19 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Round Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B313" t="str">
-        <v>round-brass-accessories-003</v>
+        <v>opell-prima-055</v>
       </c>
       <c r="C313" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-003</v>
+        <v>OPELL-PRIMA-055</v>
       </c>
       <c r="D313" t="str">
-        <v>Round Tumbler</v>
+        <v>Single Lever Sink Mixer Wall Mounted Angular Spout</v>
       </c>
       <c r="E313" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F313" t="str">
         <v/>
@@ -16027,7 +16027,7 @@
         <v/>
       </c>
       <c r="I313" t="str">
-        <v>round-brass-accessories-003-main.jpg</v>
+        <v>opell-prima-055-main.jpg</v>
       </c>
       <c r="J313" t="str">
         <v/>
@@ -16053,19 +16053,19 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Round Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B314" t="str">
-        <v>round-brass-accessories-004</v>
+        <v>opell-prima-056</v>
       </c>
       <c r="C314" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-004</v>
+        <v>OPELL-PRIMA-056</v>
       </c>
       <c r="D314" t="str">
-        <v>Towel Rack Round</v>
+        <v>Single Lever Sink Mixer Wall Mounted Round Spout</v>
       </c>
       <c r="E314" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F314" t="str">
         <v/>
@@ -16077,7 +16077,7 @@
         <v/>
       </c>
       <c r="I314" t="str">
-        <v>round-brass-accessories-004-main.jpg</v>
+        <v>opell-prima-056-main.jpg</v>
       </c>
       <c r="J314" t="str">
         <v/>
@@ -16103,19 +16103,19 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Round Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B315" t="str">
-        <v>round-brass-accessories-005</v>
+        <v>opell-prima-057</v>
       </c>
       <c r="C315" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-005</v>
+        <v>OPELL-PRIMA-057</v>
       </c>
       <c r="D315" t="str">
-        <v>Towel Rail</v>
+        <v>Single Lever Wall Mixer</v>
       </c>
       <c r="E315" t="str">
-        <v>Accessories</v>
+        <v>Faucets</v>
       </c>
       <c r="F315" t="str">
         <v/>
@@ -16127,7 +16127,7 @@
         <v/>
       </c>
       <c r="I315" t="str">
-        <v>round-brass-accessories-005-main.jpg</v>
+        <v>opell-prima-057-main.jpg</v>
       </c>
       <c r="J315" t="str">
         <v/>
@@ -16153,57 +16153,707 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round Brass Accessories</v>
+        <v>Opell Prima</v>
       </c>
       <c r="B316" t="str">
-        <v>round-brass-accessories-006</v>
+        <v>opell-prima-058</v>
       </c>
       <c r="C316" t="str">
-        <v>ROUND-BRASS-ACCESSORIES-006</v>
+        <v>OPELL-PRIMA-058</v>
       </c>
       <c r="D316" t="str">
-        <v>Towel Ring Round</v>
+        <v>Single Lever Wall Mounted Basin Mixer</v>
       </c>
       <c r="E316" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F316" t="str">
+        <v/>
+      </c>
+      <c r="G316" t="str">
+        <v/>
+      </c>
+      <c r="H316" t="str">
+        <v/>
+      </c>
+      <c r="I316" t="str">
+        <v>opell-prima-058-main.jpg</v>
+      </c>
+      <c r="J316" t="str">
+        <v/>
+      </c>
+      <c r="K316" t="str">
+        <v/>
+      </c>
+      <c r="L316" t="str">
+        <v/>
+      </c>
+      <c r="M316" t="str">
+        <v/>
+      </c>
+      <c r="N316" t="str">
+        <v/>
+      </c>
+      <c r="O316" t="str">
+        <v/>
+      </c>
+      <c r="P316" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B317" t="str">
+        <v>opell-prima-061</v>
+      </c>
+      <c r="C317" t="str">
+        <v>OPELL-PRIMA-061</v>
+      </c>
+      <c r="D317" t="str">
+        <v>Sink Cock</v>
+      </c>
+      <c r="E317" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F317" t="str">
+        <v/>
+      </c>
+      <c r="G317" t="str">
+        <v/>
+      </c>
+      <c r="H317" t="str">
+        <v/>
+      </c>
+      <c r="I317" t="str">
+        <v>opell-prima-061-main.jpg</v>
+      </c>
+      <c r="J317" t="str">
+        <v/>
+      </c>
+      <c r="K317" t="str">
+        <v/>
+      </c>
+      <c r="L317" t="str">
+        <v/>
+      </c>
+      <c r="M317" t="str">
+        <v/>
+      </c>
+      <c r="N317" t="str">
+        <v/>
+      </c>
+      <c r="O317" t="str">
+        <v/>
+      </c>
+      <c r="P317" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B318" t="str">
+        <v>opell-prima-062</v>
+      </c>
+      <c r="C318" t="str">
+        <v>OPELL-PRIMA-062</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Sink Mixer</v>
+      </c>
+      <c r="E318" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F318" t="str">
+        <v/>
+      </c>
+      <c r="G318" t="str">
+        <v/>
+      </c>
+      <c r="H318" t="str">
+        <v/>
+      </c>
+      <c r="I318" t="str">
+        <v>opell-prima-062-main.jpg</v>
+      </c>
+      <c r="J318" t="str">
+        <v/>
+      </c>
+      <c r="K318" t="str">
+        <v/>
+      </c>
+      <c r="L318" t="str">
+        <v/>
+      </c>
+      <c r="M318" t="str">
+        <v/>
+      </c>
+      <c r="N318" t="str">
+        <v/>
+      </c>
+      <c r="O318" t="str">
+        <v/>
+      </c>
+      <c r="P318" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B319" t="str">
+        <v>opell-prima-063</v>
+      </c>
+      <c r="C319" t="str">
+        <v>OPELL-PRIMA-063</v>
+      </c>
+      <c r="D319" t="str">
+        <v>Swan Neck</v>
+      </c>
+      <c r="E319" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F319" t="str">
+        <v/>
+      </c>
+      <c r="G319" t="str">
+        <v/>
+      </c>
+      <c r="H319" t="str">
+        <v/>
+      </c>
+      <c r="I319" t="str">
+        <v>opell-prima-063-main.jpg</v>
+      </c>
+      <c r="J319" t="str">
+        <v/>
+      </c>
+      <c r="K319" t="str">
+        <v/>
+      </c>
+      <c r="L319" t="str">
+        <v/>
+      </c>
+      <c r="M319" t="str">
+        <v/>
+      </c>
+      <c r="N319" t="str">
+        <v/>
+      </c>
+      <c r="O319" t="str">
+        <v/>
+      </c>
+      <c r="P319" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B320" t="str">
+        <v>opell-prima-064</v>
+      </c>
+      <c r="C320" t="str">
+        <v>OPELL-PRIMA-064</v>
+      </c>
+      <c r="D320" t="str">
+        <v>TWO WAY BIB Cock</v>
+      </c>
+      <c r="E320" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F320" t="str">
+        <v/>
+      </c>
+      <c r="G320" t="str">
+        <v/>
+      </c>
+      <c r="H320" t="str">
+        <v/>
+      </c>
+      <c r="I320" t="str">
+        <v>opell-prima-064-main.jpg</v>
+      </c>
+      <c r="J320" t="str">
+        <v/>
+      </c>
+      <c r="K320" t="str">
+        <v/>
+      </c>
+      <c r="L320" t="str">
+        <v/>
+      </c>
+      <c r="M320" t="str">
+        <v/>
+      </c>
+      <c r="N320" t="str">
+        <v/>
+      </c>
+      <c r="O320" t="str">
+        <v/>
+      </c>
+      <c r="P320" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B321" t="str">
+        <v>opell-prima-065</v>
+      </c>
+      <c r="C321" t="str">
+        <v>OPELL-PRIMA-065</v>
+      </c>
+      <c r="D321" t="str">
+        <v>Wall Mixer NON Telephonic</v>
+      </c>
+      <c r="E321" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F321" t="str">
+        <v/>
+      </c>
+      <c r="G321" t="str">
+        <v/>
+      </c>
+      <c r="H321" t="str">
+        <v/>
+      </c>
+      <c r="I321" t="str">
+        <v>opell-prima-065-main.jpg</v>
+      </c>
+      <c r="J321" t="str">
+        <v/>
+      </c>
+      <c r="K321" t="str">
+        <v/>
+      </c>
+      <c r="L321" t="str">
+        <v/>
+      </c>
+      <c r="M321" t="str">
+        <v/>
+      </c>
+      <c r="N321" t="str">
+        <v/>
+      </c>
+      <c r="O321" t="str">
+        <v/>
+      </c>
+      <c r="P321" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B322" t="str">
+        <v>opell-prima-066</v>
+      </c>
+      <c r="C322" t="str">
+        <v>OPELL-PRIMA-066</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Wall Mixer Telephonic with Crutch</v>
+      </c>
+      <c r="E322" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F322" t="str">
+        <v/>
+      </c>
+      <c r="G322" t="str">
+        <v/>
+      </c>
+      <c r="H322" t="str">
+        <v/>
+      </c>
+      <c r="I322" t="str">
+        <v>opell-prima-066-main.jpg</v>
+      </c>
+      <c r="J322" t="str">
+        <v/>
+      </c>
+      <c r="K322" t="str">
+        <v/>
+      </c>
+      <c r="L322" t="str">
+        <v/>
+      </c>
+      <c r="M322" t="str">
+        <v/>
+      </c>
+      <c r="N322" t="str">
+        <v/>
+      </c>
+      <c r="O322" t="str">
+        <v/>
+      </c>
+      <c r="P322" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B323" t="str">
+        <v>opell-prima-067</v>
+      </c>
+      <c r="C323" t="str">
+        <v>OPELL-PRIMA-067</v>
+      </c>
+      <c r="D323" t="str">
+        <v>Wall Mixer Three in ONE</v>
+      </c>
+      <c r="E323" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F323" t="str">
+        <v/>
+      </c>
+      <c r="G323" t="str">
+        <v/>
+      </c>
+      <c r="H323" t="str">
+        <v/>
+      </c>
+      <c r="I323" t="str">
+        <v>opell-prima-067-main.jpg</v>
+      </c>
+      <c r="J323" t="str">
+        <v/>
+      </c>
+      <c r="K323" t="str">
+        <v/>
+      </c>
+      <c r="L323" t="str">
+        <v/>
+      </c>
+      <c r="M323" t="str">
+        <v/>
+      </c>
+      <c r="N323" t="str">
+        <v/>
+      </c>
+      <c r="O323" t="str">
+        <v/>
+      </c>
+      <c r="P323" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B324" t="str">
+        <v>opell-prima-068</v>
+      </c>
+      <c r="C324" t="str">
+        <v>OPELL-PRIMA-068</v>
+      </c>
+      <c r="D324" t="str">
+        <v>Wall Mixer with Bend</v>
+      </c>
+      <c r="E324" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F324" t="str">
+        <v/>
+      </c>
+      <c r="G324" t="str">
+        <v/>
+      </c>
+      <c r="H324" t="str">
+        <v/>
+      </c>
+      <c r="I324" t="str">
+        <v>opell-prima-068-main.jpg</v>
+      </c>
+      <c r="J324" t="str">
+        <v/>
+      </c>
+      <c r="K324" t="str">
+        <v/>
+      </c>
+      <c r="L324" t="str">
+        <v/>
+      </c>
+      <c r="M324" t="str">
+        <v/>
+      </c>
+      <c r="N324" t="str">
+        <v/>
+      </c>
+      <c r="O324" t="str">
+        <v/>
+      </c>
+      <c r="P324" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B325" t="str">
+        <v>opell-prima-069</v>
+      </c>
+      <c r="C325" t="str">
+        <v>OPELL-PRIMA-069</v>
+      </c>
+      <c r="D325" t="str">
+        <v>Wall Mount Basin Mixer Upper Parts</v>
+      </c>
+      <c r="E325" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F325" t="str">
+        <v>Rich Gold</v>
+      </c>
+      <c r="G325" t="str">
+        <v/>
+      </c>
+      <c r="H325" t="str">
+        <v/>
+      </c>
+      <c r="I325" t="str">
+        <v>opell-prima-069-main.png</v>
+      </c>
+      <c r="J325" t="str">
+        <v/>
+      </c>
+      <c r="K325" t="str">
+        <v/>
+      </c>
+      <c r="L325" t="str">
+        <v/>
+      </c>
+      <c r="M325" t="str">
+        <v/>
+      </c>
+      <c r="N325" t="str">
+        <v/>
+      </c>
+      <c r="O325" t="str">
+        <v/>
+      </c>
+      <c r="P325" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B326" t="str">
+        <v>opell-prima-069</v>
+      </c>
+      <c r="C326" t="str">
+        <v>OPELL-PRIMA-070</v>
+      </c>
+      <c r="D326" t="str">
+        <v/>
+      </c>
+      <c r="E326" t="str">
+        <v/>
+      </c>
+      <c r="F326" t="str">
+        <v>Matt Beige</v>
+      </c>
+      <c r="G326" t="str">
+        <v/>
+      </c>
+      <c r="H326" t="str">
+        <v/>
+      </c>
+      <c r="I326" t="str">
+        <v>opell-prima-070-main.png</v>
+      </c>
+      <c r="J326" t="str">
+        <v/>
+      </c>
+      <c r="K326" t="str">
+        <v/>
+      </c>
+      <c r="L326" t="str">
+        <v/>
+      </c>
+      <c r="M326" t="str">
+        <v/>
+      </c>
+      <c r="N326" t="str">
+        <v/>
+      </c>
+      <c r="O326" t="str">
+        <v/>
+      </c>
+      <c r="P326" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B327" t="str">
+        <v>opell-prima-071</v>
+      </c>
+      <c r="C327" t="str">
+        <v>OPELL-PRIMA-071</v>
+      </c>
+      <c r="D327" t="str">
+        <v>Waste Coupling</v>
+      </c>
+      <c r="E327" t="str">
         <v>Accessories</v>
       </c>
-      <c r="F316" t="str">
-        <v/>
-      </c>
-      <c r="G316" t="str">
-        <v/>
-      </c>
-      <c r="H316" t="str">
-        <v/>
-      </c>
-      <c r="I316" t="str">
-        <v>round-brass-accessories-006-main.jpg</v>
-      </c>
-      <c r="J316" t="str">
-        <v/>
-      </c>
-      <c r="K316" t="str">
-        <v/>
-      </c>
-      <c r="L316" t="str">
-        <v/>
-      </c>
-      <c r="M316" t="str">
-        <v/>
-      </c>
-      <c r="N316" t="str">
-        <v/>
-      </c>
-      <c r="O316" t="str">
-        <v/>
-      </c>
-      <c r="P316" t="str">
+      <c r="F327" t="str">
+        <v>Rich Gold</v>
+      </c>
+      <c r="G327" t="str">
+        <v/>
+      </c>
+      <c r="H327" t="str">
+        <v/>
+      </c>
+      <c r="I327" t="str">
+        <v>opell-prima-071-main.png</v>
+      </c>
+      <c r="J327" t="str">
+        <v/>
+      </c>
+      <c r="K327" t="str">
+        <v/>
+      </c>
+      <c r="L327" t="str">
+        <v/>
+      </c>
+      <c r="M327" t="str">
+        <v/>
+      </c>
+      <c r="N327" t="str">
+        <v/>
+      </c>
+      <c r="O327" t="str">
+        <v/>
+      </c>
+      <c r="P327" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B328" t="str">
+        <v>opell-prima-071</v>
+      </c>
+      <c r="C328" t="str">
+        <v>OPELL-PRIMA-072</v>
+      </c>
+      <c r="D328" t="str">
+        <v/>
+      </c>
+      <c r="E328" t="str">
+        <v/>
+      </c>
+      <c r="F328" t="str">
+        <v>Matt Beige Gold</v>
+      </c>
+      <c r="G328" t="str">
+        <v/>
+      </c>
+      <c r="H328" t="str">
+        <v/>
+      </c>
+      <c r="I328" t="str">
+        <v>opell-prima-072-main.png</v>
+      </c>
+      <c r="J328" t="str">
+        <v/>
+      </c>
+      <c r="K328" t="str">
+        <v/>
+      </c>
+      <c r="L328" t="str">
+        <v/>
+      </c>
+      <c r="M328" t="str">
+        <v/>
+      </c>
+      <c r="N328" t="str">
+        <v/>
+      </c>
+      <c r="O328" t="str">
+        <v/>
+      </c>
+      <c r="P328" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="B329" t="str">
+        <v>opell-prima-071</v>
+      </c>
+      <c r="C329" t="str">
+        <v>OPELL-PRIMA-073</v>
+      </c>
+      <c r="D329" t="str">
+        <v/>
+      </c>
+      <c r="E329" t="str">
+        <v/>
+      </c>
+      <c r="F329" t="str">
+        <v>Matt White</v>
+      </c>
+      <c r="G329" t="str">
+        <v/>
+      </c>
+      <c r="H329" t="str">
+        <v/>
+      </c>
+      <c r="I329" t="str">
+        <v>opell-prima-073-main.png</v>
+      </c>
+      <c r="J329" t="str">
+        <v/>
+      </c>
+      <c r="K329" t="str">
+        <v/>
+      </c>
+      <c r="L329" t="str">
+        <v/>
+      </c>
+      <c r="M329" t="str">
+        <v/>
+      </c>
+      <c r="N329" t="str">
+        <v/>
+      </c>
+      <c r="O329" t="str">
+        <v/>
+      </c>
+      <c r="P329" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P316"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P329"/>
   </ignoredErrors>
 </worksheet>
 </file>
